--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08D9D660-6BD4-4698-AC26-FC5DEB273FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E20867-BD69-42BE-9700-CDABBD0375E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="885" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2640" yWindow="1155" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -36958,7 +36958,7 @@
         <v>0</v>
       </c>
       <c r="J224" s="3">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K224" s="3">
         <v>0</v>
@@ -37111,7 +37111,7 @@
         <v>0</v>
       </c>
       <c r="J225" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K225" s="3">
         <v>0</v>
@@ -37264,7 +37264,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K226" s="3">
         <v>0</v>
@@ -37417,7 +37417,7 @@
         <v>0</v>
       </c>
       <c r="J227" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K227" s="3">
         <v>0</v>
@@ -37570,7 +37570,7 @@
         <v>0</v>
       </c>
       <c r="J228" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K228" s="3">
         <v>0</v>
@@ -37723,7 +37723,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K229" s="3">
         <v>0</v>
@@ -37876,7 +37876,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="3">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="K230" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E20867-BD69-42BE-9700-CDABBD0375E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2570DF-7A46-476F-9028-48432F9E065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="1155" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1530" yWindow="525" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2570DF-7A46-476F-9028-48432F9E065D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982EB68B-F2BA-451A-8E79-B3DB0860778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1530" yWindow="525" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982EB68B-F2BA-451A-8E79-B3DB0860778B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3421E2-9011-442D-B3EB-D5AAC489DAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C3421E2-9011-442D-B3EB-D5AAC489DAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C335860C-C2D1-4A11-8D33-E2F876D5FF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1215" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -42766,7 +42766,7 @@
         <v>80</v>
       </c>
       <c r="H262" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I262" s="3">
         <v>0</v>
@@ -42778,7 +42778,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M262" s="3">
         <v>0</v>
@@ -42793,13 +42793,13 @@
         <v>0</v>
       </c>
       <c r="Q262" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R262" s="3">
         <v>0</v>
       </c>
       <c r="S262" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T262" s="3">
         <v>0</v>
@@ -42919,7 +42919,7 @@
         <v>80</v>
       </c>
       <c r="H263" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I263" s="3">
         <v>0</v>
@@ -42931,7 +42931,7 @@
         <v>0</v>
       </c>
       <c r="L263" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M263" s="3">
         <v>0</v>
@@ -42946,13 +42946,13 @@
         <v>0</v>
       </c>
       <c r="Q263" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R263" s="3">
         <v>0</v>
       </c>
       <c r="S263" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T263" s="3">
         <v>0</v>
@@ -43072,7 +43072,7 @@
         <v>80</v>
       </c>
       <c r="H264" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I264" s="3">
         <v>0</v>
@@ -43084,7 +43084,7 @@
         <v>0</v>
       </c>
       <c r="L264" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M264" s="3">
         <v>0</v>
@@ -43099,13 +43099,13 @@
         <v>0</v>
       </c>
       <c r="Q264" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R264" s="3">
         <v>0</v>
       </c>
       <c r="S264" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T264" s="3">
         <v>0</v>
@@ -43225,7 +43225,7 @@
         <v>80</v>
       </c>
       <c r="H265" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I265" s="3">
         <v>0</v>
@@ -43237,7 +43237,7 @@
         <v>0</v>
       </c>
       <c r="L265" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M265" s="3">
         <v>0</v>
@@ -43252,13 +43252,13 @@
         <v>0</v>
       </c>
       <c r="Q265" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R265" s="3">
         <v>0</v>
       </c>
       <c r="S265" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T265" s="3">
         <v>0</v>
@@ -43378,7 +43378,7 @@
         <v>80</v>
       </c>
       <c r="H266" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I266" s="3">
         <v>0</v>
@@ -43390,7 +43390,7 @@
         <v>0</v>
       </c>
       <c r="L266" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M266" s="3">
         <v>0</v>
@@ -43405,13 +43405,13 @@
         <v>0</v>
       </c>
       <c r="Q266" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R266" s="3">
         <v>0</v>
       </c>
       <c r="S266" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T266" s="3">
         <v>0</v>
@@ -43531,7 +43531,7 @@
         <v>80</v>
       </c>
       <c r="H267" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I267" s="3">
         <v>0</v>
@@ -43543,7 +43543,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M267" s="3">
         <v>0</v>
@@ -43558,13 +43558,13 @@
         <v>0</v>
       </c>
       <c r="Q267" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R267" s="3">
         <v>0</v>
       </c>
       <c r="S267" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T267" s="3">
         <v>0</v>
@@ -43684,7 +43684,7 @@
         <v>80</v>
       </c>
       <c r="H268" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I268" s="3">
         <v>0</v>
@@ -43696,7 +43696,7 @@
         <v>0</v>
       </c>
       <c r="L268" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M268" s="3">
         <v>0</v>
@@ -43711,13 +43711,13 @@
         <v>0</v>
       </c>
       <c r="Q268" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R268" s="3">
         <v>0</v>
       </c>
       <c r="S268" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T268" s="3">
         <v>0</v>
@@ -43837,7 +43837,7 @@
         <v>80</v>
       </c>
       <c r="H269" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I269" s="3">
         <v>0</v>
@@ -43849,7 +43849,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M269" s="3">
         <v>0</v>
@@ -43864,13 +43864,13 @@
         <v>0</v>
       </c>
       <c r="Q269" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R269" s="3">
         <v>0</v>
       </c>
       <c r="S269" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T269" s="3">
         <v>0</v>
@@ -43990,7 +43990,7 @@
         <v>80</v>
       </c>
       <c r="H270" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I270" s="3">
         <v>0</v>
@@ -44002,7 +44002,7 @@
         <v>0</v>
       </c>
       <c r="L270" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="M270" s="3">
         <v>0</v>
@@ -44017,13 +44017,13 @@
         <v>0</v>
       </c>
       <c r="Q270" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R270" s="3">
         <v>0</v>
       </c>
       <c r="S270" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T270" s="3">
         <v>0</v>
@@ -44143,7 +44143,7 @@
         <v>80</v>
       </c>
       <c r="H271" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I271" s="3">
         <v>0</v>
@@ -44155,7 +44155,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M271" s="3">
         <v>0</v>
@@ -44170,13 +44170,13 @@
         <v>0</v>
       </c>
       <c r="Q271" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R271" s="3">
         <v>0</v>
       </c>
       <c r="S271" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T271" s="3">
         <v>0</v>
@@ -44296,7 +44296,7 @@
         <v>80</v>
       </c>
       <c r="H272" s="3">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="I272" s="3">
         <v>0</v>
@@ -44308,7 +44308,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M272" s="3">
         <v>0</v>
@@ -44323,13 +44323,13 @@
         <v>0</v>
       </c>
       <c r="Q272" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R272" s="3">
         <v>0</v>
       </c>
       <c r="S272" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="T272" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C335860C-C2D1-4A11-8D33-E2F876D5FF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0398700-7177-43FC-BA39-1FB2F6A00136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="690" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2925" yWindow="1005" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -11254,10 +11254,10 @@
         <v>0</v>
       </c>
       <c r="J56" s="3">
+        <v>0</v>
+      </c>
+      <c r="K56" s="3">
         <v>33</v>
-      </c>
-      <c r="K56" s="3">
-        <v>0</v>
       </c>
       <c r="L56" s="3">
         <v>0</v>
@@ -11407,10 +11407,10 @@
         <v>30</v>
       </c>
       <c r="J57" s="3">
+        <v>0</v>
+      </c>
+      <c r="K57" s="3">
         <v>40</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -11485,34 +11485,34 @@
         <v>55</v>
       </c>
       <c r="AJ57" s="5" t="s">
-        <v>7</v>
+        <v>284</v>
       </c>
       <c r="AK57" s="5" t="s">
         <v>7</v>
       </c>
       <c r="AL57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AM57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AN57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AO57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AP57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AQ57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AR57" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AS57" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT57" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0398700-7177-43FC-BA39-1FB2F6A00136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42AF6E8-C3FF-439A-B687-2E865F0918A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2925" yWindow="1005" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -48112,19 +48112,19 @@
         <v>7</v>
       </c>
       <c r="E297" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F297" s="3">
         <v>0</v>
       </c>
       <c r="G297" s="3">
-        <v>180</v>
+        <v>570</v>
       </c>
       <c r="H297" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I297" s="3">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="J297" s="3">
         <v>0</v>
@@ -48271,13 +48271,13 @@
         <v>0</v>
       </c>
       <c r="G298" s="3">
-        <v>180</v>
+        <v>570</v>
       </c>
       <c r="H298" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I298" s="3">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="J298" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42AF6E8-C3FF-439A-B687-2E865F0918A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A58310-52F4-4CF2-9A8F-9B1EBB7E1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -44626,7 +44626,7 @@
         <v>0</v>
       </c>
       <c r="P274" s="3">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="Q274" s="3">
         <v>55</v>
@@ -44779,7 +44779,7 @@
         <v>0</v>
       </c>
       <c r="P275" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q275" s="3">
         <v>55</v>
@@ -44932,7 +44932,7 @@
         <v>0</v>
       </c>
       <c r="P276" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q276" s="3">
         <v>55</v>
@@ -45085,7 +45085,7 @@
         <v>0</v>
       </c>
       <c r="P277" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q277" s="3">
         <v>55</v>
@@ -45238,7 +45238,7 @@
         <v>0</v>
       </c>
       <c r="P278" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q278" s="3">
         <v>55</v>
@@ -45391,7 +45391,7 @@
         <v>0</v>
       </c>
       <c r="P279" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q279" s="3">
         <v>55</v>
@@ -45544,7 +45544,7 @@
         <v>0</v>
       </c>
       <c r="P280" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q280" s="3">
         <v>55</v>
@@ -45697,7 +45697,7 @@
         <v>0</v>
       </c>
       <c r="P281" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q281" s="3">
         <v>55</v>
@@ -45850,7 +45850,7 @@
         <v>0</v>
       </c>
       <c r="P282" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q282" s="3">
         <v>55</v>
@@ -46003,7 +46003,7 @@
         <v>0</v>
       </c>
       <c r="P283" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q283" s="3">
         <v>55</v>
@@ -46156,7 +46156,7 @@
         <v>0</v>
       </c>
       <c r="P284" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q284" s="3">
         <v>55</v>
@@ -46309,7 +46309,7 @@
         <v>0</v>
       </c>
       <c r="P285" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q285" s="3">
         <v>55</v>
@@ -46615,7 +46615,7 @@
         <v>0</v>
       </c>
       <c r="P287" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q287" s="3">
         <v>55</v>
@@ -46768,7 +46768,7 @@
         <v>0</v>
       </c>
       <c r="P288" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q288" s="3">
         <v>55</v>
@@ -46921,7 +46921,7 @@
         <v>0</v>
       </c>
       <c r="P289" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q289" s="3">
         <v>55</v>
@@ -47074,7 +47074,7 @@
         <v>0</v>
       </c>
       <c r="P290" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q290" s="3">
         <v>55</v>
@@ -47227,7 +47227,7 @@
         <v>0</v>
       </c>
       <c r="P291" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q291" s="3">
         <v>55</v>
@@ -47380,7 +47380,7 @@
         <v>0</v>
       </c>
       <c r="P292" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q292" s="3">
         <v>55</v>
@@ -47533,7 +47533,7 @@
         <v>0</v>
       </c>
       <c r="P293" s="3">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="Q293" s="3">
         <v>55</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A58310-52F4-4CF2-9A8F-9B1EBB7E1246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C049D86-B687-4701-ACCE-A6094F3A22ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="1275" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="585" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -2158,10 +2158,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>milk_frozen_twister</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ice_statue_twister</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2354,6 +2350,10 @@
     <rPh sb="4" eb="5">
       <t>ケイ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>icemilk_frozen_twister</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -18577,7 +18577,7 @@
         <v>999999</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D104" s="11" t="s">
         <v>7</v>
@@ -19189,7 +19189,7 @@
         <v>633</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>7</v>
@@ -19807,7 +19807,7 @@
         <v>7</v>
       </c>
       <c r="E112" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F112" s="3">
         <v>0</v>
@@ -24526,7 +24526,7 @@
         <v>0</v>
       </c>
       <c r="AV142" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AW142" s="5">
         <v>0</v>
@@ -24679,7 +24679,7 @@
         <v>0</v>
       </c>
       <c r="AV143" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AW143" s="5">
         <v>0</v>
@@ -24832,7 +24832,7 @@
         <v>0</v>
       </c>
       <c r="AV144" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AW144" s="5">
         <v>0</v>
@@ -24985,7 +24985,7 @@
         <v>0</v>
       </c>
       <c r="AV145" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AW145" s="5">
         <v>0</v>
@@ -33265,7 +33265,7 @@
         <v>890</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>7</v>
@@ -33418,7 +33418,7 @@
         <v>891</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>7</v>
@@ -35491,10 +35491,10 @@
         <v>75</v>
       </c>
       <c r="AE214" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AF214" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AF214" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="AG214" s="5" t="s">
         <v>7</v>
@@ -35518,10 +35518,10 @@
         <v>30</v>
       </c>
       <c r="AN214" s="5">
+        <v>20</v>
+      </c>
+      <c r="AO214" s="5">
         <v>30</v>
-      </c>
-      <c r="AO214" s="5">
-        <v>20</v>
       </c>
       <c r="AP214" s="5">
         <v>0</v>
@@ -35644,10 +35644,10 @@
         <v>75</v>
       </c>
       <c r="AE215" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AF215" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="AF215" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="AG215" s="5" t="s">
         <v>7</v>
@@ -35671,10 +35671,10 @@
         <v>15</v>
       </c>
       <c r="AN215" s="5">
+        <v>20</v>
+      </c>
+      <c r="AO215" s="5">
         <v>15</v>
-      </c>
-      <c r="AO215" s="5">
-        <v>20</v>
       </c>
       <c r="AP215" s="5">
         <v>0</v>
@@ -35797,10 +35797,10 @@
         <v>7</v>
       </c>
       <c r="AE216" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AF216" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="AF216" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="AG216" s="5" t="s">
         <v>7</v>
@@ -40567,7 +40567,7 @@
         <v>30</v>
       </c>
       <c r="AN247" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO247" s="5">
         <v>0</v>
@@ -40720,7 +40720,7 @@
         <v>30</v>
       </c>
       <c r="AN248" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO248" s="5">
         <v>0</v>
@@ -40873,7 +40873,7 @@
         <v>30</v>
       </c>
       <c r="AN249" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO249" s="5">
         <v>0</v>
@@ -41026,7 +41026,7 @@
         <v>30</v>
       </c>
       <c r="AN250" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO250" s="5">
         <v>0</v>
@@ -41152,10 +41152,10 @@
         <v>75</v>
       </c>
       <c r="AE251" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="AF251" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AF251" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="AG251" s="5" t="s">
         <v>7</v>
@@ -41182,7 +41182,7 @@
         <v>30</v>
       </c>
       <c r="AO251" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AP251" s="5">
         <v>0</v>
@@ -41332,7 +41332,7 @@
         <v>30</v>
       </c>
       <c r="AN252" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO252" s="5">
         <v>0</v>
@@ -41533,7 +41533,7 @@
         <v>7</v>
       </c>
       <c r="E254" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F254" s="3">
         <v>0</v>
@@ -41548,7 +41548,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="3">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="K254" s="3">
         <v>0</v>
@@ -41590,13 +41590,13 @@
         <v>0</v>
       </c>
       <c r="X254" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y254" s="3">
         <v>0</v>
       </c>
       <c r="Z254" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA254" s="3">
         <v>0</v>
@@ -41986,7 +41986,7 @@
         <v>999999</v>
       </c>
       <c r="C257" s="11" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D257" s="11" t="s">
         <v>7</v>
@@ -42139,7 +42139,7 @@
         <v>1600</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>7</v>
@@ -42151,7 +42151,7 @@
         <v>0</v>
       </c>
       <c r="G258" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H258" s="3">
         <v>0</v>
@@ -42166,7 +42166,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M258" s="3">
         <v>0</v>
@@ -42181,7 +42181,7 @@
         <v>0</v>
       </c>
       <c r="Q258" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="R258" s="3">
         <v>0</v>
@@ -42202,13 +42202,13 @@
         <v>0</v>
       </c>
       <c r="X258" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y258" s="3">
         <v>0</v>
       </c>
       <c r="Z258" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA258" s="3">
         <v>0</v>
@@ -42274,7 +42274,7 @@
         <v>0</v>
       </c>
       <c r="AV258" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AW258" s="5">
         <v>0</v>
@@ -42292,7 +42292,7 @@
         <v>1601</v>
       </c>
       <c r="C259" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>7</v>
@@ -42334,7 +42334,7 @@
         <v>0</v>
       </c>
       <c r="Q259" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="R259" s="3">
         <v>0</v>
@@ -42361,7 +42361,7 @@
         <v>0</v>
       </c>
       <c r="Z259" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA259" s="3">
         <v>0</v>
@@ -42427,7 +42427,7 @@
         <v>0</v>
       </c>
       <c r="AV259" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AW259" s="5">
         <v>0</v>
@@ -42445,7 +42445,7 @@
         <v>1602</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>7</v>
@@ -42457,7 +42457,7 @@
         <v>0</v>
       </c>
       <c r="G260" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H260" s="3">
         <v>0</v>
@@ -42472,7 +42472,7 @@
         <v>0</v>
       </c>
       <c r="L260" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M260" s="3">
         <v>0</v>
@@ -42487,7 +42487,7 @@
         <v>0</v>
       </c>
       <c r="Q260" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="R260" s="3">
         <v>0</v>
@@ -42508,13 +42508,13 @@
         <v>0</v>
       </c>
       <c r="X260" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y260" s="3">
         <v>0</v>
       </c>
       <c r="Z260" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA260" s="3">
         <v>0</v>
@@ -42580,7 +42580,7 @@
         <v>0</v>
       </c>
       <c r="AV260" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AW260" s="5">
         <v>0</v>
@@ -42952,7 +42952,7 @@
         <v>0</v>
       </c>
       <c r="S263" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T263" s="3">
         <v>0</v>
@@ -43108,7 +43108,7 @@
         <v>0</v>
       </c>
       <c r="T264" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U264" s="3">
         <v>0</v>
@@ -43261,7 +43261,7 @@
         <v>0</v>
       </c>
       <c r="T265" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U265" s="3">
         <v>0</v>
@@ -43411,7 +43411,7 @@
         <v>0</v>
       </c>
       <c r="S266" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T266" s="3">
         <v>0</v>
@@ -43432,7 +43432,7 @@
         <v>0</v>
       </c>
       <c r="Z266" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA266" s="3">
         <v>0</v>
@@ -43579,7 +43579,7 @@
         <v>0</v>
       </c>
       <c r="X267" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y267" s="3">
         <v>0</v>
@@ -43681,10 +43681,10 @@
         <v>0</v>
       </c>
       <c r="G268" s="3">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="H268" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I268" s="3">
         <v>0</v>
@@ -43723,7 +43723,7 @@
         <v>0</v>
       </c>
       <c r="U268" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V268" s="3">
         <v>0</v>
@@ -43891,7 +43891,7 @@
         <v>0</v>
       </c>
       <c r="Z269" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA269" s="3">
         <v>0</v>
@@ -43981,7 +43981,7 @@
         <v>7</v>
       </c>
       <c r="E270" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F270" s="3">
         <v>0</v>
@@ -43990,7 +43990,7 @@
         <v>80</v>
       </c>
       <c r="H270" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I270" s="3">
         <v>0</v>
@@ -44143,7 +44143,7 @@
         <v>80</v>
       </c>
       <c r="H271" s="3">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="I271" s="3">
         <v>0</v>
@@ -44296,7 +44296,7 @@
         <v>80</v>
       </c>
       <c r="H272" s="3">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="I272" s="3">
         <v>0</v>
@@ -44434,7 +44434,7 @@
         <v>999999</v>
       </c>
       <c r="C273" s="11" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D273" s="11" t="s">
         <v>7</v>
@@ -44587,7 +44587,7 @@
         <v>1800</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D274" s="3" t="s">
         <v>7</v>
@@ -44698,7 +44698,7 @@
         <v>30</v>
       </c>
       <c r="AN274" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO274" s="5">
         <v>0</v>
@@ -44740,7 +44740,7 @@
         <v>1801</v>
       </c>
       <c r="C275" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>7</v>
@@ -44851,7 +44851,7 @@
         <v>30</v>
       </c>
       <c r="AN275" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO275" s="5">
         <v>0</v>
@@ -44893,7 +44893,7 @@
         <v>1802</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>7</v>
@@ -45004,7 +45004,7 @@
         <v>30</v>
       </c>
       <c r="AN276" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO276" s="5">
         <v>0</v>
@@ -45046,7 +45046,7 @@
         <v>1803</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D277" s="3" t="s">
         <v>7</v>
@@ -45157,7 +45157,7 @@
         <v>30</v>
       </c>
       <c r="AN277" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO277" s="5">
         <v>0</v>
@@ -45199,7 +45199,7 @@
         <v>1804</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>7</v>
@@ -45310,7 +45310,7 @@
         <v>30</v>
       </c>
       <c r="AN278" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO278" s="5">
         <v>0</v>
@@ -45352,7 +45352,7 @@
         <v>1805</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>7</v>
@@ -45463,7 +45463,7 @@
         <v>30</v>
       </c>
       <c r="AN279" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO279" s="5">
         <v>0</v>
@@ -45505,7 +45505,7 @@
         <v>1806</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>7</v>
@@ -45616,7 +45616,7 @@
         <v>30</v>
       </c>
       <c r="AN280" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO280" s="5">
         <v>0</v>
@@ -45658,7 +45658,7 @@
         <v>1807</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>7</v>
@@ -45769,7 +45769,7 @@
         <v>30</v>
       </c>
       <c r="AN281" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO281" s="5">
         <v>0</v>
@@ -45811,7 +45811,7 @@
         <v>1808</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>7</v>
@@ -45922,7 +45922,7 @@
         <v>30</v>
       </c>
       <c r="AN282" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO282" s="5">
         <v>0</v>
@@ -45964,7 +45964,7 @@
         <v>1809</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>7</v>
@@ -46075,7 +46075,7 @@
         <v>30</v>
       </c>
       <c r="AN283" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO283" s="5">
         <v>30</v>
@@ -46117,7 +46117,7 @@
         <v>1810</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>7</v>
@@ -46228,7 +46228,7 @@
         <v>30</v>
       </c>
       <c r="AN284" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO284" s="5">
         <v>30</v>
@@ -46270,7 +46270,7 @@
         <v>1811</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>7</v>
@@ -46381,7 +46381,7 @@
         <v>30</v>
       </c>
       <c r="AN285" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO285" s="5">
         <v>0</v>
@@ -46423,7 +46423,7 @@
         <v>999999</v>
       </c>
       <c r="C286" s="11" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D286" s="11" t="s">
         <v>7</v>
@@ -46576,7 +46576,7 @@
         <v>1820</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>7</v>
@@ -46687,7 +46687,7 @@
         <v>30</v>
       </c>
       <c r="AN287" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO287" s="5">
         <v>0</v>
@@ -46729,7 +46729,7 @@
         <v>1821</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>7</v>
@@ -46840,7 +46840,7 @@
         <v>30</v>
       </c>
       <c r="AN288" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO288" s="5">
         <v>0</v>
@@ -46882,7 +46882,7 @@
         <v>1822</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>7</v>
@@ -46993,7 +46993,7 @@
         <v>30</v>
       </c>
       <c r="AN289" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO289" s="5">
         <v>0</v>
@@ -47035,7 +47035,7 @@
         <v>1823</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>7</v>
@@ -47146,7 +47146,7 @@
         <v>30</v>
       </c>
       <c r="AN290" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO290" s="5">
         <v>0</v>
@@ -47188,7 +47188,7 @@
         <v>1824</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>7</v>
@@ -47299,7 +47299,7 @@
         <v>30</v>
       </c>
       <c r="AN291" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO291" s="5">
         <v>0</v>
@@ -47341,7 +47341,7 @@
         <v>1825</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>7</v>
@@ -47452,7 +47452,7 @@
         <v>30</v>
       </c>
       <c r="AN292" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO292" s="5">
         <v>0</v>
@@ -47494,7 +47494,7 @@
         <v>1826</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>7</v>
@@ -47605,7 +47605,7 @@
         <v>30</v>
       </c>
       <c r="AN293" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AO293" s="5">
         <v>0</v>
@@ -49465,7 +49465,7 @@
         <v>0</v>
       </c>
       <c r="AV305" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AW305" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C049D86-B687-4701-ACCE-A6094F3A22ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10A64F2-AE46-41E2-A137-D96F4A1946B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="585" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10A64F2-AE46-41E2-A137-D96F4A1946B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F148DE-199E-428D-8366-3CF6A89704FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="390" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="930" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="452">
   <si>
     <t>desc</t>
   </si>
@@ -2356,6 +2356,22 @@
     <t>icemilk_frozen_twister</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>FreezedFlower</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SodaSuger</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IceCubeHigh</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IceCubeEx</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -24175,7 +24191,7 @@
         <v>64</v>
       </c>
       <c r="AG140" s="5" t="s">
-        <v>255</v>
+        <v>448</v>
       </c>
       <c r="AH140" s="5" t="s">
         <v>75</v>
@@ -24202,7 +24218,7 @@
         <v>20</v>
       </c>
       <c r="AP140" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AQ140" s="5">
         <v>20</v>
@@ -24211,7 +24227,7 @@
         <v>20</v>
       </c>
       <c r="AS140" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AT140" s="5">
         <v>0</v>
@@ -24325,7 +24341,7 @@
         <v>284</v>
       </c>
       <c r="AF141" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AG141" s="5" t="s">
         <v>7</v>
@@ -24352,7 +24368,7 @@
         <v>40</v>
       </c>
       <c r="AO141" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP141" s="5">
         <v>0</v>
@@ -24499,25 +24515,25 @@
         <v>10</v>
       </c>
       <c r="AM142" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN142" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO142" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP142" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ142" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR142" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS142" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT142" s="5">
         <v>0</v>
@@ -24652,25 +24668,25 @@
         <v>10</v>
       </c>
       <c r="AM143" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN143" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO143" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP143" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ143" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR143" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS143" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT143" s="5">
         <v>0</v>
@@ -24805,25 +24821,25 @@
         <v>10</v>
       </c>
       <c r="AM144" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN144" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO144" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP144" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ144" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR144" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS144" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT144" s="5">
         <v>0</v>
@@ -24958,25 +24974,25 @@
         <v>10</v>
       </c>
       <c r="AM145" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN145" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO145" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP145" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ145" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR145" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS145" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT145" s="5">
         <v>0</v>
@@ -25084,7 +25100,7 @@
         <v>75</v>
       </c>
       <c r="AD146" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AE146" s="5" t="s">
         <v>7</v>
@@ -25111,7 +25127,7 @@
         <v>20</v>
       </c>
       <c r="AM146" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN146" s="5">
         <v>0</v>
@@ -25858,7 +25874,7 @@
         <v>64</v>
       </c>
       <c r="AG151" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AH151" s="5" t="s">
         <v>7</v>
@@ -25885,16 +25901,16 @@
         <v>20</v>
       </c>
       <c r="AP151" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AQ151" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR151" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS151" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT151" s="5">
         <v>0</v>
@@ -26011,7 +26027,7 @@
         <v>64</v>
       </c>
       <c r="AG152" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AH152" s="5" t="s">
         <v>7</v>
@@ -26038,16 +26054,16 @@
         <v>20</v>
       </c>
       <c r="AP152" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AQ152" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR152" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS152" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT152" s="5">
         <v>0</v>
@@ -26152,13 +26168,13 @@
         <v>0</v>
       </c>
       <c r="AC153" s="5" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="AD153" s="5" t="s">
         <v>47</v>
       </c>
       <c r="AE153" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AF153" s="5" t="s">
         <v>7</v>
@@ -26185,22 +26201,22 @@
         <v>20</v>
       </c>
       <c r="AN153" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO153" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP153" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ153" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR153" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS153" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT153" s="5">
         <v>0</v>
@@ -26305,10 +26321,10 @@
         <v>0</v>
       </c>
       <c r="AC154" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AD154" s="5" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="AE154" s="5" t="s">
         <v>7</v>
@@ -26332,28 +26348,28 @@
         <v>7</v>
       </c>
       <c r="AL154" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AM154" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN154" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO154" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP154" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ154" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR154" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS154" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT154" s="5">
         <v>0</v>
@@ -26764,7 +26780,7 @@
         <v>0</v>
       </c>
       <c r="AC157" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AD157" s="5" t="s">
         <v>7</v>
@@ -26791,28 +26807,28 @@
         <v>7</v>
       </c>
       <c r="AL157" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AM157" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN157" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO157" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP157" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ157" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR157" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS157" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT157" s="5">
         <v>0</v>
@@ -26917,7 +26933,7 @@
         <v>0</v>
       </c>
       <c r="AC158" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AD158" s="5" t="s">
         <v>7</v>
@@ -26944,28 +26960,28 @@
         <v>7</v>
       </c>
       <c r="AL158" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AM158" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN158" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO158" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP158" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ158" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR158" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS158" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT158" s="5">
         <v>0</v>
@@ -27070,7 +27086,7 @@
         <v>0</v>
       </c>
       <c r="AC159" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AD159" s="5" t="s">
         <v>7</v>
@@ -27097,28 +27113,28 @@
         <v>7</v>
       </c>
       <c r="AL159" s="5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AM159" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN159" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO159" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP159" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ159" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR159" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS159" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT159" s="5">
         <v>0</v>
@@ -27223,7 +27239,7 @@
         <v>0</v>
       </c>
       <c r="AC160" s="5" t="s">
-        <v>7</v>
+        <v>448</v>
       </c>
       <c r="AD160" s="5" t="s">
         <v>7</v>
@@ -27250,28 +27266,28 @@
         <v>7</v>
       </c>
       <c r="AL160" s="5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AM160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR160" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS160" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT160" s="5">
         <v>0</v>
@@ -33811,10 +33827,10 @@
         <v>301</v>
       </c>
       <c r="AF203" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG203" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH203" s="5" t="s">
         <v>7</v>
@@ -33832,16 +33848,16 @@
         <v>-50</v>
       </c>
       <c r="AM203" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN203" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO203" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP203" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ203" s="5">
         <v>0</v>
@@ -33964,10 +33980,10 @@
         <v>301</v>
       </c>
       <c r="AF204" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG204" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH204" s="5" t="s">
         <v>7</v>
@@ -33985,16 +34001,16 @@
         <v>-50</v>
       </c>
       <c r="AM204" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN204" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO204" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP204" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ204" s="5">
         <v>0</v>
@@ -34117,10 +34133,10 @@
         <v>301</v>
       </c>
       <c r="AF205" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG205" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH205" s="5" t="s">
         <v>7</v>
@@ -34138,16 +34154,16 @@
         <v>-50</v>
       </c>
       <c r="AM205" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN205" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO205" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP205" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ205" s="5">
         <v>0</v>
@@ -34270,10 +34286,10 @@
         <v>301</v>
       </c>
       <c r="AF206" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG206" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH206" s="5" t="s">
         <v>7</v>
@@ -34291,16 +34307,16 @@
         <v>-50</v>
       </c>
       <c r="AM206" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN206" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO206" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP206" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ206" s="5">
         <v>0</v>
@@ -34423,10 +34439,10 @@
         <v>301</v>
       </c>
       <c r="AF207" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG207" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH207" s="5" t="s">
         <v>7</v>
@@ -34444,16 +34460,16 @@
         <v>-50</v>
       </c>
       <c r="AM207" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN207" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO207" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP207" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ207" s="5">
         <v>0</v>
@@ -34576,10 +34592,10 @@
         <v>301</v>
       </c>
       <c r="AF208" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG208" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH208" s="5" t="s">
         <v>7</v>
@@ -34597,16 +34613,16 @@
         <v>-50</v>
       </c>
       <c r="AM208" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN208" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO208" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP208" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ208" s="5">
         <v>0</v>
@@ -34729,10 +34745,10 @@
         <v>301</v>
       </c>
       <c r="AF209" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG209" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH209" s="5" t="s">
         <v>7</v>
@@ -34750,16 +34766,16 @@
         <v>-50</v>
       </c>
       <c r="AM209" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN209" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO209" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP209" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ209" s="5">
         <v>0</v>
@@ -34882,10 +34898,10 @@
         <v>301</v>
       </c>
       <c r="AF210" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG210" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH210" s="5" t="s">
         <v>7</v>
@@ -34903,16 +34919,16 @@
         <v>-50</v>
       </c>
       <c r="AM210" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN210" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO210" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP210" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ210" s="5">
         <v>0</v>
@@ -35035,10 +35051,10 @@
         <v>301</v>
       </c>
       <c r="AF211" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG211" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH211" s="5" t="s">
         <v>7</v>
@@ -35056,16 +35072,16 @@
         <v>-50</v>
       </c>
       <c r="AM211" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN211" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO211" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP211" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ211" s="5">
         <v>0</v>
@@ -35188,10 +35204,10 @@
         <v>301</v>
       </c>
       <c r="AF212" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG212" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH212" s="5" t="s">
         <v>7</v>
@@ -35209,16 +35225,16 @@
         <v>-50</v>
       </c>
       <c r="AM212" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN212" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO212" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP212" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ212" s="5">
         <v>0</v>
@@ -35341,10 +35357,10 @@
         <v>301</v>
       </c>
       <c r="AF213" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG213" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH213" s="5" t="s">
         <v>7</v>
@@ -35362,16 +35378,16 @@
         <v>-50</v>
       </c>
       <c r="AM213" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN213" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO213" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP213" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ213" s="5">
         <v>0</v>
@@ -35494,13 +35510,13 @@
         <v>301</v>
       </c>
       <c r="AF214" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AG214" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH214" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AG214" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH214" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AI214" s="5" t="s">
         <v>7</v>
@@ -35515,19 +35531,19 @@
         <v>-50</v>
       </c>
       <c r="AM214" s="5">
+        <v>15</v>
+      </c>
+      <c r="AN214" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO214" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP214" s="5">
+        <v>55</v>
+      </c>
+      <c r="AQ214" s="5">
         <v>30</v>
-      </c>
-      <c r="AN214" s="5">
-        <v>20</v>
-      </c>
-      <c r="AO214" s="5">
-        <v>30</v>
-      </c>
-      <c r="AP214" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ214" s="5">
-        <v>0</v>
       </c>
       <c r="AR214" s="5">
         <v>0</v>
@@ -35647,13 +35663,13 @@
         <v>301</v>
       </c>
       <c r="AF215" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AG215" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH215" s="5" t="s">
         <v>55</v>
-      </c>
-      <c r="AG215" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH215" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AI215" s="5" t="s">
         <v>7</v>
@@ -35668,19 +35684,19 @@
         <v>-50</v>
       </c>
       <c r="AM215" s="5">
+        <v>10</v>
+      </c>
+      <c r="AN215" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO215" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP215" s="5">
+        <v>55</v>
+      </c>
+      <c r="AQ215" s="5">
         <v>15</v>
-      </c>
-      <c r="AN215" s="5">
-        <v>20</v>
-      </c>
-      <c r="AO215" s="5">
-        <v>15</v>
-      </c>
-      <c r="AP215" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ215" s="5">
-        <v>0</v>
       </c>
       <c r="AR215" s="5">
         <v>0</v>
@@ -35800,13 +35816,13 @@
         <v>301</v>
       </c>
       <c r="AF216" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AG216" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH216" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="AG216" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH216" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AI216" s="5" t="s">
         <v>7</v>
@@ -35824,16 +35840,16 @@
         <v>0</v>
       </c>
       <c r="AN216" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO216" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP216" s="5">
+        <v>55</v>
+      </c>
+      <c r="AQ216" s="5">
         <v>20</v>
-      </c>
-      <c r="AO216" s="5">
-        <v>20</v>
-      </c>
-      <c r="AP216" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ216" s="5">
-        <v>0</v>
       </c>
       <c r="AR216" s="5">
         <v>0</v>
@@ -35953,10 +35969,10 @@
         <v>301</v>
       </c>
       <c r="AF217" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG217" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH217" s="5" t="s">
         <v>7</v>
@@ -35974,16 +35990,16 @@
         <v>-50</v>
       </c>
       <c r="AM217" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN217" s="5">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AO217" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP217" s="5">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AQ217" s="5">
         <v>0</v>
@@ -40543,10 +40559,10 @@
         <v>301</v>
       </c>
       <c r="AF247" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG247" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH247" s="5" t="s">
         <v>7</v>
@@ -40564,16 +40580,16 @@
         <v>-50</v>
       </c>
       <c r="AM247" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN247" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO247" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP247" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ247" s="5">
         <v>0</v>
@@ -40696,10 +40712,10 @@
         <v>301</v>
       </c>
       <c r="AF248" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG248" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH248" s="5" t="s">
         <v>7</v>
@@ -40717,16 +40733,16 @@
         <v>-50</v>
       </c>
       <c r="AM248" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN248" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO248" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP248" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ248" s="5">
         <v>0</v>
@@ -40849,10 +40865,10 @@
         <v>301</v>
       </c>
       <c r="AF249" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG249" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH249" s="5" t="s">
         <v>7</v>
@@ -40870,16 +40886,16 @@
         <v>-50</v>
       </c>
       <c r="AM249" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN249" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO249" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP249" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ249" s="5">
         <v>0</v>
@@ -41002,10 +41018,10 @@
         <v>301</v>
       </c>
       <c r="AF250" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG250" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH250" s="5" t="s">
         <v>7</v>
@@ -41023,16 +41039,16 @@
         <v>-50</v>
       </c>
       <c r="AM250" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN250" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO250" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP250" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ250" s="5">
         <v>0</v>
@@ -41155,13 +41171,13 @@
         <v>301</v>
       </c>
       <c r="AF251" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AG251" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH251" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="AG251" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH251" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AI251" s="5" t="s">
         <v>7</v>
@@ -41176,19 +41192,19 @@
         <v>-50</v>
       </c>
       <c r="AM251" s="5">
+        <v>15</v>
+      </c>
+      <c r="AN251" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO251" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP251" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ251" s="5">
         <v>30</v>
-      </c>
-      <c r="AN251" s="5">
-        <v>30</v>
-      </c>
-      <c r="AO251" s="5">
-        <v>30</v>
-      </c>
-      <c r="AP251" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ251" s="5">
-        <v>0</v>
       </c>
       <c r="AR251" s="5">
         <v>0</v>
@@ -41308,10 +41324,10 @@
         <v>301</v>
       </c>
       <c r="AF252" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG252" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH252" s="5" t="s">
         <v>7</v>
@@ -41329,16 +41345,16 @@
         <v>-50</v>
       </c>
       <c r="AM252" s="5">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AN252" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO252" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP252" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ252" s="5">
         <v>0</v>
@@ -44674,13 +44690,13 @@
         <v>301</v>
       </c>
       <c r="AF274" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG274" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH274" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI274" s="5" t="s">
         <v>7</v>
@@ -44698,16 +44714,16 @@
         <v>30</v>
       </c>
       <c r="AN274" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO274" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP274" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ274" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR274" s="5">
         <v>0</v>
@@ -44827,13 +44843,13 @@
         <v>301</v>
       </c>
       <c r="AF275" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG275" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH275" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI275" s="5" t="s">
         <v>7</v>
@@ -44851,16 +44867,16 @@
         <v>30</v>
       </c>
       <c r="AN275" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO275" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP275" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ275" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR275" s="5">
         <v>0</v>
@@ -44980,13 +44996,13 @@
         <v>301</v>
       </c>
       <c r="AF276" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG276" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH276" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI276" s="5" t="s">
         <v>7</v>
@@ -45004,16 +45020,16 @@
         <v>30</v>
       </c>
       <c r="AN276" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO276" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP276" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ276" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR276" s="5">
         <v>0</v>
@@ -45133,13 +45149,13 @@
         <v>301</v>
       </c>
       <c r="AF277" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG277" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH277" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI277" s="5" t="s">
         <v>7</v>
@@ -45157,16 +45173,16 @@
         <v>30</v>
       </c>
       <c r="AN277" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO277" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP277" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ277" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR277" s="5">
         <v>0</v>
@@ -45286,13 +45302,13 @@
         <v>301</v>
       </c>
       <c r="AF278" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG278" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH278" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI278" s="5" t="s">
         <v>7</v>
@@ -45310,16 +45326,16 @@
         <v>30</v>
       </c>
       <c r="AN278" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO278" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP278" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ278" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR278" s="5">
         <v>0</v>
@@ -45439,13 +45455,13 @@
         <v>301</v>
       </c>
       <c r="AF279" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG279" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH279" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI279" s="5" t="s">
         <v>7</v>
@@ -45463,16 +45479,16 @@
         <v>30</v>
       </c>
       <c r="AN279" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO279" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP279" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ279" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR279" s="5">
         <v>0</v>
@@ -45592,13 +45608,13 @@
         <v>301</v>
       </c>
       <c r="AF280" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG280" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH280" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI280" s="5" t="s">
         <v>7</v>
@@ -45616,16 +45632,16 @@
         <v>30</v>
       </c>
       <c r="AN280" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO280" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP280" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ280" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR280" s="5">
         <v>0</v>
@@ -45745,13 +45761,13 @@
         <v>301</v>
       </c>
       <c r="AF281" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG281" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH281" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI281" s="5" t="s">
         <v>7</v>
@@ -45769,16 +45785,16 @@
         <v>30</v>
       </c>
       <c r="AN281" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO281" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP281" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ281" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR281" s="5">
         <v>0</v>
@@ -45898,13 +45914,13 @@
         <v>301</v>
       </c>
       <c r="AF282" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG282" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH282" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI282" s="5" t="s">
         <v>7</v>
@@ -45922,16 +45938,16 @@
         <v>30</v>
       </c>
       <c r="AN282" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO282" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP282" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ282" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR282" s="5">
         <v>0</v>
@@ -46051,16 +46067,16 @@
         <v>301</v>
       </c>
       <c r="AF283" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AG283" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH283" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="AI283" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="AG283" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH283" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI283" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AJ283" s="5" t="s">
         <v>7</v>
@@ -46075,19 +46091,19 @@
         <v>30</v>
       </c>
       <c r="AN283" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO283" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP283" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ283" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR283" s="5">
         <v>30</v>
-      </c>
-      <c r="AO283" s="5">
-        <v>30</v>
-      </c>
-      <c r="AP283" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ283" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR283" s="5">
-        <v>0</v>
       </c>
       <c r="AS283" s="5">
         <v>0</v>
@@ -46123,7 +46139,7 @@
         <v>7</v>
       </c>
       <c r="E284" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F284" s="3">
         <v>0</v>
@@ -46204,16 +46220,16 @@
         <v>301</v>
       </c>
       <c r="AF284" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="AG284" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="AH284" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="AI284" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="AG284" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH284" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI284" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AJ284" s="5" t="s">
         <v>7</v>
@@ -46228,19 +46244,19 @@
         <v>30</v>
       </c>
       <c r="AN284" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO284" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP284" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ284" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR284" s="5">
         <v>30</v>
-      </c>
-      <c r="AO284" s="5">
-        <v>30</v>
-      </c>
-      <c r="AP284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR284" s="5">
-        <v>0</v>
       </c>
       <c r="AS284" s="5">
         <v>0</v>
@@ -46276,7 +46292,7 @@
         <v>7</v>
       </c>
       <c r="E285" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F285" s="3">
         <v>0</v>
@@ -46357,13 +46373,13 @@
         <v>301</v>
       </c>
       <c r="AF285" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG285" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH285" s="5" t="s">
-        <v>7</v>
+        <v>449</v>
       </c>
       <c r="AI285" s="5" t="s">
         <v>7</v>
@@ -46381,16 +46397,16 @@
         <v>30</v>
       </c>
       <c r="AN285" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO285" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP285" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ285" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR285" s="5">
         <v>0</v>
@@ -46663,10 +46679,10 @@
         <v>301</v>
       </c>
       <c r="AF287" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG287" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH287" s="5" t="s">
         <v>7</v>
@@ -46687,13 +46703,13 @@
         <v>30</v>
       </c>
       <c r="AN287" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO287" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP287" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ287" s="5">
         <v>0</v>
@@ -46735,7 +46751,7 @@
         <v>7</v>
       </c>
       <c r="E288" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F288" s="3">
         <v>0</v>
@@ -46816,10 +46832,10 @@
         <v>301</v>
       </c>
       <c r="AF288" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG288" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH288" s="5" t="s">
         <v>7</v>
@@ -46840,13 +46856,13 @@
         <v>30</v>
       </c>
       <c r="AN288" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO288" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP288" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ288" s="5">
         <v>0</v>
@@ -46969,10 +46985,10 @@
         <v>301</v>
       </c>
       <c r="AF289" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG289" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH289" s="5" t="s">
         <v>7</v>
@@ -46993,13 +47009,13 @@
         <v>30</v>
       </c>
       <c r="AN289" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO289" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP289" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ289" s="5">
         <v>0</v>
@@ -47122,10 +47138,10 @@
         <v>301</v>
       </c>
       <c r="AF290" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG290" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH290" s="5" t="s">
         <v>7</v>
@@ -47146,13 +47162,13 @@
         <v>30</v>
       </c>
       <c r="AN290" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO290" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP290" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ290" s="5">
         <v>0</v>
@@ -47275,10 +47291,10 @@
         <v>301</v>
       </c>
       <c r="AF291" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG291" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH291" s="5" t="s">
         <v>7</v>
@@ -47299,13 +47315,13 @@
         <v>30</v>
       </c>
       <c r="AN291" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO291" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP291" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ291" s="5">
         <v>0</v>
@@ -47428,10 +47444,10 @@
         <v>301</v>
       </c>
       <c r="AF292" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG292" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH292" s="5" t="s">
         <v>7</v>
@@ -47452,13 +47468,13 @@
         <v>30</v>
       </c>
       <c r="AN292" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO292" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP292" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ292" s="5">
         <v>0</v>
@@ -47581,10 +47597,10 @@
         <v>301</v>
       </c>
       <c r="AF293" s="5" t="s">
-        <v>7</v>
+        <v>450</v>
       </c>
       <c r="AG293" s="5" t="s">
-        <v>7</v>
+        <v>451</v>
       </c>
       <c r="AH293" s="5" t="s">
         <v>7</v>
@@ -47605,13 +47621,13 @@
         <v>30</v>
       </c>
       <c r="AN293" s="5">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AO293" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP293" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ293" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F148DE-199E-428D-8366-3CF6A89704FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334121DA-D0DF-4585-9549-3911AC6FB49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="930" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2115" yWindow="1230" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -14567,7 +14567,7 @@
         <v>7</v>
       </c>
       <c r="AL77" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM77" s="5">
         <v>10</v>
@@ -14720,7 +14720,7 @@
         <v>7</v>
       </c>
       <c r="AL78" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM78" s="5">
         <v>10</v>
@@ -14873,7 +14873,7 @@
         <v>7</v>
       </c>
       <c r="AL79" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM79" s="5">
         <v>10</v>
@@ -15026,7 +15026,7 @@
         <v>7</v>
       </c>
       <c r="AL80" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM80" s="5">
         <v>10</v>
@@ -15179,7 +15179,7 @@
         <v>7</v>
       </c>
       <c r="AL81" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM81" s="5">
         <v>10</v>
@@ -15332,7 +15332,7 @@
         <v>7</v>
       </c>
       <c r="AL82" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM82" s="5">
         <v>10</v>
@@ -15485,7 +15485,7 @@
         <v>7</v>
       </c>
       <c r="AL83" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM83" s="5">
         <v>10</v>
@@ -15638,7 +15638,7 @@
         <v>7</v>
       </c>
       <c r="AL84" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM84" s="5">
         <v>10</v>
@@ -15791,7 +15791,7 @@
         <v>7</v>
       </c>
       <c r="AL85" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM85" s="5">
         <v>10</v>
@@ -15944,7 +15944,7 @@
         <v>7</v>
       </c>
       <c r="AL86" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM86" s="5">
         <v>10</v>
@@ -16097,7 +16097,7 @@
         <v>7</v>
       </c>
       <c r="AL87" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM87" s="5">
         <v>10</v>
@@ -16250,7 +16250,7 @@
         <v>7</v>
       </c>
       <c r="AL88" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM88" s="5">
         <v>15</v>
@@ -16403,7 +16403,7 @@
         <v>7</v>
       </c>
       <c r="AL89" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM89" s="5">
         <v>15</v>
@@ -16556,7 +16556,7 @@
         <v>7</v>
       </c>
       <c r="AL90" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM90" s="5">
         <v>15</v>
@@ -16709,7 +16709,7 @@
         <v>7</v>
       </c>
       <c r="AL91" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM91" s="5">
         <v>15</v>
@@ -16862,7 +16862,7 @@
         <v>7</v>
       </c>
       <c r="AL92" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM92" s="5">
         <v>15</v>
@@ -17015,7 +17015,7 @@
         <v>7</v>
       </c>
       <c r="AL93" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM93" s="5">
         <v>10</v>
@@ -19004,7 +19004,7 @@
         <v>7</v>
       </c>
       <c r="AL106" s="5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AM106" s="5">
         <v>0</v>
@@ -19157,7 +19157,7 @@
         <v>7</v>
       </c>
       <c r="AL107" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AM107" s="5">
         <v>15</v>
@@ -19310,7 +19310,7 @@
         <v>7</v>
       </c>
       <c r="AL108" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AM108" s="5">
         <v>15</v>
@@ -41801,7 +41801,7 @@
         <v>7</v>
       </c>
       <c r="AL255" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM255" s="5">
         <v>10</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334121DA-D0DF-4585-9549-3911AC6FB49C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEC7A31-05C6-4335-B3EA-3A0AA76D34F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2115" yWindow="1230" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2265" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3710" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3734" uniqueCount="452">
   <si>
     <t>desc</t>
   </si>
@@ -1249,18 +1249,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Jasmin</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ElderFlower</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Hydrangea</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>cafelatte</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2372,6 +2360,35 @@
     <t>IceCubeEx</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>お花系##</t>
+    </r>
+    <rPh sb="3" eb="4">
+      <t>ハナ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>lavender_cookie</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ラベンダークッキー</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -2802,7 +2819,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AX306"/>
+  <dimension ref="A1:AX308"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -2879,37 +2896,37 @@
         <v>137</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="S1" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="Z1" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="AB1" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>8</v>
@@ -2975,12 +2992,12 @@
         <v>43</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A306" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A308" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -3905,7 +3922,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>7</v>
@@ -4040,7 +4057,7 @@
         <v>-20</v>
       </c>
       <c r="AV8" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AW8" s="5">
         <v>0</v>
@@ -6965,7 +6982,7 @@
         <v>999999</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>7</v>
@@ -7100,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="AV28" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW28" s="12">
         <v>0</v>
@@ -9491,7 +9508,7 @@
         <v>0</v>
       </c>
       <c r="AC44" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AD44" s="5" t="s">
         <v>34</v>
@@ -10178,7 +10195,7 @@
         <v>999999</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>7</v>
@@ -10313,7 +10330,7 @@
         <v>0</v>
       </c>
       <c r="AV49" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW49" s="12">
         <v>0</v>
@@ -11249,7 +11266,7 @@
         <v>528</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>7</v>
@@ -11402,7 +11419,7 @@
         <v>529</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>7</v>
@@ -11486,7 +11503,7 @@
         <v>29</v>
       </c>
       <c r="AE57" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="AF57" s="5" t="s">
         <v>47</v>
@@ -11501,7 +11518,7 @@
         <v>55</v>
       </c>
       <c r="AJ57" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AK57" s="5" t="s">
         <v>7</v>
@@ -11555,7 +11572,7 @@
         <v>999999</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>7</v>
@@ -11690,7 +11707,7 @@
         <v>0</v>
       </c>
       <c r="AV58" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW58" s="12">
         <v>0</v>
@@ -13085,7 +13102,7 @@
         <v>551</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>7</v>
@@ -13238,7 +13255,7 @@
         <v>552</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>7</v>
@@ -13391,7 +13408,7 @@
         <v>553</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>7</v>
@@ -13544,7 +13561,7 @@
         <v>554</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>7</v>
@@ -13697,7 +13714,7 @@
         <v>555</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>7</v>
@@ -13850,7 +13867,7 @@
         <v>556</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>7</v>
@@ -14003,7 +14020,7 @@
         <v>557</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>7</v>
@@ -14156,7 +14173,7 @@
         <v>999999</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>7</v>
@@ -14291,7 +14308,7 @@
         <v>0</v>
       </c>
       <c r="AV75" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW75" s="12">
         <v>0</v>
@@ -17063,7 +17080,7 @@
         <v>999999</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>7</v>
@@ -17198,7 +17215,7 @@
         <v>0</v>
       </c>
       <c r="AV94" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW94" s="12">
         <v>0</v>
@@ -17306,19 +17323,19 @@
         <v>84</v>
       </c>
       <c r="AG95" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AH95" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AI95" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AJ95" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="AH95" s="5" t="s">
+      <c r="AK95" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="AI95" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AJ95" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK95" s="5" t="s">
-        <v>7</v>
       </c>
       <c r="AL95" s="5">
         <v>-50</v>
@@ -17333,19 +17350,19 @@
         <v>40</v>
       </c>
       <c r="AP95" s="5">
+        <v>-100</v>
+      </c>
+      <c r="AQ95" s="5">
+        <v>-100</v>
+      </c>
+      <c r="AR95" s="5">
+        <v>-100</v>
+      </c>
+      <c r="AS95" s="5">
         <v>50</v>
       </c>
-      <c r="AQ95" s="5">
+      <c r="AT95" s="5">
         <v>20</v>
-      </c>
-      <c r="AR95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS95" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT95" s="5">
-        <v>0</v>
       </c>
       <c r="AU95" s="5">
         <v>0</v>
@@ -17459,19 +17476,19 @@
         <v>75</v>
       </c>
       <c r="AG96" s="5" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="AH96" s="5" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="AI96" s="5" t="s">
-        <v>64</v>
+        <v>448</v>
       </c>
       <c r="AJ96" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AK96" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="AL96" s="5">
         <v>-50</v>
@@ -17486,19 +17503,19 @@
         <v>12</v>
       </c>
       <c r="AP96" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AQ96" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AR96" s="5">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="AS96" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT96" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU96" s="5">
         <v>0</v>
@@ -17612,19 +17629,19 @@
         <v>75</v>
       </c>
       <c r="AG97" s="5" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="AH97" s="5" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="AI97" s="5" t="s">
-        <v>64</v>
+        <v>448</v>
       </c>
       <c r="AJ97" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AK97" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="AL97" s="5">
         <v>-50</v>
@@ -17639,19 +17656,19 @@
         <v>12</v>
       </c>
       <c r="AP97" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AQ97" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AR97" s="5">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="AS97" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT97" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU97" s="5">
         <v>0</v>
@@ -17765,19 +17782,19 @@
         <v>75</v>
       </c>
       <c r="AG98" s="5" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="AH98" s="5" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="AI98" s="5" t="s">
-        <v>64</v>
+        <v>448</v>
       </c>
       <c r="AJ98" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AK98" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="AL98" s="5">
         <v>-50</v>
@@ -17792,19 +17809,19 @@
         <v>12</v>
       </c>
       <c r="AP98" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AQ98" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AR98" s="5">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="AS98" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT98" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU98" s="5">
         <v>0</v>
@@ -17918,19 +17935,19 @@
         <v>75</v>
       </c>
       <c r="AG99" s="5" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="AH99" s="5" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="AI99" s="5" t="s">
-        <v>64</v>
+        <v>448</v>
       </c>
       <c r="AJ99" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AK99" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="AL99" s="5">
         <v>-50</v>
@@ -17945,19 +17962,19 @@
         <v>12</v>
       </c>
       <c r="AP99" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AQ99" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AR99" s="5">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="AS99" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT99" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU99" s="5">
         <v>0</v>
@@ -18071,19 +18088,19 @@
         <v>75</v>
       </c>
       <c r="AG100" s="5" t="s">
-        <v>255</v>
+        <v>298</v>
       </c>
       <c r="AH100" s="5" t="s">
-        <v>256</v>
+        <v>447</v>
       </c>
       <c r="AI100" s="5" t="s">
-        <v>64</v>
+        <v>448</v>
       </c>
       <c r="AJ100" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AK100" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="AL100" s="5">
         <v>-50</v>
@@ -18098,19 +18115,19 @@
         <v>12</v>
       </c>
       <c r="AP100" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AQ100" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AR100" s="5">
-        <v>10</v>
+        <v>-100</v>
       </c>
       <c r="AS100" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT100" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU100" s="5">
         <v>0</v>
@@ -18224,19 +18241,19 @@
         <v>62</v>
       </c>
       <c r="AG101" s="5" t="s">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="AH101" s="5" t="s">
-        <v>255</v>
+        <v>447</v>
       </c>
       <c r="AI101" s="5" t="s">
-        <v>256</v>
+        <v>448</v>
       </c>
       <c r="AJ101" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="AK101" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="AL101" s="5">
         <v>-50</v>
@@ -18251,19 +18268,19 @@
         <v>20</v>
       </c>
       <c r="AP101" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AQ101" s="5">
-        <v>12</v>
+        <v>-100</v>
       </c>
       <c r="AR101" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AS101" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT101" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU101" s="5">
         <v>0</v>
@@ -18377,19 +18394,19 @@
         <v>75</v>
       </c>
       <c r="AG102" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AH102" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AI102" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AJ102" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="AH102" s="5" t="s">
+      <c r="AK102" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="AI102" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ102" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK102" s="5" t="s">
-        <v>257</v>
       </c>
       <c r="AL102" s="5">
         <v>-50</v>
@@ -18404,19 +18421,19 @@
         <v>12</v>
       </c>
       <c r="AP102" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AQ102" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AR102" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AS102" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AT102" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AU102" s="5">
         <v>0</v>
@@ -18530,16 +18547,16 @@
         <v>279</v>
       </c>
       <c r="AG103" s="5" t="s">
-        <v>181</v>
+        <v>298</v>
       </c>
       <c r="AH103" s="5" t="s">
-        <v>280</v>
+        <v>447</v>
       </c>
       <c r="AI103" s="5" t="s">
-        <v>281</v>
+        <v>448</v>
       </c>
       <c r="AJ103" s="5" t="s">
-        <v>282</v>
+        <v>7</v>
       </c>
       <c r="AK103" s="5" t="s">
         <v>7</v>
@@ -18557,16 +18574,16 @@
         <v>30</v>
       </c>
       <c r="AP103" s="5">
-        <v>20</v>
+        <v>-100</v>
       </c>
       <c r="AQ103" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AR103" s="5">
-        <v>40</v>
+        <v>-100</v>
       </c>
       <c r="AS103" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT103" s="5">
         <v>0</v>
@@ -18593,7 +18610,7 @@
         <v>999999</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D104" s="11" t="s">
         <v>7</v>
@@ -18728,7 +18745,7 @@
         <v>0</v>
       </c>
       <c r="AV104" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW104" s="12">
         <v>0</v>
@@ -19052,7 +19069,7 @@
         <v>632</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>7</v>
@@ -19205,7 +19222,7 @@
         <v>633</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>7</v>
@@ -19358,7 +19375,7 @@
         <v>999999</v>
       </c>
       <c r="C109" s="11" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D109" s="11" t="s">
         <v>7</v>
@@ -19493,7 +19510,7 @@
         <v>0</v>
       </c>
       <c r="AV109" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW109" s="12">
         <v>0</v>
@@ -20123,7 +20140,7 @@
         <v>999999</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>7</v>
@@ -20258,7 +20275,7 @@
         <v>0</v>
       </c>
       <c r="AV114" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW114" s="12">
         <v>0</v>
@@ -20429,7 +20446,7 @@
         <v>685</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>7</v>
@@ -20507,16 +20524,16 @@
         <v>0</v>
       </c>
       <c r="AC116" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AD116" s="5" t="s">
-        <v>7</v>
+        <v>249</v>
       </c>
       <c r="AE116" s="5" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="AF116" s="5" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="AG116" s="5" t="s">
         <v>7</v>
@@ -20534,16 +20551,16 @@
         <v>7</v>
       </c>
       <c r="AL116" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM116" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN116" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO116" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AP116" s="5">
         <v>0</v>
@@ -20582,7 +20599,7 @@
         <v>999999</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D117" s="11" t="s">
         <v>7</v>
@@ -20717,7 +20734,7 @@
         <v>0</v>
       </c>
       <c r="AV117" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW117" s="12">
         <v>0</v>
@@ -21041,7 +21058,7 @@
         <v>999999</v>
       </c>
       <c r="C120" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D120" s="11" t="s">
         <v>7</v>
@@ -21176,7 +21193,7 @@
         <v>0</v>
       </c>
       <c r="AV120" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW120" s="12">
         <v>0</v>
@@ -21500,7 +21517,7 @@
         <v>722</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>7</v>
@@ -21653,7 +21670,7 @@
         <v>723</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>7</v>
@@ -21806,7 +21823,7 @@
         <v>724</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>7</v>
@@ -21959,7 +21976,7 @@
         <v>725</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>7</v>
@@ -22112,7 +22129,7 @@
         <v>726</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>7</v>
@@ -22265,7 +22282,7 @@
         <v>999999</v>
       </c>
       <c r="C128" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D128" s="11" t="s">
         <v>7</v>
@@ -22400,7 +22417,7 @@
         <v>0</v>
       </c>
       <c r="AV128" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW128" s="12">
         <v>0</v>
@@ -22571,7 +22588,7 @@
         <v>741</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>7</v>
@@ -22724,7 +22741,7 @@
         <v>999999</v>
       </c>
       <c r="C131" s="11" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D131" s="11" t="s">
         <v>7</v>
@@ -22859,7 +22876,7 @@
         <v>0</v>
       </c>
       <c r="AV131" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW131" s="12">
         <v>0</v>
@@ -23030,7 +23047,7 @@
         <v>746</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>7</v>
@@ -23183,7 +23200,7 @@
         <v>747</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>7</v>
@@ -23336,7 +23353,7 @@
         <v>748</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>7</v>
@@ -23489,7 +23506,7 @@
         <v>749</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>7</v>
@@ -23642,7 +23659,7 @@
         <v>999999</v>
       </c>
       <c r="C137" s="11" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="D137" s="11" t="s">
         <v>7</v>
@@ -23777,7 +23794,7 @@
         <v>0</v>
       </c>
       <c r="AV137" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW137" s="12">
         <v>0</v>
@@ -24191,7 +24208,7 @@
         <v>64</v>
       </c>
       <c r="AG140" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AH140" s="5" t="s">
         <v>75</v>
@@ -24200,7 +24217,7 @@
         <v>136</v>
       </c>
       <c r="AJ140" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AK140" s="5" t="s">
         <v>7</v>
@@ -24338,10 +24355,10 @@
         <v>249</v>
       </c>
       <c r="AE141" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AF141" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AG141" s="5" t="s">
         <v>7</v>
@@ -24407,7 +24424,7 @@
         <v>754</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>7</v>
@@ -24542,7 +24559,7 @@
         <v>0</v>
       </c>
       <c r="AV142" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AW142" s="5">
         <v>0</v>
@@ -24560,7 +24577,7 @@
         <v>755</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>7</v>
@@ -24695,7 +24712,7 @@
         <v>0</v>
       </c>
       <c r="AV143" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AW143" s="5">
         <v>0</v>
@@ -24713,7 +24730,7 @@
         <v>756</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>7</v>
@@ -24848,7 +24865,7 @@
         <v>0</v>
       </c>
       <c r="AV144" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AW144" s="5">
         <v>0</v>
@@ -24866,7 +24883,7 @@
         <v>757</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>7</v>
@@ -25001,7 +25018,7 @@
         <v>0</v>
       </c>
       <c r="AV145" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="AW145" s="5">
         <v>0</v>
@@ -25019,7 +25036,7 @@
         <v>760</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>7</v>
@@ -25100,7 +25117,7 @@
         <v>75</v>
       </c>
       <c r="AD146" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AE146" s="5" t="s">
         <v>7</v>
@@ -25175,7 +25192,7 @@
         <v>7</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E147" s="3">
         <v>0</v>
@@ -25328,7 +25345,7 @@
         <v>7</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E148" s="3">
         <v>0</v>
@@ -25481,7 +25498,7 @@
         <v>7</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E149" s="3">
         <v>0</v>
@@ -25634,7 +25651,7 @@
         <v>7</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E150" s="3">
         <v>0</v>
@@ -25784,7 +25801,7 @@
         <v>765</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>7</v>
@@ -25874,7 +25891,7 @@
         <v>64</v>
       </c>
       <c r="AG151" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AH151" s="5" t="s">
         <v>7</v>
@@ -25937,7 +25954,7 @@
         <v>766</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>7</v>
@@ -26027,7 +26044,7 @@
         <v>64</v>
       </c>
       <c r="AG152" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AH152" s="5" t="s">
         <v>7</v>
@@ -26090,7 +26107,7 @@
         <v>767</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>7</v>
@@ -26174,7 +26191,7 @@
         <v>47</v>
       </c>
       <c r="AE153" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AF153" s="5" t="s">
         <v>7</v>
@@ -26243,7 +26260,7 @@
         <v>768</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>7</v>
@@ -26321,7 +26338,7 @@
         <v>0</v>
       </c>
       <c r="AC154" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AD154" s="5" t="s">
         <v>45</v>
@@ -26399,7 +26416,7 @@
         <v>7</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E155" s="3">
         <v>0</v>
@@ -26552,7 +26569,7 @@
         <v>7</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E156" s="3">
         <v>0</v>
@@ -26702,7 +26719,7 @@
         <v>771</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>7</v>
@@ -26780,7 +26797,7 @@
         <v>0</v>
       </c>
       <c r="AC157" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AD157" s="5" t="s">
         <v>7</v>
@@ -26855,7 +26872,7 @@
         <v>772</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>7</v>
@@ -26933,7 +26950,7 @@
         <v>0</v>
       </c>
       <c r="AC158" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AD158" s="5" t="s">
         <v>7</v>
@@ -27008,7 +27025,7 @@
         <v>773</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>7</v>
@@ -27086,7 +27103,7 @@
         <v>0</v>
       </c>
       <c r="AC159" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AD159" s="5" t="s">
         <v>7</v>
@@ -27161,7 +27178,7 @@
         <v>774</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>7</v>
@@ -27239,7 +27256,7 @@
         <v>0</v>
       </c>
       <c r="AC160" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="AD160" s="5" t="s">
         <v>7</v>
@@ -27314,7 +27331,7 @@
         <v>999999</v>
       </c>
       <c r="C161" s="11" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D161" s="11" t="s">
         <v>7</v>
@@ -27449,7 +27466,7 @@
         <v>0</v>
       </c>
       <c r="AV161" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW161" s="12">
         <v>0</v>
@@ -27620,7 +27637,7 @@
         <v>781</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>7</v>
@@ -28079,7 +28096,7 @@
         <v>784</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>7</v>
@@ -28232,7 +28249,7 @@
         <v>785</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>7</v>
@@ -28385,7 +28402,7 @@
         <v>786</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>7</v>
@@ -28538,7 +28555,7 @@
         <v>787</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>7</v>
@@ -28691,7 +28708,7 @@
         <v>999999</v>
       </c>
       <c r="C170" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D170" s="11" t="s">
         <v>7</v>
@@ -28826,7 +28843,7 @@
         <v>0</v>
       </c>
       <c r="AV170" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW170" s="12">
         <v>0</v>
@@ -29303,7 +29320,7 @@
         <v>999999</v>
       </c>
       <c r="C174" s="11" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D174" s="11" t="s">
         <v>7</v>
@@ -29438,7 +29455,7 @@
         <v>0</v>
       </c>
       <c r="AV174" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW174" s="12">
         <v>0</v>
@@ -30770,7 +30787,7 @@
         <v>117</v>
       </c>
       <c r="AG183" s="5" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AH183" s="5" t="s">
         <v>7</v>
@@ -30986,7 +31003,7 @@
         <v>999999</v>
       </c>
       <c r="C185" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D185" s="11" t="s">
         <v>7</v>
@@ -31121,7 +31138,7 @@
         <v>0</v>
       </c>
       <c r="AV185" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW185" s="12">
         <v>0</v>
@@ -31445,7 +31462,7 @@
         <v>852</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D188" s="3" t="s">
         <v>7</v>
@@ -31598,7 +31615,7 @@
         <v>999999</v>
       </c>
       <c r="C189" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D189" s="11" t="s">
         <v>7</v>
@@ -31733,7 +31750,7 @@
         <v>0</v>
       </c>
       <c r="AV189" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW189" s="12">
         <v>0</v>
@@ -32975,7 +32992,7 @@
         <v>878</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>7</v>
@@ -33128,7 +33145,7 @@
         <v>885</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>7</v>
@@ -33281,7 +33298,7 @@
         <v>890</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D200" s="3" t="s">
         <v>7</v>
@@ -33434,7 +33451,7 @@
         <v>891</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D201" s="3" t="s">
         <v>7</v>
@@ -33587,7 +33604,7 @@
         <v>999999</v>
       </c>
       <c r="C202" s="11" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="D202" s="11" t="s">
         <v>7</v>
@@ -33722,7 +33739,7 @@
         <v>0</v>
       </c>
       <c r="AV202" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW202" s="12">
         <v>0</v>
@@ -33824,13 +33841,13 @@
         <v>75</v>
       </c>
       <c r="AE203" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF203" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG203" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH203" s="5" t="s">
         <v>7</v>
@@ -33977,13 +33994,13 @@
         <v>75</v>
       </c>
       <c r="AE204" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF204" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG204" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH204" s="5" t="s">
         <v>7</v>
@@ -34130,13 +34147,13 @@
         <v>75</v>
       </c>
       <c r="AE205" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF205" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG205" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH205" s="5" t="s">
         <v>7</v>
@@ -34283,13 +34300,13 @@
         <v>75</v>
       </c>
       <c r="AE206" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF206" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG206" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH206" s="5" t="s">
         <v>7</v>
@@ -34436,13 +34453,13 @@
         <v>75</v>
       </c>
       <c r="AE207" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF207" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG207" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH207" s="5" t="s">
         <v>7</v>
@@ -34589,13 +34606,13 @@
         <v>75</v>
       </c>
       <c r="AE208" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF208" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG208" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH208" s="5" t="s">
         <v>7</v>
@@ -34742,13 +34759,13 @@
         <v>75</v>
       </c>
       <c r="AE209" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF209" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG209" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH209" s="5" t="s">
         <v>7</v>
@@ -34895,13 +34912,13 @@
         <v>75</v>
       </c>
       <c r="AE210" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF210" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG210" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH210" s="5" t="s">
         <v>7</v>
@@ -35048,13 +35065,13 @@
         <v>75</v>
       </c>
       <c r="AE211" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF211" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG211" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH211" s="5" t="s">
         <v>7</v>
@@ -35201,13 +35218,13 @@
         <v>75</v>
       </c>
       <c r="AE212" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF212" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG212" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH212" s="5" t="s">
         <v>7</v>
@@ -35354,13 +35371,13 @@
         <v>75</v>
       </c>
       <c r="AE213" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF213" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG213" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH213" s="5" t="s">
         <v>7</v>
@@ -35507,13 +35524,13 @@
         <v>75</v>
       </c>
       <c r="AE214" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF214" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG214" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH214" s="5" t="s">
         <v>122</v>
@@ -35660,13 +35677,13 @@
         <v>75</v>
       </c>
       <c r="AE215" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF215" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG215" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH215" s="5" t="s">
         <v>55</v>
@@ -35813,13 +35830,13 @@
         <v>7</v>
       </c>
       <c r="AE216" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF216" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG216" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH216" s="5" t="s">
         <v>47</v>
@@ -35966,13 +35983,13 @@
         <v>75</v>
       </c>
       <c r="AE217" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF217" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG217" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH217" s="5" t="s">
         <v>7</v>
@@ -36035,7 +36052,7 @@
         <v>999999</v>
       </c>
       <c r="C218" s="11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D218" s="11" t="s">
         <v>7</v>
@@ -36170,7 +36187,7 @@
         <v>0</v>
       </c>
       <c r="AV218" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW218" s="12">
         <v>0</v>
@@ -36800,7 +36817,7 @@
         <v>999999</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D223" s="11" t="s">
         <v>7</v>
@@ -36935,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="AV223" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW223" s="12">
         <v>0</v>
@@ -36953,7 +36970,7 @@
         <v>1200</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D224" s="3" t="s">
         <v>7</v>
@@ -37088,7 +37105,7 @@
         <v>0</v>
       </c>
       <c r="AV224" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW224" s="5">
         <v>0</v>
@@ -37106,7 +37123,7 @@
         <v>1201</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>7</v>
@@ -37241,7 +37258,7 @@
         <v>0</v>
       </c>
       <c r="AV225" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW225" s="5">
         <v>0</v>
@@ -37259,7 +37276,7 @@
         <v>1202</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>7</v>
@@ -37394,7 +37411,7 @@
         <v>0</v>
       </c>
       <c r="AV226" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW226" s="5">
         <v>0</v>
@@ -37412,7 +37429,7 @@
         <v>1203</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>7</v>
@@ -37547,7 +37564,7 @@
         <v>0</v>
       </c>
       <c r="AV227" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW227" s="5">
         <v>0</v>
@@ -37565,7 +37582,7 @@
         <v>1204</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>7</v>
@@ -37700,7 +37717,7 @@
         <v>0</v>
       </c>
       <c r="AV228" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW228" s="5">
         <v>0</v>
@@ -37718,7 +37735,7 @@
         <v>1205</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>7</v>
@@ -37853,7 +37870,7 @@
         <v>0</v>
       </c>
       <c r="AV229" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW229" s="5">
         <v>0</v>
@@ -37871,7 +37888,7 @@
         <v>1206</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>7</v>
@@ -38006,7 +38023,7 @@
         <v>0</v>
       </c>
       <c r="AV230" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AW230" s="5">
         <v>0</v>
@@ -38177,7 +38194,7 @@
         <v>999999</v>
       </c>
       <c r="C232" s="11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D232" s="11" t="s">
         <v>7</v>
@@ -38312,7 +38329,7 @@
         <v>0</v>
       </c>
       <c r="AV232" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW232" s="12">
         <v>0</v>
@@ -38330,7 +38347,7 @@
         <v>1300</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>7</v>
@@ -38483,7 +38500,7 @@
         <v>1301</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>7</v>
@@ -38636,7 +38653,7 @@
         <v>1302</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>7</v>
@@ -38789,7 +38806,7 @@
         <v>1303</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>7</v>
@@ -38942,7 +38959,7 @@
         <v>1304</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>7</v>
@@ -39095,7 +39112,7 @@
         <v>1310</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>7</v>
@@ -39248,7 +39265,7 @@
         <v>1311</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>7</v>
@@ -39401,7 +39418,7 @@
         <v>1312</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>7</v>
@@ -39554,7 +39571,7 @@
         <v>1313</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>7</v>
@@ -39707,7 +39724,7 @@
         <v>1314</v>
       </c>
       <c r="C242" s="3" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>7</v>
@@ -39860,7 +39877,7 @@
         <v>1315</v>
       </c>
       <c r="C243" s="3" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>7</v>
@@ -40013,7 +40030,7 @@
         <v>1320</v>
       </c>
       <c r="C244" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>7</v>
@@ -40166,7 +40183,7 @@
         <v>1321</v>
       </c>
       <c r="C245" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>7</v>
@@ -40319,7 +40336,7 @@
         <v>1322</v>
       </c>
       <c r="C246" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>7</v>
@@ -40472,7 +40489,7 @@
         <v>1330</v>
       </c>
       <c r="C247" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>7</v>
@@ -40556,13 +40573,13 @@
         <v>75</v>
       </c>
       <c r="AE247" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF247" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG247" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH247" s="5" t="s">
         <v>7</v>
@@ -40625,7 +40642,7 @@
         <v>1331</v>
       </c>
       <c r="C248" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>7</v>
@@ -40709,13 +40726,13 @@
         <v>75</v>
       </c>
       <c r="AE248" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF248" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG248" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH248" s="5" t="s">
         <v>7</v>
@@ -40778,7 +40795,7 @@
         <v>1332</v>
       </c>
       <c r="C249" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>7</v>
@@ -40862,13 +40879,13 @@
         <v>75</v>
       </c>
       <c r="AE249" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF249" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG249" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH249" s="5" t="s">
         <v>7</v>
@@ -40931,7 +40948,7 @@
         <v>1333</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>7</v>
@@ -41015,13 +41032,13 @@
         <v>75</v>
       </c>
       <c r="AE250" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF250" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG250" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH250" s="5" t="s">
         <v>7</v>
@@ -41084,7 +41101,7 @@
         <v>1334</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>7</v>
@@ -41168,13 +41185,13 @@
         <v>75</v>
       </c>
       <c r="AE251" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF251" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG251" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH251" s="5" t="s">
         <v>122</v>
@@ -41237,7 +41254,7 @@
         <v>1335</v>
       </c>
       <c r="C252" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>7</v>
@@ -41321,13 +41338,13 @@
         <v>75</v>
       </c>
       <c r="AE252" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF252" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG252" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH252" s="5" t="s">
         <v>7</v>
@@ -41383,14 +41400,14 @@
     </row>
     <row r="253" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A253" si="8">ROW()-2</f>
         <v>251</v>
       </c>
       <c r="B253" s="11">
         <v>999999</v>
       </c>
       <c r="C253" s="11" t="s">
-        <v>351</v>
+        <v>449</v>
       </c>
       <c r="D253" s="11" t="s">
         <v>7</v>
@@ -41525,7 +41542,7 @@
         <v>0</v>
       </c>
       <c r="AV253" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AW253" s="12">
         <v>0</v>
@@ -41536,14 +41553,14 @@
     </row>
     <row r="254" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A254" si="9">ROW()-2</f>
         <v>252</v>
       </c>
       <c r="B254" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="C254" s="3" t="s">
-        <v>352</v>
+        <v>450</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>7</v>
@@ -41606,13 +41623,13 @@
         <v>0</v>
       </c>
       <c r="X254" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Y254" s="3">
         <v>0</v>
       </c>
       <c r="Z254" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA254" s="3">
         <v>0</v>
@@ -41678,7 +41695,7 @@
         <v>0</v>
       </c>
       <c r="AV254" s="4" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="AW254" s="5">
         <v>0</v>
@@ -41687,181 +41704,181 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="3">
+    <row r="255" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A255" s="11">
         <f t="shared" si="0"/>
         <v>253</v>
       </c>
-      <c r="B255" s="3">
-        <v>1501</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E255" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F255" s="3">
-        <v>0</v>
-      </c>
-      <c r="G255" s="3">
-        <v>100</v>
-      </c>
-      <c r="H255" s="3">
-        <v>0</v>
-      </c>
-      <c r="I255" s="3">
-        <v>30</v>
-      </c>
-      <c r="J255" s="3">
-        <v>0</v>
-      </c>
-      <c r="K255" s="3">
-        <v>85</v>
-      </c>
-      <c r="L255" s="3">
-        <v>0</v>
-      </c>
-      <c r="M255" s="3">
-        <v>0</v>
-      </c>
-      <c r="N255" s="3">
-        <v>0</v>
-      </c>
-      <c r="O255" s="3">
-        <v>0</v>
-      </c>
-      <c r="P255" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q255" s="3">
-        <v>90</v>
-      </c>
-      <c r="R255" s="3">
-        <v>0</v>
-      </c>
-      <c r="S255" s="3">
-        <v>0</v>
-      </c>
-      <c r="T255" s="3">
-        <v>0</v>
-      </c>
-      <c r="U255" s="3">
-        <v>0</v>
-      </c>
-      <c r="V255" s="3">
-        <v>0</v>
-      </c>
-      <c r="W255" s="3">
-        <v>0</v>
-      </c>
-      <c r="X255" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y255" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z255" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA255" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB255" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC255" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="AD255" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AE255" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="AF255" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG255" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH255" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI255" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ255" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK255" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL255" s="5">
-        <v>10</v>
-      </c>
-      <c r="AM255" s="5">
-        <v>10</v>
-      </c>
-      <c r="AN255" s="5">
-        <v>30</v>
-      </c>
-      <c r="AO255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV255" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AW255" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX255" s="5">
+      <c r="B255" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C255" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="D255" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E255" s="11">
+        <v>0</v>
+      </c>
+      <c r="F255" s="11">
+        <v>0</v>
+      </c>
+      <c r="G255" s="11">
+        <v>0</v>
+      </c>
+      <c r="H255" s="11">
+        <v>0</v>
+      </c>
+      <c r="I255" s="11">
+        <v>0</v>
+      </c>
+      <c r="J255" s="11">
+        <v>0</v>
+      </c>
+      <c r="K255" s="11">
+        <v>0</v>
+      </c>
+      <c r="L255" s="11">
+        <v>0</v>
+      </c>
+      <c r="M255" s="11">
+        <v>0</v>
+      </c>
+      <c r="N255" s="11">
+        <v>0</v>
+      </c>
+      <c r="O255" s="11">
+        <v>0</v>
+      </c>
+      <c r="P255" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q255" s="11">
+        <v>0</v>
+      </c>
+      <c r="R255" s="11">
+        <v>0</v>
+      </c>
+      <c r="S255" s="11">
+        <v>0</v>
+      </c>
+      <c r="T255" s="11">
+        <v>0</v>
+      </c>
+      <c r="U255" s="11">
+        <v>0</v>
+      </c>
+      <c r="V255" s="11">
+        <v>0</v>
+      </c>
+      <c r="W255" s="11">
+        <v>0</v>
+      </c>
+      <c r="X255" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y255" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z255" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA255" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB255" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK255" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV255" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW255" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX255" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="256" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="3">
-        <f t="shared" ref="A256:A260" si="8">ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>254</v>
       </c>
       <c r="B256" s="3">
-        <v>1502</v>
+        <v>1500</v>
       </c>
       <c r="C256" s="3" t="s">
-        <v>415</v>
+        <v>349</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E256" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F256" s="3">
         <v>0</v>
       </c>
       <c r="G256" s="3">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H256" s="3">
         <v>0</v>
@@ -41870,13 +41887,13 @@
         <v>0</v>
       </c>
       <c r="J256" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="K256" s="3">
         <v>0</v>
       </c>
       <c r="L256" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M256" s="3">
         <v>0</v>
@@ -41912,13 +41929,13 @@
         <v>0</v>
       </c>
       <c r="X256" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y256" s="3">
         <v>0</v>
       </c>
       <c r="Z256" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA256" s="3">
         <v>0</v>
@@ -41984,7 +42001,7 @@
         <v>0</v>
       </c>
       <c r="AV256" s="4" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="AW256" s="5">
         <v>0</v>
@@ -41993,181 +42010,181 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="11">
-        <f t="shared" si="8"/>
+    <row r="257" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A257" s="3">
+        <f t="shared" si="0"/>
         <v>255</v>
       </c>
-      <c r="B257" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C257" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="D257" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E257" s="11">
-        <v>0</v>
-      </c>
-      <c r="F257" s="11">
-        <v>0</v>
-      </c>
-      <c r="G257" s="11">
-        <v>0</v>
-      </c>
-      <c r="H257" s="11">
-        <v>0</v>
-      </c>
-      <c r="I257" s="11">
-        <v>0</v>
-      </c>
-      <c r="J257" s="11">
-        <v>0</v>
-      </c>
-      <c r="K257" s="11">
-        <v>0</v>
-      </c>
-      <c r="L257" s="11">
-        <v>0</v>
-      </c>
-      <c r="M257" s="11">
-        <v>0</v>
-      </c>
-      <c r="N257" s="11">
-        <v>0</v>
-      </c>
-      <c r="O257" s="11">
-        <v>0</v>
-      </c>
-      <c r="P257" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q257" s="11">
-        <v>0</v>
-      </c>
-      <c r="R257" s="11">
-        <v>0</v>
-      </c>
-      <c r="S257" s="11">
-        <v>0</v>
-      </c>
-      <c r="T257" s="11">
-        <v>0</v>
-      </c>
-      <c r="U257" s="11">
-        <v>0</v>
-      </c>
-      <c r="V257" s="11">
-        <v>0</v>
-      </c>
-      <c r="W257" s="11">
-        <v>0</v>
-      </c>
-      <c r="X257" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y257" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z257" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA257" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB257" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK257" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV257" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW257" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX257" s="12">
+      <c r="B257" s="3">
+        <v>1501</v>
+      </c>
+      <c r="C257" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E257" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F257" s="3">
+        <v>0</v>
+      </c>
+      <c r="G257" s="3">
+        <v>100</v>
+      </c>
+      <c r="H257" s="3">
+        <v>0</v>
+      </c>
+      <c r="I257" s="3">
+        <v>30</v>
+      </c>
+      <c r="J257" s="3">
+        <v>0</v>
+      </c>
+      <c r="K257" s="3">
+        <v>85</v>
+      </c>
+      <c r="L257" s="3">
+        <v>0</v>
+      </c>
+      <c r="M257" s="3">
+        <v>0</v>
+      </c>
+      <c r="N257" s="3">
+        <v>0</v>
+      </c>
+      <c r="O257" s="3">
+        <v>0</v>
+      </c>
+      <c r="P257" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q257" s="3">
+        <v>90</v>
+      </c>
+      <c r="R257" s="3">
+        <v>0</v>
+      </c>
+      <c r="S257" s="3">
+        <v>0</v>
+      </c>
+      <c r="T257" s="3">
+        <v>0</v>
+      </c>
+      <c r="U257" s="3">
+        <v>0</v>
+      </c>
+      <c r="V257" s="3">
+        <v>0</v>
+      </c>
+      <c r="W257" s="3">
+        <v>0</v>
+      </c>
+      <c r="X257" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y257" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z257" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA257" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB257" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC257" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD257" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AE257" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL257" s="5">
+        <v>10</v>
+      </c>
+      <c r="AM257" s="5">
+        <v>10</v>
+      </c>
+      <c r="AN257" s="5">
+        <v>30</v>
+      </c>
+      <c r="AO257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV257" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="AW257" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX257" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="258" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="A258:A262" si="10">ROW()-2</f>
         <v>256</v>
       </c>
       <c r="B258" s="3">
-        <v>1600</v>
+        <v>1502</v>
       </c>
       <c r="C258" s="3" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E258" s="3">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F258" s="3">
         <v>0</v>
       </c>
       <c r="G258" s="3">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="H258" s="3">
         <v>0</v>
@@ -42182,7 +42199,7 @@
         <v>0</v>
       </c>
       <c r="L258" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M258" s="3">
         <v>0</v>
@@ -42218,13 +42235,13 @@
         <v>0</v>
       </c>
       <c r="X258" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y258" s="3">
         <v>0</v>
       </c>
       <c r="Z258" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA258" s="3">
         <v>0</v>
@@ -42290,7 +42307,7 @@
         <v>0</v>
       </c>
       <c r="AV258" s="4" t="s">
-        <v>419</v>
+        <v>350</v>
       </c>
       <c r="AW258" s="5">
         <v>0</v>
@@ -42299,175 +42316,175 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="3">
-        <f t="shared" si="8"/>
+    <row r="259" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A259" s="11">
+        <f t="shared" si="10"/>
         <v>257</v>
       </c>
-      <c r="B259" s="3">
-        <v>1601</v>
-      </c>
-      <c r="C259" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E259" s="3">
-        <v>50</v>
-      </c>
-      <c r="F259" s="3">
-        <v>0</v>
-      </c>
-      <c r="G259" s="3">
-        <v>0</v>
-      </c>
-      <c r="H259" s="3">
-        <v>0</v>
-      </c>
-      <c r="I259" s="3">
-        <v>0</v>
-      </c>
-      <c r="J259" s="3">
-        <v>0</v>
-      </c>
-      <c r="K259" s="3">
-        <v>0</v>
-      </c>
-      <c r="L259" s="3">
-        <v>0</v>
-      </c>
-      <c r="M259" s="3">
-        <v>0</v>
-      </c>
-      <c r="N259" s="3">
-        <v>0</v>
-      </c>
-      <c r="O259" s="3">
-        <v>0</v>
-      </c>
-      <c r="P259" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q259" s="3">
-        <v>50</v>
-      </c>
-      <c r="R259" s="3">
-        <v>0</v>
-      </c>
-      <c r="S259" s="3">
-        <v>0</v>
-      </c>
-      <c r="T259" s="3">
-        <v>0</v>
-      </c>
-      <c r="U259" s="3">
-        <v>0</v>
-      </c>
-      <c r="V259" s="3">
-        <v>0</v>
-      </c>
-      <c r="W259" s="3">
-        <v>0</v>
-      </c>
-      <c r="X259" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y259" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z259" s="3">
-        <v>10</v>
-      </c>
-      <c r="AA259" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB259" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK259" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV259" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="AW259" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX259" s="5">
+      <c r="B259" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C259" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="D259" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E259" s="11">
+        <v>0</v>
+      </c>
+      <c r="F259" s="11">
+        <v>0</v>
+      </c>
+      <c r="G259" s="11">
+        <v>0</v>
+      </c>
+      <c r="H259" s="11">
+        <v>0</v>
+      </c>
+      <c r="I259" s="11">
+        <v>0</v>
+      </c>
+      <c r="J259" s="11">
+        <v>0</v>
+      </c>
+      <c r="K259" s="11">
+        <v>0</v>
+      </c>
+      <c r="L259" s="11">
+        <v>0</v>
+      </c>
+      <c r="M259" s="11">
+        <v>0</v>
+      </c>
+      <c r="N259" s="11">
+        <v>0</v>
+      </c>
+      <c r="O259" s="11">
+        <v>0</v>
+      </c>
+      <c r="P259" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q259" s="11">
+        <v>0</v>
+      </c>
+      <c r="R259" s="11">
+        <v>0</v>
+      </c>
+      <c r="S259" s="11">
+        <v>0</v>
+      </c>
+      <c r="T259" s="11">
+        <v>0</v>
+      </c>
+      <c r="U259" s="11">
+        <v>0</v>
+      </c>
+      <c r="V259" s="11">
+        <v>0</v>
+      </c>
+      <c r="W259" s="11">
+        <v>0</v>
+      </c>
+      <c r="X259" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y259" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z259" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA259" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB259" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK259" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV259" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW259" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX259" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="260" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="3">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>258</v>
       </c>
       <c r="B260" s="3">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="C260" s="3" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E260" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F260" s="3">
         <v>0</v>
@@ -42596,7 +42613,7 @@
         <v>0</v>
       </c>
       <c r="AV260" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="AW260" s="5">
         <v>0</v>
@@ -42605,184 +42622,184 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="11">
-        <f t="shared" ref="A261" si="9">ROW()-2</f>
+    <row r="261" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A261" s="3">
+        <f t="shared" si="10"/>
         <v>259</v>
       </c>
-      <c r="B261" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C261" s="11" t="s">
-        <v>397</v>
-      </c>
-      <c r="D261" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E261" s="11">
-        <v>0</v>
-      </c>
-      <c r="F261" s="11">
-        <v>0</v>
-      </c>
-      <c r="G261" s="11">
-        <v>0</v>
-      </c>
-      <c r="H261" s="11">
-        <v>0</v>
-      </c>
-      <c r="I261" s="11">
-        <v>0</v>
-      </c>
-      <c r="J261" s="11">
-        <v>0</v>
-      </c>
-      <c r="K261" s="11">
-        <v>0</v>
-      </c>
-      <c r="L261" s="11">
-        <v>0</v>
-      </c>
-      <c r="M261" s="11">
-        <v>0</v>
-      </c>
-      <c r="N261" s="11">
-        <v>0</v>
-      </c>
-      <c r="O261" s="11">
-        <v>0</v>
-      </c>
-      <c r="P261" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q261" s="11">
-        <v>0</v>
-      </c>
-      <c r="R261" s="11">
-        <v>0</v>
-      </c>
-      <c r="S261" s="11">
-        <v>0</v>
-      </c>
-      <c r="T261" s="11">
-        <v>0</v>
-      </c>
-      <c r="U261" s="11">
-        <v>0</v>
-      </c>
-      <c r="V261" s="11">
-        <v>0</v>
-      </c>
-      <c r="W261" s="11">
-        <v>0</v>
-      </c>
-      <c r="X261" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y261" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z261" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA261" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB261" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK261" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV261" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW261" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX261" s="12">
+      <c r="B261" s="3">
+        <v>1601</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E261" s="3">
+        <v>50</v>
+      </c>
+      <c r="F261" s="3">
+        <v>0</v>
+      </c>
+      <c r="G261" s="3">
+        <v>0</v>
+      </c>
+      <c r="H261" s="3">
+        <v>0</v>
+      </c>
+      <c r="I261" s="3">
+        <v>0</v>
+      </c>
+      <c r="J261" s="3">
+        <v>0</v>
+      </c>
+      <c r="K261" s="3">
+        <v>0</v>
+      </c>
+      <c r="L261" s="3">
+        <v>0</v>
+      </c>
+      <c r="M261" s="3">
+        <v>0</v>
+      </c>
+      <c r="N261" s="3">
+        <v>0</v>
+      </c>
+      <c r="O261" s="3">
+        <v>0</v>
+      </c>
+      <c r="P261" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q261" s="3">
+        <v>50</v>
+      </c>
+      <c r="R261" s="3">
+        <v>0</v>
+      </c>
+      <c r="S261" s="3">
+        <v>0</v>
+      </c>
+      <c r="T261" s="3">
+        <v>0</v>
+      </c>
+      <c r="U261" s="3">
+        <v>0</v>
+      </c>
+      <c r="V261" s="3">
+        <v>0</v>
+      </c>
+      <c r="W261" s="3">
+        <v>0</v>
+      </c>
+      <c r="X261" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y261" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z261" s="3">
+        <v>10</v>
+      </c>
+      <c r="AA261" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB261" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV261" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="AW261" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX261" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="3">
-        <f t="shared" ref="A262:A293" si="10">ROW()-2</f>
+        <f t="shared" si="10"/>
         <v>260</v>
       </c>
       <c r="B262" s="3">
-        <v>1700</v>
+        <v>1602</v>
       </c>
       <c r="C262" s="3" t="s">
-        <v>396</v>
+        <v>415</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E262" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F262" s="3">
         <v>0</v>
       </c>
       <c r="G262" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H262" s="3">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="I262" s="3">
         <v>0</v>
@@ -42794,7 +42811,7 @@
         <v>0</v>
       </c>
       <c r="L262" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M262" s="3">
         <v>0</v>
@@ -42830,13 +42847,13 @@
         <v>0</v>
       </c>
       <c r="X262" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y262" s="3">
         <v>0</v>
       </c>
       <c r="Z262" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA262" s="3">
         <v>0</v>
@@ -42845,7 +42862,7 @@
         <v>0</v>
       </c>
       <c r="AC262" s="5" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="AD262" s="5" t="s">
         <v>7</v>
@@ -42872,7 +42889,7 @@
         <v>7</v>
       </c>
       <c r="AL262" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AM262" s="5">
         <v>0</v>
@@ -42902,7 +42919,7 @@
         <v>0</v>
       </c>
       <c r="AV262" s="4" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="AW262" s="5">
         <v>0</v>
@@ -42911,169 +42928,169 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="3">
-        <f t="shared" si="10"/>
+    <row r="263" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A263" s="11">
+        <f t="shared" ref="A263" si="11">ROW()-2</f>
         <v>261</v>
       </c>
-      <c r="B263" s="3">
-        <v>1701</v>
-      </c>
-      <c r="C263" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E263" s="3">
-        <v>0</v>
-      </c>
-      <c r="F263" s="3">
-        <v>0</v>
-      </c>
-      <c r="G263" s="3">
-        <v>80</v>
-      </c>
-      <c r="H263" s="3">
-        <v>230</v>
-      </c>
-      <c r="I263" s="3">
-        <v>0</v>
-      </c>
-      <c r="J263" s="3">
-        <v>0</v>
-      </c>
-      <c r="K263" s="3">
-        <v>0</v>
-      </c>
-      <c r="L263" s="3">
-        <v>70</v>
-      </c>
-      <c r="M263" s="3">
-        <v>0</v>
-      </c>
-      <c r="N263" s="3">
-        <v>0</v>
-      </c>
-      <c r="O263" s="3">
-        <v>0</v>
-      </c>
-      <c r="P263" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q263" s="3">
-        <v>50</v>
-      </c>
-      <c r="R263" s="3">
-        <v>0</v>
-      </c>
-      <c r="S263" s="3">
-        <v>10</v>
-      </c>
-      <c r="T263" s="3">
-        <v>0</v>
-      </c>
-      <c r="U263" s="3">
-        <v>0</v>
-      </c>
-      <c r="V263" s="3">
-        <v>0</v>
-      </c>
-      <c r="W263" s="3">
-        <v>0</v>
-      </c>
-      <c r="X263" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y263" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z263" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA263" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB263" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC263" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK263" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL263" s="5">
-        <v>20</v>
-      </c>
-      <c r="AM263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV263" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="AW263" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX263" s="5">
+      <c r="B263" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C263" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="D263" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E263" s="11">
+        <v>0</v>
+      </c>
+      <c r="F263" s="11">
+        <v>0</v>
+      </c>
+      <c r="G263" s="11">
+        <v>0</v>
+      </c>
+      <c r="H263" s="11">
+        <v>0</v>
+      </c>
+      <c r="I263" s="11">
+        <v>0</v>
+      </c>
+      <c r="J263" s="11">
+        <v>0</v>
+      </c>
+      <c r="K263" s="11">
+        <v>0</v>
+      </c>
+      <c r="L263" s="11">
+        <v>0</v>
+      </c>
+      <c r="M263" s="11">
+        <v>0</v>
+      </c>
+      <c r="N263" s="11">
+        <v>0</v>
+      </c>
+      <c r="O263" s="11">
+        <v>0</v>
+      </c>
+      <c r="P263" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q263" s="11">
+        <v>0</v>
+      </c>
+      <c r="R263" s="11">
+        <v>0</v>
+      </c>
+      <c r="S263" s="11">
+        <v>0</v>
+      </c>
+      <c r="T263" s="11">
+        <v>0</v>
+      </c>
+      <c r="U263" s="11">
+        <v>0</v>
+      </c>
+      <c r="V263" s="11">
+        <v>0</v>
+      </c>
+      <c r="W263" s="11">
+        <v>0</v>
+      </c>
+      <c r="X263" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y263" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z263" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA263" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB263" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK263" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV263" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW263" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX263" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="A264:A295" si="12">ROW()-2</f>
         <v>262</v>
       </c>
       <c r="B264" s="3">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="C264" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>7</v>
@@ -43124,7 +43141,7 @@
         <v>0</v>
       </c>
       <c r="T264" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U264" s="3">
         <v>0</v>
@@ -43208,7 +43225,7 @@
         <v>0</v>
       </c>
       <c r="AV264" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW264" s="5">
         <v>0</v>
@@ -43219,20 +43236,20 @@
     </row>
     <row r="265" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>263</v>
       </c>
       <c r="B265" s="3">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="C265" s="3" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E265" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F265" s="3">
         <v>0</v>
@@ -43274,10 +43291,10 @@
         <v>0</v>
       </c>
       <c r="S265" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T265" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U265" s="3">
         <v>0</v>
@@ -43361,7 +43378,7 @@
         <v>0</v>
       </c>
       <c r="AV265" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW265" s="5">
         <v>0</v>
@@ -43372,17 +43389,17 @@
     </row>
     <row r="266" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>264</v>
       </c>
       <c r="B266" s="3">
-        <v>1710</v>
+        <v>1702</v>
       </c>
       <c r="C266" s="3" t="s">
-        <v>7</v>
+        <v>400</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>398</v>
+        <v>7</v>
       </c>
       <c r="E266" s="3">
         <v>0</v>
@@ -43427,11 +43444,11 @@
         <v>0</v>
       </c>
       <c r="S266" s="3">
+        <v>0</v>
+      </c>
+      <c r="T266" s="3">
         <v>10</v>
       </c>
-      <c r="T266" s="3">
-        <v>0</v>
-      </c>
       <c r="U266" s="3">
         <v>0</v>
       </c>
@@ -43448,7 +43465,7 @@
         <v>0</v>
       </c>
       <c r="Z266" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA266" s="3">
         <v>0</v>
@@ -43514,7 +43531,7 @@
         <v>0</v>
       </c>
       <c r="AV266" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW266" s="5">
         <v>0</v>
@@ -43525,20 +43542,20 @@
     </row>
     <row r="267" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>265</v>
       </c>
       <c r="B267" s="3">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="C267" s="3" t="s">
-        <v>7</v>
+        <v>401</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>399</v>
+        <v>7</v>
       </c>
       <c r="E267" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F267" s="3">
         <v>0</v>
@@ -43583,7 +43600,7 @@
         <v>0</v>
       </c>
       <c r="T267" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U267" s="3">
         <v>0</v>
@@ -43595,7 +43612,7 @@
         <v>0</v>
       </c>
       <c r="X267" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y267" s="3">
         <v>0</v>
@@ -43667,7 +43684,7 @@
         <v>0</v>
       </c>
       <c r="AV267" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW267" s="5">
         <v>0</v>
@@ -43678,17 +43695,17 @@
     </row>
     <row r="268" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>266</v>
       </c>
       <c r="B268" s="3">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="E268" s="3">
         <v>0</v>
@@ -43697,10 +43714,10 @@
         <v>0</v>
       </c>
       <c r="G268" s="3">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="H268" s="3">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="I268" s="3">
         <v>0</v>
@@ -43733,28 +43750,28 @@
         <v>0</v>
       </c>
       <c r="S268" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T268" s="3">
         <v>0</v>
       </c>
       <c r="U268" s="3">
+        <v>0</v>
+      </c>
+      <c r="V268" s="3">
+        <v>0</v>
+      </c>
+      <c r="W268" s="3">
+        <v>0</v>
+      </c>
+      <c r="X268" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y268" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z268" s="3">
         <v>10</v>
-      </c>
-      <c r="V268" s="3">
-        <v>0</v>
-      </c>
-      <c r="W268" s="3">
-        <v>0</v>
-      </c>
-      <c r="X268" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y268" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z268" s="3">
-        <v>0</v>
       </c>
       <c r="AA268" s="3">
         <v>0</v>
@@ -43820,7 +43837,7 @@
         <v>0</v>
       </c>
       <c r="AV268" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW268" s="5">
         <v>0</v>
@@ -43831,17 +43848,17 @@
     </row>
     <row r="269" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>267</v>
       </c>
       <c r="B269" s="3">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="C269" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E269" s="3">
         <v>0</v>
@@ -43901,13 +43918,13 @@
         <v>0</v>
       </c>
       <c r="X269" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y269" s="3">
         <v>0</v>
       </c>
       <c r="Z269" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA269" s="3">
         <v>0</v>
@@ -43973,7 +43990,7 @@
         <v>0</v>
       </c>
       <c r="AV269" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW269" s="5">
         <v>0</v>
@@ -43984,26 +44001,26 @@
     </row>
     <row r="270" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>268</v>
       </c>
       <c r="B270" s="3">
-        <v>1720</v>
+        <v>1712</v>
       </c>
       <c r="C270" s="3" t="s">
-        <v>405</v>
+        <v>7</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>7</v>
+        <v>397</v>
       </c>
       <c r="E270" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F270" s="3">
         <v>0</v>
       </c>
       <c r="G270" s="3">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="H270" s="3">
         <v>150</v>
@@ -44045,7 +44062,7 @@
         <v>0</v>
       </c>
       <c r="U270" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V270" s="3">
         <v>0</v>
@@ -44069,7 +44086,7 @@
         <v>0</v>
       </c>
       <c r="AC270" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AD270" s="5" t="s">
         <v>7</v>
@@ -44126,7 +44143,7 @@
         <v>0</v>
       </c>
       <c r="AV270" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW270" s="5">
         <v>0</v>
@@ -44137,17 +44154,17 @@
     </row>
     <row r="271" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>269</v>
       </c>
       <c r="B271" s="3">
-        <v>1730</v>
+        <v>1713</v>
       </c>
       <c r="C271" s="3" t="s">
-        <v>406</v>
+        <v>7</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="E271" s="3">
         <v>0</v>
@@ -44159,7 +44176,7 @@
         <v>80</v>
       </c>
       <c r="H271" s="3">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="I271" s="3">
         <v>0</v>
@@ -44171,7 +44188,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M271" s="3">
         <v>0</v>
@@ -44213,7 +44230,7 @@
         <v>0</v>
       </c>
       <c r="Z271" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA271" s="3">
         <v>0</v>
@@ -44222,7 +44239,7 @@
         <v>0</v>
       </c>
       <c r="AC271" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AD271" s="5" t="s">
         <v>7</v>
@@ -44279,7 +44296,7 @@
         <v>0</v>
       </c>
       <c r="AV271" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW271" s="5">
         <v>0</v>
@@ -44290,20 +44307,20 @@
     </row>
     <row r="272" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>270</v>
       </c>
       <c r="B272" s="3">
-        <v>1731</v>
+        <v>1720</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E272" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F272" s="3">
         <v>0</v>
@@ -44312,7 +44329,7 @@
         <v>80</v>
       </c>
       <c r="H272" s="3">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="I272" s="3">
         <v>0</v>
@@ -44324,7 +44341,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M272" s="3">
         <v>0</v>
@@ -44432,7 +44449,7 @@
         <v>0</v>
       </c>
       <c r="AV272" s="4" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="AW272" s="5">
         <v>0</v>
@@ -44441,169 +44458,169 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="11">
-        <f t="shared" si="10"/>
+    <row r="273" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A273" s="3">
+        <f t="shared" si="12"/>
         <v>271</v>
       </c>
-      <c r="B273" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C273" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="D273" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E273" s="11">
-        <v>0</v>
-      </c>
-      <c r="F273" s="11">
-        <v>0</v>
-      </c>
-      <c r="G273" s="11">
-        <v>0</v>
-      </c>
-      <c r="H273" s="11">
-        <v>0</v>
-      </c>
-      <c r="I273" s="11">
-        <v>0</v>
-      </c>
-      <c r="J273" s="11">
-        <v>0</v>
-      </c>
-      <c r="K273" s="11">
-        <v>0</v>
-      </c>
-      <c r="L273" s="11">
-        <v>0</v>
-      </c>
-      <c r="M273" s="11">
-        <v>0</v>
-      </c>
-      <c r="N273" s="11">
-        <v>0</v>
-      </c>
-      <c r="O273" s="11">
-        <v>0</v>
-      </c>
-      <c r="P273" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q273" s="11">
-        <v>0</v>
-      </c>
-      <c r="R273" s="11">
-        <v>0</v>
-      </c>
-      <c r="S273" s="11">
-        <v>0</v>
-      </c>
-      <c r="T273" s="11">
-        <v>0</v>
-      </c>
-      <c r="U273" s="11">
-        <v>0</v>
-      </c>
-      <c r="V273" s="11">
-        <v>0</v>
-      </c>
-      <c r="W273" s="11">
-        <v>0</v>
-      </c>
-      <c r="X273" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y273" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z273" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA273" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB273" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK273" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV273" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW273" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX273" s="12">
+      <c r="B273" s="3">
+        <v>1730</v>
+      </c>
+      <c r="C273" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E273" s="3">
+        <v>0</v>
+      </c>
+      <c r="F273" s="3">
+        <v>0</v>
+      </c>
+      <c r="G273" s="3">
+        <v>80</v>
+      </c>
+      <c r="H273" s="3">
+        <v>110</v>
+      </c>
+      <c r="I273" s="3">
+        <v>0</v>
+      </c>
+      <c r="J273" s="3">
+        <v>0</v>
+      </c>
+      <c r="K273" s="3">
+        <v>0</v>
+      </c>
+      <c r="L273" s="3">
+        <v>50</v>
+      </c>
+      <c r="M273" s="3">
+        <v>0</v>
+      </c>
+      <c r="N273" s="3">
+        <v>0</v>
+      </c>
+      <c r="O273" s="3">
+        <v>0</v>
+      </c>
+      <c r="P273" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q273" s="3">
+        <v>50</v>
+      </c>
+      <c r="R273" s="3">
+        <v>0</v>
+      </c>
+      <c r="S273" s="3">
+        <v>0</v>
+      </c>
+      <c r="T273" s="3">
+        <v>0</v>
+      </c>
+      <c r="U273" s="3">
+        <v>0</v>
+      </c>
+      <c r="V273" s="3">
+        <v>0</v>
+      </c>
+      <c r="W273" s="3">
+        <v>0</v>
+      </c>
+      <c r="X273" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y273" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB273" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK273" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL273" s="5">
+        <v>20</v>
+      </c>
+      <c r="AM273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV273" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW273" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX273" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="274" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>272</v>
       </c>
       <c r="B274" s="3">
-        <v>1800</v>
+        <v>1731</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="D274" s="3" t="s">
         <v>7</v>
@@ -44615,13 +44632,13 @@
         <v>0</v>
       </c>
       <c r="G274" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H274" s="3">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="I274" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J274" s="3">
         <v>0</v>
@@ -44630,7 +44647,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M274" s="3">
         <v>0</v>
@@ -44642,10 +44659,10 @@
         <v>0</v>
       </c>
       <c r="P274" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q274" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R274" s="3">
         <v>0</v>
@@ -44681,22 +44698,22 @@
         <v>0</v>
       </c>
       <c r="AC274" s="5" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="AD274" s="5" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="AE274" s="5" t="s">
-        <v>301</v>
+        <v>7</v>
       </c>
       <c r="AF274" s="5" t="s">
-        <v>450</v>
+        <v>7</v>
       </c>
       <c r="AG274" s="5" t="s">
-        <v>451</v>
+        <v>7</v>
       </c>
       <c r="AH274" s="5" t="s">
-        <v>449</v>
+        <v>7</v>
       </c>
       <c r="AI274" s="5" t="s">
         <v>7</v>
@@ -44708,22 +44725,22 @@
         <v>7</v>
       </c>
       <c r="AL274" s="5">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="AM274" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AN274" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AO274" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AP274" s="5">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AQ274" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR274" s="5">
         <v>0</v>
@@ -44738,7 +44755,7 @@
         <v>0</v>
       </c>
       <c r="AV274" s="4" t="s">
-        <v>214</v>
+        <v>392</v>
       </c>
       <c r="AW274" s="5">
         <v>0</v>
@@ -44747,169 +44764,169 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="3">
-        <f t="shared" si="10"/>
+    <row r="275" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A275" s="11">
+        <f t="shared" si="12"/>
         <v>273</v>
       </c>
-      <c r="B275" s="3">
-        <v>1801</v>
-      </c>
-      <c r="C275" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E275" s="3">
-        <v>0</v>
-      </c>
-      <c r="F275" s="3">
-        <v>0</v>
-      </c>
-      <c r="G275" s="3">
-        <v>55</v>
-      </c>
-      <c r="H275" s="3">
-        <v>0</v>
-      </c>
-      <c r="I275" s="3">
-        <v>30</v>
-      </c>
-      <c r="J275" s="3">
-        <v>0</v>
-      </c>
-      <c r="K275" s="3">
-        <v>0</v>
-      </c>
-      <c r="L275" s="3">
-        <v>0</v>
-      </c>
-      <c r="M275" s="3">
-        <v>0</v>
-      </c>
-      <c r="N275" s="3">
-        <v>0</v>
-      </c>
-      <c r="O275" s="3">
-        <v>0</v>
-      </c>
-      <c r="P275" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q275" s="3">
-        <v>55</v>
-      </c>
-      <c r="R275" s="3">
-        <v>0</v>
-      </c>
-      <c r="S275" s="3">
-        <v>0</v>
-      </c>
-      <c r="T275" s="3">
-        <v>0</v>
-      </c>
-      <c r="U275" s="3">
-        <v>0</v>
-      </c>
-      <c r="V275" s="3">
-        <v>0</v>
-      </c>
-      <c r="W275" s="3">
-        <v>0</v>
-      </c>
-      <c r="X275" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y275" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z275" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA275" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB275" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC275" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD275" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE275" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="AF275" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="AG275" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="AH275" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="AI275" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ275" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK275" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL275" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM275" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN275" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO275" s="5">
-        <v>50</v>
-      </c>
-      <c r="AP275" s="5">
-        <v>65</v>
-      </c>
-      <c r="AQ275" s="5">
-        <v>10</v>
-      </c>
-      <c r="AR275" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS275" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT275" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU275" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV275" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW275" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX275" s="5">
+      <c r="B275" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C275" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D275" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E275" s="11">
+        <v>0</v>
+      </c>
+      <c r="F275" s="11">
+        <v>0</v>
+      </c>
+      <c r="G275" s="11">
+        <v>0</v>
+      </c>
+      <c r="H275" s="11">
+        <v>0</v>
+      </c>
+      <c r="I275" s="11">
+        <v>0</v>
+      </c>
+      <c r="J275" s="11">
+        <v>0</v>
+      </c>
+      <c r="K275" s="11">
+        <v>0</v>
+      </c>
+      <c r="L275" s="11">
+        <v>0</v>
+      </c>
+      <c r="M275" s="11">
+        <v>0</v>
+      </c>
+      <c r="N275" s="11">
+        <v>0</v>
+      </c>
+      <c r="O275" s="11">
+        <v>0</v>
+      </c>
+      <c r="P275" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q275" s="11">
+        <v>0</v>
+      </c>
+      <c r="R275" s="11">
+        <v>0</v>
+      </c>
+      <c r="S275" s="11">
+        <v>0</v>
+      </c>
+      <c r="T275" s="11">
+        <v>0</v>
+      </c>
+      <c r="U275" s="11">
+        <v>0</v>
+      </c>
+      <c r="V275" s="11">
+        <v>0</v>
+      </c>
+      <c r="W275" s="11">
+        <v>0</v>
+      </c>
+      <c r="X275" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y275" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z275" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA275" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB275" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK275" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV275" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW275" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX275" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="276" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>274</v>
       </c>
       <c r="B276" s="3">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C276" s="3" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>7</v>
@@ -44948,7 +44965,7 @@
         <v>0</v>
       </c>
       <c r="P276" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q276" s="3">
         <v>55</v>
@@ -44993,16 +45010,16 @@
         <v>75</v>
       </c>
       <c r="AE276" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF276" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG276" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH276" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI276" s="5" t="s">
         <v>7</v>
@@ -45055,14 +45072,14 @@
     </row>
     <row r="277" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>275</v>
       </c>
       <c r="B277" s="3">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D277" s="3" t="s">
         <v>7</v>
@@ -45146,16 +45163,16 @@
         <v>75</v>
       </c>
       <c r="AE277" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF277" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG277" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH277" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI277" s="5" t="s">
         <v>7</v>
@@ -45208,14 +45225,14 @@
     </row>
     <row r="278" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>276</v>
       </c>
       <c r="B278" s="3">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>7</v>
@@ -45227,13 +45244,13 @@
         <v>0</v>
       </c>
       <c r="G278" s="3">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H278" s="3">
         <v>0</v>
       </c>
       <c r="I278" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J278" s="3">
         <v>0</v>
@@ -45299,16 +45316,16 @@
         <v>75</v>
       </c>
       <c r="AE278" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF278" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG278" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH278" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI278" s="5" t="s">
         <v>7</v>
@@ -45361,14 +45378,14 @@
     </row>
     <row r="279" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>277</v>
       </c>
       <c r="B279" s="3">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>7</v>
@@ -45380,13 +45397,13 @@
         <v>0</v>
       </c>
       <c r="G279" s="3">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H279" s="3">
         <v>0</v>
       </c>
       <c r="I279" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J279" s="3">
         <v>0</v>
@@ -45452,16 +45469,16 @@
         <v>75</v>
       </c>
       <c r="AE279" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF279" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG279" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH279" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI279" s="5" t="s">
         <v>7</v>
@@ -45514,14 +45531,14 @@
     </row>
     <row r="280" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>278</v>
       </c>
       <c r="B280" s="3">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>7</v>
@@ -45533,13 +45550,13 @@
         <v>0</v>
       </c>
       <c r="G280" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H280" s="3">
         <v>0</v>
       </c>
       <c r="I280" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J280" s="3">
         <v>0</v>
@@ -45605,16 +45622,16 @@
         <v>75</v>
       </c>
       <c r="AE280" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF280" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG280" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH280" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI280" s="5" t="s">
         <v>7</v>
@@ -45667,14 +45684,14 @@
     </row>
     <row r="281" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>279</v>
       </c>
       <c r="B281" s="3">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>7</v>
@@ -45686,13 +45703,13 @@
         <v>0</v>
       </c>
       <c r="G281" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H281" s="3">
         <v>0</v>
       </c>
       <c r="I281" s="3">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J281" s="3">
         <v>0</v>
@@ -45758,16 +45775,16 @@
         <v>75</v>
       </c>
       <c r="AE281" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF281" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG281" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH281" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI281" s="5" t="s">
         <v>7</v>
@@ -45820,20 +45837,20 @@
     </row>
     <row r="282" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>280</v>
       </c>
       <c r="B282" s="3">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C282" s="3" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E282" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F282" s="3">
         <v>0</v>
@@ -45911,16 +45928,16 @@
         <v>75</v>
       </c>
       <c r="AE282" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF282" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG282" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH282" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI282" s="5" t="s">
         <v>7</v>
@@ -45973,32 +45990,32 @@
     </row>
     <row r="283" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>281</v>
       </c>
       <c r="B283" s="3">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E283" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F283" s="3">
         <v>0</v>
       </c>
       <c r="G283" s="3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H283" s="3">
         <v>0</v>
       </c>
       <c r="I283" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J283" s="3">
         <v>0</v>
@@ -46064,19 +46081,19 @@
         <v>75</v>
       </c>
       <c r="AE283" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF283" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG283" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH283" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI283" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AJ283" s="5" t="s">
         <v>7</v>
@@ -46103,7 +46120,7 @@
         <v>10</v>
       </c>
       <c r="AR283" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS283" s="5">
         <v>0</v>
@@ -46126,32 +46143,32 @@
     </row>
     <row r="284" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>282</v>
       </c>
       <c r="B284" s="3">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E284" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F284" s="3">
         <v>0</v>
       </c>
       <c r="G284" s="3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H284" s="3">
         <v>0</v>
       </c>
       <c r="I284" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J284" s="3">
         <v>0</v>
@@ -46217,19 +46234,19 @@
         <v>75</v>
       </c>
       <c r="AE284" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF284" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG284" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH284" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI284" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AJ284" s="5" t="s">
         <v>7</v>
@@ -46256,7 +46273,7 @@
         <v>10</v>
       </c>
       <c r="AR284" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS284" s="5">
         <v>0</v>
@@ -46279,32 +46296,32 @@
     </row>
     <row r="285" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>283</v>
       </c>
       <c r="B285" s="3">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E285" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F285" s="3">
         <v>0</v>
       </c>
       <c r="G285" s="3">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H285" s="3">
         <v>0</v>
       </c>
       <c r="I285" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J285" s="3">
         <v>0</v>
@@ -46370,19 +46387,19 @@
         <v>75</v>
       </c>
       <c r="AE285" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF285" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG285" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH285" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="AI285" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ285" s="5" t="s">
         <v>7</v>
@@ -46409,7 +46426,7 @@
         <v>10</v>
       </c>
       <c r="AR285" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS285" s="5">
         <v>0</v>
@@ -46430,175 +46447,175 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="11">
-        <f t="shared" si="10"/>
+    <row r="286" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A286" s="3">
+        <f t="shared" si="12"/>
         <v>284</v>
       </c>
-      <c r="B286" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C286" s="11" t="s">
-        <v>441</v>
-      </c>
-      <c r="D286" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E286" s="11">
-        <v>0</v>
-      </c>
-      <c r="F286" s="11">
-        <v>0</v>
-      </c>
-      <c r="G286" s="11">
-        <v>0</v>
-      </c>
-      <c r="H286" s="11">
-        <v>0</v>
-      </c>
-      <c r="I286" s="11">
-        <v>0</v>
-      </c>
-      <c r="J286" s="11">
-        <v>0</v>
-      </c>
-      <c r="K286" s="11">
-        <v>0</v>
-      </c>
-      <c r="L286" s="11">
-        <v>0</v>
-      </c>
-      <c r="M286" s="11">
-        <v>0</v>
-      </c>
-      <c r="N286" s="11">
-        <v>0</v>
-      </c>
-      <c r="O286" s="11">
-        <v>0</v>
-      </c>
-      <c r="P286" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q286" s="11">
-        <v>0</v>
-      </c>
-      <c r="R286" s="11">
-        <v>0</v>
-      </c>
-      <c r="S286" s="11">
-        <v>0</v>
-      </c>
-      <c r="T286" s="11">
-        <v>0</v>
-      </c>
-      <c r="U286" s="11">
-        <v>0</v>
-      </c>
-      <c r="V286" s="11">
-        <v>0</v>
-      </c>
-      <c r="W286" s="11">
-        <v>0</v>
-      </c>
-      <c r="X286" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y286" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z286" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA286" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB286" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK286" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV286" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW286" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX286" s="12">
+      <c r="B286" s="3">
+        <v>1810</v>
+      </c>
+      <c r="C286" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E286" s="3">
+        <v>20</v>
+      </c>
+      <c r="F286" s="3">
+        <v>0</v>
+      </c>
+      <c r="G286" s="3">
+        <v>100</v>
+      </c>
+      <c r="H286" s="3">
+        <v>0</v>
+      </c>
+      <c r="I286" s="3">
+        <v>60</v>
+      </c>
+      <c r="J286" s="3">
+        <v>0</v>
+      </c>
+      <c r="K286" s="3">
+        <v>0</v>
+      </c>
+      <c r="L286" s="3">
+        <v>0</v>
+      </c>
+      <c r="M286" s="3">
+        <v>0</v>
+      </c>
+      <c r="N286" s="3">
+        <v>0</v>
+      </c>
+      <c r="O286" s="3">
+        <v>0</v>
+      </c>
+      <c r="P286" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q286" s="3">
+        <v>55</v>
+      </c>
+      <c r="R286" s="3">
+        <v>0</v>
+      </c>
+      <c r="S286" s="3">
+        <v>0</v>
+      </c>
+      <c r="T286" s="3">
+        <v>0</v>
+      </c>
+      <c r="U286" s="3">
+        <v>0</v>
+      </c>
+      <c r="V286" s="3">
+        <v>0</v>
+      </c>
+      <c r="W286" s="3">
+        <v>0</v>
+      </c>
+      <c r="X286" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y286" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB286" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC286" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD286" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE286" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF286" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG286" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH286" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI286" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ286" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK286" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL286" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM286" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN286" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO286" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP286" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ286" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR286" s="5">
+        <v>30</v>
+      </c>
+      <c r="AS286" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT286" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU286" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV286" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW286" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX286" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="287" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>285</v>
       </c>
       <c r="B287" s="3">
-        <v>1820</v>
+        <v>1811</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E287" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F287" s="3">
         <v>0</v>
@@ -46676,16 +46693,16 @@
         <v>75</v>
       </c>
       <c r="AE287" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF287" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG287" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH287" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI287" s="5" t="s">
         <v>7</v>
@@ -46712,7 +46729,7 @@
         <v>65</v>
       </c>
       <c r="AQ287" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR287" s="5">
         <v>0</v>
@@ -46736,175 +46753,175 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="3">
-        <f t="shared" si="10"/>
+    <row r="288" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A288" s="11">
+        <f t="shared" si="12"/>
         <v>286</v>
       </c>
-      <c r="B288" s="3">
-        <v>1821</v>
-      </c>
-      <c r="C288" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E288" s="3">
-        <v>50</v>
-      </c>
-      <c r="F288" s="3">
-        <v>0</v>
-      </c>
-      <c r="G288" s="3">
-        <v>55</v>
-      </c>
-      <c r="H288" s="3">
-        <v>0</v>
-      </c>
-      <c r="I288" s="3">
-        <v>30</v>
-      </c>
-      <c r="J288" s="3">
-        <v>0</v>
-      </c>
-      <c r="K288" s="3">
-        <v>0</v>
-      </c>
-      <c r="L288" s="3">
-        <v>0</v>
-      </c>
-      <c r="M288" s="3">
-        <v>0</v>
-      </c>
-      <c r="N288" s="3">
-        <v>0</v>
-      </c>
-      <c r="O288" s="3">
-        <v>0</v>
-      </c>
-      <c r="P288" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q288" s="3">
-        <v>55</v>
-      </c>
-      <c r="R288" s="3">
-        <v>0</v>
-      </c>
-      <c r="S288" s="3">
-        <v>0</v>
-      </c>
-      <c r="T288" s="3">
-        <v>0</v>
-      </c>
-      <c r="U288" s="3">
-        <v>0</v>
-      </c>
-      <c r="V288" s="3">
-        <v>0</v>
-      </c>
-      <c r="W288" s="3">
-        <v>0</v>
-      </c>
-      <c r="X288" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y288" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z288" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA288" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB288" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC288" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD288" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE288" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="AF288" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="AG288" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="AH288" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI288" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ288" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK288" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL288" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM288" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN288" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO288" s="5">
-        <v>50</v>
-      </c>
-      <c r="AP288" s="5">
-        <v>65</v>
-      </c>
-      <c r="AQ288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV288" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW288" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX288" s="5">
+      <c r="B288" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C288" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="D288" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E288" s="11">
+        <v>0</v>
+      </c>
+      <c r="F288" s="11">
+        <v>0</v>
+      </c>
+      <c r="G288" s="11">
+        <v>0</v>
+      </c>
+      <c r="H288" s="11">
+        <v>0</v>
+      </c>
+      <c r="I288" s="11">
+        <v>0</v>
+      </c>
+      <c r="J288" s="11">
+        <v>0</v>
+      </c>
+      <c r="K288" s="11">
+        <v>0</v>
+      </c>
+      <c r="L288" s="11">
+        <v>0</v>
+      </c>
+      <c r="M288" s="11">
+        <v>0</v>
+      </c>
+      <c r="N288" s="11">
+        <v>0</v>
+      </c>
+      <c r="O288" s="11">
+        <v>0</v>
+      </c>
+      <c r="P288" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q288" s="11">
+        <v>0</v>
+      </c>
+      <c r="R288" s="11">
+        <v>0</v>
+      </c>
+      <c r="S288" s="11">
+        <v>0</v>
+      </c>
+      <c r="T288" s="11">
+        <v>0</v>
+      </c>
+      <c r="U288" s="11">
+        <v>0</v>
+      </c>
+      <c r="V288" s="11">
+        <v>0</v>
+      </c>
+      <c r="W288" s="11">
+        <v>0</v>
+      </c>
+      <c r="X288" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y288" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z288" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA288" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB288" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK288" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV288" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW288" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX288" s="12">
         <v>0</v>
       </c>
     </row>
     <row r="289" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>287</v>
       </c>
       <c r="B289" s="3">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E289" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F289" s="3">
         <v>0</v>
@@ -46982,13 +46999,13 @@
         <v>75</v>
       </c>
       <c r="AE289" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF289" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG289" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH289" s="5" t="s">
         <v>7</v>
@@ -47044,20 +47061,20 @@
     </row>
     <row r="290" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>288</v>
       </c>
       <c r="B290" s="3">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E290" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F290" s="3">
         <v>0</v>
@@ -47135,13 +47152,13 @@
         <v>75</v>
       </c>
       <c r="AE290" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF290" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG290" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH290" s="5" t="s">
         <v>7</v>
@@ -47197,14 +47214,14 @@
     </row>
     <row r="291" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>289</v>
       </c>
       <c r="B291" s="3">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>7</v>
@@ -47288,13 +47305,13 @@
         <v>75</v>
       </c>
       <c r="AE291" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF291" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG291" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH291" s="5" t="s">
         <v>7</v>
@@ -47350,14 +47367,14 @@
     </row>
     <row r="292" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>290</v>
       </c>
       <c r="B292" s="3">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>7</v>
@@ -47441,13 +47458,13 @@
         <v>75</v>
       </c>
       <c r="AE292" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF292" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG292" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH292" s="5" t="s">
         <v>7</v>
@@ -47503,14 +47520,14 @@
     </row>
     <row r="293" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="3">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>291</v>
       </c>
       <c r="B293" s="3">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>7</v>
@@ -47594,13 +47611,13 @@
         <v>75</v>
       </c>
       <c r="AE293" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AF293" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="AG293" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="AH293" s="5" t="s">
         <v>7</v>
@@ -47654,193 +47671,193 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="11">
-        <f t="shared" si="0"/>
+    <row r="294" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A294" s="3">
+        <f t="shared" si="12"/>
         <v>292</v>
       </c>
-      <c r="B294" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C294" s="11" t="s">
-        <v>391</v>
-      </c>
-      <c r="D294" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E294" s="11">
-        <v>0</v>
-      </c>
-      <c r="F294" s="11">
-        <v>0</v>
-      </c>
-      <c r="G294" s="11">
-        <v>0</v>
-      </c>
-      <c r="H294" s="11">
-        <v>0</v>
-      </c>
-      <c r="I294" s="11">
-        <v>0</v>
-      </c>
-      <c r="J294" s="11">
-        <v>0</v>
-      </c>
-      <c r="K294" s="11">
-        <v>0</v>
-      </c>
-      <c r="L294" s="11">
-        <v>0</v>
-      </c>
-      <c r="M294" s="11">
-        <v>0</v>
-      </c>
-      <c r="N294" s="11">
-        <v>0</v>
-      </c>
-      <c r="O294" s="11">
-        <v>0</v>
-      </c>
-      <c r="P294" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q294" s="11">
-        <v>0</v>
-      </c>
-      <c r="R294" s="11">
-        <v>0</v>
-      </c>
-      <c r="S294" s="11">
-        <v>0</v>
-      </c>
-      <c r="T294" s="11">
-        <v>0</v>
-      </c>
-      <c r="U294" s="11">
-        <v>0</v>
-      </c>
-      <c r="V294" s="11">
-        <v>0</v>
-      </c>
-      <c r="W294" s="11">
-        <v>0</v>
-      </c>
-      <c r="X294" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y294" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z294" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA294" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB294" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK294" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV294" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW294" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX294" s="12">
+      <c r="B294" s="3">
+        <v>1825</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E294" s="3">
+        <v>30</v>
+      </c>
+      <c r="F294" s="3">
+        <v>0</v>
+      </c>
+      <c r="G294" s="3">
+        <v>55</v>
+      </c>
+      <c r="H294" s="3">
+        <v>0</v>
+      </c>
+      <c r="I294" s="3">
+        <v>30</v>
+      </c>
+      <c r="J294" s="3">
+        <v>0</v>
+      </c>
+      <c r="K294" s="3">
+        <v>0</v>
+      </c>
+      <c r="L294" s="3">
+        <v>0</v>
+      </c>
+      <c r="M294" s="3">
+        <v>0</v>
+      </c>
+      <c r="N294" s="3">
+        <v>0</v>
+      </c>
+      <c r="O294" s="3">
+        <v>0</v>
+      </c>
+      <c r="P294" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q294" s="3">
+        <v>55</v>
+      </c>
+      <c r="R294" s="3">
+        <v>0</v>
+      </c>
+      <c r="S294" s="3">
+        <v>0</v>
+      </c>
+      <c r="T294" s="3">
+        <v>0</v>
+      </c>
+      <c r="U294" s="3">
+        <v>0</v>
+      </c>
+      <c r="V294" s="3">
+        <v>0</v>
+      </c>
+      <c r="W294" s="3">
+        <v>0</v>
+      </c>
+      <c r="X294" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y294" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z294" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA294" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB294" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC294" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD294" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE294" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF294" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG294" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH294" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI294" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ294" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK294" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL294" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM294" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN294" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO294" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP294" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV294" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW294" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX294" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>293</v>
       </c>
       <c r="B295" s="3">
-        <v>2000</v>
+        <v>1826</v>
       </c>
       <c r="C295" s="3" t="s">
-        <v>7</v>
+        <v>437</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>381</v>
+        <v>7</v>
       </c>
       <c r="E295" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F295" s="3">
         <v>0</v>
       </c>
       <c r="G295" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H295" s="3">
         <v>0</v>
       </c>
       <c r="I295" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J295" s="3">
         <v>0</v>
       </c>
       <c r="K295" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L295" s="3">
         <v>0</v>
@@ -47855,85 +47872,85 @@
         <v>0</v>
       </c>
       <c r="P295" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q295" s="3">
+        <v>55</v>
+      </c>
+      <c r="R295" s="3">
+        <v>0</v>
+      </c>
+      <c r="S295" s="3">
+        <v>0</v>
+      </c>
+      <c r="T295" s="3">
+        <v>0</v>
+      </c>
+      <c r="U295" s="3">
+        <v>0</v>
+      </c>
+      <c r="V295" s="3">
+        <v>0</v>
+      </c>
+      <c r="W295" s="3">
+        <v>0</v>
+      </c>
+      <c r="X295" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y295" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z295" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA295" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB295" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC295" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD295" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE295" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF295" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG295" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL295" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM295" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN295" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO295" s="5">
         <v>50</v>
       </c>
-      <c r="R295" s="3">
-        <v>0</v>
-      </c>
-      <c r="S295" s="3">
-        <v>0</v>
-      </c>
-      <c r="T295" s="3">
-        <v>0</v>
-      </c>
-      <c r="U295" s="3">
-        <v>0</v>
-      </c>
-      <c r="V295" s="3">
-        <v>0</v>
-      </c>
-      <c r="W295" s="3">
-        <v>0</v>
-      </c>
-      <c r="X295" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y295" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z295" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA295" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB295" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO295" s="5">
-        <v>0</v>
-      </c>
       <c r="AP295" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ295" s="5">
         <v>0</v>
@@ -47951,7 +47968,7 @@
         <v>0</v>
       </c>
       <c r="AV295" s="4" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="AW295" s="5">
         <v>0</v>
@@ -47960,156 +47977,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="3">
+    <row r="296" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A296" s="11">
         <f t="shared" si="0"/>
         <v>294</v>
       </c>
-      <c r="B296" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C296" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="E296" s="3">
-        <v>0</v>
-      </c>
-      <c r="F296" s="3">
-        <v>0</v>
-      </c>
-      <c r="G296" s="3">
-        <v>60</v>
-      </c>
-      <c r="H296" s="3">
-        <v>0</v>
-      </c>
-      <c r="I296" s="3">
-        <v>0</v>
-      </c>
-      <c r="J296" s="3">
-        <v>0</v>
-      </c>
-      <c r="K296" s="3">
-        <v>100</v>
-      </c>
-      <c r="L296" s="3">
-        <v>0</v>
-      </c>
-      <c r="M296" s="3">
-        <v>0</v>
-      </c>
-      <c r="N296" s="3">
-        <v>0</v>
-      </c>
-      <c r="O296" s="3">
-        <v>0</v>
-      </c>
-      <c r="P296" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q296" s="3">
-        <v>50</v>
-      </c>
-      <c r="R296" s="3">
-        <v>0</v>
-      </c>
-      <c r="S296" s="3">
-        <v>0</v>
-      </c>
-      <c r="T296" s="3">
-        <v>0</v>
-      </c>
-      <c r="U296" s="3">
-        <v>0</v>
-      </c>
-      <c r="V296" s="3">
-        <v>0</v>
-      </c>
-      <c r="W296" s="3">
-        <v>0</v>
-      </c>
-      <c r="X296" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y296" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z296" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA296" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB296" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK296" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV296" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW296" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX296" s="5">
+      <c r="B296" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C296" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D296" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E296" s="11">
+        <v>0</v>
+      </c>
+      <c r="F296" s="11">
+        <v>0</v>
+      </c>
+      <c r="G296" s="11">
+        <v>0</v>
+      </c>
+      <c r="H296" s="11">
+        <v>0</v>
+      </c>
+      <c r="I296" s="11">
+        <v>0</v>
+      </c>
+      <c r="J296" s="11">
+        <v>0</v>
+      </c>
+      <c r="K296" s="11">
+        <v>0</v>
+      </c>
+      <c r="L296" s="11">
+        <v>0</v>
+      </c>
+      <c r="M296" s="11">
+        <v>0</v>
+      </c>
+      <c r="N296" s="11">
+        <v>0</v>
+      </c>
+      <c r="O296" s="11">
+        <v>0</v>
+      </c>
+      <c r="P296" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q296" s="11">
+        <v>0</v>
+      </c>
+      <c r="R296" s="11">
+        <v>0</v>
+      </c>
+      <c r="S296" s="11">
+        <v>0</v>
+      </c>
+      <c r="T296" s="11">
+        <v>0</v>
+      </c>
+      <c r="U296" s="11">
+        <v>0</v>
+      </c>
+      <c r="V296" s="11">
+        <v>0</v>
+      </c>
+      <c r="W296" s="11">
+        <v>0</v>
+      </c>
+      <c r="X296" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y296" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z296" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA296" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB296" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK296" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV296" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW296" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX296" s="12">
         <v>0</v>
       </c>
     </row>
@@ -48119,13 +48136,13 @@
         <v>295</v>
       </c>
       <c r="B297" s="3">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>392</v>
+        <v>7</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>7</v>
+        <v>378</v>
       </c>
       <c r="E297" s="3">
         <v>0</v>
@@ -48134,13 +48151,13 @@
         <v>0</v>
       </c>
       <c r="G297" s="3">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="H297" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I297" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J297" s="3">
         <v>0</v>
@@ -48164,7 +48181,7 @@
         <v>0</v>
       </c>
       <c r="Q297" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R297" s="3">
         <v>0</v>
@@ -48227,28 +48244,28 @@
         <v>7</v>
       </c>
       <c r="AL297" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM297" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN297" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO297" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP297" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ297" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR297" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS297" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT297" s="5">
         <v>0</v>
@@ -48272,13 +48289,13 @@
         <v>296</v>
       </c>
       <c r="B298" s="3">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>393</v>
+        <v>7</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>7</v>
+        <v>379</v>
       </c>
       <c r="E298" s="3">
         <v>0</v>
@@ -48287,13 +48304,13 @@
         <v>0</v>
       </c>
       <c r="G298" s="3">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="H298" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I298" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J298" s="3">
         <v>0</v>
@@ -48317,7 +48334,7 @@
         <v>0</v>
       </c>
       <c r="Q298" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R298" s="3">
         <v>0</v>
@@ -48380,28 +48397,28 @@
         <v>7</v>
       </c>
       <c r="AL298" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM298" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN298" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO298" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP298" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ298" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR298" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS298" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT298" s="5">
         <v>0</v>
@@ -48419,156 +48436,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="11">
+    <row r="299" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A299" s="3">
         <f t="shared" si="0"/>
         <v>297</v>
       </c>
-      <c r="B299" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C299" s="11" t="s">
-        <v>315</v>
-      </c>
-      <c r="D299" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E299" s="11">
-        <v>0</v>
-      </c>
-      <c r="F299" s="11">
-        <v>0</v>
-      </c>
-      <c r="G299" s="11">
-        <v>0</v>
-      </c>
-      <c r="H299" s="11">
-        <v>0</v>
-      </c>
-      <c r="I299" s="11">
-        <v>0</v>
-      </c>
-      <c r="J299" s="11">
-        <v>0</v>
-      </c>
-      <c r="K299" s="11">
-        <v>0</v>
-      </c>
-      <c r="L299" s="11">
-        <v>0</v>
-      </c>
-      <c r="M299" s="11">
-        <v>0</v>
-      </c>
-      <c r="N299" s="11">
-        <v>0</v>
-      </c>
-      <c r="O299" s="11">
-        <v>0</v>
-      </c>
-      <c r="P299" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q299" s="11">
-        <v>0</v>
-      </c>
-      <c r="R299" s="11">
-        <v>0</v>
-      </c>
-      <c r="S299" s="11">
-        <v>0</v>
-      </c>
-      <c r="T299" s="11">
-        <v>0</v>
-      </c>
-      <c r="U299" s="11">
-        <v>0</v>
-      </c>
-      <c r="V299" s="11">
-        <v>0</v>
-      </c>
-      <c r="W299" s="11">
-        <v>0</v>
-      </c>
-      <c r="X299" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y299" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z299" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA299" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB299" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK299" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV299" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW299" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX299" s="12">
+      <c r="B299" s="3">
+        <v>2002</v>
+      </c>
+      <c r="C299" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E299" s="3">
+        <v>0</v>
+      </c>
+      <c r="F299" s="3">
+        <v>0</v>
+      </c>
+      <c r="G299" s="3">
+        <v>570</v>
+      </c>
+      <c r="H299" s="3">
+        <v>200</v>
+      </c>
+      <c r="I299" s="3">
+        <v>250</v>
+      </c>
+      <c r="J299" s="3">
+        <v>0</v>
+      </c>
+      <c r="K299" s="3">
+        <v>100</v>
+      </c>
+      <c r="L299" s="3">
+        <v>0</v>
+      </c>
+      <c r="M299" s="3">
+        <v>0</v>
+      </c>
+      <c r="N299" s="3">
+        <v>0</v>
+      </c>
+      <c r="O299" s="3">
+        <v>0</v>
+      </c>
+      <c r="P299" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q299" s="3">
+        <v>80</v>
+      </c>
+      <c r="R299" s="3">
+        <v>0</v>
+      </c>
+      <c r="S299" s="3">
+        <v>0</v>
+      </c>
+      <c r="T299" s="3">
+        <v>0</v>
+      </c>
+      <c r="U299" s="3">
+        <v>0</v>
+      </c>
+      <c r="V299" s="3">
+        <v>0</v>
+      </c>
+      <c r="W299" s="3">
+        <v>0</v>
+      </c>
+      <c r="X299" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y299" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z299" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA299" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB299" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK299" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL299" s="5">
+        <v>10</v>
+      </c>
+      <c r="AM299" s="5">
+        <v>20</v>
+      </c>
+      <c r="AN299" s="5">
+        <v>20</v>
+      </c>
+      <c r="AO299" s="5">
+        <v>20</v>
+      </c>
+      <c r="AP299" s="5">
+        <v>20</v>
+      </c>
+      <c r="AQ299" s="5">
+        <v>20</v>
+      </c>
+      <c r="AR299" s="5">
+        <v>20</v>
+      </c>
+      <c r="AS299" s="5">
+        <v>40</v>
+      </c>
+      <c r="AT299" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU299" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV299" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW299" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX299" s="5">
         <v>0</v>
       </c>
     </row>
@@ -48578,10 +48595,10 @@
         <v>298</v>
       </c>
       <c r="B300" s="3">
-        <v>100000</v>
+        <v>2003</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>7</v>
@@ -48593,19 +48610,19 @@
         <v>0</v>
       </c>
       <c r="G300" s="3">
-        <v>120</v>
+        <v>570</v>
       </c>
       <c r="H300" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I300" s="3">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="J300" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K300" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L300" s="3">
         <v>0</v>
@@ -48623,7 +48640,7 @@
         <v>0</v>
       </c>
       <c r="Q300" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R300" s="3">
         <v>0</v>
@@ -48662,10 +48679,10 @@
         <v>7</v>
       </c>
       <c r="AD300" s="5" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="AE300" s="5" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="AF300" s="5" t="s">
         <v>7</v>
@@ -48686,37 +48703,37 @@
         <v>7</v>
       </c>
       <c r="AL300" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM300" s="5">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AN300" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO300" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP300" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ300" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR300" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS300" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT300" s="5">
         <v>0</v>
       </c>
       <c r="AU300" s="5">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AV300" s="4" t="s">
-        <v>268</v>
+        <v>98</v>
       </c>
       <c r="AW300" s="5">
         <v>0</v>
@@ -48725,156 +48742,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="3">
+    <row r="301" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="11">
         <f t="shared" si="0"/>
         <v>299</v>
       </c>
-      <c r="B301" s="3">
-        <v>100010</v>
-      </c>
-      <c r="C301" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E301" s="3">
-        <v>0</v>
-      </c>
-      <c r="F301" s="3">
-        <v>0</v>
-      </c>
-      <c r="G301" s="3">
-        <v>52</v>
-      </c>
-      <c r="H301" s="3">
-        <v>30</v>
-      </c>
-      <c r="I301" s="3">
-        <v>0</v>
-      </c>
-      <c r="J301" s="3">
-        <v>70</v>
-      </c>
-      <c r="K301" s="3">
-        <v>0</v>
-      </c>
-      <c r="L301" s="3">
-        <v>0</v>
-      </c>
-      <c r="M301" s="3">
-        <v>0</v>
-      </c>
-      <c r="N301" s="3">
-        <v>0</v>
-      </c>
-      <c r="O301" s="3">
-        <v>0</v>
-      </c>
-      <c r="P301" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q301" s="3">
-        <v>80</v>
-      </c>
-      <c r="R301" s="3">
-        <v>0</v>
-      </c>
-      <c r="S301" s="3">
-        <v>0</v>
-      </c>
-      <c r="T301" s="3">
-        <v>0</v>
-      </c>
-      <c r="U301" s="3">
-        <v>0</v>
-      </c>
-      <c r="V301" s="3">
-        <v>0</v>
-      </c>
-      <c r="W301" s="3">
-        <v>0</v>
-      </c>
-      <c r="X301" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y301" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z301" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA301" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB301" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC301" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD301" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE301" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF301" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG301" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH301" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI301" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ301" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK301" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL301" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM301" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN301" s="5">
-        <v>20</v>
-      </c>
-      <c r="AO301" s="5">
-        <v>12</v>
-      </c>
-      <c r="AP301" s="5">
-        <v>12</v>
-      </c>
-      <c r="AQ301" s="5">
-        <v>40</v>
-      </c>
-      <c r="AR301" s="5">
-        <v>10</v>
-      </c>
-      <c r="AS301" s="5">
-        <v>10</v>
-      </c>
-      <c r="AT301" s="5">
-        <v>30</v>
-      </c>
-      <c r="AU301" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV301" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AW301" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX301" s="5">
+      <c r="B301" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C301" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D301" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E301" s="11">
+        <v>0</v>
+      </c>
+      <c r="F301" s="11">
+        <v>0</v>
+      </c>
+      <c r="G301" s="11">
+        <v>0</v>
+      </c>
+      <c r="H301" s="11">
+        <v>0</v>
+      </c>
+      <c r="I301" s="11">
+        <v>0</v>
+      </c>
+      <c r="J301" s="11">
+        <v>0</v>
+      </c>
+      <c r="K301" s="11">
+        <v>0</v>
+      </c>
+      <c r="L301" s="11">
+        <v>0</v>
+      </c>
+      <c r="M301" s="11">
+        <v>0</v>
+      </c>
+      <c r="N301" s="11">
+        <v>0</v>
+      </c>
+      <c r="O301" s="11">
+        <v>0</v>
+      </c>
+      <c r="P301" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q301" s="11">
+        <v>0</v>
+      </c>
+      <c r="R301" s="11">
+        <v>0</v>
+      </c>
+      <c r="S301" s="11">
+        <v>0</v>
+      </c>
+      <c r="T301" s="11">
+        <v>0</v>
+      </c>
+      <c r="U301" s="11">
+        <v>0</v>
+      </c>
+      <c r="V301" s="11">
+        <v>0</v>
+      </c>
+      <c r="W301" s="11">
+        <v>0</v>
+      </c>
+      <c r="X301" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y301" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z301" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA301" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB301" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK301" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV301" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW301" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX301" s="12">
         <v>0</v>
       </c>
     </row>
@@ -48884,13 +48901,13 @@
         <v>300</v>
       </c>
       <c r="B302" s="3">
-        <v>100011</v>
+        <v>100000</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>263</v>
+        <v>7</v>
       </c>
       <c r="E302" s="3">
         <v>0</v>
@@ -48899,130 +48916,130 @@
         <v>0</v>
       </c>
       <c r="G302" s="3">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H302" s="3">
+        <v>0</v>
+      </c>
+      <c r="I302" s="3">
+        <v>60</v>
+      </c>
+      <c r="J302" s="3">
+        <v>120</v>
+      </c>
+      <c r="K302" s="3">
+        <v>0</v>
+      </c>
+      <c r="L302" s="3">
+        <v>0</v>
+      </c>
+      <c r="M302" s="3">
+        <v>0</v>
+      </c>
+      <c r="N302" s="3">
+        <v>0</v>
+      </c>
+      <c r="O302" s="3">
+        <v>0</v>
+      </c>
+      <c r="P302" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q302" s="3">
+        <v>50</v>
+      </c>
+      <c r="R302" s="3">
+        <v>0</v>
+      </c>
+      <c r="S302" s="3">
+        <v>0</v>
+      </c>
+      <c r="T302" s="3">
+        <v>0</v>
+      </c>
+      <c r="U302" s="3">
+        <v>0</v>
+      </c>
+      <c r="V302" s="3">
+        <v>0</v>
+      </c>
+      <c r="W302" s="3">
+        <v>0</v>
+      </c>
+      <c r="X302" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y302" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z302" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA302" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB302" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD302" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE302" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL302" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM302" s="5">
+        <v>60</v>
+      </c>
+      <c r="AN302" s="5">
         <v>30</v>
       </c>
-      <c r="I302" s="3">
-        <v>0</v>
-      </c>
-      <c r="J302" s="3">
-        <v>70</v>
-      </c>
-      <c r="K302" s="3">
-        <v>0</v>
-      </c>
-      <c r="L302" s="3">
-        <v>0</v>
-      </c>
-      <c r="M302" s="3">
-        <v>0</v>
-      </c>
-      <c r="N302" s="3">
-        <v>0</v>
-      </c>
-      <c r="O302" s="3">
-        <v>0</v>
-      </c>
-      <c r="P302" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q302" s="3">
-        <v>80</v>
-      </c>
-      <c r="R302" s="3">
-        <v>0</v>
-      </c>
-      <c r="S302" s="3">
-        <v>0</v>
-      </c>
-      <c r="T302" s="3">
-        <v>0</v>
-      </c>
-      <c r="U302" s="3">
-        <v>0</v>
-      </c>
-      <c r="V302" s="3">
-        <v>0</v>
-      </c>
-      <c r="W302" s="3">
-        <v>0</v>
-      </c>
-      <c r="X302" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y302" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z302" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA302" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB302" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC302" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD302" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE302" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF302" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG302" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH302" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI302" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ302" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK302" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL302" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM302" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN302" s="5">
-        <v>20</v>
-      </c>
       <c r="AO302" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP302" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ302" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AR302" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS302" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT302" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU302" s="5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AV302" s="4" t="s">
-        <v>113</v>
+        <v>268</v>
       </c>
       <c r="AW302" s="5">
         <v>0</v>
@@ -49037,13 +49054,13 @@
         <v>301</v>
       </c>
       <c r="B303" s="3">
-        <v>100020</v>
+        <v>100010</v>
       </c>
       <c r="C303" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>56</v>
+        <v>250</v>
       </c>
       <c r="E303" s="3">
         <v>0</v>
@@ -49052,19 +49069,19 @@
         <v>0</v>
       </c>
       <c r="G303" s="3">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="H303" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I303" s="3">
         <v>0</v>
       </c>
       <c r="J303" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K303" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L303" s="3">
         <v>0</v>
@@ -49082,7 +49099,7 @@
         <v>0</v>
       </c>
       <c r="Q303" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R303" s="3">
         <v>0</v>
@@ -49118,64 +49135,64 @@
         <v>0</v>
       </c>
       <c r="AC303" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD303" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="AD303" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="AE303" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="AF303" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="AG303" s="5" t="s">
-        <v>7</v>
+        <v>255</v>
       </c>
       <c r="AH303" s="5" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="AI303" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ303" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AK303" s="5" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="AL303" s="5">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="AM303" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN303" s="5">
         <v>20</v>
       </c>
       <c r="AO303" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP303" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ303" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AR303" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS303" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT303" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU303" s="5">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AV303" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AW303" s="5">
         <v>0</v>
@@ -49190,13 +49207,13 @@
         <v>302</v>
       </c>
       <c r="B304" s="3">
-        <v>100030</v>
+        <v>100011</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="E304" s="3">
         <v>0</v>
@@ -49205,19 +49222,19 @@
         <v>0</v>
       </c>
       <c r="G304" s="3">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H304" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I304" s="3">
         <v>0</v>
       </c>
       <c r="J304" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K304" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L304" s="3">
         <v>0</v>
@@ -49235,7 +49252,7 @@
         <v>0</v>
       </c>
       <c r="Q304" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R304" s="3">
         <v>0</v>
@@ -49271,64 +49288,64 @@
         <v>0</v>
       </c>
       <c r="AC304" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AD304" s="5" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="AE304" s="5" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="AF304" s="5" t="s">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="AG304" s="5" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="AH304" s="5" t="s">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="AI304" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AJ304" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AK304" s="5" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="AL304" s="5">
-        <v>30</v>
+        <v>-50</v>
       </c>
       <c r="AM304" s="5">
         <v>30</v>
       </c>
       <c r="AN304" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO304" s="5">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AP304" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ304" s="5">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AR304" s="5">
         <v>10</v>
       </c>
       <c r="AS304" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT304" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU304" s="5">
         <v>0</v>
       </c>
       <c r="AV304" s="4" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="AW304" s="5">
         <v>0</v>
@@ -49339,17 +49356,17 @@
     </row>
     <row r="305" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="3">
-        <f t="shared" ref="A305" si="11">ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>303</v>
       </c>
       <c r="B305" s="3">
-        <v>100040</v>
+        <v>100020</v>
       </c>
       <c r="C305" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E305" s="3">
         <v>0</v>
@@ -49358,7 +49375,7 @@
         <v>0</v>
       </c>
       <c r="G305" s="3">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="H305" s="3">
         <v>0</v>
@@ -49367,10 +49384,10 @@
         <v>0</v>
       </c>
       <c r="J305" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K305" s="3">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L305" s="3">
         <v>0</v>
@@ -49388,7 +49405,7 @@
         <v>0</v>
       </c>
       <c r="Q305" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R305" s="3">
         <v>0</v>
@@ -49424,22 +49441,22 @@
         <v>0</v>
       </c>
       <c r="AC305" s="5" t="s">
-        <v>34</v>
+        <v>254</v>
       </c>
       <c r="AD305" s="5" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="AE305" s="5" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="AF305" s="5" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="AG305" s="5" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="AH305" s="5" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="AI305" s="5" t="s">
         <v>7</v>
@@ -49451,22 +49468,22 @@
         <v>7</v>
       </c>
       <c r="AL305" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AM305" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN305" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AO305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP305" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ305" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR305" s="5">
         <v>0</v>
@@ -49478,10 +49495,10 @@
         <v>0</v>
       </c>
       <c r="AU305" s="5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AV305" s="4" t="s">
-        <v>443</v>
+        <v>116</v>
       </c>
       <c r="AW305" s="5">
         <v>0</v>
@@ -49496,150 +49513,456 @@
         <v>304</v>
       </c>
       <c r="B306" s="3">
+        <v>100030</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E306" s="3">
+        <v>0</v>
+      </c>
+      <c r="F306" s="3">
+        <v>0</v>
+      </c>
+      <c r="G306" s="3">
+        <v>120</v>
+      </c>
+      <c r="H306" s="3">
+        <v>0</v>
+      </c>
+      <c r="I306" s="3">
+        <v>0</v>
+      </c>
+      <c r="J306" s="3">
+        <v>0</v>
+      </c>
+      <c r="K306" s="3">
+        <v>70</v>
+      </c>
+      <c r="L306" s="3">
+        <v>0</v>
+      </c>
+      <c r="M306" s="3">
+        <v>0</v>
+      </c>
+      <c r="N306" s="3">
+        <v>0</v>
+      </c>
+      <c r="O306" s="3">
+        <v>0</v>
+      </c>
+      <c r="P306" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q306" s="3">
+        <v>70</v>
+      </c>
+      <c r="R306" s="3">
+        <v>0</v>
+      </c>
+      <c r="S306" s="3">
+        <v>0</v>
+      </c>
+      <c r="T306" s="3">
+        <v>0</v>
+      </c>
+      <c r="U306" s="3">
+        <v>0</v>
+      </c>
+      <c r="V306" s="3">
+        <v>0</v>
+      </c>
+      <c r="W306" s="3">
+        <v>0</v>
+      </c>
+      <c r="X306" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y306" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z306" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA306" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB306" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC306" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD306" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AE306" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF306" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG306" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH306" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI306" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL306" s="5">
+        <v>30</v>
+      </c>
+      <c r="AM306" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN306" s="5">
+        <v>30</v>
+      </c>
+      <c r="AO306" s="5">
+        <v>30</v>
+      </c>
+      <c r="AP306" s="5">
+        <v>10</v>
+      </c>
+      <c r="AQ306" s="5">
+        <v>15</v>
+      </c>
+      <c r="AR306" s="5">
+        <v>10</v>
+      </c>
+      <c r="AS306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV306" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX306" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A307" s="3">
+        <f t="shared" ref="A307" si="13">ROW()-2</f>
+        <v>305</v>
+      </c>
+      <c r="B307" s="3">
+        <v>100040</v>
+      </c>
+      <c r="C307" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E307" s="3">
+        <v>0</v>
+      </c>
+      <c r="F307" s="3">
+        <v>0</v>
+      </c>
+      <c r="G307" s="3">
+        <v>32</v>
+      </c>
+      <c r="H307" s="3">
+        <v>0</v>
+      </c>
+      <c r="I307" s="3">
+        <v>0</v>
+      </c>
+      <c r="J307" s="3">
+        <v>60</v>
+      </c>
+      <c r="K307" s="3">
+        <v>0</v>
+      </c>
+      <c r="L307" s="3">
+        <v>0</v>
+      </c>
+      <c r="M307" s="3">
+        <v>0</v>
+      </c>
+      <c r="N307" s="3">
+        <v>0</v>
+      </c>
+      <c r="O307" s="3">
+        <v>0</v>
+      </c>
+      <c r="P307" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q307" s="3">
+        <v>50</v>
+      </c>
+      <c r="R307" s="3">
+        <v>0</v>
+      </c>
+      <c r="S307" s="3">
+        <v>0</v>
+      </c>
+      <c r="T307" s="3">
+        <v>0</v>
+      </c>
+      <c r="U307" s="3">
+        <v>0</v>
+      </c>
+      <c r="V307" s="3">
+        <v>0</v>
+      </c>
+      <c r="W307" s="3">
+        <v>0</v>
+      </c>
+      <c r="X307" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y307" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z307" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA307" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB307" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC307" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD307" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE307" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF307" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG307" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH307" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI307" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ307" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK307" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL307" s="5">
+        <v>5</v>
+      </c>
+      <c r="AM307" s="5">
+        <v>10</v>
+      </c>
+      <c r="AN307" s="5">
+        <v>12</v>
+      </c>
+      <c r="AO307" s="5">
+        <v>20</v>
+      </c>
+      <c r="AP307" s="5">
+        <v>5</v>
+      </c>
+      <c r="AQ307" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR307" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS307" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT307" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU307" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV307" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="AW307" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX307" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="3">
+        <f t="shared" si="0"/>
+        <v>306</v>
+      </c>
+      <c r="B308" s="3">
         <v>999999</v>
       </c>
-      <c r="C306" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E306" s="3">
-        <v>0</v>
-      </c>
-      <c r="F306" s="3">
-        <v>0</v>
-      </c>
-      <c r="G306" s="3">
-        <v>0</v>
-      </c>
-      <c r="H306" s="3">
-        <v>0</v>
-      </c>
-      <c r="I306" s="3">
-        <v>0</v>
-      </c>
-      <c r="J306" s="3">
-        <v>0</v>
-      </c>
-      <c r="K306" s="3">
-        <v>0</v>
-      </c>
-      <c r="L306" s="3">
-        <v>0</v>
-      </c>
-      <c r="M306" s="3">
-        <v>0</v>
-      </c>
-      <c r="N306" s="3">
-        <v>0</v>
-      </c>
-      <c r="O306" s="3">
-        <v>0</v>
-      </c>
-      <c r="P306" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q306" s="3">
-        <v>0</v>
-      </c>
-      <c r="R306" s="3">
-        <v>0</v>
-      </c>
-      <c r="S306" s="3">
-        <v>0</v>
-      </c>
-      <c r="T306" s="3">
-        <v>0</v>
-      </c>
-      <c r="U306" s="3">
-        <v>0</v>
-      </c>
-      <c r="V306" s="3">
-        <v>0</v>
-      </c>
-      <c r="W306" s="3">
-        <v>0</v>
-      </c>
-      <c r="X306" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y306" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z306" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA306" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB306" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK306" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV306" s="4" t="s">
+      <c r="C308" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E308" s="3">
+        <v>0</v>
+      </c>
+      <c r="F308" s="3">
+        <v>0</v>
+      </c>
+      <c r="G308" s="3">
+        <v>0</v>
+      </c>
+      <c r="H308" s="3">
+        <v>0</v>
+      </c>
+      <c r="I308" s="3">
+        <v>0</v>
+      </c>
+      <c r="J308" s="3">
+        <v>0</v>
+      </c>
+      <c r="K308" s="3">
+        <v>0</v>
+      </c>
+      <c r="L308" s="3">
+        <v>0</v>
+      </c>
+      <c r="M308" s="3">
+        <v>0</v>
+      </c>
+      <c r="N308" s="3">
+        <v>0</v>
+      </c>
+      <c r="O308" s="3">
+        <v>0</v>
+      </c>
+      <c r="P308" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q308" s="3">
+        <v>0</v>
+      </c>
+      <c r="R308" s="3">
+        <v>0</v>
+      </c>
+      <c r="S308" s="3">
+        <v>0</v>
+      </c>
+      <c r="T308" s="3">
+        <v>0</v>
+      </c>
+      <c r="U308" s="3">
+        <v>0</v>
+      </c>
+      <c r="V308" s="3">
+        <v>0</v>
+      </c>
+      <c r="W308" s="3">
+        <v>0</v>
+      </c>
+      <c r="X308" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y308" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z308" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB308" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV308" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AW306" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX306" s="5">
+      <c r="AW308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX308" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEC7A31-05C6-4335-B3EA-3A0AA76D34F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558A9682-858F-4955-80D1-639180FDEBD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2265" yWindow="1080" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -3331,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -7156,7 +7156,7 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FFFDC6B-3507-4BD7-8676-5910F7DCBCF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EDEE51-8C5C-4FF5-9495-D86C3A00FE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2775" yWindow="900" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="720" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -38465,7 +38465,7 @@
         <v>0</v>
       </c>
       <c r="X233" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y233" s="3">
         <v>0</v>
@@ -42290,7 +42290,7 @@
         <v>0</v>
       </c>
       <c r="X258" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Y258" s="3">
         <v>0</v>
@@ -42596,13 +42596,13 @@
         <v>0</v>
       </c>
       <c r="X260" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y260" s="3">
         <v>0</v>
       </c>
       <c r="Z260" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA260" s="3">
         <v>0</v>
@@ -43208,7 +43208,7 @@
         <v>0</v>
       </c>
       <c r="X264" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y264" s="3">
         <v>0</v>
@@ -43514,7 +43514,7 @@
         <v>0</v>
       </c>
       <c r="X266" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y266" s="3">
         <v>0</v>
@@ -44585,7 +44585,7 @@
         <v>0</v>
       </c>
       <c r="X273" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y273" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8EDEE51-8C5C-4FF5-9495-D86C3A00FE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE63A723-AD65-4E09-8D6C-3816AC871F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1650" yWindow="720" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -7967,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="3">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="H34" s="3">
         <v>0</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="H35" s="3">
         <v>0</v>
@@ -8732,7 +8732,7 @@
         <v>0</v>
       </c>
       <c r="G39" s="3">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="H39" s="3">
         <v>100</v>
@@ -9191,7 +9191,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="H42" s="3">
         <v>20</v>
@@ -9344,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H43" s="3">
         <v>0</v>
@@ -9650,7 +9650,7 @@
         <v>0</v>
       </c>
       <c r="G45" s="3">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="H45" s="3">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G64" s="3">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="H64" s="3">
         <v>0</v>
@@ -12710,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="G65" s="3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H65" s="3">
         <v>0</v>
@@ -12863,7 +12863,7 @@
         <v>0</v>
       </c>
       <c r="G66" s="3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H66" s="3">
         <v>0</v>
@@ -13628,7 +13628,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="3">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="H71" s="3">
         <v>0</v>
@@ -14795,10 +14795,10 @@
         <v>10</v>
       </c>
       <c r="AM78" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN78" s="5">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="AO78" s="5">
         <v>0</v>
@@ -14948,10 +14948,10 @@
         <v>10</v>
       </c>
       <c r="AM79" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN79" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO79" s="5">
         <v>0</v>
@@ -15101,7 +15101,7 @@
         <v>10</v>
       </c>
       <c r="AM80" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN80">
         <v>30</v>
@@ -15254,7 +15254,7 @@
         <v>10</v>
       </c>
       <c r="AM81" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN81">
         <v>30</v>
@@ -15407,7 +15407,7 @@
         <v>10</v>
       </c>
       <c r="AM82" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN82" s="5">
         <v>30</v>
@@ -15560,10 +15560,10 @@
         <v>10</v>
       </c>
       <c r="AM83" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN83" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO83" s="5">
         <v>30</v>
@@ -15713,10 +15713,10 @@
         <v>10</v>
       </c>
       <c r="AM84" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN84" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO84" s="5">
         <v>30</v>
@@ -15770,7 +15770,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H85" s="3">
         <v>0</v>
@@ -15866,10 +15866,10 @@
         <v>10</v>
       </c>
       <c r="AM85" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN85" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO85" s="5">
         <v>30</v>
@@ -16019,10 +16019,10 @@
         <v>10</v>
       </c>
       <c r="AM86" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN86" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO86" s="5">
         <v>0</v>
@@ -16172,10 +16172,10 @@
         <v>10</v>
       </c>
       <c r="AM87" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN87" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO87" s="5">
         <v>0</v>
@@ -16325,10 +16325,10 @@
         <v>10</v>
       </c>
       <c r="AM88" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN88" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO88" s="5">
         <v>0</v>
@@ -16478,10 +16478,10 @@
         <v>10</v>
       </c>
       <c r="AM89" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AN89" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO89" s="5">
         <v>10</v>
@@ -16631,10 +16631,10 @@
         <v>10</v>
       </c>
       <c r="AM90" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AN90" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO90" s="5">
         <v>10</v>
@@ -16784,10 +16784,10 @@
         <v>10</v>
       </c>
       <c r="AM91" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AN91" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO91" s="5">
         <v>10</v>
@@ -16937,10 +16937,10 @@
         <v>10</v>
       </c>
       <c r="AM92" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AN92" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO92" s="5">
         <v>10</v>
@@ -16994,7 +16994,7 @@
         <v>0</v>
       </c>
       <c r="G93" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H93" s="3">
         <v>0</v>
@@ -17090,10 +17090,10 @@
         <v>10</v>
       </c>
       <c r="AM93" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AN93" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO93" s="5">
         <v>50</v>
@@ -17243,10 +17243,10 @@
         <v>10</v>
       </c>
       <c r="AM94" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN94" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO94" s="5">
         <v>0</v>
@@ -17606,7 +17606,7 @@
         <v>0</v>
       </c>
       <c r="G97" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H97" s="3">
         <v>30</v>
@@ -17759,7 +17759,7 @@
         <v>0</v>
       </c>
       <c r="G98" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H98" s="3">
         <v>30</v>
@@ -17912,7 +17912,7 @@
         <v>0</v>
       </c>
       <c r="G99" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H99" s="3">
         <v>30</v>
@@ -18065,7 +18065,7 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H100" s="3">
         <v>30</v>
@@ -18218,7 +18218,7 @@
         <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3">
         <v>30</v>
@@ -18371,7 +18371,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="H102" s="3">
         <v>30</v>
@@ -18986,7 +18986,7 @@
         <v>27</v>
       </c>
       <c r="H106" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="I106" s="3">
         <v>0</v>
@@ -19016,7 +19016,7 @@
         <v>50</v>
       </c>
       <c r="R106" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="S106" s="3">
         <v>0</v>
@@ -19139,7 +19139,7 @@
         <v>55</v>
       </c>
       <c r="H107" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="I107" s="3">
         <v>0</v>
@@ -19169,7 +19169,7 @@
         <v>50</v>
       </c>
       <c r="R107" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="S107" s="3">
         <v>0</v>
@@ -19292,7 +19292,7 @@
         <v>35</v>
       </c>
       <c r="H108" s="3">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="I108" s="3">
         <v>0</v>
@@ -19322,7 +19322,7 @@
         <v>50</v>
       </c>
       <c r="R108" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="S108" s="3">
         <v>0</v>
@@ -19445,7 +19445,7 @@
         <v>35</v>
       </c>
       <c r="H109" s="3">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="I109" s="3">
         <v>0</v>
@@ -19475,7 +19475,7 @@
         <v>50</v>
       </c>
       <c r="R109" s="3">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="S109" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE63A723-AD65-4E09-8D6C-3816AC871F9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B71D751-D263-4ABC-AB4B-D976EDBB6C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -37352,7 +37352,7 @@
         <v>0</v>
       </c>
       <c r="J226" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K226" s="3">
         <v>0</v>
@@ -37505,7 +37505,7 @@
         <v>0</v>
       </c>
       <c r="J227" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K227" s="3">
         <v>0</v>
@@ -37658,7 +37658,7 @@
         <v>0</v>
       </c>
       <c r="J228" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K228" s="3">
         <v>0</v>
@@ -37811,7 +37811,7 @@
         <v>0</v>
       </c>
       <c r="J229" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K229" s="3">
         <v>0</v>
@@ -37964,7 +37964,7 @@
         <v>0</v>
       </c>
       <c r="J230" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K230" s="3">
         <v>0</v>
@@ -38117,7 +38117,7 @@
         <v>0</v>
       </c>
       <c r="J231" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K231" s="3">
         <v>0</v>
@@ -38270,7 +38270,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K232" s="3">
         <v>0</v>
@@ -44396,7 +44396,7 @@
         <v>0</v>
       </c>
       <c r="L272" s="3">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="M272" s="3">
         <v>0</v>
@@ -44855,7 +44855,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="3">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="M275" s="3">
         <v>0</v>
@@ -44897,7 +44897,7 @@
         <v>0</v>
       </c>
       <c r="Z275" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AA275" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B71D751-D263-4ABC-AB4B-D976EDBB6C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4500AA2-3EAE-4FAF-A3B7-098677C850F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2715" yWindow="1110" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="1875" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -37373,7 +37373,7 @@
         <v>0</v>
       </c>
       <c r="Q226" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R226" s="3">
         <v>0</v>
@@ -37526,7 +37526,7 @@
         <v>0</v>
       </c>
       <c r="Q227" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R227" s="3">
         <v>0</v>
@@ -37679,7 +37679,7 @@
         <v>0</v>
       </c>
       <c r="Q228" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R228" s="3">
         <v>0</v>
@@ -37832,7 +37832,7 @@
         <v>0</v>
       </c>
       <c r="Q229" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R229" s="3">
         <v>0</v>
@@ -37985,7 +37985,7 @@
         <v>0</v>
       </c>
       <c r="Q230" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R230" s="3">
         <v>0</v>
@@ -38138,7 +38138,7 @@
         <v>0</v>
       </c>
       <c r="Q231" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R231" s="3">
         <v>0</v>
@@ -38291,7 +38291,7 @@
         <v>0</v>
       </c>
       <c r="Q232" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R232" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F483FA-1FE8-457C-A726-6032EFBA8AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0183DE-D45B-4A29-810B-CB6B8B601EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="1380" windowWidth="25560" windowHeight="14325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="795" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -8730,7 +8730,7 @@
         <v>7</v>
       </c>
       <c r="E39" s="3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F39" s="3">
         <v>0</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>7</v>
       </c>
       <c r="E82" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F82" s="3">
         <v>0</v>
@@ -15615,7 +15615,7 @@
         <v>7</v>
       </c>
       <c r="E84" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F84" s="3">
         <v>0</v>
@@ -16533,7 +16533,7 @@
         <v>7</v>
       </c>
       <c r="E90" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F90" s="3">
         <v>0</v>
@@ -16839,7 +16839,7 @@
         <v>7</v>
       </c>
       <c r="E92" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F92" s="3">
         <v>0</v>
@@ -16992,7 +16992,7 @@
         <v>7</v>
       </c>
       <c r="E93" s="3">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="F93" s="3">
         <v>0</v>
@@ -17001,16 +17001,16 @@
         <v>60</v>
       </c>
       <c r="H93" s="3">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I93" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J93" s="3">
         <v>0</v>
       </c>
       <c r="K93" s="3">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="L93" s="3">
         <v>0</v>
@@ -17100,7 +17100,7 @@
         <v>20</v>
       </c>
       <c r="AO93" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AP93" s="5">
         <v>50</v>
@@ -17145,7 +17145,7 @@
         <v>7</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D0183DE-D45B-4A29-810B-CB6B8B601EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5984F1E1-B40F-4854-8FC0-9F214BCD6D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="795" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3794" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3818" uniqueCount="459">
   <si>
     <t>desc</t>
   </si>
@@ -2448,6 +2448,14 @@
     <t>ice_coffee</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>figure_bear_choco</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>figure_bear_whitechoco</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -2878,7 +2886,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AX313"/>
+  <dimension ref="A1:AX315"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -3056,7 +3064,7 @@
     </row>
     <row r="2" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A313" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A315" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -43907,7 +43915,7 @@
     </row>
     <row r="269" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="3">
-        <f t="shared" ref="A269:A300" si="16">ROW()-2</f>
+        <f t="shared" ref="A269:A302" si="16">ROW()-2</f>
         <v>267</v>
       </c>
       <c r="B269" s="3">
@@ -45588,156 +45596,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="11">
+    <row r="280" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A280" s="3">
         <f t="shared" si="16"/>
         <v>278</v>
       </c>
-      <c r="B280" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C280" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="D280" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E280" s="11">
-        <v>0</v>
-      </c>
-      <c r="F280" s="11">
-        <v>0</v>
-      </c>
-      <c r="G280" s="11">
-        <v>0</v>
-      </c>
-      <c r="H280" s="11">
-        <v>0</v>
-      </c>
-      <c r="I280" s="11">
-        <v>0</v>
-      </c>
-      <c r="J280" s="11">
-        <v>0</v>
-      </c>
-      <c r="K280" s="11">
-        <v>0</v>
-      </c>
-      <c r="L280" s="11">
-        <v>0</v>
-      </c>
-      <c r="M280" s="11">
-        <v>0</v>
-      </c>
-      <c r="N280" s="11">
-        <v>0</v>
-      </c>
-      <c r="O280" s="11">
-        <v>0</v>
-      </c>
-      <c r="P280" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q280" s="11">
-        <v>0</v>
-      </c>
-      <c r="R280" s="11">
-        <v>0</v>
-      </c>
-      <c r="S280" s="11">
-        <v>0</v>
-      </c>
-      <c r="T280" s="11">
-        <v>0</v>
-      </c>
-      <c r="U280" s="11">
-        <v>0</v>
-      </c>
-      <c r="V280" s="11">
-        <v>0</v>
-      </c>
-      <c r="W280" s="11">
-        <v>0</v>
-      </c>
-      <c r="X280" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y280" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z280" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA280" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB280" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK280" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV280" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW280" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX280" s="12">
+      <c r="B280" s="3">
+        <v>1740</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E280" s="3">
+        <v>0</v>
+      </c>
+      <c r="F280" s="3">
+        <v>0</v>
+      </c>
+      <c r="G280" s="3">
+        <v>80</v>
+      </c>
+      <c r="H280" s="3">
+        <v>230</v>
+      </c>
+      <c r="I280" s="3">
+        <v>0</v>
+      </c>
+      <c r="J280" s="3">
+        <v>0</v>
+      </c>
+      <c r="K280" s="3">
+        <v>0</v>
+      </c>
+      <c r="L280" s="3">
+        <v>70</v>
+      </c>
+      <c r="M280" s="3">
+        <v>0</v>
+      </c>
+      <c r="N280" s="3">
+        <v>0</v>
+      </c>
+      <c r="O280" s="3">
+        <v>0</v>
+      </c>
+      <c r="P280" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q280" s="3">
+        <v>50</v>
+      </c>
+      <c r="R280" s="3">
+        <v>0</v>
+      </c>
+      <c r="S280" s="3">
+        <v>0</v>
+      </c>
+      <c r="T280" s="3">
+        <v>0</v>
+      </c>
+      <c r="U280" s="3">
+        <v>0</v>
+      </c>
+      <c r="V280" s="3">
+        <v>0</v>
+      </c>
+      <c r="W280" s="3">
+        <v>0</v>
+      </c>
+      <c r="X280" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y280" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB280" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC280" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK280" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL280" s="5">
+        <v>20</v>
+      </c>
+      <c r="AM280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV280" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW280" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX280" s="5">
         <v>0</v>
       </c>
     </row>
@@ -45747,10 +45755,10 @@
         <v>279</v>
       </c>
       <c r="B281" s="3">
-        <v>1800</v>
+        <v>1741</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>7</v>
@@ -45762,13 +45770,13 @@
         <v>0</v>
       </c>
       <c r="G281" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H281" s="3">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="I281" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J281" s="3">
         <v>0</v>
@@ -45777,7 +45785,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M281" s="3">
         <v>0</v>
@@ -45789,10 +45797,10 @@
         <v>0</v>
       </c>
       <c r="P281" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q281" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R281" s="3">
         <v>0</v>
@@ -45828,22 +45836,22 @@
         <v>0</v>
       </c>
       <c r="AC281" s="5" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="AD281" s="5" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="AE281" s="5" t="s">
-        <v>298</v>
+        <v>7</v>
       </c>
       <c r="AF281" s="5" t="s">
-        <v>447</v>
+        <v>7</v>
       </c>
       <c r="AG281" s="5" t="s">
-        <v>448</v>
+        <v>7</v>
       </c>
       <c r="AH281" s="5" t="s">
-        <v>446</v>
+        <v>7</v>
       </c>
       <c r="AI281" s="5" t="s">
         <v>7</v>
@@ -45855,22 +45863,22 @@
         <v>7</v>
       </c>
       <c r="AL281" s="5">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="AM281" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AN281" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AO281" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AP281" s="5">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AQ281" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR281" s="5">
         <v>0</v>
@@ -45885,7 +45893,7 @@
         <v>0</v>
       </c>
       <c r="AV281" s="4" t="s">
-        <v>214</v>
+        <v>392</v>
       </c>
       <c r="AW281" s="5">
         <v>0</v>
@@ -45894,156 +45902,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="3">
+    <row r="282" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="11">
         <f t="shared" si="16"/>
         <v>280</v>
       </c>
-      <c r="B282" s="3">
-        <v>1801</v>
-      </c>
-      <c r="C282" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E282" s="3">
-        <v>0</v>
-      </c>
-      <c r="F282" s="3">
-        <v>0</v>
-      </c>
-      <c r="G282" s="3">
-        <v>55</v>
-      </c>
-      <c r="H282" s="3">
-        <v>0</v>
-      </c>
-      <c r="I282" s="3">
-        <v>30</v>
-      </c>
-      <c r="J282" s="3">
-        <v>0</v>
-      </c>
-      <c r="K282" s="3">
-        <v>0</v>
-      </c>
-      <c r="L282" s="3">
-        <v>0</v>
-      </c>
-      <c r="M282" s="3">
-        <v>0</v>
-      </c>
-      <c r="N282" s="3">
-        <v>0</v>
-      </c>
-      <c r="O282" s="3">
-        <v>0</v>
-      </c>
-      <c r="P282" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q282" s="3">
-        <v>55</v>
-      </c>
-      <c r="R282" s="3">
-        <v>0</v>
-      </c>
-      <c r="S282" s="3">
-        <v>0</v>
-      </c>
-      <c r="T282" s="3">
-        <v>0</v>
-      </c>
-      <c r="U282" s="3">
-        <v>0</v>
-      </c>
-      <c r="V282" s="3">
-        <v>0</v>
-      </c>
-      <c r="W282" s="3">
-        <v>0</v>
-      </c>
-      <c r="X282" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y282" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z282" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA282" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB282" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC282" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD282" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE282" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AF282" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG282" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH282" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="AI282" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ282" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK282" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL282" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM282" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN282" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO282" s="5">
-        <v>50</v>
-      </c>
-      <c r="AP282" s="5">
-        <v>65</v>
-      </c>
-      <c r="AQ282" s="5">
-        <v>10</v>
-      </c>
-      <c r="AR282" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS282" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT282" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU282" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV282" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW282" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX282" s="5">
+      <c r="B282" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C282" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D282" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E282" s="11">
+        <v>0</v>
+      </c>
+      <c r="F282" s="11">
+        <v>0</v>
+      </c>
+      <c r="G282" s="11">
+        <v>0</v>
+      </c>
+      <c r="H282" s="11">
+        <v>0</v>
+      </c>
+      <c r="I282" s="11">
+        <v>0</v>
+      </c>
+      <c r="J282" s="11">
+        <v>0</v>
+      </c>
+      <c r="K282" s="11">
+        <v>0</v>
+      </c>
+      <c r="L282" s="11">
+        <v>0</v>
+      </c>
+      <c r="M282" s="11">
+        <v>0</v>
+      </c>
+      <c r="N282" s="11">
+        <v>0</v>
+      </c>
+      <c r="O282" s="11">
+        <v>0</v>
+      </c>
+      <c r="P282" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q282" s="11">
+        <v>0</v>
+      </c>
+      <c r="R282" s="11">
+        <v>0</v>
+      </c>
+      <c r="S282" s="11">
+        <v>0</v>
+      </c>
+      <c r="T282" s="11">
+        <v>0</v>
+      </c>
+      <c r="U282" s="11">
+        <v>0</v>
+      </c>
+      <c r="V282" s="11">
+        <v>0</v>
+      </c>
+      <c r="W282" s="11">
+        <v>0</v>
+      </c>
+      <c r="X282" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y282" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z282" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA282" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB282" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK282" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV282" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW282" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX282" s="12">
         <v>0</v>
       </c>
     </row>
@@ -46053,10 +46061,10 @@
         <v>281</v>
       </c>
       <c r="B283" s="3">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>7</v>
@@ -46095,7 +46103,7 @@
         <v>0</v>
       </c>
       <c r="P283" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q283" s="3">
         <v>55</v>
@@ -46206,10 +46214,10 @@
         <v>282</v>
       </c>
       <c r="B284" s="3">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C284" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>7</v>
@@ -46359,10 +46367,10 @@
         <v>283</v>
       </c>
       <c r="B285" s="3">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>7</v>
@@ -46374,13 +46382,13 @@
         <v>0</v>
       </c>
       <c r="G285" s="3">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H285" s="3">
         <v>0</v>
       </c>
       <c r="I285" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J285" s="3">
         <v>0</v>
@@ -46512,10 +46520,10 @@
         <v>284</v>
       </c>
       <c r="B286" s="3">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>7</v>
@@ -46527,13 +46535,13 @@
         <v>0</v>
       </c>
       <c r="G286" s="3">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H286" s="3">
         <v>0</v>
       </c>
       <c r="I286" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J286" s="3">
         <v>0</v>
@@ -46665,10 +46673,10 @@
         <v>285</v>
       </c>
       <c r="B287" s="3">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>7</v>
@@ -46680,13 +46688,13 @@
         <v>0</v>
       </c>
       <c r="G287" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H287" s="3">
         <v>0</v>
       </c>
       <c r="I287" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J287" s="3">
         <v>0</v>
@@ -46818,10 +46826,10 @@
         <v>286</v>
       </c>
       <c r="B288" s="3">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>7</v>
@@ -46833,13 +46841,13 @@
         <v>0</v>
       </c>
       <c r="G288" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H288" s="3">
         <v>0</v>
       </c>
       <c r="I288" s="3">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J288" s="3">
         <v>0</v>
@@ -46971,16 +46979,16 @@
         <v>287</v>
       </c>
       <c r="B289" s="3">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E289" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F289" s="3">
         <v>0</v>
@@ -47124,28 +47132,28 @@
         <v>288</v>
       </c>
       <c r="B290" s="3">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E290" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F290" s="3">
         <v>0</v>
       </c>
       <c r="G290" s="3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H290" s="3">
         <v>0</v>
       </c>
       <c r="I290" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J290" s="3">
         <v>0</v>
@@ -47223,7 +47231,7 @@
         <v>446</v>
       </c>
       <c r="AI290" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AJ290" s="5" t="s">
         <v>7</v>
@@ -47250,7 +47258,7 @@
         <v>10</v>
       </c>
       <c r="AR290" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS290" s="5">
         <v>0</v>
@@ -47277,28 +47285,28 @@
         <v>289</v>
       </c>
       <c r="B291" s="3">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E291" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F291" s="3">
         <v>0</v>
       </c>
       <c r="G291" s="3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H291" s="3">
         <v>0</v>
       </c>
       <c r="I291" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J291" s="3">
         <v>0</v>
@@ -47376,7 +47384,7 @@
         <v>446</v>
       </c>
       <c r="AI291" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AJ291" s="5" t="s">
         <v>7</v>
@@ -47403,7 +47411,7 @@
         <v>10</v>
       </c>
       <c r="AR291" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS291" s="5">
         <v>0</v>
@@ -47430,28 +47438,28 @@
         <v>290</v>
       </c>
       <c r="B292" s="3">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E292" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F292" s="3">
         <v>0</v>
       </c>
       <c r="G292" s="3">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H292" s="3">
         <v>0</v>
       </c>
       <c r="I292" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J292" s="3">
         <v>0</v>
@@ -47529,7 +47537,7 @@
         <v>446</v>
       </c>
       <c r="AI292" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ292" s="5" t="s">
         <v>7</v>
@@ -47556,7 +47564,7 @@
         <v>10</v>
       </c>
       <c r="AR292" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS292" s="5">
         <v>0</v>
@@ -47577,156 +47585,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="11">
+    <row r="293" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A293" s="3">
         <f t="shared" si="16"/>
         <v>291</v>
       </c>
-      <c r="B293" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C293" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="D293" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E293" s="11">
-        <v>0</v>
-      </c>
-      <c r="F293" s="11">
-        <v>0</v>
-      </c>
-      <c r="G293" s="11">
-        <v>0</v>
-      </c>
-      <c r="H293" s="11">
-        <v>0</v>
-      </c>
-      <c r="I293" s="11">
-        <v>0</v>
-      </c>
-      <c r="J293" s="11">
-        <v>0</v>
-      </c>
-      <c r="K293" s="11">
-        <v>0</v>
-      </c>
-      <c r="L293" s="11">
-        <v>0</v>
-      </c>
-      <c r="M293" s="11">
-        <v>0</v>
-      </c>
-      <c r="N293" s="11">
-        <v>0</v>
-      </c>
-      <c r="O293" s="11">
-        <v>0</v>
-      </c>
-      <c r="P293" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q293" s="11">
-        <v>0</v>
-      </c>
-      <c r="R293" s="11">
-        <v>0</v>
-      </c>
-      <c r="S293" s="11">
-        <v>0</v>
-      </c>
-      <c r="T293" s="11">
-        <v>0</v>
-      </c>
-      <c r="U293" s="11">
-        <v>0</v>
-      </c>
-      <c r="V293" s="11">
-        <v>0</v>
-      </c>
-      <c r="W293" s="11">
-        <v>0</v>
-      </c>
-      <c r="X293" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y293" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z293" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA293" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB293" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK293" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV293" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW293" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX293" s="12">
+      <c r="B293" s="3">
+        <v>1810</v>
+      </c>
+      <c r="C293" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E293" s="3">
+        <v>20</v>
+      </c>
+      <c r="F293" s="3">
+        <v>0</v>
+      </c>
+      <c r="G293" s="3">
+        <v>100</v>
+      </c>
+      <c r="H293" s="3">
+        <v>0</v>
+      </c>
+      <c r="I293" s="3">
+        <v>60</v>
+      </c>
+      <c r="J293" s="3">
+        <v>0</v>
+      </c>
+      <c r="K293" s="3">
+        <v>0</v>
+      </c>
+      <c r="L293" s="3">
+        <v>0</v>
+      </c>
+      <c r="M293" s="3">
+        <v>0</v>
+      </c>
+      <c r="N293" s="3">
+        <v>0</v>
+      </c>
+      <c r="O293" s="3">
+        <v>0</v>
+      </c>
+      <c r="P293" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q293" s="3">
+        <v>55</v>
+      </c>
+      <c r="R293" s="3">
+        <v>0</v>
+      </c>
+      <c r="S293" s="3">
+        <v>0</v>
+      </c>
+      <c r="T293" s="3">
+        <v>0</v>
+      </c>
+      <c r="U293" s="3">
+        <v>0</v>
+      </c>
+      <c r="V293" s="3">
+        <v>0</v>
+      </c>
+      <c r="W293" s="3">
+        <v>0</v>
+      </c>
+      <c r="X293" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y293" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z293" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA293" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB293" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC293" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD293" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE293" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF293" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG293" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH293" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI293" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ293" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK293" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL293" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM293" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN293" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO293" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP293" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ293" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR293" s="5">
+        <v>30</v>
+      </c>
+      <c r="AS293" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT293" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU293" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV293" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW293" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX293" s="5">
         <v>0</v>
       </c>
     </row>
@@ -47736,16 +47744,16 @@
         <v>292</v>
       </c>
       <c r="B294" s="3">
-        <v>1820</v>
+        <v>1811</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E294" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F294" s="3">
         <v>0</v>
@@ -47832,7 +47840,7 @@
         <v>448</v>
       </c>
       <c r="AH294" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI294" s="5" t="s">
         <v>7</v>
@@ -47859,7 +47867,7 @@
         <v>65</v>
       </c>
       <c r="AQ294" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR294" s="5">
         <v>0</v>
@@ -47883,156 +47891,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="3">
+    <row r="295" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="11">
         <f t="shared" si="16"/>
         <v>293</v>
       </c>
-      <c r="B295" s="3">
-        <v>1821</v>
-      </c>
-      <c r="C295" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E295" s="3">
-        <v>50</v>
-      </c>
-      <c r="F295" s="3">
-        <v>0</v>
-      </c>
-      <c r="G295" s="3">
-        <v>55</v>
-      </c>
-      <c r="H295" s="3">
-        <v>0</v>
-      </c>
-      <c r="I295" s="3">
-        <v>30</v>
-      </c>
-      <c r="J295" s="3">
-        <v>0</v>
-      </c>
-      <c r="K295" s="3">
-        <v>0</v>
-      </c>
-      <c r="L295" s="3">
-        <v>0</v>
-      </c>
-      <c r="M295" s="3">
-        <v>0</v>
-      </c>
-      <c r="N295" s="3">
-        <v>0</v>
-      </c>
-      <c r="O295" s="3">
-        <v>0</v>
-      </c>
-      <c r="P295" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q295" s="3">
-        <v>55</v>
-      </c>
-      <c r="R295" s="3">
-        <v>0</v>
-      </c>
-      <c r="S295" s="3">
-        <v>0</v>
-      </c>
-      <c r="T295" s="3">
-        <v>0</v>
-      </c>
-      <c r="U295" s="3">
-        <v>0</v>
-      </c>
-      <c r="V295" s="3">
-        <v>0</v>
-      </c>
-      <c r="W295" s="3">
-        <v>0</v>
-      </c>
-      <c r="X295" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y295" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z295" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA295" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB295" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC295" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD295" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE295" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AF295" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG295" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK295" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL295" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM295" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN295" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO295" s="5">
-        <v>50</v>
-      </c>
-      <c r="AP295" s="5">
-        <v>65</v>
-      </c>
-      <c r="AQ295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV295" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW295" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX295" s="5">
+      <c r="B295" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C295" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="D295" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E295" s="11">
+        <v>0</v>
+      </c>
+      <c r="F295" s="11">
+        <v>0</v>
+      </c>
+      <c r="G295" s="11">
+        <v>0</v>
+      </c>
+      <c r="H295" s="11">
+        <v>0</v>
+      </c>
+      <c r="I295" s="11">
+        <v>0</v>
+      </c>
+      <c r="J295" s="11">
+        <v>0</v>
+      </c>
+      <c r="K295" s="11">
+        <v>0</v>
+      </c>
+      <c r="L295" s="11">
+        <v>0</v>
+      </c>
+      <c r="M295" s="11">
+        <v>0</v>
+      </c>
+      <c r="N295" s="11">
+        <v>0</v>
+      </c>
+      <c r="O295" s="11">
+        <v>0</v>
+      </c>
+      <c r="P295" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q295" s="11">
+        <v>0</v>
+      </c>
+      <c r="R295" s="11">
+        <v>0</v>
+      </c>
+      <c r="S295" s="11">
+        <v>0</v>
+      </c>
+      <c r="T295" s="11">
+        <v>0</v>
+      </c>
+      <c r="U295" s="11">
+        <v>0</v>
+      </c>
+      <c r="V295" s="11">
+        <v>0</v>
+      </c>
+      <c r="W295" s="11">
+        <v>0</v>
+      </c>
+      <c r="X295" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y295" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z295" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA295" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB295" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK295" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV295" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW295" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX295" s="12">
         <v>0</v>
       </c>
     </row>
@@ -48042,16 +48050,16 @@
         <v>294</v>
       </c>
       <c r="B296" s="3">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E296" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F296" s="3">
         <v>0</v>
@@ -48195,16 +48203,16 @@
         <v>295</v>
       </c>
       <c r="B297" s="3">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C297" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D297" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E297" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F297" s="3">
         <v>0</v>
@@ -48348,10 +48356,10 @@
         <v>296</v>
       </c>
       <c r="B298" s="3">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>7</v>
@@ -48501,10 +48509,10 @@
         <v>297</v>
       </c>
       <c r="B299" s="3">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>7</v>
@@ -48654,10 +48662,10 @@
         <v>298</v>
       </c>
       <c r="B300" s="3">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>7</v>
@@ -48801,193 +48809,193 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="11">
-        <f t="shared" si="0"/>
+    <row r="301" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A301" s="3">
+        <f t="shared" si="16"/>
         <v>299</v>
       </c>
-      <c r="B301" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C301" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="D301" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E301" s="11">
-        <v>0</v>
-      </c>
-      <c r="F301" s="11">
-        <v>0</v>
-      </c>
-      <c r="G301" s="11">
-        <v>0</v>
-      </c>
-      <c r="H301" s="11">
-        <v>0</v>
-      </c>
-      <c r="I301" s="11">
-        <v>0</v>
-      </c>
-      <c r="J301" s="11">
-        <v>0</v>
-      </c>
-      <c r="K301" s="11">
-        <v>0</v>
-      </c>
-      <c r="L301" s="11">
-        <v>0</v>
-      </c>
-      <c r="M301" s="11">
-        <v>0</v>
-      </c>
-      <c r="N301" s="11">
-        <v>0</v>
-      </c>
-      <c r="O301" s="11">
-        <v>0</v>
-      </c>
-      <c r="P301" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q301" s="11">
-        <v>0</v>
-      </c>
-      <c r="R301" s="11">
-        <v>0</v>
-      </c>
-      <c r="S301" s="11">
-        <v>0</v>
-      </c>
-      <c r="T301" s="11">
-        <v>0</v>
-      </c>
-      <c r="U301" s="11">
-        <v>0</v>
-      </c>
-      <c r="V301" s="11">
-        <v>0</v>
-      </c>
-      <c r="W301" s="11">
-        <v>0</v>
-      </c>
-      <c r="X301" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y301" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z301" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA301" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB301" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK301" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV301" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW301" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX301" s="12">
+      <c r="B301" s="3">
+        <v>1825</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E301" s="3">
+        <v>30</v>
+      </c>
+      <c r="F301" s="3">
+        <v>0</v>
+      </c>
+      <c r="G301" s="3">
+        <v>55</v>
+      </c>
+      <c r="H301" s="3">
+        <v>0</v>
+      </c>
+      <c r="I301" s="3">
+        <v>30</v>
+      </c>
+      <c r="J301" s="3">
+        <v>0</v>
+      </c>
+      <c r="K301" s="3">
+        <v>0</v>
+      </c>
+      <c r="L301" s="3">
+        <v>0</v>
+      </c>
+      <c r="M301" s="3">
+        <v>0</v>
+      </c>
+      <c r="N301" s="3">
+        <v>0</v>
+      </c>
+      <c r="O301" s="3">
+        <v>0</v>
+      </c>
+      <c r="P301" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q301" s="3">
+        <v>55</v>
+      </c>
+      <c r="R301" s="3">
+        <v>0</v>
+      </c>
+      <c r="S301" s="3">
+        <v>0</v>
+      </c>
+      <c r="T301" s="3">
+        <v>0</v>
+      </c>
+      <c r="U301" s="3">
+        <v>0</v>
+      </c>
+      <c r="V301" s="3">
+        <v>0</v>
+      </c>
+      <c r="W301" s="3">
+        <v>0</v>
+      </c>
+      <c r="X301" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y301" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z301" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA301" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB301" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC301" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD301" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE301" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF301" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG301" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH301" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI301" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ301" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK301" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL301" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM301" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN301" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO301" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP301" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV301" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW301" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX301" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="302" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>300</v>
       </c>
       <c r="B302" s="3">
-        <v>2000</v>
+        <v>1826</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>7</v>
+        <v>437</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>378</v>
+        <v>7</v>
       </c>
       <c r="E302" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F302" s="3">
         <v>0</v>
       </c>
       <c r="G302" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H302" s="3">
         <v>0</v>
       </c>
       <c r="I302" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J302" s="3">
         <v>0</v>
       </c>
       <c r="K302" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L302" s="3">
         <v>0</v>
@@ -49002,85 +49010,85 @@
         <v>0</v>
       </c>
       <c r="P302" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q302" s="3">
+        <v>55</v>
+      </c>
+      <c r="R302" s="3">
+        <v>0</v>
+      </c>
+      <c r="S302" s="3">
+        <v>0</v>
+      </c>
+      <c r="T302" s="3">
+        <v>0</v>
+      </c>
+      <c r="U302" s="3">
+        <v>0</v>
+      </c>
+      <c r="V302" s="3">
+        <v>0</v>
+      </c>
+      <c r="W302" s="3">
+        <v>0</v>
+      </c>
+      <c r="X302" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y302" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z302" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA302" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB302" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC302" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD302" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE302" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF302" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG302" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK302" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL302" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM302" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN302" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO302" s="5">
         <v>50</v>
       </c>
-      <c r="R302" s="3">
-        <v>0</v>
-      </c>
-      <c r="S302" s="3">
-        <v>0</v>
-      </c>
-      <c r="T302" s="3">
-        <v>0</v>
-      </c>
-      <c r="U302" s="3">
-        <v>0</v>
-      </c>
-      <c r="V302" s="3">
-        <v>0</v>
-      </c>
-      <c r="W302" s="3">
-        <v>0</v>
-      </c>
-      <c r="X302" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y302" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z302" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA302" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB302" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK302" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL302" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM302" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN302" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO302" s="5">
-        <v>0</v>
-      </c>
       <c r="AP302" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ302" s="5">
         <v>0</v>
@@ -49098,7 +49106,7 @@
         <v>0</v>
       </c>
       <c r="AV302" s="4" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="AW302" s="5">
         <v>0</v>
@@ -49107,156 +49115,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="3">
+    <row r="303" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="11">
         <f t="shared" si="0"/>
         <v>301</v>
       </c>
-      <c r="B303" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C303" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E303" s="3">
-        <v>0</v>
-      </c>
-      <c r="F303" s="3">
-        <v>0</v>
-      </c>
-      <c r="G303" s="3">
-        <v>60</v>
-      </c>
-      <c r="H303" s="3">
-        <v>0</v>
-      </c>
-      <c r="I303" s="3">
-        <v>0</v>
-      </c>
-      <c r="J303" s="3">
-        <v>0</v>
-      </c>
-      <c r="K303" s="3">
-        <v>100</v>
-      </c>
-      <c r="L303" s="3">
-        <v>0</v>
-      </c>
-      <c r="M303" s="3">
-        <v>0</v>
-      </c>
-      <c r="N303" s="3">
-        <v>0</v>
-      </c>
-      <c r="O303" s="3">
-        <v>0</v>
-      </c>
-      <c r="P303" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q303" s="3">
-        <v>50</v>
-      </c>
-      <c r="R303" s="3">
-        <v>0</v>
-      </c>
-      <c r="S303" s="3">
-        <v>0</v>
-      </c>
-      <c r="T303" s="3">
-        <v>0</v>
-      </c>
-      <c r="U303" s="3">
-        <v>0</v>
-      </c>
-      <c r="V303" s="3">
-        <v>0</v>
-      </c>
-      <c r="W303" s="3">
-        <v>0</v>
-      </c>
-      <c r="X303" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y303" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z303" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA303" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB303" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK303" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV303" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW303" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX303" s="5">
+      <c r="B303" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C303" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D303" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E303" s="11">
+        <v>0</v>
+      </c>
+      <c r="F303" s="11">
+        <v>0</v>
+      </c>
+      <c r="G303" s="11">
+        <v>0</v>
+      </c>
+      <c r="H303" s="11">
+        <v>0</v>
+      </c>
+      <c r="I303" s="11">
+        <v>0</v>
+      </c>
+      <c r="J303" s="11">
+        <v>0</v>
+      </c>
+      <c r="K303" s="11">
+        <v>0</v>
+      </c>
+      <c r="L303" s="11">
+        <v>0</v>
+      </c>
+      <c r="M303" s="11">
+        <v>0</v>
+      </c>
+      <c r="N303" s="11">
+        <v>0</v>
+      </c>
+      <c r="O303" s="11">
+        <v>0</v>
+      </c>
+      <c r="P303" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q303" s="11">
+        <v>0</v>
+      </c>
+      <c r="R303" s="11">
+        <v>0</v>
+      </c>
+      <c r="S303" s="11">
+        <v>0</v>
+      </c>
+      <c r="T303" s="11">
+        <v>0</v>
+      </c>
+      <c r="U303" s="11">
+        <v>0</v>
+      </c>
+      <c r="V303" s="11">
+        <v>0</v>
+      </c>
+      <c r="W303" s="11">
+        <v>0</v>
+      </c>
+      <c r="X303" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y303" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z303" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA303" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB303" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK303" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV303" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW303" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX303" s="12">
         <v>0</v>
       </c>
     </row>
@@ -49266,13 +49274,13 @@
         <v>302</v>
       </c>
       <c r="B304" s="3">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>389</v>
+        <v>7</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>7</v>
+        <v>378</v>
       </c>
       <c r="E304" s="3">
         <v>0</v>
@@ -49281,13 +49289,13 @@
         <v>0</v>
       </c>
       <c r="G304" s="3">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="H304" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I304" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J304" s="3">
         <v>0</v>
@@ -49311,7 +49319,7 @@
         <v>0</v>
       </c>
       <c r="Q304" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R304" s="3">
         <v>0</v>
@@ -49374,28 +49382,28 @@
         <v>7</v>
       </c>
       <c r="AL304" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM304" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN304" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO304" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP304" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ304" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR304" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS304" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT304" s="5">
         <v>0</v>
@@ -49419,13 +49427,13 @@
         <v>303</v>
       </c>
       <c r="B305" s="3">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C305" s="3" t="s">
-        <v>390</v>
+        <v>7</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>7</v>
+        <v>379</v>
       </c>
       <c r="E305" s="3">
         <v>0</v>
@@ -49434,13 +49442,13 @@
         <v>0</v>
       </c>
       <c r="G305" s="3">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="H305" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I305" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J305" s="3">
         <v>0</v>
@@ -49464,7 +49472,7 @@
         <v>0</v>
       </c>
       <c r="Q305" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R305" s="3">
         <v>0</v>
@@ -49527,28 +49535,28 @@
         <v>7</v>
       </c>
       <c r="AL305" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR305" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS305" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT305" s="5">
         <v>0</v>
@@ -49566,156 +49574,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A306" s="11">
+    <row r="306" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A306" s="3">
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
-      <c r="B306" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C306" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="D306" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E306" s="11">
-        <v>0</v>
-      </c>
-      <c r="F306" s="11">
-        <v>0</v>
-      </c>
-      <c r="G306" s="11">
-        <v>0</v>
-      </c>
-      <c r="H306" s="11">
-        <v>0</v>
-      </c>
-      <c r="I306" s="11">
-        <v>0</v>
-      </c>
-      <c r="J306" s="11">
-        <v>0</v>
-      </c>
-      <c r="K306" s="11">
-        <v>0</v>
-      </c>
-      <c r="L306" s="11">
-        <v>0</v>
-      </c>
-      <c r="M306" s="11">
-        <v>0</v>
-      </c>
-      <c r="N306" s="11">
-        <v>0</v>
-      </c>
-      <c r="O306" s="11">
-        <v>0</v>
-      </c>
-      <c r="P306" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q306" s="11">
-        <v>0</v>
-      </c>
-      <c r="R306" s="11">
-        <v>0</v>
-      </c>
-      <c r="S306" s="11">
-        <v>0</v>
-      </c>
-      <c r="T306" s="11">
-        <v>0</v>
-      </c>
-      <c r="U306" s="11">
-        <v>0</v>
-      </c>
-      <c r="V306" s="11">
-        <v>0</v>
-      </c>
-      <c r="W306" s="11">
-        <v>0</v>
-      </c>
-      <c r="X306" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y306" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z306" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA306" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB306" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK306" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV306" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW306" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX306" s="12">
+      <c r="B306" s="3">
+        <v>2002</v>
+      </c>
+      <c r="C306" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E306" s="3">
+        <v>0</v>
+      </c>
+      <c r="F306" s="3">
+        <v>0</v>
+      </c>
+      <c r="G306" s="3">
+        <v>570</v>
+      </c>
+      <c r="H306" s="3">
+        <v>200</v>
+      </c>
+      <c r="I306" s="3">
+        <v>250</v>
+      </c>
+      <c r="J306" s="3">
+        <v>0</v>
+      </c>
+      <c r="K306" s="3">
+        <v>100</v>
+      </c>
+      <c r="L306" s="3">
+        <v>0</v>
+      </c>
+      <c r="M306" s="3">
+        <v>0</v>
+      </c>
+      <c r="N306" s="3">
+        <v>0</v>
+      </c>
+      <c r="O306" s="3">
+        <v>0</v>
+      </c>
+      <c r="P306" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q306" s="3">
+        <v>80</v>
+      </c>
+      <c r="R306" s="3">
+        <v>0</v>
+      </c>
+      <c r="S306" s="3">
+        <v>0</v>
+      </c>
+      <c r="T306" s="3">
+        <v>0</v>
+      </c>
+      <c r="U306" s="3">
+        <v>0</v>
+      </c>
+      <c r="V306" s="3">
+        <v>0</v>
+      </c>
+      <c r="W306" s="3">
+        <v>0</v>
+      </c>
+      <c r="X306" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y306" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z306" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA306" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB306" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK306" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL306" s="5">
+        <v>10</v>
+      </c>
+      <c r="AM306" s="5">
+        <v>20</v>
+      </c>
+      <c r="AN306" s="5">
+        <v>20</v>
+      </c>
+      <c r="AO306" s="5">
+        <v>20</v>
+      </c>
+      <c r="AP306" s="5">
+        <v>20</v>
+      </c>
+      <c r="AQ306" s="5">
+        <v>20</v>
+      </c>
+      <c r="AR306" s="5">
+        <v>20</v>
+      </c>
+      <c r="AS306" s="5">
+        <v>40</v>
+      </c>
+      <c r="AT306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV306" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW306" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX306" s="5">
         <v>0</v>
       </c>
     </row>
@@ -49725,10 +49733,10 @@
         <v>305</v>
       </c>
       <c r="B307" s="3">
-        <v>100000</v>
+        <v>2003</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>7</v>
@@ -49740,19 +49748,19 @@
         <v>0</v>
       </c>
       <c r="G307" s="3">
-        <v>120</v>
+        <v>570</v>
       </c>
       <c r="H307" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I307" s="3">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="J307" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K307" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L307" s="3">
         <v>0</v>
@@ -49770,7 +49778,7 @@
         <v>0</v>
       </c>
       <c r="Q307" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R307" s="3">
         <v>0</v>
@@ -49809,10 +49817,10 @@
         <v>7</v>
       </c>
       <c r="AD307" s="5" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="AE307" s="5" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="AF307" s="5" t="s">
         <v>7</v>
@@ -49833,37 +49841,37 @@
         <v>7</v>
       </c>
       <c r="AL307" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM307" s="5">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AN307" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO307" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP307" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ307" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR307" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS307" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT307" s="5">
         <v>0</v>
       </c>
       <c r="AU307" s="5">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AV307" s="4" t="s">
-        <v>268</v>
+        <v>98</v>
       </c>
       <c r="AW307" s="5">
         <v>0</v>
@@ -49872,156 +49880,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="3">
+    <row r="308" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="11">
         <f t="shared" si="0"/>
         <v>306</v>
       </c>
-      <c r="B308" s="3">
-        <v>100010</v>
-      </c>
-      <c r="C308" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E308" s="3">
-        <v>0</v>
-      </c>
-      <c r="F308" s="3">
-        <v>0</v>
-      </c>
-      <c r="G308" s="3">
-        <v>52</v>
-      </c>
-      <c r="H308" s="3">
-        <v>30</v>
-      </c>
-      <c r="I308" s="3">
-        <v>0</v>
-      </c>
-      <c r="J308" s="3">
-        <v>70</v>
-      </c>
-      <c r="K308" s="3">
-        <v>0</v>
-      </c>
-      <c r="L308" s="3">
-        <v>0</v>
-      </c>
-      <c r="M308" s="3">
-        <v>0</v>
-      </c>
-      <c r="N308" s="3">
-        <v>0</v>
-      </c>
-      <c r="O308" s="3">
-        <v>0</v>
-      </c>
-      <c r="P308" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q308" s="3">
-        <v>80</v>
-      </c>
-      <c r="R308" s="3">
-        <v>0</v>
-      </c>
-      <c r="S308" s="3">
-        <v>0</v>
-      </c>
-      <c r="T308" s="3">
-        <v>0</v>
-      </c>
-      <c r="U308" s="3">
-        <v>0</v>
-      </c>
-      <c r="V308" s="3">
-        <v>0</v>
-      </c>
-      <c r="W308" s="3">
-        <v>0</v>
-      </c>
-      <c r="X308" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y308" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z308" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA308" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB308" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC308" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD308" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE308" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF308" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG308" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH308" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI308" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ308" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK308" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL308" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM308" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN308" s="5">
-        <v>20</v>
-      </c>
-      <c r="AO308" s="5">
-        <v>12</v>
-      </c>
-      <c r="AP308" s="5">
-        <v>12</v>
-      </c>
-      <c r="AQ308" s="5">
-        <v>40</v>
-      </c>
-      <c r="AR308" s="5">
-        <v>10</v>
-      </c>
-      <c r="AS308" s="5">
-        <v>10</v>
-      </c>
-      <c r="AT308" s="5">
-        <v>30</v>
-      </c>
-      <c r="AU308" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV308" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AW308" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX308" s="5">
+      <c r="B308" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C308" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D308" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E308" s="11">
+        <v>0</v>
+      </c>
+      <c r="F308" s="11">
+        <v>0</v>
+      </c>
+      <c r="G308" s="11">
+        <v>0</v>
+      </c>
+      <c r="H308" s="11">
+        <v>0</v>
+      </c>
+      <c r="I308" s="11">
+        <v>0</v>
+      </c>
+      <c r="J308" s="11">
+        <v>0</v>
+      </c>
+      <c r="K308" s="11">
+        <v>0</v>
+      </c>
+      <c r="L308" s="11">
+        <v>0</v>
+      </c>
+      <c r="M308" s="11">
+        <v>0</v>
+      </c>
+      <c r="N308" s="11">
+        <v>0</v>
+      </c>
+      <c r="O308" s="11">
+        <v>0</v>
+      </c>
+      <c r="P308" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q308" s="11">
+        <v>0</v>
+      </c>
+      <c r="R308" s="11">
+        <v>0</v>
+      </c>
+      <c r="S308" s="11">
+        <v>0</v>
+      </c>
+      <c r="T308" s="11">
+        <v>0</v>
+      </c>
+      <c r="U308" s="11">
+        <v>0</v>
+      </c>
+      <c r="V308" s="11">
+        <v>0</v>
+      </c>
+      <c r="W308" s="11">
+        <v>0</v>
+      </c>
+      <c r="X308" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y308" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z308" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB308" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK308" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV308" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW308" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX308" s="12">
         <v>0</v>
       </c>
     </row>
@@ -50031,13 +50039,13 @@
         <v>307</v>
       </c>
       <c r="B309" s="3">
-        <v>100011</v>
+        <v>100000</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>263</v>
+        <v>7</v>
       </c>
       <c r="E309" s="3">
         <v>0</v>
@@ -50046,130 +50054,130 @@
         <v>0</v>
       </c>
       <c r="G309" s="3">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H309" s="3">
+        <v>0</v>
+      </c>
+      <c r="I309" s="3">
+        <v>60</v>
+      </c>
+      <c r="J309" s="3">
+        <v>120</v>
+      </c>
+      <c r="K309" s="3">
+        <v>0</v>
+      </c>
+      <c r="L309" s="3">
+        <v>0</v>
+      </c>
+      <c r="M309" s="3">
+        <v>0</v>
+      </c>
+      <c r="N309" s="3">
+        <v>0</v>
+      </c>
+      <c r="O309" s="3">
+        <v>0</v>
+      </c>
+      <c r="P309" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q309" s="3">
+        <v>50</v>
+      </c>
+      <c r="R309" s="3">
+        <v>0</v>
+      </c>
+      <c r="S309" s="3">
+        <v>0</v>
+      </c>
+      <c r="T309" s="3">
+        <v>0</v>
+      </c>
+      <c r="U309" s="3">
+        <v>0</v>
+      </c>
+      <c r="V309" s="3">
+        <v>0</v>
+      </c>
+      <c r="W309" s="3">
+        <v>0</v>
+      </c>
+      <c r="X309" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y309" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z309" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA309" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB309" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD309" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE309" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK309" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL309" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM309" s="5">
+        <v>60</v>
+      </c>
+      <c r="AN309" s="5">
         <v>30</v>
       </c>
-      <c r="I309" s="3">
-        <v>0</v>
-      </c>
-      <c r="J309" s="3">
-        <v>70</v>
-      </c>
-      <c r="K309" s="3">
-        <v>0</v>
-      </c>
-      <c r="L309" s="3">
-        <v>0</v>
-      </c>
-      <c r="M309" s="3">
-        <v>0</v>
-      </c>
-      <c r="N309" s="3">
-        <v>0</v>
-      </c>
-      <c r="O309" s="3">
-        <v>0</v>
-      </c>
-      <c r="P309" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q309" s="3">
-        <v>80</v>
-      </c>
-      <c r="R309" s="3">
-        <v>0</v>
-      </c>
-      <c r="S309" s="3">
-        <v>0</v>
-      </c>
-      <c r="T309" s="3">
-        <v>0</v>
-      </c>
-      <c r="U309" s="3">
-        <v>0</v>
-      </c>
-      <c r="V309" s="3">
-        <v>0</v>
-      </c>
-      <c r="W309" s="3">
-        <v>0</v>
-      </c>
-      <c r="X309" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y309" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z309" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA309" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB309" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC309" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD309" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE309" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF309" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG309" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH309" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI309" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ309" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK309" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL309" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM309" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN309" s="5">
-        <v>20</v>
-      </c>
       <c r="AO309" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP309" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ309" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AR309" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS309" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT309" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU309" s="5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AV309" s="4" t="s">
-        <v>113</v>
+        <v>268</v>
       </c>
       <c r="AW309" s="5">
         <v>0</v>
@@ -50184,13 +50192,13 @@
         <v>308</v>
       </c>
       <c r="B310" s="3">
-        <v>100020</v>
+        <v>100010</v>
       </c>
       <c r="C310" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>56</v>
+        <v>250</v>
       </c>
       <c r="E310" s="3">
         <v>0</v>
@@ -50199,19 +50207,19 @@
         <v>0</v>
       </c>
       <c r="G310" s="3">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="H310" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I310" s="3">
         <v>0</v>
       </c>
       <c r="J310" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K310" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L310" s="3">
         <v>0</v>
@@ -50229,7 +50237,7 @@
         <v>0</v>
       </c>
       <c r="Q310" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R310" s="3">
         <v>0</v>
@@ -50265,64 +50273,64 @@
         <v>0</v>
       </c>
       <c r="AC310" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD310" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="AD310" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="AE310" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="AF310" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="AG310" s="5" t="s">
-        <v>7</v>
+        <v>255</v>
       </c>
       <c r="AH310" s="5" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="AI310" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ310" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AK310" s="5" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="AL310" s="5">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="AM310" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN310" s="5">
         <v>20</v>
       </c>
       <c r="AO310" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP310" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ310" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AR310" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS310" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT310" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU310" s="5">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AV310" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AW310" s="5">
         <v>0</v>
@@ -50337,13 +50345,13 @@
         <v>309</v>
       </c>
       <c r="B311" s="3">
-        <v>100030</v>
+        <v>100011</v>
       </c>
       <c r="C311" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="E311" s="3">
         <v>0</v>
@@ -50352,19 +50360,19 @@
         <v>0</v>
       </c>
       <c r="G311" s="3">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H311" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I311" s="3">
         <v>0</v>
       </c>
       <c r="J311" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K311" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L311" s="3">
         <v>0</v>
@@ -50382,7 +50390,7 @@
         <v>0</v>
       </c>
       <c r="Q311" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R311" s="3">
         <v>0</v>
@@ -50418,64 +50426,64 @@
         <v>0</v>
       </c>
       <c r="AC311" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AD311" s="5" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="AE311" s="5" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="AF311" s="5" t="s">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="AG311" s="5" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="AH311" s="5" t="s">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="AI311" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AJ311" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AK311" s="5" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="AL311" s="5">
-        <v>30</v>
+        <v>-50</v>
       </c>
       <c r="AM311" s="5">
         <v>30</v>
       </c>
       <c r="AN311" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO311" s="5">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AP311" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ311" s="5">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AR311" s="5">
         <v>10</v>
       </c>
       <c r="AS311" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT311" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU311" s="5">
         <v>0</v>
       </c>
       <c r="AV311" s="4" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="AW311" s="5">
         <v>0</v>
@@ -50486,17 +50494,17 @@
     </row>
     <row r="312" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="3">
-        <f t="shared" ref="A312" si="17">ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>310</v>
       </c>
       <c r="B312" s="3">
-        <v>100040</v>
+        <v>100020</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E312" s="3">
         <v>0</v>
@@ -50505,7 +50513,7 @@
         <v>0</v>
       </c>
       <c r="G312" s="3">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="H312" s="3">
         <v>0</v>
@@ -50514,10 +50522,10 @@
         <v>0</v>
       </c>
       <c r="J312" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K312" s="3">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L312" s="3">
         <v>0</v>
@@ -50535,7 +50543,7 @@
         <v>0</v>
       </c>
       <c r="Q312" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R312" s="3">
         <v>0</v>
@@ -50571,22 +50579,22 @@
         <v>0</v>
       </c>
       <c r="AC312" s="5" t="s">
-        <v>34</v>
+        <v>254</v>
       </c>
       <c r="AD312" s="5" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="AE312" s="5" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="AF312" s="5" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="AG312" s="5" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="AH312" s="5" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="AI312" s="5" t="s">
         <v>7</v>
@@ -50598,22 +50606,22 @@
         <v>7</v>
       </c>
       <c r="AL312" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AM312" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN312" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AO312" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP312" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ312" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR312" s="5">
         <v>0</v>
@@ -50625,10 +50633,10 @@
         <v>0</v>
       </c>
       <c r="AU312" s="5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AV312" s="4" t="s">
-        <v>440</v>
+        <v>116</v>
       </c>
       <c r="AW312" s="5">
         <v>0</v>
@@ -50643,150 +50651,456 @@
         <v>311</v>
       </c>
       <c r="B313" s="3">
+        <v>100030</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E313" s="3">
+        <v>0</v>
+      </c>
+      <c r="F313" s="3">
+        <v>0</v>
+      </c>
+      <c r="G313" s="3">
+        <v>120</v>
+      </c>
+      <c r="H313" s="3">
+        <v>0</v>
+      </c>
+      <c r="I313" s="3">
+        <v>0</v>
+      </c>
+      <c r="J313" s="3">
+        <v>0</v>
+      </c>
+      <c r="K313" s="3">
+        <v>70</v>
+      </c>
+      <c r="L313" s="3">
+        <v>0</v>
+      </c>
+      <c r="M313" s="3">
+        <v>0</v>
+      </c>
+      <c r="N313" s="3">
+        <v>0</v>
+      </c>
+      <c r="O313" s="3">
+        <v>0</v>
+      </c>
+      <c r="P313" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q313" s="3">
+        <v>70</v>
+      </c>
+      <c r="R313" s="3">
+        <v>0</v>
+      </c>
+      <c r="S313" s="3">
+        <v>0</v>
+      </c>
+      <c r="T313" s="3">
+        <v>0</v>
+      </c>
+      <c r="U313" s="3">
+        <v>0</v>
+      </c>
+      <c r="V313" s="3">
+        <v>0</v>
+      </c>
+      <c r="W313" s="3">
+        <v>0</v>
+      </c>
+      <c r="X313" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y313" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z313" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA313" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB313" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC313" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD313" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AE313" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF313" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG313" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH313" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI313" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ313" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK313" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL313" s="5">
+        <v>30</v>
+      </c>
+      <c r="AM313" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN313" s="5">
+        <v>30</v>
+      </c>
+      <c r="AO313" s="5">
+        <v>30</v>
+      </c>
+      <c r="AP313" s="5">
+        <v>10</v>
+      </c>
+      <c r="AQ313" s="5">
+        <v>15</v>
+      </c>
+      <c r="AR313" s="5">
+        <v>10</v>
+      </c>
+      <c r="AS313" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT313" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU313" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV313" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW313" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX313" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A314" s="3">
+        <f t="shared" ref="A314" si="17">ROW()-2</f>
+        <v>312</v>
+      </c>
+      <c r="B314" s="3">
+        <v>100040</v>
+      </c>
+      <c r="C314" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E314" s="3">
+        <v>0</v>
+      </c>
+      <c r="F314" s="3">
+        <v>0</v>
+      </c>
+      <c r="G314" s="3">
+        <v>32</v>
+      </c>
+      <c r="H314" s="3">
+        <v>0</v>
+      </c>
+      <c r="I314" s="3">
+        <v>0</v>
+      </c>
+      <c r="J314" s="3">
+        <v>60</v>
+      </c>
+      <c r="K314" s="3">
+        <v>0</v>
+      </c>
+      <c r="L314" s="3">
+        <v>0</v>
+      </c>
+      <c r="M314" s="3">
+        <v>0</v>
+      </c>
+      <c r="N314" s="3">
+        <v>0</v>
+      </c>
+      <c r="O314" s="3">
+        <v>0</v>
+      </c>
+      <c r="P314" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q314" s="3">
+        <v>50</v>
+      </c>
+      <c r="R314" s="3">
+        <v>0</v>
+      </c>
+      <c r="S314" s="3">
+        <v>0</v>
+      </c>
+      <c r="T314" s="3">
+        <v>0</v>
+      </c>
+      <c r="U314" s="3">
+        <v>0</v>
+      </c>
+      <c r="V314" s="3">
+        <v>0</v>
+      </c>
+      <c r="W314" s="3">
+        <v>0</v>
+      </c>
+      <c r="X314" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y314" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z314" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA314" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB314" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC314" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD314" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE314" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF314" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG314" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH314" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI314" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ314" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK314" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL314" s="5">
+        <v>5</v>
+      </c>
+      <c r="AM314" s="5">
+        <v>10</v>
+      </c>
+      <c r="AN314" s="5">
+        <v>12</v>
+      </c>
+      <c r="AO314" s="5">
+        <v>20</v>
+      </c>
+      <c r="AP314" s="5">
+        <v>5</v>
+      </c>
+      <c r="AQ314" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR314" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS314" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT314" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU314" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV314" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="AW314" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX314" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A315" s="3">
+        <f t="shared" si="0"/>
+        <v>313</v>
+      </c>
+      <c r="B315" s="3">
         <v>999999</v>
       </c>
-      <c r="C313" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D313" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E313" s="3">
-        <v>0</v>
-      </c>
-      <c r="F313" s="3">
-        <v>0</v>
-      </c>
-      <c r="G313" s="3">
-        <v>0</v>
-      </c>
-      <c r="H313" s="3">
-        <v>0</v>
-      </c>
-      <c r="I313" s="3">
-        <v>0</v>
-      </c>
-      <c r="J313" s="3">
-        <v>0</v>
-      </c>
-      <c r="K313" s="3">
-        <v>0</v>
-      </c>
-      <c r="L313" s="3">
-        <v>0</v>
-      </c>
-      <c r="M313" s="3">
-        <v>0</v>
-      </c>
-      <c r="N313" s="3">
-        <v>0</v>
-      </c>
-      <c r="O313" s="3">
-        <v>0</v>
-      </c>
-      <c r="P313" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q313" s="3">
-        <v>0</v>
-      </c>
-      <c r="R313" s="3">
-        <v>0</v>
-      </c>
-      <c r="S313" s="3">
-        <v>0</v>
-      </c>
-      <c r="T313" s="3">
-        <v>0</v>
-      </c>
-      <c r="U313" s="3">
-        <v>0</v>
-      </c>
-      <c r="V313" s="3">
-        <v>0</v>
-      </c>
-      <c r="W313" s="3">
-        <v>0</v>
-      </c>
-      <c r="X313" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y313" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z313" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA313" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB313" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK313" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV313" s="4" t="s">
+      <c r="C315" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E315" s="3">
+        <v>0</v>
+      </c>
+      <c r="F315" s="3">
+        <v>0</v>
+      </c>
+      <c r="G315" s="3">
+        <v>0</v>
+      </c>
+      <c r="H315" s="3">
+        <v>0</v>
+      </c>
+      <c r="I315" s="3">
+        <v>0</v>
+      </c>
+      <c r="J315" s="3">
+        <v>0</v>
+      </c>
+      <c r="K315" s="3">
+        <v>0</v>
+      </c>
+      <c r="L315" s="3">
+        <v>0</v>
+      </c>
+      <c r="M315" s="3">
+        <v>0</v>
+      </c>
+      <c r="N315" s="3">
+        <v>0</v>
+      </c>
+      <c r="O315" s="3">
+        <v>0</v>
+      </c>
+      <c r="P315" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q315" s="3">
+        <v>0</v>
+      </c>
+      <c r="R315" s="3">
+        <v>0</v>
+      </c>
+      <c r="S315" s="3">
+        <v>0</v>
+      </c>
+      <c r="T315" s="3">
+        <v>0</v>
+      </c>
+      <c r="U315" s="3">
+        <v>0</v>
+      </c>
+      <c r="V315" s="3">
+        <v>0</v>
+      </c>
+      <c r="W315" s="3">
+        <v>0</v>
+      </c>
+      <c r="X315" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y315" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z315" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA315" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB315" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV315" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AW313" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX313" s="5">
+      <c r="AW315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX315" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5984F1E1-B40F-4854-8FC0-9F214BCD6D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E649263-5CA4-47B9-AE69-DCA8D947E4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="960" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -34241,10 +34241,10 @@
         <v>15</v>
       </c>
       <c r="AN205" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO205" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP205" s="5">
         <v>55</v>
@@ -34394,10 +34394,10 @@
         <v>15</v>
       </c>
       <c r="AN206" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO206" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP206" s="5">
         <v>55</v>
@@ -34547,10 +34547,10 @@
         <v>15</v>
       </c>
       <c r="AN207" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO207" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP207" s="5">
         <v>55</v>
@@ -34700,10 +34700,10 @@
         <v>15</v>
       </c>
       <c r="AN208" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO208" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP208" s="5">
         <v>55</v>
@@ -34853,10 +34853,10 @@
         <v>15</v>
       </c>
       <c r="AN209" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO209" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP209" s="5">
         <v>55</v>
@@ -35006,10 +35006,10 @@
         <v>15</v>
       </c>
       <c r="AN210" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO210" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP210" s="5">
         <v>55</v>
@@ -35159,10 +35159,10 @@
         <v>15</v>
       </c>
       <c r="AN211" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO211" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP211" s="5">
         <v>55</v>
@@ -35312,10 +35312,10 @@
         <v>15</v>
       </c>
       <c r="AN212" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO212" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP212" s="5">
         <v>55</v>
@@ -35465,10 +35465,10 @@
         <v>15</v>
       </c>
       <c r="AN213" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO213" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP213" s="5">
         <v>55</v>
@@ -35618,10 +35618,10 @@
         <v>15</v>
       </c>
       <c r="AN214" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO214" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP214" s="5">
         <v>55</v>
@@ -35771,10 +35771,10 @@
         <v>15</v>
       </c>
       <c r="AN215" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO215" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP215" s="5">
         <v>55</v>
@@ -35924,10 +35924,10 @@
         <v>15</v>
       </c>
       <c r="AN216" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO216" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP216" s="5">
         <v>55</v>
@@ -36077,10 +36077,10 @@
         <v>10</v>
       </c>
       <c r="AN217" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO217" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP217" s="5">
         <v>55</v>
@@ -36230,10 +36230,10 @@
         <v>0</v>
       </c>
       <c r="AN218" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO218" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP218" s="5">
         <v>55</v>
@@ -36383,10 +36383,10 @@
         <v>15</v>
       </c>
       <c r="AN219" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO219" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP219" s="5">
         <v>55</v>
@@ -41432,13 +41432,13 @@
         <v>15</v>
       </c>
       <c r="AN252" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO252" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP252" s="5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AQ252" s="5">
         <v>0</v>
@@ -41585,13 +41585,13 @@
         <v>15</v>
       </c>
       <c r="AN253" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO253" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP253" s="5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AQ253" s="5">
         <v>0</v>
@@ -41738,13 +41738,13 @@
         <v>15</v>
       </c>
       <c r="AN254" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO254" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP254" s="5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AQ254" s="5">
         <v>0</v>
@@ -41891,13 +41891,13 @@
         <v>15</v>
       </c>
       <c r="AN255" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO255" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP255" s="5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AQ255" s="5">
         <v>0</v>
@@ -42044,13 +42044,13 @@
         <v>15</v>
       </c>
       <c r="AN256" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO256" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP256" s="5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AQ256" s="5">
         <v>30</v>
@@ -42197,13 +42197,13 @@
         <v>15</v>
       </c>
       <c r="AN257" s="5">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AO257" s="5">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AP257" s="5">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AQ257" s="5">
         <v>0</v>
@@ -43937,7 +43937,7 @@
         <v>80</v>
       </c>
       <c r="H269" s="3">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="I269" s="3">
         <v>0</v>
@@ -44243,7 +44243,7 @@
         <v>80</v>
       </c>
       <c r="H271" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I271" s="3">
         <v>0</v>
@@ -44549,7 +44549,7 @@
         <v>80</v>
       </c>
       <c r="H273" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I273" s="3">
         <v>0</v>
@@ -44702,7 +44702,7 @@
         <v>80</v>
       </c>
       <c r="H274" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I274" s="3">
         <v>0</v>
@@ -45008,7 +45008,7 @@
         <v>80</v>
       </c>
       <c r="H276" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I276" s="3">
         <v>0</v>
@@ -45311,10 +45311,10 @@
         <v>0</v>
       </c>
       <c r="G278" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H278" s="3">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I278" s="3">
         <v>0</v>
@@ -45362,7 +45362,7 @@
         <v>0</v>
       </c>
       <c r="X278" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y278" s="3">
         <v>0</v>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="G279" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H279" s="3">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I279" s="3">
         <v>0</v>
@@ -45515,7 +45515,7 @@
         <v>0</v>
       </c>
       <c r="X279" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y279" s="3">
         <v>0</v>
@@ -45620,7 +45620,7 @@
         <v>80</v>
       </c>
       <c r="H280" s="3">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="I280" s="3">
         <v>0</v>
@@ -45773,7 +45773,7 @@
         <v>80</v>
       </c>
       <c r="H281" s="3">
-        <v>230</v>
+        <v>120</v>
       </c>
       <c r="I281" s="3">
         <v>0</v>
@@ -46184,7 +46184,7 @@
         <v>65</v>
       </c>
       <c r="AQ283" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR283" s="5">
         <v>0</v>
@@ -46337,7 +46337,7 @@
         <v>65</v>
       </c>
       <c r="AQ284" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR284" s="5">
         <v>0</v>
@@ -46490,7 +46490,7 @@
         <v>65</v>
       </c>
       <c r="AQ285" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR285" s="5">
         <v>0</v>
@@ -46643,7 +46643,7 @@
         <v>65</v>
       </c>
       <c r="AQ286" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR286" s="5">
         <v>0</v>
@@ -46796,7 +46796,7 @@
         <v>65</v>
       </c>
       <c r="AQ287" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR287" s="5">
         <v>0</v>
@@ -46949,7 +46949,7 @@
         <v>65</v>
       </c>
       <c r="AQ288" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR288" s="5">
         <v>0</v>
@@ -47102,7 +47102,7 @@
         <v>65</v>
       </c>
       <c r="AQ289" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR289" s="5">
         <v>0</v>
@@ -47255,7 +47255,7 @@
         <v>65</v>
       </c>
       <c r="AQ290" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR290" s="5">
         <v>0</v>
@@ -47408,7 +47408,7 @@
         <v>65</v>
       </c>
       <c r="AQ291" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR291" s="5">
         <v>0</v>
@@ -47561,7 +47561,7 @@
         <v>65</v>
       </c>
       <c r="AQ292" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR292" s="5">
         <v>30</v>
@@ -47714,7 +47714,7 @@
         <v>65</v>
       </c>
       <c r="AQ293" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR293" s="5">
         <v>30</v>
@@ -47867,7 +47867,7 @@
         <v>65</v>
       </c>
       <c r="AQ294" s="5">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="AR294" s="5">
         <v>0</v>
@@ -48146,7 +48146,7 @@
         <v>448</v>
       </c>
       <c r="AH296" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI296" s="5" t="s">
         <v>7</v>
@@ -48173,7 +48173,7 @@
         <v>65</v>
       </c>
       <c r="AQ296" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR296" s="5">
         <v>0</v>
@@ -48299,7 +48299,7 @@
         <v>448</v>
       </c>
       <c r="AH297" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI297" s="5" t="s">
         <v>7</v>
@@ -48326,7 +48326,7 @@
         <v>65</v>
       </c>
       <c r="AQ297" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR297" s="5">
         <v>0</v>
@@ -48452,7 +48452,7 @@
         <v>448</v>
       </c>
       <c r="AH298" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI298" s="5" t="s">
         <v>7</v>
@@ -48479,7 +48479,7 @@
         <v>65</v>
       </c>
       <c r="AQ298" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR298" s="5">
         <v>0</v>
@@ -48605,7 +48605,7 @@
         <v>448</v>
       </c>
       <c r="AH299" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI299" s="5" t="s">
         <v>7</v>
@@ -48632,7 +48632,7 @@
         <v>65</v>
       </c>
       <c r="AQ299" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR299" s="5">
         <v>0</v>
@@ -48758,7 +48758,7 @@
         <v>448</v>
       </c>
       <c r="AH300" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI300" s="5" t="s">
         <v>7</v>
@@ -48785,7 +48785,7 @@
         <v>65</v>
       </c>
       <c r="AQ300" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR300" s="5">
         <v>0</v>
@@ -48911,7 +48911,7 @@
         <v>448</v>
       </c>
       <c r="AH301" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI301" s="5" t="s">
         <v>7</v>
@@ -48938,7 +48938,7 @@
         <v>65</v>
       </c>
       <c r="AQ301" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR301" s="5">
         <v>0</v>
@@ -49064,7 +49064,7 @@
         <v>448</v>
       </c>
       <c r="AH302" s="5" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="AI302" s="5" t="s">
         <v>7</v>
@@ -49091,7 +49091,7 @@
         <v>65</v>
       </c>
       <c r="AQ302" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR302" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E649263-5CA4-47B9-AE69-DCA8D947E4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2B232C-1908-4C3A-84A6-5C20FD67ECF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1815" yWindow="960" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="915" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3818" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3842" uniqueCount="461">
   <si>
     <t>desc</t>
   </si>
@@ -2456,6 +2456,14 @@
     <t>figure_bear_whitechoco</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>chocolate_white</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>chocolate_ruby</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -2886,7 +2894,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AX315"/>
+  <dimension ref="A1:AX317"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -3064,7 +3072,7 @@
     </row>
     <row r="2" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A315" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A317" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -13259,13 +13267,13 @@
         <v>256</v>
       </c>
       <c r="AG68" s="5" t="s">
-        <v>7</v>
+        <v>254</v>
       </c>
       <c r="AH68" s="5" t="s">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="AI68" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AJ68" s="5" t="s">
         <v>7</v>
@@ -13277,22 +13285,22 @@
         <v>10</v>
       </c>
       <c r="AM68" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AN68" s="5">
         <v>30</v>
       </c>
       <c r="AO68" s="5">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AP68" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ68" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR68" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS68" s="5">
         <v>0</v>
@@ -43915,7 +43923,7 @@
     </row>
     <row r="269" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="3">
-        <f t="shared" ref="A269:A302" si="16">ROW()-2</f>
+        <f t="shared" ref="A269:A304" si="16">ROW()-2</f>
         <v>267</v>
       </c>
       <c r="B269" s="3">
@@ -44378,16 +44386,16 @@
         <v>270</v>
       </c>
       <c r="B272" s="3">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="C272" s="3" t="s">
-        <v>401</v>
+        <v>460</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E272" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F272" s="3">
         <v>0</v>
@@ -44396,7 +44404,7 @@
         <v>80</v>
       </c>
       <c r="H272" s="3">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="I272" s="3">
         <v>0</v>
@@ -44432,10 +44440,10 @@
         <v>0</v>
       </c>
       <c r="T272" s="3">
+        <v>0</v>
+      </c>
+      <c r="U272" s="3">
         <v>10</v>
-      </c>
-      <c r="U272" s="3">
-        <v>0</v>
       </c>
       <c r="V272" s="3">
         <v>0</v>
@@ -44531,13 +44539,13 @@
         <v>271</v>
       </c>
       <c r="B273" s="3">
-        <v>1710</v>
+        <v>1704</v>
       </c>
       <c r="C273" s="3" t="s">
-        <v>7</v>
+        <v>459</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>395</v>
+        <v>7</v>
       </c>
       <c r="E273" s="3">
         <v>0</v>
@@ -44561,7 +44569,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="3">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="M273" s="3">
         <v>0</v>
@@ -44582,28 +44590,28 @@
         <v>0</v>
       </c>
       <c r="S273" s="3">
+        <v>0</v>
+      </c>
+      <c r="T273" s="3">
+        <v>0</v>
+      </c>
+      <c r="U273" s="3">
+        <v>0</v>
+      </c>
+      <c r="V273" s="3">
+        <v>0</v>
+      </c>
+      <c r="W273" s="3">
+        <v>0</v>
+      </c>
+      <c r="X273" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y273" s="3">
         <v>10</v>
       </c>
-      <c r="T273" s="3">
-        <v>0</v>
-      </c>
-      <c r="U273" s="3">
-        <v>0</v>
-      </c>
-      <c r="V273" s="3">
-        <v>0</v>
-      </c>
-      <c r="W273" s="3">
-        <v>0</v>
-      </c>
-      <c r="X273" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y273" s="3">
-        <v>0</v>
-      </c>
       <c r="Z273" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA273" s="3">
         <v>0</v>
@@ -44684,16 +44692,16 @@
         <v>272</v>
       </c>
       <c r="B274" s="3">
-        <v>1711</v>
+        <v>1705</v>
       </c>
       <c r="C274" s="3" t="s">
-        <v>7</v>
+        <v>401</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>396</v>
+        <v>7</v>
       </c>
       <c r="E274" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F274" s="3">
         <v>0</v>
@@ -44702,7 +44710,7 @@
         <v>80</v>
       </c>
       <c r="H274" s="3">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="I274" s="3">
         <v>0</v>
@@ -44738,7 +44746,7 @@
         <v>0</v>
       </c>
       <c r="T274" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U274" s="3">
         <v>0</v>
@@ -44837,13 +44845,13 @@
         <v>273</v>
       </c>
       <c r="B275" s="3">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="C275" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E275" s="3">
         <v>0</v>
@@ -44852,7 +44860,7 @@
         <v>0</v>
       </c>
       <c r="G275" s="3">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="H275" s="3">
         <v>150</v>
@@ -44867,7 +44875,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="3">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="M275" s="3">
         <v>0</v>
@@ -44888,28 +44896,28 @@
         <v>0</v>
       </c>
       <c r="S275" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T275" s="3">
         <v>0</v>
       </c>
       <c r="U275" s="3">
+        <v>0</v>
+      </c>
+      <c r="V275" s="3">
+        <v>0</v>
+      </c>
+      <c r="W275" s="3">
+        <v>0</v>
+      </c>
+      <c r="X275" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y275" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z275" s="3">
         <v>10</v>
-      </c>
-      <c r="V275" s="3">
-        <v>0</v>
-      </c>
-      <c r="W275" s="3">
-        <v>0</v>
-      </c>
-      <c r="X275" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y275" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z275" s="3">
-        <v>0</v>
       </c>
       <c r="AA275" s="3">
         <v>0</v>
@@ -44990,13 +44998,13 @@
         <v>274</v>
       </c>
       <c r="B276" s="3">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E276" s="3">
         <v>0</v>
@@ -45020,7 +45028,7 @@
         <v>0</v>
       </c>
       <c r="L276" s="3">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="M276" s="3">
         <v>0</v>
@@ -45062,7 +45070,7 @@
         <v>0</v>
       </c>
       <c r="Z276" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA276" s="3">
         <v>0</v>
@@ -45143,22 +45151,22 @@
         <v>275</v>
       </c>
       <c r="B277" s="3">
-        <v>1720</v>
+        <v>1712</v>
       </c>
       <c r="C277" s="3" t="s">
-        <v>402</v>
+        <v>7</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>7</v>
+        <v>397</v>
       </c>
       <c r="E277" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F277" s="3">
         <v>0</v>
       </c>
       <c r="G277" s="3">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="H277" s="3">
         <v>150</v>
@@ -45200,7 +45208,7 @@
         <v>0</v>
       </c>
       <c r="U277" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V277" s="3">
         <v>0</v>
@@ -45224,7 +45232,7 @@
         <v>0</v>
       </c>
       <c r="AC277" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AD277" s="5" t="s">
         <v>7</v>
@@ -45296,13 +45304,13 @@
         <v>276</v>
       </c>
       <c r="B278" s="3">
-        <v>1730</v>
+        <v>1713</v>
       </c>
       <c r="C278" s="3" t="s">
-        <v>403</v>
+        <v>7</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>7</v>
+        <v>398</v>
       </c>
       <c r="E278" s="3">
         <v>0</v>
@@ -45311,10 +45319,10 @@
         <v>0</v>
       </c>
       <c r="G278" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H278" s="3">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I278" s="3">
         <v>0</v>
@@ -45326,7 +45334,7 @@
         <v>0</v>
       </c>
       <c r="L278" s="3">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="M278" s="3">
         <v>0</v>
@@ -45362,13 +45370,13 @@
         <v>0</v>
       </c>
       <c r="X278" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y278" s="3">
         <v>0</v>
       </c>
       <c r="Z278" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA278" s="3">
         <v>0</v>
@@ -45377,7 +45385,7 @@
         <v>0</v>
       </c>
       <c r="AC278" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AD278" s="5" t="s">
         <v>7</v>
@@ -45449,25 +45457,25 @@
         <v>277</v>
       </c>
       <c r="B279" s="3">
-        <v>1731</v>
+        <v>1720</v>
       </c>
       <c r="C279" s="3" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E279" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F279" s="3">
         <v>0</v>
       </c>
       <c r="G279" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="H279" s="3">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="I279" s="3">
         <v>0</v>
@@ -45479,7 +45487,7 @@
         <v>0</v>
       </c>
       <c r="L279" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M279" s="3">
         <v>0</v>
@@ -45515,7 +45523,7 @@
         <v>0</v>
       </c>
       <c r="X279" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y279" s="3">
         <v>0</v>
@@ -45602,10 +45610,10 @@
         <v>278</v>
       </c>
       <c r="B280" s="3">
-        <v>1740</v>
+        <v>1730</v>
       </c>
       <c r="C280" s="3" t="s">
-        <v>457</v>
+        <v>403</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>7</v>
@@ -45617,10 +45625,10 @@
         <v>0</v>
       </c>
       <c r="G280" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H280" s="3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I280" s="3">
         <v>0</v>
@@ -45632,7 +45640,7 @@
         <v>0</v>
       </c>
       <c r="L280" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M280" s="3">
         <v>0</v>
@@ -45668,7 +45676,7 @@
         <v>0</v>
       </c>
       <c r="X280" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y280" s="3">
         <v>0</v>
@@ -45683,7 +45691,7 @@
         <v>0</v>
       </c>
       <c r="AC280" s="5" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="AD280" s="5" t="s">
         <v>7</v>
@@ -45755,10 +45763,10 @@
         <v>279</v>
       </c>
       <c r="B281" s="3">
-        <v>1741</v>
+        <v>1731</v>
       </c>
       <c r="C281" s="3" t="s">
-        <v>458</v>
+        <v>404</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>7</v>
@@ -45770,10 +45778,10 @@
         <v>0</v>
       </c>
       <c r="G281" s="3">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H281" s="3">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="I281" s="3">
         <v>0</v>
@@ -45785,7 +45793,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="M281" s="3">
         <v>0</v>
@@ -45821,7 +45829,7 @@
         <v>0</v>
       </c>
       <c r="X281" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y281" s="3">
         <v>0</v>
@@ -45836,7 +45844,7 @@
         <v>0</v>
       </c>
       <c r="AC281" s="5" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="AD281" s="5" t="s">
         <v>7</v>
@@ -45902,156 +45910,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="11">
+    <row r="282" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A282" s="3">
         <f t="shared" si="16"/>
         <v>280</v>
       </c>
-      <c r="B282" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C282" s="11" t="s">
-        <v>418</v>
-      </c>
-      <c r="D282" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E282" s="11">
-        <v>0</v>
-      </c>
-      <c r="F282" s="11">
-        <v>0</v>
-      </c>
-      <c r="G282" s="11">
-        <v>0</v>
-      </c>
-      <c r="H282" s="11">
-        <v>0</v>
-      </c>
-      <c r="I282" s="11">
-        <v>0</v>
-      </c>
-      <c r="J282" s="11">
-        <v>0</v>
-      </c>
-      <c r="K282" s="11">
-        <v>0</v>
-      </c>
-      <c r="L282" s="11">
-        <v>0</v>
-      </c>
-      <c r="M282" s="11">
-        <v>0</v>
-      </c>
-      <c r="N282" s="11">
-        <v>0</v>
-      </c>
-      <c r="O282" s="11">
-        <v>0</v>
-      </c>
-      <c r="P282" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q282" s="11">
-        <v>0</v>
-      </c>
-      <c r="R282" s="11">
-        <v>0</v>
-      </c>
-      <c r="S282" s="11">
-        <v>0</v>
-      </c>
-      <c r="T282" s="11">
-        <v>0</v>
-      </c>
-      <c r="U282" s="11">
-        <v>0</v>
-      </c>
-      <c r="V282" s="11">
-        <v>0</v>
-      </c>
-      <c r="W282" s="11">
-        <v>0</v>
-      </c>
-      <c r="X282" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y282" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z282" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA282" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB282" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK282" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV282" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW282" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX282" s="12">
+      <c r="B282" s="3">
+        <v>1740</v>
+      </c>
+      <c r="C282" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E282" s="3">
+        <v>0</v>
+      </c>
+      <c r="F282" s="3">
+        <v>0</v>
+      </c>
+      <c r="G282" s="3">
+        <v>80</v>
+      </c>
+      <c r="H282" s="3">
+        <v>120</v>
+      </c>
+      <c r="I282" s="3">
+        <v>0</v>
+      </c>
+      <c r="J282" s="3">
+        <v>0</v>
+      </c>
+      <c r="K282" s="3">
+        <v>0</v>
+      </c>
+      <c r="L282" s="3">
+        <v>70</v>
+      </c>
+      <c r="M282" s="3">
+        <v>0</v>
+      </c>
+      <c r="N282" s="3">
+        <v>0</v>
+      </c>
+      <c r="O282" s="3">
+        <v>0</v>
+      </c>
+      <c r="P282" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q282" s="3">
+        <v>50</v>
+      </c>
+      <c r="R282" s="3">
+        <v>0</v>
+      </c>
+      <c r="S282" s="3">
+        <v>0</v>
+      </c>
+      <c r="T282" s="3">
+        <v>0</v>
+      </c>
+      <c r="U282" s="3">
+        <v>0</v>
+      </c>
+      <c r="V282" s="3">
+        <v>0</v>
+      </c>
+      <c r="W282" s="3">
+        <v>0</v>
+      </c>
+      <c r="X282" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y282" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB282" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC282" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK282" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL282" s="5">
+        <v>20</v>
+      </c>
+      <c r="AM282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV282" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW282" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX282" s="5">
         <v>0</v>
       </c>
     </row>
@@ -46061,10 +46069,10 @@
         <v>281</v>
       </c>
       <c r="B283" s="3">
-        <v>1800</v>
+        <v>1741</v>
       </c>
       <c r="C283" s="3" t="s">
-        <v>419</v>
+        <v>458</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>7</v>
@@ -46076,13 +46084,13 @@
         <v>0</v>
       </c>
       <c r="G283" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H283" s="3">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I283" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J283" s="3">
         <v>0</v>
@@ -46091,7 +46099,7 @@
         <v>0</v>
       </c>
       <c r="L283" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M283" s="3">
         <v>0</v>
@@ -46103,10 +46111,10 @@
         <v>0</v>
       </c>
       <c r="P283" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q283" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="R283" s="3">
         <v>0</v>
@@ -46142,22 +46150,22 @@
         <v>0</v>
       </c>
       <c r="AC283" s="5" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="AD283" s="5" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="AE283" s="5" t="s">
-        <v>298</v>
+        <v>7</v>
       </c>
       <c r="AF283" s="5" t="s">
-        <v>447</v>
+        <v>7</v>
       </c>
       <c r="AG283" s="5" t="s">
-        <v>448</v>
+        <v>7</v>
       </c>
       <c r="AH283" s="5" t="s">
-        <v>446</v>
+        <v>7</v>
       </c>
       <c r="AI283" s="5" t="s">
         <v>7</v>
@@ -46169,22 +46177,22 @@
         <v>7</v>
       </c>
       <c r="AL283" s="5">
-        <v>-50</v>
+        <v>20</v>
       </c>
       <c r="AM283" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AN283" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AO283" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AP283" s="5">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AQ283" s="5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AR283" s="5">
         <v>0</v>
@@ -46199,7 +46207,7 @@
         <v>0</v>
       </c>
       <c r="AV283" s="4" t="s">
-        <v>214</v>
+        <v>392</v>
       </c>
       <c r="AW283" s="5">
         <v>0</v>
@@ -46208,156 +46216,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="3">
+    <row r="284" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A284" s="11">
         <f t="shared" si="16"/>
         <v>282</v>
       </c>
-      <c r="B284" s="3">
-        <v>1801</v>
-      </c>
-      <c r="C284" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E284" s="3">
-        <v>0</v>
-      </c>
-      <c r="F284" s="3">
-        <v>0</v>
-      </c>
-      <c r="G284" s="3">
-        <v>55</v>
-      </c>
-      <c r="H284" s="3">
-        <v>0</v>
-      </c>
-      <c r="I284" s="3">
-        <v>30</v>
-      </c>
-      <c r="J284" s="3">
-        <v>0</v>
-      </c>
-      <c r="K284" s="3">
-        <v>0</v>
-      </c>
-      <c r="L284" s="3">
-        <v>0</v>
-      </c>
-      <c r="M284" s="3">
-        <v>0</v>
-      </c>
-      <c r="N284" s="3">
-        <v>0</v>
-      </c>
-      <c r="O284" s="3">
-        <v>0</v>
-      </c>
-      <c r="P284" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q284" s="3">
-        <v>55</v>
-      </c>
-      <c r="R284" s="3">
-        <v>0</v>
-      </c>
-      <c r="S284" s="3">
-        <v>0</v>
-      </c>
-      <c r="T284" s="3">
-        <v>0</v>
-      </c>
-      <c r="U284" s="3">
-        <v>0</v>
-      </c>
-      <c r="V284" s="3">
-        <v>0</v>
-      </c>
-      <c r="W284" s="3">
-        <v>0</v>
-      </c>
-      <c r="X284" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y284" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z284" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA284" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB284" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC284" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD284" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE284" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AF284" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG284" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH284" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="AI284" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ284" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK284" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL284" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM284" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN284" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO284" s="5">
-        <v>50</v>
-      </c>
-      <c r="AP284" s="5">
-        <v>65</v>
-      </c>
-      <c r="AQ284" s="5">
-        <v>50</v>
-      </c>
-      <c r="AR284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV284" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW284" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX284" s="5">
+      <c r="B284" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C284" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="D284" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E284" s="11">
+        <v>0</v>
+      </c>
+      <c r="F284" s="11">
+        <v>0</v>
+      </c>
+      <c r="G284" s="11">
+        <v>0</v>
+      </c>
+      <c r="H284" s="11">
+        <v>0</v>
+      </c>
+      <c r="I284" s="11">
+        <v>0</v>
+      </c>
+      <c r="J284" s="11">
+        <v>0</v>
+      </c>
+      <c r="K284" s="11">
+        <v>0</v>
+      </c>
+      <c r="L284" s="11">
+        <v>0</v>
+      </c>
+      <c r="M284" s="11">
+        <v>0</v>
+      </c>
+      <c r="N284" s="11">
+        <v>0</v>
+      </c>
+      <c r="O284" s="11">
+        <v>0</v>
+      </c>
+      <c r="P284" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q284" s="11">
+        <v>0</v>
+      </c>
+      <c r="R284" s="11">
+        <v>0</v>
+      </c>
+      <c r="S284" s="11">
+        <v>0</v>
+      </c>
+      <c r="T284" s="11">
+        <v>0</v>
+      </c>
+      <c r="U284" s="11">
+        <v>0</v>
+      </c>
+      <c r="V284" s="11">
+        <v>0</v>
+      </c>
+      <c r="W284" s="11">
+        <v>0</v>
+      </c>
+      <c r="X284" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y284" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z284" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA284" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB284" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK284" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV284" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW284" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX284" s="12">
         <v>0</v>
       </c>
     </row>
@@ -46367,10 +46375,10 @@
         <v>283</v>
       </c>
       <c r="B285" s="3">
-        <v>1802</v>
+        <v>1800</v>
       </c>
       <c r="C285" s="3" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>7</v>
@@ -46409,7 +46417,7 @@
         <v>0</v>
       </c>
       <c r="P285" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="Q285" s="3">
         <v>55</v>
@@ -46520,10 +46528,10 @@
         <v>284</v>
       </c>
       <c r="B286" s="3">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C286" s="3" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>7</v>
@@ -46673,10 +46681,10 @@
         <v>285</v>
       </c>
       <c r="B287" s="3">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="C287" s="3" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>7</v>
@@ -46688,13 +46696,13 @@
         <v>0</v>
       </c>
       <c r="G287" s="3">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H287" s="3">
         <v>0</v>
       </c>
       <c r="I287" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J287" s="3">
         <v>0</v>
@@ -46826,10 +46834,10 @@
         <v>286</v>
       </c>
       <c r="B288" s="3">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="C288" s="3" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>7</v>
@@ -46841,13 +46849,13 @@
         <v>0</v>
       </c>
       <c r="G288" s="3">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H288" s="3">
         <v>0</v>
       </c>
       <c r="I288" s="3">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J288" s="3">
         <v>0</v>
@@ -46979,10 +46987,10 @@
         <v>287</v>
       </c>
       <c r="B289" s="3">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="C289" s="3" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>7</v>
@@ -46994,13 +47002,13 @@
         <v>0</v>
       </c>
       <c r="G289" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H289" s="3">
         <v>0</v>
       </c>
       <c r="I289" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J289" s="3">
         <v>0</v>
@@ -47132,10 +47140,10 @@
         <v>288</v>
       </c>
       <c r="B290" s="3">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C290" s="3" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>7</v>
@@ -47147,13 +47155,13 @@
         <v>0</v>
       </c>
       <c r="G290" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="H290" s="3">
         <v>0</v>
       </c>
       <c r="I290" s="3">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J290" s="3">
         <v>0</v>
@@ -47285,16 +47293,16 @@
         <v>289</v>
       </c>
       <c r="B291" s="3">
-        <v>1808</v>
+        <v>1806</v>
       </c>
       <c r="C291" s="3" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E291" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F291" s="3">
         <v>0</v>
@@ -47438,28 +47446,28 @@
         <v>290</v>
       </c>
       <c r="B292" s="3">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="C292" s="3" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E292" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F292" s="3">
         <v>0</v>
       </c>
       <c r="G292" s="3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H292" s="3">
         <v>0</v>
       </c>
       <c r="I292" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J292" s="3">
         <v>0</v>
@@ -47537,7 +47545,7 @@
         <v>446</v>
       </c>
       <c r="AI292" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AJ292" s="5" t="s">
         <v>7</v>
@@ -47564,7 +47572,7 @@
         <v>50</v>
       </c>
       <c r="AR292" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS292" s="5">
         <v>0</v>
@@ -47591,28 +47599,28 @@
         <v>291</v>
       </c>
       <c r="B293" s="3">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="C293" s="3" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E293" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F293" s="3">
         <v>0</v>
       </c>
       <c r="G293" s="3">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="H293" s="3">
         <v>0</v>
       </c>
       <c r="I293" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="J293" s="3">
         <v>0</v>
@@ -47690,7 +47698,7 @@
         <v>446</v>
       </c>
       <c r="AI293" s="5" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="AJ293" s="5" t="s">
         <v>7</v>
@@ -47717,7 +47725,7 @@
         <v>50</v>
       </c>
       <c r="AR293" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AS293" s="5">
         <v>0</v>
@@ -47744,28 +47752,28 @@
         <v>292</v>
       </c>
       <c r="B294" s="3">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="C294" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E294" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F294" s="3">
         <v>0</v>
       </c>
       <c r="G294" s="3">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="H294" s="3">
         <v>0</v>
       </c>
       <c r="I294" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J294" s="3">
         <v>0</v>
@@ -47843,7 +47851,7 @@
         <v>446</v>
       </c>
       <c r="AI294" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ294" s="5" t="s">
         <v>7</v>
@@ -47870,7 +47878,7 @@
         <v>50</v>
       </c>
       <c r="AR294" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS294" s="5">
         <v>0</v>
@@ -47891,156 +47899,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="11">
+    <row r="295" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A295" s="3">
         <f t="shared" si="16"/>
         <v>293</v>
       </c>
-      <c r="B295" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C295" s="11" t="s">
-        <v>438</v>
-      </c>
-      <c r="D295" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E295" s="11">
-        <v>0</v>
-      </c>
-      <c r="F295" s="11">
-        <v>0</v>
-      </c>
-      <c r="G295" s="11">
-        <v>0</v>
-      </c>
-      <c r="H295" s="11">
-        <v>0</v>
-      </c>
-      <c r="I295" s="11">
-        <v>0</v>
-      </c>
-      <c r="J295" s="11">
-        <v>0</v>
-      </c>
-      <c r="K295" s="11">
-        <v>0</v>
-      </c>
-      <c r="L295" s="11">
-        <v>0</v>
-      </c>
-      <c r="M295" s="11">
-        <v>0</v>
-      </c>
-      <c r="N295" s="11">
-        <v>0</v>
-      </c>
-      <c r="O295" s="11">
-        <v>0</v>
-      </c>
-      <c r="P295" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q295" s="11">
-        <v>0</v>
-      </c>
-      <c r="R295" s="11">
-        <v>0</v>
-      </c>
-      <c r="S295" s="11">
-        <v>0</v>
-      </c>
-      <c r="T295" s="11">
-        <v>0</v>
-      </c>
-      <c r="U295" s="11">
-        <v>0</v>
-      </c>
-      <c r="V295" s="11">
-        <v>0</v>
-      </c>
-      <c r="W295" s="11">
-        <v>0</v>
-      </c>
-      <c r="X295" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y295" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z295" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA295" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB295" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK295" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV295" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW295" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX295" s="12">
+      <c r="B295" s="3">
+        <v>1810</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E295" s="3">
+        <v>20</v>
+      </c>
+      <c r="F295" s="3">
+        <v>0</v>
+      </c>
+      <c r="G295" s="3">
+        <v>100</v>
+      </c>
+      <c r="H295" s="3">
+        <v>0</v>
+      </c>
+      <c r="I295" s="3">
+        <v>60</v>
+      </c>
+      <c r="J295" s="3">
+        <v>0</v>
+      </c>
+      <c r="K295" s="3">
+        <v>0</v>
+      </c>
+      <c r="L295" s="3">
+        <v>0</v>
+      </c>
+      <c r="M295" s="3">
+        <v>0</v>
+      </c>
+      <c r="N295" s="3">
+        <v>0</v>
+      </c>
+      <c r="O295" s="3">
+        <v>0</v>
+      </c>
+      <c r="P295" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q295" s="3">
+        <v>55</v>
+      </c>
+      <c r="R295" s="3">
+        <v>0</v>
+      </c>
+      <c r="S295" s="3">
+        <v>0</v>
+      </c>
+      <c r="T295" s="3">
+        <v>0</v>
+      </c>
+      <c r="U295" s="3">
+        <v>0</v>
+      </c>
+      <c r="V295" s="3">
+        <v>0</v>
+      </c>
+      <c r="W295" s="3">
+        <v>0</v>
+      </c>
+      <c r="X295" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y295" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z295" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA295" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB295" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC295" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD295" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE295" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF295" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG295" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH295" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI295" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AJ295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL295" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM295" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN295" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO295" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP295" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ295" s="5">
+        <v>50</v>
+      </c>
+      <c r="AR295" s="5">
+        <v>30</v>
+      </c>
+      <c r="AS295" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT295" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU295" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV295" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW295" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX295" s="5">
         <v>0</v>
       </c>
     </row>
@@ -48050,16 +48058,16 @@
         <v>294</v>
       </c>
       <c r="B296" s="3">
-        <v>1820</v>
+        <v>1811</v>
       </c>
       <c r="C296" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E296" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F296" s="3">
         <v>0</v>
@@ -48197,156 +48205,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="3">
+    <row r="297" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A297" s="11">
         <f t="shared" si="16"/>
         <v>295</v>
       </c>
-      <c r="B297" s="3">
-        <v>1821</v>
-      </c>
-      <c r="C297" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E297" s="3">
-        <v>50</v>
-      </c>
-      <c r="F297" s="3">
-        <v>0</v>
-      </c>
-      <c r="G297" s="3">
-        <v>55</v>
-      </c>
-      <c r="H297" s="3">
-        <v>0</v>
-      </c>
-      <c r="I297" s="3">
-        <v>30</v>
-      </c>
-      <c r="J297" s="3">
-        <v>0</v>
-      </c>
-      <c r="K297" s="3">
-        <v>0</v>
-      </c>
-      <c r="L297" s="3">
-        <v>0</v>
-      </c>
-      <c r="M297" s="3">
-        <v>0</v>
-      </c>
-      <c r="N297" s="3">
-        <v>0</v>
-      </c>
-      <c r="O297" s="3">
-        <v>0</v>
-      </c>
-      <c r="P297" s="3">
-        <v>50</v>
-      </c>
-      <c r="Q297" s="3">
-        <v>55</v>
-      </c>
-      <c r="R297" s="3">
-        <v>0</v>
-      </c>
-      <c r="S297" s="3">
-        <v>0</v>
-      </c>
-      <c r="T297" s="3">
-        <v>0</v>
-      </c>
-      <c r="U297" s="3">
-        <v>0</v>
-      </c>
-      <c r="V297" s="3">
-        <v>0</v>
-      </c>
-      <c r="W297" s="3">
-        <v>0</v>
-      </c>
-      <c r="X297" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y297" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z297" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA297" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB297" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC297" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD297" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AE297" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="AF297" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="AG297" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="AH297" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="AI297" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ297" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK297" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL297" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM297" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN297" s="5">
-        <v>40</v>
-      </c>
-      <c r="AO297" s="5">
-        <v>50</v>
-      </c>
-      <c r="AP297" s="5">
-        <v>65</v>
-      </c>
-      <c r="AQ297" s="5">
-        <v>50</v>
-      </c>
-      <c r="AR297" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS297" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT297" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU297" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV297" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="AW297" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX297" s="5">
+      <c r="B297" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C297" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="D297" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E297" s="11">
+        <v>0</v>
+      </c>
+      <c r="F297" s="11">
+        <v>0</v>
+      </c>
+      <c r="G297" s="11">
+        <v>0</v>
+      </c>
+      <c r="H297" s="11">
+        <v>0</v>
+      </c>
+      <c r="I297" s="11">
+        <v>0</v>
+      </c>
+      <c r="J297" s="11">
+        <v>0</v>
+      </c>
+      <c r="K297" s="11">
+        <v>0</v>
+      </c>
+      <c r="L297" s="11">
+        <v>0</v>
+      </c>
+      <c r="M297" s="11">
+        <v>0</v>
+      </c>
+      <c r="N297" s="11">
+        <v>0</v>
+      </c>
+      <c r="O297" s="11">
+        <v>0</v>
+      </c>
+      <c r="P297" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q297" s="11">
+        <v>0</v>
+      </c>
+      <c r="R297" s="11">
+        <v>0</v>
+      </c>
+      <c r="S297" s="11">
+        <v>0</v>
+      </c>
+      <c r="T297" s="11">
+        <v>0</v>
+      </c>
+      <c r="U297" s="11">
+        <v>0</v>
+      </c>
+      <c r="V297" s="11">
+        <v>0</v>
+      </c>
+      <c r="W297" s="11">
+        <v>0</v>
+      </c>
+      <c r="X297" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y297" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z297" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA297" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB297" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK297" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV297" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW297" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX297" s="12">
         <v>0</v>
       </c>
     </row>
@@ -48356,16 +48364,16 @@
         <v>296</v>
       </c>
       <c r="B298" s="3">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="C298" s="3" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E298" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F298" s="3">
         <v>0</v>
@@ -48509,16 +48517,16 @@
         <v>297</v>
       </c>
       <c r="B299" s="3">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="C299" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>7</v>
       </c>
       <c r="E299" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F299" s="3">
         <v>0</v>
@@ -48662,10 +48670,10 @@
         <v>298</v>
       </c>
       <c r="B300" s="3">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="C300" s="3" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>7</v>
@@ -48815,10 +48823,10 @@
         <v>299</v>
       </c>
       <c r="B301" s="3">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C301" s="3" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D301" s="3" t="s">
         <v>7</v>
@@ -48968,10 +48976,10 @@
         <v>300</v>
       </c>
       <c r="B302" s="3">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="C302" s="3" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>7</v>
@@ -49115,193 +49123,193 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="11">
-        <f t="shared" si="0"/>
+    <row r="303" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A303" s="3">
+        <f t="shared" si="16"/>
         <v>301</v>
       </c>
-      <c r="B303" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C303" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="D303" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E303" s="11">
-        <v>0</v>
-      </c>
-      <c r="F303" s="11">
-        <v>0</v>
-      </c>
-      <c r="G303" s="11">
-        <v>0</v>
-      </c>
-      <c r="H303" s="11">
-        <v>0</v>
-      </c>
-      <c r="I303" s="11">
-        <v>0</v>
-      </c>
-      <c r="J303" s="11">
-        <v>0</v>
-      </c>
-      <c r="K303" s="11">
-        <v>0</v>
-      </c>
-      <c r="L303" s="11">
-        <v>0</v>
-      </c>
-      <c r="M303" s="11">
-        <v>0</v>
-      </c>
-      <c r="N303" s="11">
-        <v>0</v>
-      </c>
-      <c r="O303" s="11">
-        <v>0</v>
-      </c>
-      <c r="P303" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q303" s="11">
-        <v>0</v>
-      </c>
-      <c r="R303" s="11">
-        <v>0</v>
-      </c>
-      <c r="S303" s="11">
-        <v>0</v>
-      </c>
-      <c r="T303" s="11">
-        <v>0</v>
-      </c>
-      <c r="U303" s="11">
-        <v>0</v>
-      </c>
-      <c r="V303" s="11">
-        <v>0</v>
-      </c>
-      <c r="W303" s="11">
-        <v>0</v>
-      </c>
-      <c r="X303" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y303" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z303" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA303" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB303" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK303" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV303" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW303" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX303" s="12">
+      <c r="B303" s="3">
+        <v>1825</v>
+      </c>
+      <c r="C303" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E303" s="3">
+        <v>30</v>
+      </c>
+      <c r="F303" s="3">
+        <v>0</v>
+      </c>
+      <c r="G303" s="3">
+        <v>55</v>
+      </c>
+      <c r="H303" s="3">
+        <v>0</v>
+      </c>
+      <c r="I303" s="3">
+        <v>30</v>
+      </c>
+      <c r="J303" s="3">
+        <v>0</v>
+      </c>
+      <c r="K303" s="3">
+        <v>0</v>
+      </c>
+      <c r="L303" s="3">
+        <v>0</v>
+      </c>
+      <c r="M303" s="3">
+        <v>0</v>
+      </c>
+      <c r="N303" s="3">
+        <v>0</v>
+      </c>
+      <c r="O303" s="3">
+        <v>0</v>
+      </c>
+      <c r="P303" s="3">
+        <v>50</v>
+      </c>
+      <c r="Q303" s="3">
+        <v>55</v>
+      </c>
+      <c r="R303" s="3">
+        <v>0</v>
+      </c>
+      <c r="S303" s="3">
+        <v>0</v>
+      </c>
+      <c r="T303" s="3">
+        <v>0</v>
+      </c>
+      <c r="U303" s="3">
+        <v>0</v>
+      </c>
+      <c r="V303" s="3">
+        <v>0</v>
+      </c>
+      <c r="W303" s="3">
+        <v>0</v>
+      </c>
+      <c r="X303" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y303" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z303" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA303" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB303" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC303" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD303" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE303" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF303" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG303" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH303" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI303" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ303" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK303" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL303" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM303" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN303" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO303" s="5">
+        <v>50</v>
+      </c>
+      <c r="AP303" s="5">
+        <v>65</v>
+      </c>
+      <c r="AQ303" s="5">
+        <v>50</v>
+      </c>
+      <c r="AR303" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS303" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT303" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU303" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV303" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="AW303" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX303" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="304" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="16"/>
         <v>302</v>
       </c>
       <c r="B304" s="3">
-        <v>2000</v>
+        <v>1826</v>
       </c>
       <c r="C304" s="3" t="s">
-        <v>7</v>
+        <v>437</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>378</v>
+        <v>7</v>
       </c>
       <c r="E304" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F304" s="3">
         <v>0</v>
       </c>
       <c r="G304" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="H304" s="3">
         <v>0</v>
       </c>
       <c r="I304" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J304" s="3">
         <v>0</v>
       </c>
       <c r="K304" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L304" s="3">
         <v>0</v>
@@ -49316,88 +49324,88 @@
         <v>0</v>
       </c>
       <c r="P304" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="Q304" s="3">
+        <v>55</v>
+      </c>
+      <c r="R304" s="3">
+        <v>0</v>
+      </c>
+      <c r="S304" s="3">
+        <v>0</v>
+      </c>
+      <c r="T304" s="3">
+        <v>0</v>
+      </c>
+      <c r="U304" s="3">
+        <v>0</v>
+      </c>
+      <c r="V304" s="3">
+        <v>0</v>
+      </c>
+      <c r="W304" s="3">
+        <v>0</v>
+      </c>
+      <c r="X304" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y304" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z304" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA304" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB304" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC304" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD304" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE304" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="AF304" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="AG304" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="AH304" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="AI304" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ304" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK304" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL304" s="5">
+        <v>-50</v>
+      </c>
+      <c r="AM304" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN304" s="5">
+        <v>40</v>
+      </c>
+      <c r="AO304" s="5">
         <v>50</v>
       </c>
-      <c r="R304" s="3">
-        <v>0</v>
-      </c>
-      <c r="S304" s="3">
-        <v>0</v>
-      </c>
-      <c r="T304" s="3">
-        <v>0</v>
-      </c>
-      <c r="U304" s="3">
-        <v>0</v>
-      </c>
-      <c r="V304" s="3">
-        <v>0</v>
-      </c>
-      <c r="W304" s="3">
-        <v>0</v>
-      </c>
-      <c r="X304" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y304" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z304" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA304" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB304" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK304" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL304" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM304" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN304" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO304" s="5">
-        <v>0</v>
-      </c>
       <c r="AP304" s="5">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AQ304" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AR304" s="5">
         <v>0</v>
@@ -49412,7 +49420,7 @@
         <v>0</v>
       </c>
       <c r="AV304" s="4" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
       <c r="AW304" s="5">
         <v>0</v>
@@ -49421,156 +49429,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="3">
+    <row r="305" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A305" s="11">
         <f t="shared" si="0"/>
         <v>303</v>
       </c>
-      <c r="B305" s="3">
-        <v>2001</v>
-      </c>
-      <c r="C305" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D305" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E305" s="3">
-        <v>0</v>
-      </c>
-      <c r="F305" s="3">
-        <v>0</v>
-      </c>
-      <c r="G305" s="3">
-        <v>60</v>
-      </c>
-      <c r="H305" s="3">
-        <v>0</v>
-      </c>
-      <c r="I305" s="3">
-        <v>0</v>
-      </c>
-      <c r="J305" s="3">
-        <v>0</v>
-      </c>
-      <c r="K305" s="3">
-        <v>100</v>
-      </c>
-      <c r="L305" s="3">
-        <v>0</v>
-      </c>
-      <c r="M305" s="3">
-        <v>0</v>
-      </c>
-      <c r="N305" s="3">
-        <v>0</v>
-      </c>
-      <c r="O305" s="3">
-        <v>0</v>
-      </c>
-      <c r="P305" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q305" s="3">
-        <v>50</v>
-      </c>
-      <c r="R305" s="3">
-        <v>0</v>
-      </c>
-      <c r="S305" s="3">
-        <v>0</v>
-      </c>
-      <c r="T305" s="3">
-        <v>0</v>
-      </c>
-      <c r="U305" s="3">
-        <v>0</v>
-      </c>
-      <c r="V305" s="3">
-        <v>0</v>
-      </c>
-      <c r="W305" s="3">
-        <v>0</v>
-      </c>
-      <c r="X305" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y305" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z305" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA305" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB305" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK305" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV305" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="AW305" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX305" s="5">
+      <c r="B305" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C305" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="D305" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E305" s="11">
+        <v>0</v>
+      </c>
+      <c r="F305" s="11">
+        <v>0</v>
+      </c>
+      <c r="G305" s="11">
+        <v>0</v>
+      </c>
+      <c r="H305" s="11">
+        <v>0</v>
+      </c>
+      <c r="I305" s="11">
+        <v>0</v>
+      </c>
+      <c r="J305" s="11">
+        <v>0</v>
+      </c>
+      <c r="K305" s="11">
+        <v>0</v>
+      </c>
+      <c r="L305" s="11">
+        <v>0</v>
+      </c>
+      <c r="M305" s="11">
+        <v>0</v>
+      </c>
+      <c r="N305" s="11">
+        <v>0</v>
+      </c>
+      <c r="O305" s="11">
+        <v>0</v>
+      </c>
+      <c r="P305" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q305" s="11">
+        <v>0</v>
+      </c>
+      <c r="R305" s="11">
+        <v>0</v>
+      </c>
+      <c r="S305" s="11">
+        <v>0</v>
+      </c>
+      <c r="T305" s="11">
+        <v>0</v>
+      </c>
+      <c r="U305" s="11">
+        <v>0</v>
+      </c>
+      <c r="V305" s="11">
+        <v>0</v>
+      </c>
+      <c r="W305" s="11">
+        <v>0</v>
+      </c>
+      <c r="X305" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y305" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z305" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA305" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB305" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK305" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV305" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW305" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX305" s="12">
         <v>0</v>
       </c>
     </row>
@@ -49580,13 +49588,13 @@
         <v>304</v>
       </c>
       <c r="B306" s="3">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="C306" s="3" t="s">
-        <v>389</v>
+        <v>7</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>7</v>
+        <v>378</v>
       </c>
       <c r="E306" s="3">
         <v>0</v>
@@ -49595,13 +49603,13 @@
         <v>0</v>
       </c>
       <c r="G306" s="3">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="H306" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I306" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J306" s="3">
         <v>0</v>
@@ -49625,7 +49633,7 @@
         <v>0</v>
       </c>
       <c r="Q306" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R306" s="3">
         <v>0</v>
@@ -49688,28 +49696,28 @@
         <v>7</v>
       </c>
       <c r="AL306" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM306" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN306" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO306" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP306" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ306" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR306" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS306" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT306" s="5">
         <v>0</v>
@@ -49733,13 +49741,13 @@
         <v>305</v>
       </c>
       <c r="B307" s="3">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C307" s="3" t="s">
-        <v>390</v>
+        <v>7</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>7</v>
+        <v>379</v>
       </c>
       <c r="E307" s="3">
         <v>0</v>
@@ -49748,13 +49756,13 @@
         <v>0</v>
       </c>
       <c r="G307" s="3">
-        <v>570</v>
+        <v>60</v>
       </c>
       <c r="H307" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I307" s="3">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="J307" s="3">
         <v>0</v>
@@ -49778,7 +49786,7 @@
         <v>0</v>
       </c>
       <c r="Q307" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R307" s="3">
         <v>0</v>
@@ -49841,28 +49849,28 @@
         <v>7</v>
       </c>
       <c r="AL307" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AM307" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AN307" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AO307" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP307" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AQ307" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR307" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS307" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT307" s="5">
         <v>0</v>
@@ -49880,156 +49888,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="11">
+    <row r="308" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A308" s="3">
         <f t="shared" si="0"/>
         <v>306</v>
       </c>
-      <c r="B308" s="11">
-        <v>999999</v>
-      </c>
-      <c r="C308" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="D308" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E308" s="11">
-        <v>0</v>
-      </c>
-      <c r="F308" s="11">
-        <v>0</v>
-      </c>
-      <c r="G308" s="11">
-        <v>0</v>
-      </c>
-      <c r="H308" s="11">
-        <v>0</v>
-      </c>
-      <c r="I308" s="11">
-        <v>0</v>
-      </c>
-      <c r="J308" s="11">
-        <v>0</v>
-      </c>
-      <c r="K308" s="11">
-        <v>0</v>
-      </c>
-      <c r="L308" s="11">
-        <v>0</v>
-      </c>
-      <c r="M308" s="11">
-        <v>0</v>
-      </c>
-      <c r="N308" s="11">
-        <v>0</v>
-      </c>
-      <c r="O308" s="11">
-        <v>0</v>
-      </c>
-      <c r="P308" s="11">
-        <v>0</v>
-      </c>
-      <c r="Q308" s="11">
-        <v>0</v>
-      </c>
-      <c r="R308" s="11">
-        <v>0</v>
-      </c>
-      <c r="S308" s="11">
-        <v>0</v>
-      </c>
-      <c r="T308" s="11">
-        <v>0</v>
-      </c>
-      <c r="U308" s="11">
-        <v>0</v>
-      </c>
-      <c r="V308" s="11">
-        <v>0</v>
-      </c>
-      <c r="W308" s="11">
-        <v>0</v>
-      </c>
-      <c r="X308" s="11">
-        <v>0</v>
-      </c>
-      <c r="Y308" s="11">
-        <v>0</v>
-      </c>
-      <c r="Z308" s="11">
-        <v>0</v>
-      </c>
-      <c r="AA308" s="11">
-        <v>0</v>
-      </c>
-      <c r="AB308" s="11">
-        <v>0</v>
-      </c>
-      <c r="AC308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK308" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AM308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AN308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AO308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AP308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AQ308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AR308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AS308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AT308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AU308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AV308" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="AW308" s="12">
-        <v>0</v>
-      </c>
-      <c r="AX308" s="12">
+      <c r="B308" s="3">
+        <v>2002</v>
+      </c>
+      <c r="C308" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E308" s="3">
+        <v>0</v>
+      </c>
+      <c r="F308" s="3">
+        <v>0</v>
+      </c>
+      <c r="G308" s="3">
+        <v>570</v>
+      </c>
+      <c r="H308" s="3">
+        <v>200</v>
+      </c>
+      <c r="I308" s="3">
+        <v>250</v>
+      </c>
+      <c r="J308" s="3">
+        <v>0</v>
+      </c>
+      <c r="K308" s="3">
+        <v>100</v>
+      </c>
+      <c r="L308" s="3">
+        <v>0</v>
+      </c>
+      <c r="M308" s="3">
+        <v>0</v>
+      </c>
+      <c r="N308" s="3">
+        <v>0</v>
+      </c>
+      <c r="O308" s="3">
+        <v>0</v>
+      </c>
+      <c r="P308" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q308" s="3">
+        <v>80</v>
+      </c>
+      <c r="R308" s="3">
+        <v>0</v>
+      </c>
+      <c r="S308" s="3">
+        <v>0</v>
+      </c>
+      <c r="T308" s="3">
+        <v>0</v>
+      </c>
+      <c r="U308" s="3">
+        <v>0</v>
+      </c>
+      <c r="V308" s="3">
+        <v>0</v>
+      </c>
+      <c r="W308" s="3">
+        <v>0</v>
+      </c>
+      <c r="X308" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y308" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z308" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA308" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB308" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK308" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL308" s="5">
+        <v>10</v>
+      </c>
+      <c r="AM308" s="5">
+        <v>20</v>
+      </c>
+      <c r="AN308" s="5">
+        <v>20</v>
+      </c>
+      <c r="AO308" s="5">
+        <v>20</v>
+      </c>
+      <c r="AP308" s="5">
+        <v>20</v>
+      </c>
+      <c r="AQ308" s="5">
+        <v>20</v>
+      </c>
+      <c r="AR308" s="5">
+        <v>20</v>
+      </c>
+      <c r="AS308" s="5">
+        <v>40</v>
+      </c>
+      <c r="AT308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV308" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="AW308" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX308" s="5">
         <v>0</v>
       </c>
     </row>
@@ -50039,10 +50047,10 @@
         <v>307</v>
       </c>
       <c r="B309" s="3">
-        <v>100000</v>
+        <v>2003</v>
       </c>
       <c r="C309" s="3" t="s">
-        <v>148</v>
+        <v>390</v>
       </c>
       <c r="D309" s="3" t="s">
         <v>7</v>
@@ -50054,19 +50062,19 @@
         <v>0</v>
       </c>
       <c r="G309" s="3">
-        <v>120</v>
+        <v>570</v>
       </c>
       <c r="H309" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I309" s="3">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="J309" s="3">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K309" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L309" s="3">
         <v>0</v>
@@ -50084,7 +50092,7 @@
         <v>0</v>
       </c>
       <c r="Q309" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R309" s="3">
         <v>0</v>
@@ -50123,10 +50131,10 @@
         <v>7</v>
       </c>
       <c r="AD309" s="5" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="AE309" s="5" t="s">
-        <v>59</v>
+        <v>7</v>
       </c>
       <c r="AF309" s="5" t="s">
         <v>7</v>
@@ -50147,37 +50155,37 @@
         <v>7</v>
       </c>
       <c r="AL309" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AM309" s="5">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="AN309" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO309" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP309" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ309" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR309" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS309" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT309" s="5">
         <v>0</v>
       </c>
       <c r="AU309" s="5">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AV309" s="4" t="s">
-        <v>268</v>
+        <v>98</v>
       </c>
       <c r="AW309" s="5">
         <v>0</v>
@@ -50186,156 +50194,156 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A310" s="3">
+    <row r="310" spans="1:50" s="14" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A310" s="11">
         <f t="shared" si="0"/>
         <v>308</v>
       </c>
-      <c r="B310" s="3">
-        <v>100010</v>
-      </c>
-      <c r="C310" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="E310" s="3">
-        <v>0</v>
-      </c>
-      <c r="F310" s="3">
-        <v>0</v>
-      </c>
-      <c r="G310" s="3">
-        <v>52</v>
-      </c>
-      <c r="H310" s="3">
-        <v>30</v>
-      </c>
-      <c r="I310" s="3">
-        <v>0</v>
-      </c>
-      <c r="J310" s="3">
-        <v>70</v>
-      </c>
-      <c r="K310" s="3">
-        <v>0</v>
-      </c>
-      <c r="L310" s="3">
-        <v>0</v>
-      </c>
-      <c r="M310" s="3">
-        <v>0</v>
-      </c>
-      <c r="N310" s="3">
-        <v>0</v>
-      </c>
-      <c r="O310" s="3">
-        <v>0</v>
-      </c>
-      <c r="P310" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q310" s="3">
-        <v>80</v>
-      </c>
-      <c r="R310" s="3">
-        <v>0</v>
-      </c>
-      <c r="S310" s="3">
-        <v>0</v>
-      </c>
-      <c r="T310" s="3">
-        <v>0</v>
-      </c>
-      <c r="U310" s="3">
-        <v>0</v>
-      </c>
-      <c r="V310" s="3">
-        <v>0</v>
-      </c>
-      <c r="W310" s="3">
-        <v>0</v>
-      </c>
-      <c r="X310" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y310" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z310" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA310" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB310" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC310" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD310" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE310" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF310" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG310" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH310" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI310" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ310" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK310" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL310" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM310" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN310" s="5">
-        <v>20</v>
-      </c>
-      <c r="AO310" s="5">
-        <v>12</v>
-      </c>
-      <c r="AP310" s="5">
-        <v>12</v>
-      </c>
-      <c r="AQ310" s="5">
-        <v>40</v>
-      </c>
-      <c r="AR310" s="5">
-        <v>10</v>
-      </c>
-      <c r="AS310" s="5">
-        <v>10</v>
-      </c>
-      <c r="AT310" s="5">
-        <v>30</v>
-      </c>
-      <c r="AU310" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV310" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="AW310" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX310" s="5">
+      <c r="B310" s="11">
+        <v>999999</v>
+      </c>
+      <c r="C310" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D310" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E310" s="11">
+        <v>0</v>
+      </c>
+      <c r="F310" s="11">
+        <v>0</v>
+      </c>
+      <c r="G310" s="11">
+        <v>0</v>
+      </c>
+      <c r="H310" s="11">
+        <v>0</v>
+      </c>
+      <c r="I310" s="11">
+        <v>0</v>
+      </c>
+      <c r="J310" s="11">
+        <v>0</v>
+      </c>
+      <c r="K310" s="11">
+        <v>0</v>
+      </c>
+      <c r="L310" s="11">
+        <v>0</v>
+      </c>
+      <c r="M310" s="11">
+        <v>0</v>
+      </c>
+      <c r="N310" s="11">
+        <v>0</v>
+      </c>
+      <c r="O310" s="11">
+        <v>0</v>
+      </c>
+      <c r="P310" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q310" s="11">
+        <v>0</v>
+      </c>
+      <c r="R310" s="11">
+        <v>0</v>
+      </c>
+      <c r="S310" s="11">
+        <v>0</v>
+      </c>
+      <c r="T310" s="11">
+        <v>0</v>
+      </c>
+      <c r="U310" s="11">
+        <v>0</v>
+      </c>
+      <c r="V310" s="11">
+        <v>0</v>
+      </c>
+      <c r="W310" s="11">
+        <v>0</v>
+      </c>
+      <c r="X310" s="11">
+        <v>0</v>
+      </c>
+      <c r="Y310" s="11">
+        <v>0</v>
+      </c>
+      <c r="Z310" s="11">
+        <v>0</v>
+      </c>
+      <c r="AA310" s="11">
+        <v>0</v>
+      </c>
+      <c r="AB310" s="11">
+        <v>0</v>
+      </c>
+      <c r="AC310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK310" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AM310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AN310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AO310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AP310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AS310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AT310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AU310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AV310" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="AW310" s="12">
+        <v>0</v>
+      </c>
+      <c r="AX310" s="12">
         <v>0</v>
       </c>
     </row>
@@ -50345,13 +50353,13 @@
         <v>309</v>
       </c>
       <c r="B311" s="3">
-        <v>100011</v>
+        <v>100000</v>
       </c>
       <c r="C311" s="3" t="s">
-        <v>7</v>
+        <v>148</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>263</v>
+        <v>7</v>
       </c>
       <c r="E311" s="3">
         <v>0</v>
@@ -50360,130 +50368,130 @@
         <v>0</v>
       </c>
       <c r="G311" s="3">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="H311" s="3">
+        <v>0</v>
+      </c>
+      <c r="I311" s="3">
+        <v>60</v>
+      </c>
+      <c r="J311" s="3">
+        <v>120</v>
+      </c>
+      <c r="K311" s="3">
+        <v>0</v>
+      </c>
+      <c r="L311" s="3">
+        <v>0</v>
+      </c>
+      <c r="M311" s="3">
+        <v>0</v>
+      </c>
+      <c r="N311" s="3">
+        <v>0</v>
+      </c>
+      <c r="O311" s="3">
+        <v>0</v>
+      </c>
+      <c r="P311" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q311" s="3">
+        <v>50</v>
+      </c>
+      <c r="R311" s="3">
+        <v>0</v>
+      </c>
+      <c r="S311" s="3">
+        <v>0</v>
+      </c>
+      <c r="T311" s="3">
+        <v>0</v>
+      </c>
+      <c r="U311" s="3">
+        <v>0</v>
+      </c>
+      <c r="V311" s="3">
+        <v>0</v>
+      </c>
+      <c r="W311" s="3">
+        <v>0</v>
+      </c>
+      <c r="X311" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y311" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z311" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA311" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB311" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD311" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE311" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK311" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL311" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM311" s="5">
+        <v>60</v>
+      </c>
+      <c r="AN311" s="5">
         <v>30</v>
       </c>
-      <c r="I311" s="3">
-        <v>0</v>
-      </c>
-      <c r="J311" s="3">
-        <v>70</v>
-      </c>
-      <c r="K311" s="3">
-        <v>0</v>
-      </c>
-      <c r="L311" s="3">
-        <v>0</v>
-      </c>
-      <c r="M311" s="3">
-        <v>0</v>
-      </c>
-      <c r="N311" s="3">
-        <v>0</v>
-      </c>
-      <c r="O311" s="3">
-        <v>0</v>
-      </c>
-      <c r="P311" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q311" s="3">
-        <v>80</v>
-      </c>
-      <c r="R311" s="3">
-        <v>0</v>
-      </c>
-      <c r="S311" s="3">
-        <v>0</v>
-      </c>
-      <c r="T311" s="3">
-        <v>0</v>
-      </c>
-      <c r="U311" s="3">
-        <v>0</v>
-      </c>
-      <c r="V311" s="3">
-        <v>0</v>
-      </c>
-      <c r="W311" s="3">
-        <v>0</v>
-      </c>
-      <c r="X311" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y311" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z311" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA311" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB311" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC311" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AD311" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AE311" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF311" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="AG311" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AH311" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AI311" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="AJ311" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="AK311" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AL311" s="5">
-        <v>-50</v>
-      </c>
-      <c r="AM311" s="5">
-        <v>30</v>
-      </c>
-      <c r="AN311" s="5">
-        <v>20</v>
-      </c>
       <c r="AO311" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AP311" s="5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ311" s="5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AR311" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS311" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT311" s="5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AU311" s="5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AV311" s="4" t="s">
-        <v>113</v>
+        <v>268</v>
       </c>
       <c r="AW311" s="5">
         <v>0</v>
@@ -50498,13 +50506,13 @@
         <v>310</v>
       </c>
       <c r="B312" s="3">
-        <v>100020</v>
+        <v>100010</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>56</v>
+        <v>250</v>
       </c>
       <c r="E312" s="3">
         <v>0</v>
@@ -50513,19 +50521,19 @@
         <v>0</v>
       </c>
       <c r="G312" s="3">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="H312" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I312" s="3">
         <v>0</v>
       </c>
       <c r="J312" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K312" s="3">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="L312" s="3">
         <v>0</v>
@@ -50543,7 +50551,7 @@
         <v>0</v>
       </c>
       <c r="Q312" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R312" s="3">
         <v>0</v>
@@ -50579,64 +50587,64 @@
         <v>0</v>
       </c>
       <c r="AC312" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD312" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="AD312" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="AE312" s="5" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="AF312" s="5" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="AG312" s="5" t="s">
-        <v>7</v>
+        <v>255</v>
       </c>
       <c r="AH312" s="5" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="AI312" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AJ312" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AK312" s="5" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="AL312" s="5">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="AM312" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN312" s="5">
         <v>20</v>
       </c>
       <c r="AO312" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP312" s="5">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ312" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AR312" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS312" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT312" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU312" s="5">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AV312" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AW312" s="5">
         <v>0</v>
@@ -50651,13 +50659,13 @@
         <v>311</v>
       </c>
       <c r="B313" s="3">
-        <v>100030</v>
+        <v>100011</v>
       </c>
       <c r="C313" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="E313" s="3">
         <v>0</v>
@@ -50666,19 +50674,19 @@
         <v>0</v>
       </c>
       <c r="G313" s="3">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="H313" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I313" s="3">
         <v>0</v>
       </c>
       <c r="J313" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="K313" s="3">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="L313" s="3">
         <v>0</v>
@@ -50696,7 +50704,7 @@
         <v>0</v>
       </c>
       <c r="Q313" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R313" s="3">
         <v>0</v>
@@ -50732,64 +50740,64 @@
         <v>0</v>
       </c>
       <c r="AC313" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="AD313" s="5" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="AE313" s="5" t="s">
-        <v>240</v>
+        <v>62</v>
       </c>
       <c r="AF313" s="5" t="s">
-        <v>252</v>
+        <v>75</v>
       </c>
       <c r="AG313" s="5" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="AH313" s="5" t="s">
-        <v>121</v>
+        <v>256</v>
       </c>
       <c r="AI313" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="AJ313" s="5" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AK313" s="5" t="s">
-        <v>7</v>
+        <v>257</v>
       </c>
       <c r="AL313" s="5">
-        <v>30</v>
+        <v>-50</v>
       </c>
       <c r="AM313" s="5">
         <v>30</v>
       </c>
       <c r="AN313" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AO313" s="5">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AP313" s="5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ313" s="5">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AR313" s="5">
         <v>10</v>
       </c>
       <c r="AS313" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT313" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU313" s="5">
         <v>0</v>
       </c>
       <c r="AV313" s="4" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="AW313" s="5">
         <v>0</v>
@@ -50800,17 +50808,17 @@
     </row>
     <row r="314" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="3">
-        <f t="shared" ref="A314" si="17">ROW()-2</f>
+        <f t="shared" si="0"/>
         <v>312</v>
       </c>
       <c r="B314" s="3">
-        <v>100040</v>
+        <v>100020</v>
       </c>
       <c r="C314" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E314" s="3">
         <v>0</v>
@@ -50819,7 +50827,7 @@
         <v>0</v>
       </c>
       <c r="G314" s="3">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="H314" s="3">
         <v>0</v>
@@ -50828,10 +50836,10 @@
         <v>0</v>
       </c>
       <c r="J314" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K314" s="3">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="L314" s="3">
         <v>0</v>
@@ -50849,7 +50857,7 @@
         <v>0</v>
       </c>
       <c r="Q314" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R314" s="3">
         <v>0</v>
@@ -50885,22 +50893,22 @@
         <v>0</v>
       </c>
       <c r="AC314" s="5" t="s">
-        <v>34</v>
+        <v>254</v>
       </c>
       <c r="AD314" s="5" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="AE314" s="5" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="AF314" s="5" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="AG314" s="5" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="AH314" s="5" t="s">
-        <v>80</v>
+        <v>7</v>
       </c>
       <c r="AI314" s="5" t="s">
         <v>7</v>
@@ -50912,22 +50920,22 @@
         <v>7</v>
       </c>
       <c r="AL314" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AM314" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AN314" s="5">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AO314" s="5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AP314" s="5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AQ314" s="5">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR314" s="5">
         <v>0</v>
@@ -50939,10 +50947,10 @@
         <v>0</v>
       </c>
       <c r="AU314" s="5">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AV314" s="4" t="s">
-        <v>440</v>
+        <v>116</v>
       </c>
       <c r="AW314" s="5">
         <v>0</v>
@@ -50957,150 +50965,456 @@
         <v>313</v>
       </c>
       <c r="B315" s="3">
+        <v>100030</v>
+      </c>
+      <c r="C315" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E315" s="3">
+        <v>0</v>
+      </c>
+      <c r="F315" s="3">
+        <v>0</v>
+      </c>
+      <c r="G315" s="3">
+        <v>120</v>
+      </c>
+      <c r="H315" s="3">
+        <v>0</v>
+      </c>
+      <c r="I315" s="3">
+        <v>0</v>
+      </c>
+      <c r="J315" s="3">
+        <v>0</v>
+      </c>
+      <c r="K315" s="3">
+        <v>70</v>
+      </c>
+      <c r="L315" s="3">
+        <v>0</v>
+      </c>
+      <c r="M315" s="3">
+        <v>0</v>
+      </c>
+      <c r="N315" s="3">
+        <v>0</v>
+      </c>
+      <c r="O315" s="3">
+        <v>0</v>
+      </c>
+      <c r="P315" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q315" s="3">
+        <v>70</v>
+      </c>
+      <c r="R315" s="3">
+        <v>0</v>
+      </c>
+      <c r="S315" s="3">
+        <v>0</v>
+      </c>
+      <c r="T315" s="3">
+        <v>0</v>
+      </c>
+      <c r="U315" s="3">
+        <v>0</v>
+      </c>
+      <c r="V315" s="3">
+        <v>0</v>
+      </c>
+      <c r="W315" s="3">
+        <v>0</v>
+      </c>
+      <c r="X315" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y315" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z315" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA315" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB315" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC315" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD315" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="AE315" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="AF315" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG315" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="AH315" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI315" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AJ315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK315" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL315" s="5">
+        <v>30</v>
+      </c>
+      <c r="AM315" s="5">
+        <v>30</v>
+      </c>
+      <c r="AN315" s="5">
+        <v>30</v>
+      </c>
+      <c r="AO315" s="5">
+        <v>30</v>
+      </c>
+      <c r="AP315" s="5">
+        <v>10</v>
+      </c>
+      <c r="AQ315" s="5">
+        <v>15</v>
+      </c>
+      <c r="AR315" s="5">
+        <v>10</v>
+      </c>
+      <c r="AS315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV315" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AW315" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX315" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A316" s="3">
+        <f t="shared" ref="A316" si="17">ROW()-2</f>
+        <v>314</v>
+      </c>
+      <c r="B316" s="3">
+        <v>100040</v>
+      </c>
+      <c r="C316" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E316" s="3">
+        <v>0</v>
+      </c>
+      <c r="F316" s="3">
+        <v>0</v>
+      </c>
+      <c r="G316" s="3">
+        <v>32</v>
+      </c>
+      <c r="H316" s="3">
+        <v>0</v>
+      </c>
+      <c r="I316" s="3">
+        <v>0</v>
+      </c>
+      <c r="J316" s="3">
+        <v>60</v>
+      </c>
+      <c r="K316" s="3">
+        <v>0</v>
+      </c>
+      <c r="L316" s="3">
+        <v>0</v>
+      </c>
+      <c r="M316" s="3">
+        <v>0</v>
+      </c>
+      <c r="N316" s="3">
+        <v>0</v>
+      </c>
+      <c r="O316" s="3">
+        <v>0</v>
+      </c>
+      <c r="P316" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q316" s="3">
+        <v>50</v>
+      </c>
+      <c r="R316" s="3">
+        <v>0</v>
+      </c>
+      <c r="S316" s="3">
+        <v>0</v>
+      </c>
+      <c r="T316" s="3">
+        <v>0</v>
+      </c>
+      <c r="U316" s="3">
+        <v>0</v>
+      </c>
+      <c r="V316" s="3">
+        <v>0</v>
+      </c>
+      <c r="W316" s="3">
+        <v>0</v>
+      </c>
+      <c r="X316" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y316" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z316" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA316" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB316" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC316" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD316" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE316" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="AF316" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="AG316" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH316" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI316" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ316" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK316" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL316" s="5">
+        <v>5</v>
+      </c>
+      <c r="AM316" s="5">
+        <v>10</v>
+      </c>
+      <c r="AN316" s="5">
+        <v>12</v>
+      </c>
+      <c r="AO316" s="5">
+        <v>20</v>
+      </c>
+      <c r="AP316" s="5">
+        <v>5</v>
+      </c>
+      <c r="AQ316" s="5">
+        <v>10</v>
+      </c>
+      <c r="AR316" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS316" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT316" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU316" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV316" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="AW316" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX316" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A317" s="3">
+        <f t="shared" si="0"/>
+        <v>315</v>
+      </c>
+      <c r="B317" s="3">
         <v>999999</v>
       </c>
-      <c r="C315" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E315" s="3">
-        <v>0</v>
-      </c>
-      <c r="F315" s="3">
-        <v>0</v>
-      </c>
-      <c r="G315" s="3">
-        <v>0</v>
-      </c>
-      <c r="H315" s="3">
-        <v>0</v>
-      </c>
-      <c r="I315" s="3">
-        <v>0</v>
-      </c>
-      <c r="J315" s="3">
-        <v>0</v>
-      </c>
-      <c r="K315" s="3">
-        <v>0</v>
-      </c>
-      <c r="L315" s="3">
-        <v>0</v>
-      </c>
-      <c r="M315" s="3">
-        <v>0</v>
-      </c>
-      <c r="N315" s="3">
-        <v>0</v>
-      </c>
-      <c r="O315" s="3">
-        <v>0</v>
-      </c>
-      <c r="P315" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q315" s="3">
-        <v>0</v>
-      </c>
-      <c r="R315" s="3">
-        <v>0</v>
-      </c>
-      <c r="S315" s="3">
-        <v>0</v>
-      </c>
-      <c r="T315" s="3">
-        <v>0</v>
-      </c>
-      <c r="U315" s="3">
-        <v>0</v>
-      </c>
-      <c r="V315" s="3">
-        <v>0</v>
-      </c>
-      <c r="W315" s="3">
-        <v>0</v>
-      </c>
-      <c r="X315" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y315" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z315" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA315" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB315" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK315" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV315" s="4" t="s">
+      <c r="C317" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E317" s="3">
+        <v>0</v>
+      </c>
+      <c r="F317" s="3">
+        <v>0</v>
+      </c>
+      <c r="G317" s="3">
+        <v>0</v>
+      </c>
+      <c r="H317" s="3">
+        <v>0</v>
+      </c>
+      <c r="I317" s="3">
+        <v>0</v>
+      </c>
+      <c r="J317" s="3">
+        <v>0</v>
+      </c>
+      <c r="K317" s="3">
+        <v>0</v>
+      </c>
+      <c r="L317" s="3">
+        <v>0</v>
+      </c>
+      <c r="M317" s="3">
+        <v>0</v>
+      </c>
+      <c r="N317" s="3">
+        <v>0</v>
+      </c>
+      <c r="O317" s="3">
+        <v>0</v>
+      </c>
+      <c r="P317" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q317" s="3">
+        <v>0</v>
+      </c>
+      <c r="R317" s="3">
+        <v>0</v>
+      </c>
+      <c r="S317" s="3">
+        <v>0</v>
+      </c>
+      <c r="T317" s="3">
+        <v>0</v>
+      </c>
+      <c r="U317" s="3">
+        <v>0</v>
+      </c>
+      <c r="V317" s="3">
+        <v>0</v>
+      </c>
+      <c r="W317" s="3">
+        <v>0</v>
+      </c>
+      <c r="X317" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y317" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z317" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA317" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB317" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK317" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV317" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AW315" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX315" s="5">
+      <c r="AW317" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX317" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A209712D-0577-4359-A596-DFC88E037BB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7FF623-8BCB-4883-A98A-A6583F2151A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="765" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -17695,7 +17695,7 @@
         <v>50</v>
       </c>
       <c r="R97" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S97" s="3">
         <v>0</v>
@@ -17848,7 +17848,7 @@
         <v>50</v>
       </c>
       <c r="R98" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S98" s="3">
         <v>0</v>
@@ -18307,7 +18307,7 @@
         <v>50</v>
       </c>
       <c r="R101" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -18421,7 +18421,7 @@
         <v>7</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F102" s="3">
         <v>0</v>
@@ -18433,7 +18433,7 @@
         <v>30</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
@@ -18574,7 +18574,7 @@
         <v>7</v>
       </c>
       <c r="E103" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F103" s="3">
         <v>0</v>
@@ -18586,7 +18586,7 @@
         <v>30</v>
       </c>
       <c r="I103" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J103" s="3">
         <v>0</v>
@@ -18613,7 +18613,7 @@
         <v>50</v>
       </c>
       <c r="R103" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="S103" s="3">
         <v>0</v>
@@ -18727,7 +18727,7 @@
         <v>7</v>
       </c>
       <c r="E104" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F104" s="3">
         <v>0</v>
@@ -18766,7 +18766,7 @@
         <v>50</v>
       </c>
       <c r="R104" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="S104" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E6026A4-CD2B-4A04-A624-DC67A64A26C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E463D0F-570D-4137-99AA-F76294411214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="1260" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="660" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -11861,7 +11861,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -12014,7 +12014,7 @@
         <v>30</v>
       </c>
       <c r="J60" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -12167,7 +12167,7 @@
         <v>30</v>
       </c>
       <c r="J61" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -12320,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -12473,7 +12473,7 @@
         <v>30</v>
       </c>
       <c r="J63" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K63" s="3">
         <v>0</v>
@@ -12626,7 +12626,7 @@
         <v>30</v>
       </c>
       <c r="J64" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K64" s="3">
         <v>0</v>
@@ -12779,7 +12779,7 @@
         <v>30</v>
       </c>
       <c r="J65" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K65" s="3">
         <v>0</v>
@@ -12932,7 +12932,7 @@
         <v>30</v>
       </c>
       <c r="J66" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E463D0F-570D-4137-99AA-F76294411214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C196843C-EAB7-470A-B494-C09B498AD28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="660" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1155" yWindow="1050" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -24545,7 +24545,7 @@
         <v>7</v>
       </c>
       <c r="E142" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F142" s="3">
         <v>0</v>
@@ -24698,7 +24698,7 @@
         <v>7</v>
       </c>
       <c r="E143" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F143" s="3">
         <v>0</v>
@@ -24851,7 +24851,7 @@
         <v>7</v>
       </c>
       <c r="E144" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F144" s="3">
         <v>0</v>
@@ -24926,7 +24926,7 @@
         <v>196</v>
       </c>
       <c r="AD144" s="5" t="s">
-        <v>7</v>
+        <v>445</v>
       </c>
       <c r="AE144" s="5" t="s">
         <v>7</v>
@@ -24953,7 +24953,7 @@
         <v>10</v>
       </c>
       <c r="AM144" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN144" s="5">
         <v>0</v>
@@ -25079,7 +25079,7 @@
         <v>196</v>
       </c>
       <c r="AD145" s="5" t="s">
-        <v>7</v>
+        <v>445</v>
       </c>
       <c r="AE145" s="5" t="s">
         <v>7</v>
@@ -25106,7 +25106,7 @@
         <v>10</v>
       </c>
       <c r="AM145" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN145" s="5">
         <v>0</v>
@@ -25232,7 +25232,7 @@
         <v>196</v>
       </c>
       <c r="AD146" s="5" t="s">
-        <v>7</v>
+        <v>445</v>
       </c>
       <c r="AE146" s="5" t="s">
         <v>7</v>
@@ -25259,7 +25259,7 @@
         <v>10</v>
       </c>
       <c r="AM146" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN146" s="5">
         <v>0</v>
@@ -25385,7 +25385,7 @@
         <v>196</v>
       </c>
       <c r="AD147" s="5" t="s">
-        <v>7</v>
+        <v>445</v>
       </c>
       <c r="AE147" s="5" t="s">
         <v>7</v>
@@ -25412,7 +25412,7 @@
         <v>10</v>
       </c>
       <c r="AM147" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN147" s="5">
         <v>0</v>
@@ -26228,7 +26228,7 @@
         <v>7</v>
       </c>
       <c r="E153" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F153" s="3">
         <v>0</v>
@@ -26534,7 +26534,7 @@
         <v>7</v>
       </c>
       <c r="E155" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F155" s="3">
         <v>0</v>
@@ -26615,7 +26615,7 @@
         <v>445</v>
       </c>
       <c r="AF155" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AG155" s="5" t="s">
         <v>7</v>
@@ -26642,7 +26642,7 @@
         <v>30</v>
       </c>
       <c r="AO155" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP155" s="5">
         <v>0</v>
@@ -26687,7 +26687,7 @@
         <v>7</v>
       </c>
       <c r="E156" s="3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F156" s="3">
         <v>0</v>
@@ -44435,7 +44435,7 @@
         <v>7</v>
       </c>
       <c r="E272" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F272" s="3">
         <v>0</v>
@@ -44588,7 +44588,7 @@
         <v>7</v>
       </c>
       <c r="E273" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F273" s="3">
         <v>0</v>
@@ -44741,7 +44741,7 @@
         <v>7</v>
       </c>
       <c r="E274" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F274" s="3">
         <v>0</v>
@@ -44894,7 +44894,7 @@
         <v>7</v>
       </c>
       <c r="E275" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F275" s="3">
         <v>0</v>
@@ -45047,7 +45047,7 @@
         <v>7</v>
       </c>
       <c r="E276" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F276" s="3">
         <v>0</v>
@@ -45200,7 +45200,7 @@
         <v>7</v>
       </c>
       <c r="E277" s="3">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F277" s="3">
         <v>0</v>
@@ -45353,7 +45353,7 @@
         <v>395</v>
       </c>
       <c r="E278" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F278" s="3">
         <v>0</v>
@@ -45506,7 +45506,7 @@
         <v>396</v>
       </c>
       <c r="E279" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F279" s="3">
         <v>0</v>
@@ -45659,7 +45659,7 @@
         <v>397</v>
       </c>
       <c r="E280" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F280" s="3">
         <v>0</v>
@@ -45812,7 +45812,7 @@
         <v>398</v>
       </c>
       <c r="E281" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F281" s="3">
         <v>0</v>
@@ -45965,7 +45965,7 @@
         <v>7</v>
       </c>
       <c r="E282" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F282" s="3">
         <v>0</v>
@@ -46118,7 +46118,7 @@
         <v>7</v>
       </c>
       <c r="E283" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F283" s="3">
         <v>0</v>
@@ -46271,7 +46271,7 @@
         <v>7</v>
       </c>
       <c r="E284" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F284" s="3">
         <v>0</v>
@@ -46424,7 +46424,7 @@
         <v>7</v>
       </c>
       <c r="E285" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F285" s="3">
         <v>0</v>
@@ -46577,7 +46577,7 @@
         <v>7</v>
       </c>
       <c r="E286" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F286" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F8DAA5C-FA96-44AC-8A15-4BF7A1FEBB4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063DFC8D-390C-479F-9740-D753ED7CEA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2535" yWindow="435" windowWidth="25560" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3902" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3914" uniqueCount="474">
   <si>
     <t>desc</t>
   </si>
@@ -2508,6 +2508,14 @@
     <t>lemon_juice</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>lumi_banana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ルーティにムーンバナナあげる</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -2938,7 +2946,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AX322"/>
+  <dimension ref="A1:AX323"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -3116,7 +3124,7 @@
     </row>
     <row r="2" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A322" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A323" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -7296,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="Q29" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -7449,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="Q30" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R30" s="3">
         <v>0</v>
@@ -7602,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="Q31" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R31" s="3">
         <v>0</v>
@@ -7755,7 +7763,7 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -7887,7 +7895,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -7908,7 +7916,7 @@
         <v>0</v>
       </c>
       <c r="Q33" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R33" s="3">
         <v>0</v>
@@ -8040,7 +8048,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K34" s="3">
         <v>0</v>
@@ -8061,7 +8069,7 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R34" s="3">
         <v>0</v>
@@ -8214,7 +8222,7 @@
         <v>0</v>
       </c>
       <c r="Q35" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R35" s="3">
         <v>0</v>
@@ -8346,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K36" s="3">
         <v>0</v>
@@ -8367,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="Q36" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R36" s="3">
         <v>0</v>
@@ -8520,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R37" s="3">
         <v>0</v>
@@ -8673,7 +8681,7 @@
         <v>0</v>
       </c>
       <c r="Q38" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R38" s="3">
         <v>0</v>
@@ -8805,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -8979,7 +8987,7 @@
         <v>0</v>
       </c>
       <c r="Q40" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R40" s="3">
         <v>0</v>
@@ -9132,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="Q41" s="3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="R41" s="3">
         <v>0</v>
@@ -9264,7 +9272,7 @@
         <v>30</v>
       </c>
       <c r="J42" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -9273,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
@@ -9285,7 +9293,7 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -9438,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="Q43" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
@@ -9591,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="Q44" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -9723,7 +9731,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -9744,7 +9752,7 @@
         <v>0</v>
       </c>
       <c r="Q45" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -9876,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -9897,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="Q46" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R46" s="3">
         <v>0</v>
@@ -10029,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -10050,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="Q47" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -10203,7 +10211,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -10509,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="Q50" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R50" s="3">
         <v>0</v>
@@ -10662,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R51" s="3">
         <v>0</v>
@@ -10815,7 +10823,7 @@
         <v>0</v>
       </c>
       <c r="Q52" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R52" s="3">
         <v>0</v>
@@ -10968,7 +10976,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R53" s="3">
         <v>0</v>
@@ -11121,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="Q54" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R54" s="3">
         <v>0</v>
@@ -11274,7 +11282,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="3">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="R55" s="3">
         <v>0</v>
@@ -11427,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="R56" s="3">
         <v>0</v>
@@ -11580,7 +11588,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -11886,7 +11894,7 @@
         <v>0</v>
       </c>
       <c r="Q59" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -12039,7 +12047,7 @@
         <v>0</v>
       </c>
       <c r="Q60" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R60" s="3">
         <v>0</v>
@@ -12192,7 +12200,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -12345,7 +12353,7 @@
         <v>0</v>
       </c>
       <c r="Q62" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -12498,7 +12506,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R63" s="3">
         <v>0</v>
@@ -12651,7 +12659,7 @@
         <v>0</v>
       </c>
       <c r="Q64" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R64" s="3">
         <v>0</v>
@@ -12804,7 +12812,7 @@
         <v>0</v>
       </c>
       <c r="Q65" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R65" s="3">
         <v>0</v>
@@ -12957,7 +12965,7 @@
         <v>0</v>
       </c>
       <c r="Q66" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R66" s="3">
         <v>0</v>
@@ -13263,7 +13271,7 @@
         <v>0</v>
       </c>
       <c r="Q68" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R68" s="3">
         <v>0</v>
@@ -13395,28 +13403,28 @@
         <v>0</v>
       </c>
       <c r="J69" s="3">
+        <v>50</v>
+      </c>
+      <c r="K69" s="3">
+        <v>0</v>
+      </c>
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
         <v>80</v>
-      </c>
-      <c r="K69" s="3">
-        <v>0</v>
-      </c>
-      <c r="L69" s="3">
-        <v>0</v>
-      </c>
-      <c r="M69" s="3">
-        <v>0</v>
-      </c>
-      <c r="N69" s="3">
-        <v>0</v>
-      </c>
-      <c r="O69" s="3">
-        <v>0</v>
-      </c>
-      <c r="P69" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q69" s="3">
-        <v>50</v>
       </c>
       <c r="R69" s="3">
         <v>0</v>
@@ -13569,7 +13577,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -13701,28 +13709,28 @@
         <v>0</v>
       </c>
       <c r="J71" s="3">
+        <v>70</v>
+      </c>
+      <c r="K71" s="3">
+        <v>0</v>
+      </c>
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
         <v>80</v>
-      </c>
-      <c r="K71" s="3">
-        <v>0</v>
-      </c>
-      <c r="L71" s="3">
-        <v>0</v>
-      </c>
-      <c r="M71" s="3">
-        <v>0</v>
-      </c>
-      <c r="N71" s="3">
-        <v>0</v>
-      </c>
-      <c r="O71" s="3">
-        <v>0</v>
-      </c>
-      <c r="P71" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q71" s="3">
-        <v>50</v>
       </c>
       <c r="R71" s="3">
         <v>0</v>
@@ -13875,7 +13883,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -14028,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="Q73" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R73" s="3">
         <v>0</v>
@@ -14181,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R74" s="3">
         <v>0</v>
@@ -14334,7 +14342,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R75" s="3">
         <v>0</v>
@@ -14775,7 +14783,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L78" s="3">
         <v>0</v>
@@ -14928,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L79" s="3">
         <v>0</v>
@@ -15081,7 +15089,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L80" s="3">
         <v>0</v>
@@ -15234,7 +15242,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L81" s="3">
         <v>0</v>
@@ -15387,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="K82" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L82" s="3">
         <v>0</v>
@@ -15540,7 +15548,7 @@
         <v>0</v>
       </c>
       <c r="K83" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -15693,7 +15701,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L84" s="3">
         <v>0</v>
@@ -15846,7 +15854,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L85" s="3">
         <v>0</v>
@@ -15999,7 +16007,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L86" s="3">
         <v>0</v>
@@ -16152,7 +16160,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L87" s="3">
         <v>0</v>
@@ -16305,7 +16313,7 @@
         <v>0</v>
       </c>
       <c r="K88" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L88" s="3">
         <v>0</v>
@@ -16458,7 +16466,7 @@
         <v>0</v>
       </c>
       <c r="K89" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L89" s="3">
         <v>0</v>
@@ -16611,7 +16619,7 @@
         <v>0</v>
       </c>
       <c r="K90" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L90" s="3">
         <v>0</v>
@@ -16764,7 +16772,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -16917,7 +16925,7 @@
         <v>0</v>
       </c>
       <c r="K92" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L92" s="3">
         <v>0</v>
@@ -17223,7 +17231,7 @@
         <v>0</v>
       </c>
       <c r="K94" s="3">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -22884,7 +22892,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L131" s="3">
         <v>0</v>
@@ -23343,7 +23351,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L134" s="3">
         <v>0</v>
@@ -23496,7 +23504,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L135" s="3">
         <v>0</v>
@@ -23649,7 +23657,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L136" s="3">
         <v>0</v>
@@ -23802,7 +23810,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L137" s="3">
         <v>0</v>
@@ -23955,7 +23963,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="3">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L138" s="3">
         <v>0</v>
@@ -24261,7 +24269,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L140" s="3">
         <v>0</v>
@@ -24720,7 +24728,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="3">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="L143" s="3">
         <v>0</v>
@@ -25485,7 +25493,7 @@
         <v>0</v>
       </c>
       <c r="K148" s="3">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L148" s="3">
         <v>0</v>
@@ -25638,7 +25646,7 @@
         <v>0</v>
       </c>
       <c r="K149" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L149" s="3">
         <v>0</v>
@@ -25791,7 +25799,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L150" s="3">
         <v>0</v>
@@ -25944,7 +25952,7 @@
         <v>0</v>
       </c>
       <c r="K151" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L151" s="3">
         <v>0</v>
@@ -26097,7 +26105,7 @@
         <v>0</v>
       </c>
       <c r="K152" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L152" s="3">
         <v>0</v>
@@ -26556,7 +26564,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="3">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="L155" s="3">
         <v>0</v>
@@ -26709,7 +26717,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="3">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L156" s="3">
         <v>0</v>
@@ -26862,7 +26870,7 @@
         <v>0</v>
       </c>
       <c r="K157" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L157" s="3">
         <v>0</v>
@@ -27015,7 +27023,7 @@
         <v>0</v>
       </c>
       <c r="K158" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L158" s="3">
         <v>0</v>
@@ -27609,7 +27617,7 @@
         <v>7</v>
       </c>
       <c r="E162" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F162" s="3">
         <v>0</v>
@@ -27933,7 +27941,7 @@
         <v>0</v>
       </c>
       <c r="K164" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L164" s="3">
         <v>0</v>
@@ -29310,7 +29318,7 @@
         <v>0</v>
       </c>
       <c r="K173" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L173" s="3">
         <v>0</v>
@@ -29463,7 +29471,7 @@
         <v>0</v>
       </c>
       <c r="K174" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L174" s="3">
         <v>0</v>
@@ -29616,7 +29624,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="L175" s="3">
         <v>0</v>
@@ -31608,10 +31616,10 @@
         <v>0</v>
       </c>
       <c r="L188" s="3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="M188" s="3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N188" s="3">
         <v>0</v>
@@ -31761,10 +31769,10 @@
         <v>0</v>
       </c>
       <c r="L189" s="3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="M189" s="3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N189" s="3">
         <v>0</v>
@@ -31914,10 +31922,10 @@
         <v>0</v>
       </c>
       <c r="L190" s="3">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="M190" s="3">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="N190" s="3">
         <v>0</v>
@@ -32067,10 +32075,10 @@
         <v>0</v>
       </c>
       <c r="L191" s="3">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="M191" s="3">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="N191" s="3">
         <v>0</v>
@@ -34680,7 +34688,7 @@
         <v>0</v>
       </c>
       <c r="P208" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q208" s="3">
         <v>55</v>
@@ -34833,7 +34841,7 @@
         <v>0</v>
       </c>
       <c r="P209" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q209" s="3">
         <v>55</v>
@@ -34986,7 +34994,7 @@
         <v>0</v>
       </c>
       <c r="P210" s="3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q210" s="3">
         <v>70</v>
@@ -35139,7 +35147,7 @@
         <v>0</v>
       </c>
       <c r="P211" s="3">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="Q211" s="3">
         <v>70</v>
@@ -35445,7 +35453,7 @@
         <v>0</v>
       </c>
       <c r="P213" s="3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q213" s="3">
         <v>70</v>
@@ -35598,7 +35606,7 @@
         <v>0</v>
       </c>
       <c r="P214" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q214" s="3">
         <v>55</v>
@@ -35751,7 +35759,7 @@
         <v>0</v>
       </c>
       <c r="P215" s="3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q215" s="3">
         <v>55</v>
@@ -35904,7 +35912,7 @@
         <v>0</v>
       </c>
       <c r="P216" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q216" s="3">
         <v>55</v>
@@ -36057,7 +36065,7 @@
         <v>0</v>
       </c>
       <c r="P217" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q217" s="3">
         <v>55</v>
@@ -36210,7 +36218,7 @@
         <v>0</v>
       </c>
       <c r="P218" s="3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q218" s="3">
         <v>55</v>
@@ -36363,7 +36371,7 @@
         <v>0</v>
       </c>
       <c r="P219" s="3">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="Q219" s="3">
         <v>55</v>
@@ -36516,7 +36524,7 @@
         <v>0</v>
       </c>
       <c r="P220" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q220" s="3">
         <v>55</v>
@@ -36669,7 +36677,7 @@
         <v>0</v>
       </c>
       <c r="P221" s="3">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="Q221" s="3">
         <v>55</v>
@@ -39579,7 +39587,7 @@
         <v>0</v>
       </c>
       <c r="Q240" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R240" s="3">
         <v>0</v>
@@ -39732,7 +39740,7 @@
         <v>0</v>
       </c>
       <c r="Q241" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R241" s="3">
         <v>0</v>
@@ -39885,7 +39893,7 @@
         <v>0</v>
       </c>
       <c r="Q242" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R242" s="3">
         <v>0</v>
@@ -40017,7 +40025,7 @@
         <v>0</v>
       </c>
       <c r="J243" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K243" s="3">
         <v>0</v>
@@ -40038,7 +40046,7 @@
         <v>0</v>
       </c>
       <c r="Q243" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R243" s="3">
         <v>0</v>
@@ -40191,7 +40199,7 @@
         <v>0</v>
       </c>
       <c r="Q244" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R244" s="3">
         <v>0</v>
@@ -40344,7 +40352,7 @@
         <v>0</v>
       </c>
       <c r="Q245" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R245" s="3">
         <v>0</v>
@@ -40476,7 +40484,7 @@
         <v>0</v>
       </c>
       <c r="J246" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K246" s="3">
         <v>0</v>
@@ -40497,7 +40505,7 @@
         <v>0</v>
       </c>
       <c r="Q246" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R246" s="3">
         <v>0</v>
@@ -40629,7 +40637,7 @@
         <v>0</v>
       </c>
       <c r="J247" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K247" s="3">
         <v>0</v>
@@ -40650,7 +40658,7 @@
         <v>0</v>
       </c>
       <c r="Q247" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R247" s="3">
         <v>0</v>
@@ -40782,7 +40790,7 @@
         <v>0</v>
       </c>
       <c r="J248" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="K248" s="3">
         <v>0</v>
@@ -40803,7 +40811,7 @@
         <v>0</v>
       </c>
       <c r="Q248" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R248" s="3">
         <v>0</v>
@@ -40956,7 +40964,7 @@
         <v>0</v>
       </c>
       <c r="Q249" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R249" s="3">
         <v>0</v>
@@ -41109,7 +41117,7 @@
         <v>0</v>
       </c>
       <c r="Q250" s="3">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="R250" s="3">
         <v>0</v>
@@ -41394,7 +41402,7 @@
         <v>30</v>
       </c>
       <c r="J252" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K252" s="3">
         <v>0</v>
@@ -41415,7 +41423,7 @@
         <v>0</v>
       </c>
       <c r="Q252" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R252" s="3">
         <v>0</v>
@@ -41547,7 +41555,7 @@
         <v>30</v>
       </c>
       <c r="J253" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K253" s="3">
         <v>0</v>
@@ -41568,7 +41576,7 @@
         <v>0</v>
       </c>
       <c r="Q253" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R253" s="3">
         <v>0</v>
@@ -41700,7 +41708,7 @@
         <v>30</v>
       </c>
       <c r="J254" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K254" s="3">
         <v>0</v>
@@ -41721,7 +41729,7 @@
         <v>0</v>
       </c>
       <c r="Q254" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R254" s="3">
         <v>0</v>
@@ -42024,10 +42032,10 @@
         <v>0</v>
       </c>
       <c r="P256" s="3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q256" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R256" s="3">
         <v>0</v>
@@ -42177,10 +42185,10 @@
         <v>0</v>
       </c>
       <c r="P257" s="3">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q257" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R257" s="3">
         <v>0</v>
@@ -42330,10 +42338,10 @@
         <v>0</v>
       </c>
       <c r="P258" s="3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q258" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R258" s="3">
         <v>0</v>
@@ -42483,10 +42491,10 @@
         <v>0</v>
       </c>
       <c r="P259" s="3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Q259" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R259" s="3">
         <v>0</v>
@@ -42636,10 +42644,10 @@
         <v>0</v>
       </c>
       <c r="P260" s="3">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="Q260" s="3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="R260" s="3">
         <v>0</v>
@@ -42789,7 +42797,7 @@
         <v>0</v>
       </c>
       <c r="P261" s="3">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="Q261" s="3">
         <v>70</v>
@@ -43077,7 +43085,7 @@
         <v>0</v>
       </c>
       <c r="J263" s="3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="K263" s="3">
         <v>0</v>
@@ -43383,7 +43391,7 @@
         <v>0</v>
       </c>
       <c r="J265" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K265" s="3">
         <v>0</v>
@@ -43392,7 +43400,7 @@
         <v>0</v>
       </c>
       <c r="M265" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N265" s="3">
         <v>0</v>
@@ -43695,7 +43703,7 @@
         <v>0</v>
       </c>
       <c r="L267" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="M267" s="3">
         <v>0</v>
@@ -44001,7 +44009,7 @@
         <v>0</v>
       </c>
       <c r="L269" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M269" s="3">
         <v>0</v>
@@ -44307,7 +44315,7 @@
         <v>0</v>
       </c>
       <c r="L271" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M271" s="3">
         <v>0</v>
@@ -44613,7 +44621,7 @@
         <v>0</v>
       </c>
       <c r="L273" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M273" s="3">
         <v>0</v>
@@ -44766,7 +44774,7 @@
         <v>0</v>
       </c>
       <c r="L274" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M274" s="3">
         <v>0</v>
@@ -44919,7 +44927,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M275" s="3">
         <v>0</v>
@@ -45072,7 +45080,7 @@
         <v>0</v>
       </c>
       <c r="L276" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M276" s="3">
         <v>0</v>
@@ -45225,7 +45233,7 @@
         <v>0</v>
       </c>
       <c r="L277" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M277" s="3">
         <v>0</v>
@@ -45378,7 +45386,7 @@
         <v>0</v>
       </c>
       <c r="L278" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M278" s="3">
         <v>0</v>
@@ -45531,7 +45539,7 @@
         <v>0</v>
       </c>
       <c r="L279" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M279" s="3">
         <v>0</v>
@@ -45684,7 +45692,7 @@
         <v>0</v>
       </c>
       <c r="L280" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M280" s="3">
         <v>0</v>
@@ -45837,7 +45845,7 @@
         <v>0</v>
       </c>
       <c r="L281" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M281" s="3">
         <v>0</v>
@@ -45990,7 +45998,7 @@
         <v>0</v>
       </c>
       <c r="L282" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M282" s="3">
         <v>0</v>
@@ -46143,7 +46151,7 @@
         <v>0</v>
       </c>
       <c r="L283" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="M283" s="3">
         <v>0</v>
@@ -46296,7 +46304,7 @@
         <v>0</v>
       </c>
       <c r="L284" s="3">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="M284" s="3">
         <v>0</v>
@@ -46449,7 +46457,7 @@
         <v>0</v>
       </c>
       <c r="L285" s="3">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="M285" s="3">
         <v>0</v>
@@ -46602,7 +46610,7 @@
         <v>0</v>
       </c>
       <c r="L286" s="3">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="M286" s="3">
         <v>0</v>
@@ -46755,7 +46763,7 @@
         <v>0</v>
       </c>
       <c r="L287" s="3">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="M287" s="3">
         <v>0</v>
@@ -50424,7 +50432,7 @@
         <v>0</v>
       </c>
       <c r="K311" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L311" s="3">
         <v>0</v>
@@ -50577,7 +50585,7 @@
         <v>0</v>
       </c>
       <c r="K312" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L312" s="3">
         <v>0</v>
@@ -50730,7 +50738,7 @@
         <v>0</v>
       </c>
       <c r="K313" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L313" s="3">
         <v>0</v>
@@ -51923,7 +51931,7 @@
     </row>
     <row r="321" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="3">
-        <f t="shared" ref="A321" si="19">ROW()-2</f>
+        <f t="shared" ref="A321:A322" si="19">ROW()-2</f>
         <v>319</v>
       </c>
       <c r="B321" s="3">
@@ -52076,154 +52084,307 @@
     </row>
     <row r="322" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="3">
+        <f t="shared" si="19"/>
+        <v>320</v>
+      </c>
+      <c r="B322" s="3">
+        <v>100100</v>
+      </c>
+      <c r="C322" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E322" s="3">
+        <v>0</v>
+      </c>
+      <c r="F322" s="3">
+        <v>0</v>
+      </c>
+      <c r="G322" s="3">
+        <v>32</v>
+      </c>
+      <c r="H322" s="3">
+        <v>0</v>
+      </c>
+      <c r="I322" s="3">
+        <v>0</v>
+      </c>
+      <c r="J322" s="3">
+        <v>0</v>
+      </c>
+      <c r="K322" s="3">
+        <v>0</v>
+      </c>
+      <c r="L322" s="3">
+        <v>0</v>
+      </c>
+      <c r="M322" s="3">
+        <v>0</v>
+      </c>
+      <c r="N322" s="3">
+        <v>0</v>
+      </c>
+      <c r="O322" s="3">
+        <v>0</v>
+      </c>
+      <c r="P322" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q322" s="3">
+        <v>50</v>
+      </c>
+      <c r="R322" s="3">
+        <v>0</v>
+      </c>
+      <c r="S322" s="3">
+        <v>0</v>
+      </c>
+      <c r="T322" s="3">
+        <v>0</v>
+      </c>
+      <c r="U322" s="3">
+        <v>0</v>
+      </c>
+      <c r="V322" s="3">
+        <v>0</v>
+      </c>
+      <c r="W322" s="3">
+        <v>0</v>
+      </c>
+      <c r="X322" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y322" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z322" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA322" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB322" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK322" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV322" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="AW322" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX322" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="3">
         <f t="shared" si="0"/>
-        <v>320</v>
-      </c>
-      <c r="B322" s="3">
+        <v>321</v>
+      </c>
+      <c r="B323" s="3">
         <v>999999</v>
       </c>
-      <c r="C322" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D322" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E322" s="3">
-        <v>0</v>
-      </c>
-      <c r="F322" s="3">
-        <v>0</v>
-      </c>
-      <c r="G322" s="3">
-        <v>0</v>
-      </c>
-      <c r="H322" s="3">
-        <v>0</v>
-      </c>
-      <c r="I322" s="3">
-        <v>0</v>
-      </c>
-      <c r="J322" s="3">
-        <v>0</v>
-      </c>
-      <c r="K322" s="3">
-        <v>0</v>
-      </c>
-      <c r="L322" s="3">
-        <v>0</v>
-      </c>
-      <c r="M322" s="3">
-        <v>0</v>
-      </c>
-      <c r="N322" s="3">
-        <v>0</v>
-      </c>
-      <c r="O322" s="3">
-        <v>0</v>
-      </c>
-      <c r="P322" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q322" s="3">
-        <v>0</v>
-      </c>
-      <c r="R322" s="3">
-        <v>0</v>
-      </c>
-      <c r="S322" s="3">
-        <v>0</v>
-      </c>
-      <c r="T322" s="3">
-        <v>0</v>
-      </c>
-      <c r="U322" s="3">
-        <v>0</v>
-      </c>
-      <c r="V322" s="3">
-        <v>0</v>
-      </c>
-      <c r="W322" s="3">
-        <v>0</v>
-      </c>
-      <c r="X322" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y322" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z322" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA322" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB322" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK322" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV322" s="4" t="s">
+      <c r="C323" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E323" s="3">
+        <v>0</v>
+      </c>
+      <c r="F323" s="3">
+        <v>0</v>
+      </c>
+      <c r="G323" s="3">
+        <v>0</v>
+      </c>
+      <c r="H323" s="3">
+        <v>0</v>
+      </c>
+      <c r="I323" s="3">
+        <v>0</v>
+      </c>
+      <c r="J323" s="3">
+        <v>0</v>
+      </c>
+      <c r="K323" s="3">
+        <v>0</v>
+      </c>
+      <c r="L323" s="3">
+        <v>0</v>
+      </c>
+      <c r="M323" s="3">
+        <v>0</v>
+      </c>
+      <c r="N323" s="3">
+        <v>0</v>
+      </c>
+      <c r="O323" s="3">
+        <v>0</v>
+      </c>
+      <c r="P323" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q323" s="3">
+        <v>0</v>
+      </c>
+      <c r="R323" s="3">
+        <v>0</v>
+      </c>
+      <c r="S323" s="3">
+        <v>0</v>
+      </c>
+      <c r="T323" s="3">
+        <v>0</v>
+      </c>
+      <c r="U323" s="3">
+        <v>0</v>
+      </c>
+      <c r="V323" s="3">
+        <v>0</v>
+      </c>
+      <c r="W323" s="3">
+        <v>0</v>
+      </c>
+      <c r="X323" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y323" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z323" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA323" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB323" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK323" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV323" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AW322" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX322" s="5">
+      <c r="AW323" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX323" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{063DFC8D-390C-479F-9740-D753ED7CEA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B011652-A54F-4A83-BDF6-13CD457A643E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="25560" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25560" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -17765,10 +17765,10 @@
         <v>448</v>
       </c>
       <c r="AJ97" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK97" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL97" s="5">
         <v>-50</v>
@@ -17792,10 +17792,10 @@
         <v>-100</v>
       </c>
       <c r="AS97" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT97" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU97" s="5">
         <v>0</v>
@@ -17918,10 +17918,10 @@
         <v>448</v>
       </c>
       <c r="AJ98" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK98" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL98" s="5">
         <v>-50</v>
@@ -17945,10 +17945,10 @@
         <v>-100</v>
       </c>
       <c r="AS98" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT98" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU98" s="5">
         <v>0</v>
@@ -18071,10 +18071,10 @@
         <v>448</v>
       </c>
       <c r="AJ99" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK99" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL99" s="5">
         <v>-50</v>
@@ -18098,10 +18098,10 @@
         <v>-100</v>
       </c>
       <c r="AS99" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT99" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU99" s="5">
         <v>0</v>
@@ -18224,10 +18224,10 @@
         <v>448</v>
       </c>
       <c r="AJ100" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK100" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL100" s="5">
         <v>-50</v>
@@ -18251,10 +18251,10 @@
         <v>-100</v>
       </c>
       <c r="AS100" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT100" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU100" s="5">
         <v>0</v>
@@ -18377,10 +18377,10 @@
         <v>448</v>
       </c>
       <c r="AJ101" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK101" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL101" s="5">
         <v>-50</v>
@@ -18404,10 +18404,10 @@
         <v>-100</v>
       </c>
       <c r="AS101" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT101" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU101" s="5">
         <v>0</v>
@@ -18530,10 +18530,10 @@
         <v>448</v>
       </c>
       <c r="AJ102" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK102" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL102" s="5">
         <v>-50</v>
@@ -18557,10 +18557,10 @@
         <v>-100</v>
       </c>
       <c r="AS102" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT102" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU102" s="5">
         <v>0</v>
@@ -18671,7 +18671,7 @@
         <v>62</v>
       </c>
       <c r="AF103" s="5" t="s">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="AG103" s="5" t="s">
         <v>298</v>
@@ -18683,10 +18683,10 @@
         <v>448</v>
       </c>
       <c r="AJ103" s="5" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AK103" s="5" t="s">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="AL103" s="5">
         <v>-50</v>
@@ -18701,19 +18701,19 @@
         <v>12</v>
       </c>
       <c r="AP103" s="5">
-        <v>20</v>
+        <v>-100</v>
       </c>
       <c r="AQ103" s="5">
-        <v>30</v>
+        <v>-100</v>
       </c>
       <c r="AR103" s="5">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="AS103" s="5">
-        <v>20</v>
+        <v>-6</v>
       </c>
       <c r="AT103" s="5">
-        <v>20</v>
+        <v>-10</v>
       </c>
       <c r="AU103" s="5">
         <v>0</v>
@@ -18836,10 +18836,10 @@
         <v>448</v>
       </c>
       <c r="AJ104" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AK104" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AL104" s="5">
         <v>-50</v>
@@ -18863,10 +18863,10 @@
         <v>-100</v>
       </c>
       <c r="AS104" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AT104" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AU104" s="5">
         <v>0</v>
@@ -19136,10 +19136,10 @@
         <v>7</v>
       </c>
       <c r="AH106" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AI106" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AJ106" s="5" t="s">
         <v>7</v>
@@ -19163,10 +19163,10 @@
         <v>0</v>
       </c>
       <c r="AQ106" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AR106" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AS106" s="5">
         <v>0</v>
@@ -19289,10 +19289,10 @@
         <v>7</v>
       </c>
       <c r="AH107" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AI107" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AJ107" s="5" t="s">
         <v>7</v>
@@ -19316,10 +19316,10 @@
         <v>0</v>
       </c>
       <c r="AQ107" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AR107" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AS107" s="5">
         <v>0</v>
@@ -19442,10 +19442,10 @@
         <v>7</v>
       </c>
       <c r="AH108" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AI108" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AJ108" s="5" t="s">
         <v>7</v>
@@ -19469,10 +19469,10 @@
         <v>0</v>
       </c>
       <c r="AQ108" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AR108" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AS108" s="5">
         <v>0</v>
@@ -19595,10 +19595,10 @@
         <v>7</v>
       </c>
       <c r="AH109" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AI109" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AJ109" s="5" t="s">
         <v>7</v>
@@ -19622,10 +19622,10 @@
         <v>0</v>
       </c>
       <c r="AQ109" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AR109" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AS109" s="5">
         <v>0</v>
@@ -19748,10 +19748,10 @@
         <v>448</v>
       </c>
       <c r="AH110" s="5" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
       <c r="AI110" s="5" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="AJ110" s="5" t="s">
         <v>7</v>
@@ -19775,10 +19775,10 @@
         <v>30</v>
       </c>
       <c r="AQ110" s="5">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="AR110" s="5">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="AS110" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6738295-DA56-4054-B4BF-F9D152790339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C83806C-2F7C-41B2-A85D-DE2FAB53FB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="1830" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3926" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="475">
   <si>
     <t>desc</t>
   </si>
@@ -2950,7 +2950,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AX324"/>
+  <dimension ref="A1:AX325"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="2" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <f t="shared" ref="A2:A324" si="0">ROW()-2</f>
+        <f t="shared" ref="A2:A325" si="0">ROW()-2</f>
         <v>0</v>
       </c>
       <c r="B2" s="3">
@@ -52088,7 +52088,7 @@
     </row>
     <row r="322" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="3">
-        <f t="shared" ref="A322:A323" si="20">ROW()-2</f>
+        <f t="shared" ref="A322:A324" si="20">ROW()-2</f>
         <v>320</v>
       </c>
       <c r="B322" s="3">
@@ -52394,154 +52394,307 @@
     </row>
     <row r="324" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="3">
+        <f t="shared" si="20"/>
+        <v>322</v>
+      </c>
+      <c r="B324" s="3">
+        <v>101000</v>
+      </c>
+      <c r="C324" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E324" s="3">
+        <v>0</v>
+      </c>
+      <c r="F324" s="3">
+        <v>0</v>
+      </c>
+      <c r="G324" s="3">
+        <v>150</v>
+      </c>
+      <c r="H324" s="3">
+        <v>400</v>
+      </c>
+      <c r="I324" s="3">
+        <v>0</v>
+      </c>
+      <c r="J324" s="3">
+        <v>0</v>
+      </c>
+      <c r="K324" s="3">
+        <v>0</v>
+      </c>
+      <c r="L324" s="3">
+        <v>100</v>
+      </c>
+      <c r="M324" s="3">
+        <v>0</v>
+      </c>
+      <c r="N324" s="3">
+        <v>0</v>
+      </c>
+      <c r="O324" s="3">
+        <v>0</v>
+      </c>
+      <c r="P324" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q324" s="3">
+        <v>50</v>
+      </c>
+      <c r="R324" s="3">
+        <v>0</v>
+      </c>
+      <c r="S324" s="3">
+        <v>0</v>
+      </c>
+      <c r="T324" s="3">
+        <v>0</v>
+      </c>
+      <c r="U324" s="3">
+        <v>0</v>
+      </c>
+      <c r="V324" s="3">
+        <v>0</v>
+      </c>
+      <c r="W324" s="3">
+        <v>0</v>
+      </c>
+      <c r="X324" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y324" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z324" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA324" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB324" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC324" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK324" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL324" s="5">
+        <v>20</v>
+      </c>
+      <c r="AM324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV324" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="AW324" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX324" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="3">
         <f t="shared" si="0"/>
-        <v>322</v>
-      </c>
-      <c r="B324" s="3">
+        <v>323</v>
+      </c>
+      <c r="B325" s="3">
         <v>999999</v>
       </c>
-      <c r="C324" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D324" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E324" s="3">
-        <v>0</v>
-      </c>
-      <c r="F324" s="3">
-        <v>0</v>
-      </c>
-      <c r="G324" s="3">
-        <v>0</v>
-      </c>
-      <c r="H324" s="3">
-        <v>0</v>
-      </c>
-      <c r="I324" s="3">
-        <v>0</v>
-      </c>
-      <c r="J324" s="3">
-        <v>0</v>
-      </c>
-      <c r="K324" s="3">
-        <v>0</v>
-      </c>
-      <c r="L324" s="3">
-        <v>0</v>
-      </c>
-      <c r="M324" s="3">
-        <v>0</v>
-      </c>
-      <c r="N324" s="3">
-        <v>0</v>
-      </c>
-      <c r="O324" s="3">
-        <v>0</v>
-      </c>
-      <c r="P324" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q324" s="3">
-        <v>0</v>
-      </c>
-      <c r="R324" s="3">
-        <v>0</v>
-      </c>
-      <c r="S324" s="3">
-        <v>0</v>
-      </c>
-      <c r="T324" s="3">
-        <v>0</v>
-      </c>
-      <c r="U324" s="3">
-        <v>0</v>
-      </c>
-      <c r="V324" s="3">
-        <v>0</v>
-      </c>
-      <c r="W324" s="3">
-        <v>0</v>
-      </c>
-      <c r="X324" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y324" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z324" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA324" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB324" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AD324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AE324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AF324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AG324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AH324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AI324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AJ324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AK324" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AL324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AM324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AN324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AO324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AP324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AQ324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AR324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AS324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AT324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AU324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AV324" s="4" t="s">
+      <c r="C325" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E325" s="3">
+        <v>0</v>
+      </c>
+      <c r="F325" s="3">
+        <v>0</v>
+      </c>
+      <c r="G325" s="3">
+        <v>0</v>
+      </c>
+      <c r="H325" s="3">
+        <v>0</v>
+      </c>
+      <c r="I325" s="3">
+        <v>0</v>
+      </c>
+      <c r="J325" s="3">
+        <v>0</v>
+      </c>
+      <c r="K325" s="3">
+        <v>0</v>
+      </c>
+      <c r="L325" s="3">
+        <v>0</v>
+      </c>
+      <c r="M325" s="3">
+        <v>0</v>
+      </c>
+      <c r="N325" s="3">
+        <v>0</v>
+      </c>
+      <c r="O325" s="3">
+        <v>0</v>
+      </c>
+      <c r="P325" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q325" s="3">
+        <v>0</v>
+      </c>
+      <c r="R325" s="3">
+        <v>0</v>
+      </c>
+      <c r="S325" s="3">
+        <v>0</v>
+      </c>
+      <c r="T325" s="3">
+        <v>0</v>
+      </c>
+      <c r="U325" s="3">
+        <v>0</v>
+      </c>
+      <c r="V325" s="3">
+        <v>0</v>
+      </c>
+      <c r="W325" s="3">
+        <v>0</v>
+      </c>
+      <c r="X325" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y325" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z325" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA325" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB325" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AE325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AF325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AH325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AJ325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK325" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AM325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AN325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AO325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AP325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AQ325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AS325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AT325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AU325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AV325" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="AW324" s="5">
-        <v>0</v>
-      </c>
-      <c r="AX324" s="5">
+      <c r="AW325" s="5">
+        <v>0</v>
+      </c>
+      <c r="AX325" s="5">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C83806C-2F7C-41B2-A85D-DE2FAB53FB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8753C3-D030-4B87-BD7A-2AF8893ECEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="1830" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -38499,7 +38499,7 @@
         <v>0</v>
       </c>
       <c r="J233" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K233" s="3">
         <v>0</v>
@@ -38520,7 +38520,7 @@
         <v>0</v>
       </c>
       <c r="Q233" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R233" s="3">
         <v>0</v>
@@ -38652,7 +38652,7 @@
         <v>0</v>
       </c>
       <c r="J234" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K234" s="3">
         <v>0</v>
@@ -38673,7 +38673,7 @@
         <v>0</v>
       </c>
       <c r="Q234" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R234" s="3">
         <v>0</v>
@@ -38805,7 +38805,7 @@
         <v>0</v>
       </c>
       <c r="J235" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K235" s="3">
         <v>0</v>
@@ -38826,7 +38826,7 @@
         <v>0</v>
       </c>
       <c r="Q235" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R235" s="3">
         <v>0</v>
@@ -38958,7 +38958,7 @@
         <v>0</v>
       </c>
       <c r="J236" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K236" s="3">
         <v>0</v>
@@ -38979,7 +38979,7 @@
         <v>0</v>
       </c>
       <c r="Q236" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R236" s="3">
         <v>0</v>
@@ -39111,7 +39111,7 @@
         <v>0</v>
       </c>
       <c r="J237" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K237" s="3">
         <v>0</v>
@@ -39132,7 +39132,7 @@
         <v>0</v>
       </c>
       <c r="Q237" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R237" s="3">
         <v>0</v>
@@ -39264,7 +39264,7 @@
         <v>0</v>
       </c>
       <c r="J238" s="3">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K238" s="3">
         <v>0</v>
@@ -39285,7 +39285,7 @@
         <v>0</v>
       </c>
       <c r="Q238" s="3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="R238" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8753C3-D030-4B87-BD7A-2AF8893ECEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA603DEA-628A-4058-B0A1-AAC805666EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1830" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="476">
   <si>
     <t>desc</t>
   </si>
@@ -2520,6 +2520,10 @@
     <t>choco_banana_crepe</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>SaltTopping</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -18747,7 +18751,7 @@
         <v>7</v>
       </c>
       <c r="E104" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F104" s="3">
         <v>0</v>
@@ -38337,7 +38341,7 @@
         <v>0</v>
       </c>
       <c r="G232" s="3">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H232" s="3">
         <v>0</v>
@@ -38346,7 +38350,7 @@
         <v>0</v>
       </c>
       <c r="J232" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K232" s="3">
         <v>0</v>
@@ -38367,7 +38371,7 @@
         <v>0</v>
       </c>
       <c r="Q232" s="3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="R232" s="3">
         <v>0</v>
@@ -38490,7 +38494,7 @@
         <v>0</v>
       </c>
       <c r="G233" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H233" s="3">
         <v>0</v>
@@ -38556,7 +38560,7 @@
         <v>0</v>
       </c>
       <c r="AC233" s="5" t="s">
-        <v>7</v>
+        <v>475</v>
       </c>
       <c r="AD233" s="5" t="s">
         <v>7</v>
@@ -38583,7 +38587,7 @@
         <v>7</v>
       </c>
       <c r="AL233" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM233" s="5">
         <v>0</v>
@@ -38643,7 +38647,7 @@
         <v>0</v>
       </c>
       <c r="G234" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H234" s="3">
         <v>0</v>
@@ -38709,7 +38713,7 @@
         <v>0</v>
       </c>
       <c r="AC234" s="5" t="s">
-        <v>7</v>
+        <v>475</v>
       </c>
       <c r="AD234" s="5" t="s">
         <v>7</v>
@@ -38736,7 +38740,7 @@
         <v>7</v>
       </c>
       <c r="AL234" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM234" s="5">
         <v>0</v>
@@ -38796,7 +38800,7 @@
         <v>0</v>
       </c>
       <c r="G235" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="H235" s="3">
         <v>0</v>
@@ -38949,7 +38953,7 @@
         <v>0</v>
       </c>
       <c r="G236" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H236" s="3">
         <v>0</v>
@@ -39015,7 +39019,7 @@
         <v>0</v>
       </c>
       <c r="AC236" s="5" t="s">
-        <v>7</v>
+        <v>475</v>
       </c>
       <c r="AD236" s="5" t="s">
         <v>7</v>
@@ -39042,7 +39046,7 @@
         <v>7</v>
       </c>
       <c r="AL236" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM236" s="5">
         <v>0</v>
@@ -39102,7 +39106,7 @@
         <v>0</v>
       </c>
       <c r="G237" s="3">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="H237" s="3">
         <v>0</v>
@@ -39168,7 +39172,7 @@
         <v>0</v>
       </c>
       <c r="AC237" s="5" t="s">
-        <v>7</v>
+        <v>475</v>
       </c>
       <c r="AD237" s="5" t="s">
         <v>7</v>
@@ -39195,7 +39199,7 @@
         <v>7</v>
       </c>
       <c r="AL237" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM237" s="5">
         <v>0</v>
@@ -39255,7 +39259,7 @@
         <v>0</v>
       </c>
       <c r="G238" s="3">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H238" s="3">
         <v>0</v>
@@ -39321,7 +39325,7 @@
         <v>0</v>
       </c>
       <c r="AC238" s="5" t="s">
-        <v>7</v>
+        <v>475</v>
       </c>
       <c r="AD238" s="5" t="s">
         <v>7</v>
@@ -39348,7 +39352,7 @@
         <v>7</v>
       </c>
       <c r="AL238" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM238" s="5">
         <v>0</v>
@@ -39402,7 +39406,7 @@
         <v>7</v>
       </c>
       <c r="E239" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F239" s="3">
         <v>0</v>
@@ -39411,10 +39415,10 @@
         <v>35</v>
       </c>
       <c r="H239" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I239" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J239" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA603DEA-628A-4058-B0A1-AAC805666EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACE3E8A-865F-4BA0-928A-B4CD7137F646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1230" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2085" yWindow="795" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -8806,7 +8806,7 @@
         <v>7</v>
       </c>
       <c r="E39" s="3">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="F39" s="3">
         <v>0</v>
@@ -8821,7 +8821,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K39" s="3">
         <v>0</v>
@@ -8905,7 +8905,7 @@
         <v>7</v>
       </c>
       <c r="AL39" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AM39" s="5">
         <v>50</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACE3E8A-865F-4BA0-928A-B4CD7137F646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C769E9-1760-423B-9606-0ACB8E7C9492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2085" yWindow="795" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="478">
   <si>
     <t>desc</t>
   </si>
@@ -2524,6 +2524,14 @@
     <t>SaltTopping</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>WhipeedCreamMaron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>WhipeedCreamLemon</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -10102,10 +10110,10 @@
         <v>0</v>
       </c>
       <c r="AC47" s="5" t="s">
-        <v>7</v>
+        <v>476</v>
       </c>
       <c r="AD47" s="5" t="s">
-        <v>7</v>
+        <v>245</v>
       </c>
       <c r="AE47" s="5" t="s">
         <v>7</v>
@@ -10129,10 +10137,10 @@
         <v>7</v>
       </c>
       <c r="AL47" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM47" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN47" s="5">
         <v>0</v>
@@ -13774,13 +13782,13 @@
         <v>0</v>
       </c>
       <c r="AC71" s="5" t="s">
-        <v>7</v>
+        <v>476</v>
       </c>
       <c r="AD71" s="5" t="s">
-        <v>7</v>
+        <v>477</v>
       </c>
       <c r="AE71" s="5" t="s">
-        <v>7</v>
+        <v>245</v>
       </c>
       <c r="AF71" s="5" t="s">
         <v>7</v>
@@ -13801,13 +13809,13 @@
         <v>7</v>
       </c>
       <c r="AL71" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM71" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN71" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO71" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2C769E9-1760-423B-9606-0ACB8E7C9492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8D6466-8B31-4D95-A9F5-733A6984FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="1335" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K10" s="3">
         <v>0</v>
@@ -11889,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -12042,7 +12042,7 @@
         <v>30</v>
       </c>
       <c r="J60" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -12195,7 +12195,7 @@
         <v>30</v>
       </c>
       <c r="J61" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -12348,7 +12348,7 @@
         <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -12501,7 +12501,7 @@
         <v>30</v>
       </c>
       <c r="J63" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K63" s="3">
         <v>0</v>
@@ -12654,7 +12654,7 @@
         <v>30</v>
       </c>
       <c r="J64" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K64" s="3">
         <v>0</v>
@@ -12807,7 +12807,7 @@
         <v>30</v>
       </c>
       <c r="J65" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K65" s="3">
         <v>0</v>
@@ -12960,7 +12960,7 @@
         <v>30</v>
       </c>
       <c r="J66" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D8D6466-8B31-4D95-A9F5-733A6984FF66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA875A7D-C8B6-4C15-B807-C9C056A797F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1335" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1605" yWindow="1080" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -47250,7 +47250,7 @@
         <v>0</v>
       </c>
       <c r="P290" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="Q290" s="3">
         <v>55</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA875A7D-C8B6-4C15-B807-C9C056A797F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF1BA00-5E3D-479A-9DF2-4C1DCB27352F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1605" yWindow="1080" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -34386,7 +34386,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="3">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M206" s="3">
         <v>50</v>
@@ -44484,10 +44484,10 @@
         <v>0</v>
       </c>
       <c r="L272" s="3">
+        <v>0</v>
+      </c>
+      <c r="M272" s="3">
         <v>100</v>
-      </c>
-      <c r="M272" s="3">
-        <v>0</v>
       </c>
       <c r="N272" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF1BA00-5E3D-479A-9DF2-4C1DCB27352F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9C3F50-36AB-4826-A260-8CB163CDC43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -18606,7 +18606,7 @@
         <v>7</v>
       </c>
       <c r="E103" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F103" s="3">
         <v>0</v>
@@ -18759,7 +18759,7 @@
         <v>7</v>
       </c>
       <c r="E104" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F104" s="3">
         <v>0</v>
@@ -18912,7 +18912,7 @@
         <v>7</v>
       </c>
       <c r="E105" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F105" s="3">
         <v>0</v>
@@ -19830,7 +19830,7 @@
         <v>7</v>
       </c>
       <c r="E111" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F111" s="3">
         <v>0</v>
@@ -20901,7 +20901,7 @@
         <v>7</v>
       </c>
       <c r="E118" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F118" s="3">
         <v>0</v>
@@ -21054,7 +21054,7 @@
         <v>7</v>
       </c>
       <c r="E119" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F119" s="3">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>30</v>
       </c>
       <c r="I135" s="3">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J135" s="3">
         <v>0</v>
@@ -23655,7 +23655,7 @@
         <v>7</v>
       </c>
       <c r="E136" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F136" s="3">
         <v>0</v>
@@ -23667,7 +23667,7 @@
         <v>30</v>
       </c>
       <c r="I136" s="3">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="J136" s="3">
         <v>0</v>
@@ -23808,7 +23808,7 @@
         <v>7</v>
       </c>
       <c r="E137" s="3">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="F137" s="3">
         <v>0</v>
@@ -23820,7 +23820,7 @@
         <v>20</v>
       </c>
       <c r="I137" s="3">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="J137" s="3">
         <v>0</v>
@@ -23961,7 +23961,7 @@
         <v>7</v>
       </c>
       <c r="E138" s="3">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="F138" s="3">
         <v>0</v>
@@ -23973,7 +23973,7 @@
         <v>30</v>
       </c>
       <c r="I138" s="3">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="J138" s="3">
         <v>0</v>
@@ -24114,7 +24114,7 @@
         <v>7</v>
       </c>
       <c r="E139" s="3">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="F139" s="3">
         <v>0</v>
@@ -24126,7 +24126,7 @@
         <v>30</v>
       </c>
       <c r="I139" s="3">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="J139" s="3">
         <v>0</v>
@@ -25185,7 +25185,7 @@
         <v>7</v>
       </c>
       <c r="E146" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F146" s="3">
         <v>0</v>
@@ -25338,7 +25338,7 @@
         <v>7</v>
       </c>
       <c r="E147" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F147" s="3">
         <v>0</v>
@@ -25491,7 +25491,7 @@
         <v>7</v>
       </c>
       <c r="E148" s="3">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F148" s="3">
         <v>0</v>
@@ -26409,7 +26409,7 @@
         <v>7</v>
       </c>
       <c r="E154" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F154" s="3">
         <v>0</v>
@@ -26562,7 +26562,7 @@
         <v>7</v>
       </c>
       <c r="E155" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F155" s="3">
         <v>0</v>
@@ -27786,7 +27786,7 @@
         <v>7</v>
       </c>
       <c r="E163" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F163" s="3">
         <v>0</v>
@@ -29622,7 +29622,7 @@
         <v>7</v>
       </c>
       <c r="E175" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F175" s="3">
         <v>0</v>
@@ -32223,7 +32223,7 @@
         <v>7</v>
       </c>
       <c r="E192" s="3">
-        <v>-500</v>
+        <v>-50</v>
       </c>
       <c r="F192" s="3">
         <v>0</v>
@@ -37119,7 +37119,7 @@
         <v>7</v>
       </c>
       <c r="E224" s="3">
-        <v>-50</v>
+        <v>-20</v>
       </c>
       <c r="F224" s="3">
         <v>0</v>
@@ -37425,7 +37425,7 @@
         <v>7</v>
       </c>
       <c r="E226" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F226" s="3">
         <v>0</v>
@@ -37578,7 +37578,7 @@
         <v>7</v>
       </c>
       <c r="E227" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F227" s="3">
         <v>0</v>
@@ -37731,7 +37731,7 @@
         <v>7</v>
       </c>
       <c r="E228" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F228" s="3">
         <v>0</v>
@@ -39261,7 +39261,7 @@
         <v>7</v>
       </c>
       <c r="E238" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F238" s="3">
         <v>0</v>
@@ -39414,7 +39414,7 @@
         <v>7</v>
       </c>
       <c r="E239" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F239" s="3">
         <v>0</v>
@@ -43608,7 +43608,7 @@
         <v>0</v>
       </c>
       <c r="Z266" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA266" s="3">
         <v>0</v>
@@ -43761,7 +43761,7 @@
         <v>0</v>
       </c>
       <c r="Z267" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA267" s="3">
         <v>0</v>
@@ -43914,7 +43914,7 @@
         <v>0</v>
       </c>
       <c r="Z268" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA268" s="3">
         <v>0</v>
@@ -44220,7 +44220,7 @@
         <v>0</v>
       </c>
       <c r="Z270" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AA270" s="3">
         <v>0</v>
@@ -44373,7 +44373,7 @@
         <v>0</v>
       </c>
       <c r="Z271" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AA271" s="3">
         <v>0</v>
@@ -44463,7 +44463,7 @@
         <v>7</v>
       </c>
       <c r="E272" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F272" s="3">
         <v>0</v>
@@ -44526,7 +44526,7 @@
         <v>0</v>
       </c>
       <c r="Z272" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AA272" s="3">
         <v>0</v>
@@ -44769,7 +44769,7 @@
         <v>7</v>
       </c>
       <c r="E274" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F274" s="3">
         <v>0</v>
@@ -44922,7 +44922,7 @@
         <v>7</v>
       </c>
       <c r="E275" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F275" s="3">
         <v>0</v>
@@ -45075,7 +45075,7 @@
         <v>7</v>
       </c>
       <c r="E276" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F276" s="3">
         <v>0</v>
@@ -45228,7 +45228,7 @@
         <v>7</v>
       </c>
       <c r="E277" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F277" s="3">
         <v>0</v>
@@ -45381,7 +45381,7 @@
         <v>7</v>
       </c>
       <c r="E278" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F278" s="3">
         <v>0</v>
@@ -45534,7 +45534,7 @@
         <v>7</v>
       </c>
       <c r="E279" s="3">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="F279" s="3">
         <v>0</v>
@@ -45687,7 +45687,7 @@
         <v>395</v>
       </c>
       <c r="E280" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F280" s="3">
         <v>0</v>
@@ -45750,7 +45750,7 @@
         <v>0</v>
       </c>
       <c r="Z280" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AA280" s="3">
         <v>0</v>
@@ -45840,7 +45840,7 @@
         <v>396</v>
       </c>
       <c r="E281" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F281" s="3">
         <v>0</v>
@@ -45993,7 +45993,7 @@
         <v>397</v>
       </c>
       <c r="E282" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F282" s="3">
         <v>0</v>
@@ -46146,7 +46146,7 @@
         <v>398</v>
       </c>
       <c r="E283" s="3">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F283" s="3">
         <v>0</v>
@@ -46209,7 +46209,7 @@
         <v>0</v>
       </c>
       <c r="Z283" s="3">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="AA283" s="3">
         <v>0</v>
@@ -46452,7 +46452,7 @@
         <v>7</v>
       </c>
       <c r="E285" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F285" s="3">
         <v>0</v>
@@ -46605,7 +46605,7 @@
         <v>7</v>
       </c>
       <c r="E286" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F286" s="3">
         <v>0</v>
@@ -46758,7 +46758,7 @@
         <v>7</v>
       </c>
       <c r="E287" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F287" s="3">
         <v>0</v>
@@ -46911,7 +46911,7 @@
         <v>7</v>
       </c>
       <c r="E288" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F288" s="3">
         <v>0</v>
@@ -48441,7 +48441,7 @@
         <v>7</v>
       </c>
       <c r="E298" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F298" s="3">
         <v>0</v>
@@ -48594,7 +48594,7 @@
         <v>7</v>
       </c>
       <c r="E299" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F299" s="3">
         <v>0</v>
@@ -48747,7 +48747,7 @@
         <v>7</v>
       </c>
       <c r="E300" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F300" s="3">
         <v>0</v>
@@ -48900,7 +48900,7 @@
         <v>7</v>
       </c>
       <c r="E301" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F301" s="3">
         <v>0</v>
@@ -49053,7 +49053,7 @@
         <v>7</v>
       </c>
       <c r="E302" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F302" s="3">
         <v>0</v>
@@ -49665,7 +49665,7 @@
         <v>7</v>
       </c>
       <c r="E306" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F306" s="3">
         <v>0</v>
@@ -49818,7 +49818,7 @@
         <v>7</v>
       </c>
       <c r="E307" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F307" s="3">
         <v>0</v>
@@ -49971,7 +49971,7 @@
         <v>7</v>
       </c>
       <c r="E308" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F308" s="3">
         <v>0</v>
@@ -50124,7 +50124,7 @@
         <v>7</v>
       </c>
       <c r="E309" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F309" s="3">
         <v>0</v>
@@ -50277,7 +50277,7 @@
         <v>7</v>
       </c>
       <c r="E310" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F310" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F24558-8CF8-4B75-A0FE-4CA86A4FFB97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA06F48F-6A5B-4F20-87F5-894B3386C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1305" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3950" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3950" uniqueCount="485">
   <si>
     <t>desc</t>
   </si>
@@ -2536,6 +2536,30 @@
     <t>forget_me_not_base</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>ChocolateBear</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ChocolateBearWhite</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GoldLeaf</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Maron</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GlowBanana</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>GlowCherry</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -27034,7 +27058,7 @@
         <v>180</v>
       </c>
       <c r="H158" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I158" s="3">
         <v>40</v>
@@ -27103,7 +27127,7 @@
         <v>45</v>
       </c>
       <c r="AE158" s="5" t="s">
-        <v>7</v>
+        <v>482</v>
       </c>
       <c r="AF158" s="5" t="s">
         <v>7</v>
@@ -27130,7 +27154,7 @@
         <v>30</v>
       </c>
       <c r="AN158" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO158" s="5">
         <v>0</v>
@@ -27490,10 +27514,10 @@
         <v>0</v>
       </c>
       <c r="G161" s="3">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="H161" s="3">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="I161" s="3">
         <v>50</v>
@@ -27643,10 +27667,10 @@
         <v>0</v>
       </c>
       <c r="G162" s="3">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="H162" s="3">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="I162" s="3">
         <v>50</v>
@@ -27712,7 +27736,7 @@
         <v>445</v>
       </c>
       <c r="AD162" s="5" t="s">
-        <v>7</v>
+        <v>481</v>
       </c>
       <c r="AE162" s="5" t="s">
         <v>7</v>
@@ -27739,7 +27763,7 @@
         <v>30</v>
       </c>
       <c r="AM162" s="5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN162" s="5">
         <v>0</v>
@@ -27799,7 +27823,7 @@
         <v>180</v>
       </c>
       <c r="H163" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I163" s="3">
         <v>50</v>
@@ -27865,16 +27889,16 @@
         <v>445</v>
       </c>
       <c r="AD163" s="5" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="AE163" s="5" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="AF163" s="5" t="s">
-        <v>7</v>
+        <v>479</v>
       </c>
       <c r="AG163" s="5" t="s">
-        <v>7</v>
+        <v>480</v>
       </c>
       <c r="AH163" s="5" t="s">
         <v>7</v>
@@ -27892,16 +27916,16 @@
         <v>30</v>
       </c>
       <c r="AM163" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN163" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO163" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP163" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AQ163" s="5">
         <v>0</v>
@@ -27952,7 +27976,7 @@
         <v>180</v>
       </c>
       <c r="H164" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I164" s="3">
         <v>50</v>
@@ -28018,16 +28042,16 @@
         <v>445</v>
       </c>
       <c r="AD164" s="5" t="s">
-        <v>7</v>
+        <v>196</v>
       </c>
       <c r="AE164" s="5" t="s">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="AF164" s="5" t="s">
-        <v>7</v>
+        <v>479</v>
       </c>
       <c r="AG164" s="5" t="s">
-        <v>7</v>
+        <v>480</v>
       </c>
       <c r="AH164" s="5" t="s">
         <v>7</v>
@@ -28045,16 +28069,16 @@
         <v>40</v>
       </c>
       <c r="AM164" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AN164" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO164" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP164" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AQ164" s="5">
         <v>0</v>
@@ -28477,7 +28501,7 @@
         <v>45</v>
       </c>
       <c r="AD167" s="5" t="s">
-        <v>7</v>
+        <v>483</v>
       </c>
       <c r="AE167" s="5" t="s">
         <v>7</v>
@@ -28504,7 +28528,7 @@
         <v>20</v>
       </c>
       <c r="AM167" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN167" s="5">
         <v>0</v>
@@ -28936,7 +28960,7 @@
         <v>45</v>
       </c>
       <c r="AD170" s="5" t="s">
-        <v>7</v>
+        <v>483</v>
       </c>
       <c r="AE170" s="5" t="s">
         <v>7</v>
@@ -28963,7 +28987,7 @@
         <v>20</v>
       </c>
       <c r="AM170" s="5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AN170" s="5">
         <v>0</v>
@@ -31993,10 +32017,10 @@
         <v>0</v>
       </c>
       <c r="AC190" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AD190" s="5" t="s">
-        <v>7</v>
+        <v>484</v>
       </c>
       <c r="AE190" s="5" t="s">
         <v>7</v>
@@ -32020,10 +32044,10 @@
         <v>7</v>
       </c>
       <c r="AL190" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM190" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AN190" s="5">
         <v>0</v>
@@ -32146,10 +32170,10 @@
         <v>0</v>
       </c>
       <c r="AC191" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AD191" s="5" t="s">
-        <v>7</v>
+        <v>484</v>
       </c>
       <c r="AE191" s="5" t="s">
         <v>7</v>
@@ -32173,10 +32197,10 @@
         <v>7</v>
       </c>
       <c r="AL191" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM191" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AN191" s="5">
         <v>0</v>
@@ -32299,10 +32323,10 @@
         <v>0</v>
       </c>
       <c r="AC192" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AD192" s="5" t="s">
-        <v>7</v>
+        <v>484</v>
       </c>
       <c r="AE192" s="5" t="s">
         <v>7</v>
@@ -32326,10 +32350,10 @@
         <v>7</v>
       </c>
       <c r="AL192" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM192" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AN192" s="5">
         <v>0</v>
@@ -32452,10 +32476,10 @@
         <v>0</v>
       </c>
       <c r="AC193" s="5" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="AD193" s="5" t="s">
-        <v>7</v>
+        <v>484</v>
       </c>
       <c r="AE193" s="5" t="s">
         <v>7</v>
@@ -32479,10 +32503,10 @@
         <v>7</v>
       </c>
       <c r="AL193" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM193" s="5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AN193" s="5">
         <v>0</v>
@@ -35014,7 +35038,7 @@
         <v>0</v>
       </c>
       <c r="P210" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q210" s="3">
         <v>55</v>
@@ -35167,7 +35191,7 @@
         <v>0</v>
       </c>
       <c r="P211" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q211" s="3">
         <v>55</v>
@@ -35320,7 +35344,7 @@
         <v>0</v>
       </c>
       <c r="P212" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q212" s="3">
         <v>70</v>
@@ -35473,7 +35497,7 @@
         <v>0</v>
       </c>
       <c r="P213" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q213" s="3">
         <v>70</v>
@@ -35626,7 +35650,7 @@
         <v>0</v>
       </c>
       <c r="P214" s="3">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="Q214" s="3">
         <v>70</v>
@@ -35779,7 +35803,7 @@
         <v>0</v>
       </c>
       <c r="P215" s="3">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q215" s="3">
         <v>70</v>
@@ -35932,7 +35956,7 @@
         <v>0</v>
       </c>
       <c r="P216" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q216" s="3">
         <v>55</v>
@@ -36085,7 +36109,7 @@
         <v>0</v>
       </c>
       <c r="P217" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q217" s="3">
         <v>55</v>
@@ -36238,7 +36262,7 @@
         <v>0</v>
       </c>
       <c r="P218" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q218" s="3">
         <v>55</v>
@@ -36391,7 +36415,7 @@
         <v>0</v>
       </c>
       <c r="P219" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q219" s="3">
         <v>55</v>
@@ -36544,7 +36568,7 @@
         <v>0</v>
       </c>
       <c r="P220" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q220" s="3">
         <v>55</v>
@@ -36697,7 +36721,7 @@
         <v>0</v>
       </c>
       <c r="P221" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q221" s="3">
         <v>55</v>
@@ -36850,7 +36874,7 @@
         <v>0</v>
       </c>
       <c r="P222" s="3">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q222" s="3">
         <v>55</v>
@@ -37003,7 +37027,7 @@
         <v>0</v>
       </c>
       <c r="P223" s="3">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Q223" s="3">
         <v>55</v>
@@ -37156,7 +37180,7 @@
         <v>0</v>
       </c>
       <c r="P224" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q224" s="3">
         <v>55</v>
@@ -37309,7 +37333,7 @@
         <v>0</v>
       </c>
       <c r="P225" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q225" s="3">
         <v>55</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA06F48F-6A5B-4F20-87F5-894B3386C4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF521FB-89ED-41F7-ACC2-6DBF5D1C3009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="1125" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE29376-E7C8-4BEC-8C21-132439AA8CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0F6EC4-7D62-46F5-8AB4-FB42D9D22126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3315" yWindow="1830" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="705" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -32565,7 +32565,7 @@
         <v>485</v>
       </c>
       <c r="E194" s="3">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F194" s="3">
         <v>0</v>
@@ -32718,7 +32718,7 @@
         <v>7</v>
       </c>
       <c r="E195" s="3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F195" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0F6EC4-7D62-46F5-8AB4-FB42D9D22126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E62356-450E-42D6-93F8-D26FBB4B09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="705" windowWidth="25485" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2430" yWindow="1065" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -28971,10 +28971,10 @@
         <v>483</v>
       </c>
       <c r="AE170" s="5" t="s">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="AF170" s="5" t="s">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="AG170" s="5" t="s">
         <v>7</v>
@@ -28998,10 +28998,10 @@
         <v>50</v>
       </c>
       <c r="AN170" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO170" s="5">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AP170" s="5">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E62356-450E-42D6-93F8-D26FBB4B09F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7AD5EA0-F705-47DC-873A-E5C996DB4452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2430" yWindow="1065" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2715" yWindow="1230" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3974" uniqueCount="487">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3974" uniqueCount="489">
   <si>
     <t>desc</t>
   </si>
@@ -2568,6 +2568,14 @@
     <t>jelly_blacklotus</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>NutsPistachio</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>JemNuts</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -7029,7 +7037,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="3">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="K27" s="3">
         <v>0</v>
@@ -7092,10 +7100,10 @@
         <v>260</v>
       </c>
       <c r="AE27" s="5" t="s">
-        <v>7</v>
+        <v>487</v>
       </c>
       <c r="AF27" s="5" t="s">
-        <v>7</v>
+        <v>488</v>
       </c>
       <c r="AG27" s="5" t="s">
         <v>7</v>
@@ -7119,10 +7127,10 @@
         <v>15</v>
       </c>
       <c r="AN27" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AO27" s="5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AP27" s="5">
         <v>0</v>
@@ -44040,7 +44048,7 @@
         <v>7</v>
       </c>
       <c r="E269" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F269" s="3">
         <v>0</v>
@@ -44193,7 +44201,7 @@
         <v>7</v>
       </c>
       <c r="E270" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F270" s="3">
         <v>0</v>
@@ -44346,7 +44354,7 @@
         <v>7</v>
       </c>
       <c r="E271" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="F271" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAD0625-2417-45FD-B504-2788562F6B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E97B673-FCD6-4F6F-ACB1-1FB0002D4F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1230" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2190" yWindow="615" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -7515,7 +7515,7 @@
         <v>50</v>
       </c>
       <c r="J30" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K30" s="3">
         <v>0</v>
@@ -7668,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K31" s="3">
         <v>20</v>
@@ -7821,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -7974,7 +7974,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K33" s="3">
         <v>0</v>
@@ -8280,7 +8280,7 @@
         <v>50</v>
       </c>
       <c r="J35" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K35" s="3">
         <v>0</v>
@@ -8433,7 +8433,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K36" s="3">
         <v>0</v>
@@ -8586,7 +8586,7 @@
         <v>30</v>
       </c>
       <c r="J37" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K37" s="3">
         <v>0</v>
@@ -8739,7 +8739,7 @@
         <v>30</v>
       </c>
       <c r="J38" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K38" s="3">
         <v>0</v>
@@ -9045,7 +9045,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K40" s="3">
         <v>0</v>
@@ -9351,7 +9351,7 @@
         <v>30</v>
       </c>
       <c r="J42" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -9963,7 +9963,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -10116,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -10269,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -13329,7 +13329,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K68" s="3">
         <v>0</v>
@@ -13482,7 +13482,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K69" s="3">
         <v>0</v>
@@ -13635,7 +13635,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="3">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="K71" s="3">
         <v>0</v>
@@ -39936,7 +39936,7 @@
         <v>7</v>
       </c>
       <c r="E242" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F242" s="3">
         <v>0</v>
@@ -40089,7 +40089,7 @@
         <v>7</v>
       </c>
       <c r="E243" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F243" s="3">
         <v>0</v>
@@ -40395,7 +40395,7 @@
         <v>7</v>
       </c>
       <c r="E245" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F245" s="3">
         <v>0</v>
@@ -40410,28 +40410,28 @@
         <v>50</v>
       </c>
       <c r="J245" s="3">
+        <v>50</v>
+      </c>
+      <c r="K245" s="3">
+        <v>0</v>
+      </c>
+      <c r="L245" s="3">
+        <v>0</v>
+      </c>
+      <c r="M245" s="3">
+        <v>0</v>
+      </c>
+      <c r="N245" s="3">
+        <v>0</v>
+      </c>
+      <c r="O245" s="3">
+        <v>0</v>
+      </c>
+      <c r="P245" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q245" s="3">
         <v>60</v>
-      </c>
-      <c r="K245" s="3">
-        <v>0</v>
-      </c>
-      <c r="L245" s="3">
-        <v>0</v>
-      </c>
-      <c r="M245" s="3">
-        <v>0</v>
-      </c>
-      <c r="N245" s="3">
-        <v>0</v>
-      </c>
-      <c r="O245" s="3">
-        <v>0</v>
-      </c>
-      <c r="P245" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q245" s="3">
-        <v>65</v>
       </c>
       <c r="R245" s="3">
         <v>0</v>
@@ -40548,7 +40548,7 @@
         <v>7</v>
       </c>
       <c r="E246" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F246" s="3">
         <v>0</v>
@@ -40563,28 +40563,28 @@
         <v>30</v>
       </c>
       <c r="J246" s="3">
+        <v>50</v>
+      </c>
+      <c r="K246" s="3">
+        <v>0</v>
+      </c>
+      <c r="L246" s="3">
+        <v>0</v>
+      </c>
+      <c r="M246" s="3">
+        <v>0</v>
+      </c>
+      <c r="N246" s="3">
+        <v>0</v>
+      </c>
+      <c r="O246" s="3">
+        <v>0</v>
+      </c>
+      <c r="P246" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q246" s="3">
         <v>60</v>
-      </c>
-      <c r="K246" s="3">
-        <v>0</v>
-      </c>
-      <c r="L246" s="3">
-        <v>0</v>
-      </c>
-      <c r="M246" s="3">
-        <v>0</v>
-      </c>
-      <c r="N246" s="3">
-        <v>0</v>
-      </c>
-      <c r="O246" s="3">
-        <v>0</v>
-      </c>
-      <c r="P246" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q246" s="3">
-        <v>65</v>
       </c>
       <c r="R246" s="3">
         <v>0</v>
@@ -40701,7 +40701,7 @@
         <v>7</v>
       </c>
       <c r="E247" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F247" s="3">
         <v>0</v>
@@ -40716,28 +40716,28 @@
         <v>30</v>
       </c>
       <c r="J247" s="3">
+        <v>50</v>
+      </c>
+      <c r="K247" s="3">
+        <v>0</v>
+      </c>
+      <c r="L247" s="3">
+        <v>0</v>
+      </c>
+      <c r="M247" s="3">
+        <v>0</v>
+      </c>
+      <c r="N247" s="3">
+        <v>0</v>
+      </c>
+      <c r="O247" s="3">
+        <v>0</v>
+      </c>
+      <c r="P247" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q247" s="3">
         <v>60</v>
-      </c>
-      <c r="K247" s="3">
-        <v>0</v>
-      </c>
-      <c r="L247" s="3">
-        <v>0</v>
-      </c>
-      <c r="M247" s="3">
-        <v>0</v>
-      </c>
-      <c r="N247" s="3">
-        <v>0</v>
-      </c>
-      <c r="O247" s="3">
-        <v>0</v>
-      </c>
-      <c r="P247" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q247" s="3">
-        <v>65</v>
       </c>
       <c r="R247" s="3">
         <v>0</v>
@@ -40854,7 +40854,7 @@
         <v>7</v>
       </c>
       <c r="E248" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F248" s="3">
         <v>0</v>
@@ -40869,28 +40869,28 @@
         <v>0</v>
       </c>
       <c r="J248" s="3">
+        <v>50</v>
+      </c>
+      <c r="K248" s="3">
+        <v>0</v>
+      </c>
+      <c r="L248" s="3">
+        <v>0</v>
+      </c>
+      <c r="M248" s="3">
+        <v>0</v>
+      </c>
+      <c r="N248" s="3">
+        <v>0</v>
+      </c>
+      <c r="O248" s="3">
+        <v>0</v>
+      </c>
+      <c r="P248" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q248" s="3">
         <v>60</v>
-      </c>
-      <c r="K248" s="3">
-        <v>0</v>
-      </c>
-      <c r="L248" s="3">
-        <v>0</v>
-      </c>
-      <c r="M248" s="3">
-        <v>0</v>
-      </c>
-      <c r="N248" s="3">
-        <v>0</v>
-      </c>
-      <c r="O248" s="3">
-        <v>0</v>
-      </c>
-      <c r="P248" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q248" s="3">
-        <v>65</v>
       </c>
       <c r="R248" s="3">
         <v>0</v>
@@ -41007,7 +41007,7 @@
         <v>7</v>
       </c>
       <c r="E249" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F249" s="3">
         <v>0</v>
@@ -41022,28 +41022,28 @@
         <v>50</v>
       </c>
       <c r="J249" s="3">
+        <v>50</v>
+      </c>
+      <c r="K249" s="3">
+        <v>0</v>
+      </c>
+      <c r="L249" s="3">
+        <v>0</v>
+      </c>
+      <c r="M249" s="3">
+        <v>0</v>
+      </c>
+      <c r="N249" s="3">
+        <v>0</v>
+      </c>
+      <c r="O249" s="3">
+        <v>0</v>
+      </c>
+      <c r="P249" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q249" s="3">
         <v>60</v>
-      </c>
-      <c r="K249" s="3">
-        <v>0</v>
-      </c>
-      <c r="L249" s="3">
-        <v>0</v>
-      </c>
-      <c r="M249" s="3">
-        <v>0</v>
-      </c>
-      <c r="N249" s="3">
-        <v>0</v>
-      </c>
-      <c r="O249" s="3">
-        <v>0</v>
-      </c>
-      <c r="P249" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q249" s="3">
-        <v>65</v>
       </c>
       <c r="R249" s="3">
         <v>0</v>
@@ -41160,7 +41160,7 @@
         <v>7</v>
       </c>
       <c r="E250" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F250" s="3">
         <v>0</v>
@@ -41175,28 +41175,28 @@
         <v>0</v>
       </c>
       <c r="J250" s="3">
+        <v>50</v>
+      </c>
+      <c r="K250" s="3">
+        <v>0</v>
+      </c>
+      <c r="L250" s="3">
+        <v>0</v>
+      </c>
+      <c r="M250" s="3">
+        <v>0</v>
+      </c>
+      <c r="N250" s="3">
+        <v>0</v>
+      </c>
+      <c r="O250" s="3">
+        <v>0</v>
+      </c>
+      <c r="P250" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q250" s="3">
         <v>60</v>
-      </c>
-      <c r="K250" s="3">
-        <v>0</v>
-      </c>
-      <c r="L250" s="3">
-        <v>0</v>
-      </c>
-      <c r="M250" s="3">
-        <v>0</v>
-      </c>
-      <c r="N250" s="3">
-        <v>0</v>
-      </c>
-      <c r="O250" s="3">
-        <v>0</v>
-      </c>
-      <c r="P250" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q250" s="3">
-        <v>65</v>
       </c>
       <c r="R250" s="3">
         <v>0</v>
@@ -41313,7 +41313,7 @@
         <v>7</v>
       </c>
       <c r="E251" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F251" s="3">
         <v>0</v>
@@ -41328,7 +41328,7 @@
         <v>0</v>
       </c>
       <c r="J251" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K251" s="3">
         <v>0</v>
@@ -41349,7 +41349,7 @@
         <v>0</v>
       </c>
       <c r="Q251" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R251" s="3">
         <v>0</v>
@@ -41466,7 +41466,7 @@
         <v>7</v>
       </c>
       <c r="E252" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F252" s="3">
         <v>0</v>
@@ -41481,7 +41481,7 @@
         <v>0</v>
       </c>
       <c r="J252" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K252" s="3">
         <v>0</v>
@@ -41502,7 +41502,7 @@
         <v>0</v>
       </c>
       <c r="Q252" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R252" s="3">
         <v>0</v>
@@ -41619,7 +41619,7 @@
         <v>7</v>
       </c>
       <c r="E253" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F253" s="3">
         <v>0</v>
@@ -41634,7 +41634,7 @@
         <v>0</v>
       </c>
       <c r="J253" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K253" s="3">
         <v>0</v>
@@ -41655,7 +41655,7 @@
         <v>0</v>
       </c>
       <c r="Q253" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R253" s="3">
         <v>0</v>
@@ -41772,7 +41772,7 @@
         <v>7</v>
       </c>
       <c r="E254" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F254" s="3">
         <v>0</v>
@@ -41787,7 +41787,7 @@
         <v>0</v>
       </c>
       <c r="J254" s="3">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="K254" s="3">
         <v>0</v>
@@ -41808,7 +41808,7 @@
         <v>0</v>
       </c>
       <c r="Q254" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R254" s="3">
         <v>0</v>
@@ -41925,7 +41925,7 @@
         <v>7</v>
       </c>
       <c r="E255" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F255" s="3">
         <v>0</v>
@@ -41949,7 +41949,7 @@
         <v>0</v>
       </c>
       <c r="M255" s="3">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N255" s="3">
         <v>0</v>
@@ -41961,7 +41961,7 @@
         <v>0</v>
       </c>
       <c r="Q255" s="3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="R255" s="3">
         <v>0</v>
@@ -42231,7 +42231,7 @@
         <v>7</v>
       </c>
       <c r="E257" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F257" s="3">
         <v>0</v>
@@ -42246,7 +42246,7 @@
         <v>30</v>
       </c>
       <c r="J257" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K257" s="3">
         <v>0</v>
@@ -42384,7 +42384,7 @@
         <v>7</v>
       </c>
       <c r="E258" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F258" s="3">
         <v>0</v>
@@ -42399,7 +42399,7 @@
         <v>30</v>
       </c>
       <c r="J258" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K258" s="3">
         <v>0</v>
@@ -42537,7 +42537,7 @@
         <v>7</v>
       </c>
       <c r="E259" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F259" s="3">
         <v>0</v>
@@ -42552,7 +42552,7 @@
         <v>30</v>
       </c>
       <c r="J259" s="3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K259" s="3">
         <v>0</v>
@@ -42843,7 +42843,7 @@
         <v>7</v>
       </c>
       <c r="E261" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F261" s="3">
         <v>0</v>
@@ -42996,7 +42996,7 @@
         <v>7</v>
       </c>
       <c r="E262" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F262" s="3">
         <v>0</v>
@@ -43149,7 +43149,7 @@
         <v>7</v>
       </c>
       <c r="E263" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F263" s="3">
         <v>0</v>
@@ -43302,7 +43302,7 @@
         <v>7</v>
       </c>
       <c r="E264" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F264" s="3">
         <v>0</v>
@@ -43455,7 +43455,7 @@
         <v>7</v>
       </c>
       <c r="E265" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F265" s="3">
         <v>0</v>
@@ -43608,7 +43608,7 @@
         <v>7</v>
       </c>
       <c r="E266" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F266" s="3">
         <v>0</v>
@@ -43914,7 +43914,7 @@
         <v>7</v>
       </c>
       <c r="E268" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F268" s="3">
         <v>0</v>
@@ -43929,7 +43929,7 @@
         <v>0</v>
       </c>
       <c r="J268" s="3">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="K268" s="3">
         <v>0</v>
@@ -50034,7 +50034,7 @@
         <v>7</v>
       </c>
       <c r="E308" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F308" s="3">
         <v>0</v>
@@ -50340,7 +50340,7 @@
         <v>7</v>
       </c>
       <c r="E310" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F310" s="3">
         <v>0</v>
@@ -50493,7 +50493,7 @@
         <v>7</v>
       </c>
       <c r="E311" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F311" s="3">
         <v>0</v>
@@ -50646,7 +50646,7 @@
         <v>7</v>
       </c>
       <c r="E312" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F312" s="3">
         <v>0</v>
@@ -50799,7 +50799,7 @@
         <v>7</v>
       </c>
       <c r="E313" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F313" s="3">
         <v>0</v>
@@ -50952,7 +50952,7 @@
         <v>7</v>
       </c>
       <c r="E314" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F314" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E97B673-FCD6-4F6F-ACB1-1FB0002D4F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7ADB123-1F64-48CA-B911-991C7DC2D579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2190" yWindow="615" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1185" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -18093,7 +18093,7 @@
         <v>0</v>
       </c>
       <c r="Q99" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R99" s="3">
         <v>40</v>
@@ -18246,7 +18246,7 @@
         <v>0</v>
       </c>
       <c r="Q100" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R100" s="3">
         <v>40</v>
@@ -18399,7 +18399,7 @@
         <v>0</v>
       </c>
       <c r="Q101" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R101" s="3">
         <v>50</v>
@@ -18552,7 +18552,7 @@
         <v>0</v>
       </c>
       <c r="Q102" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R102" s="3">
         <v>50</v>
@@ -18705,7 +18705,7 @@
         <v>0</v>
       </c>
       <c r="Q103" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R103" s="3">
         <v>40</v>
@@ -19011,7 +19011,7 @@
         <v>0</v>
       </c>
       <c r="Q105" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R105" s="3">
         <v>30</v>
@@ -19164,7 +19164,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="3">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="R106" s="3">
         <v>40</v>
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L136" s="3">
         <v>0</v>
@@ -23889,7 +23889,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L137" s="3">
         <v>0</v>
@@ -24042,7 +24042,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L138" s="3">
         <v>0</v>
@@ -24195,7 +24195,7 @@
         <v>0</v>
       </c>
       <c r="K139" s="3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L139" s="3">
         <v>0</v>
@@ -24348,7 +24348,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="3">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="L140" s="3">
         <v>0</v>
@@ -24654,7 +24654,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="3">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="L142" s="3">
         <v>0</v>
@@ -24807,7 +24807,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="3">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="L143" s="3">
         <v>0</v>
@@ -24960,7 +24960,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L144" s="3">
         <v>0</v>
@@ -25113,7 +25113,7 @@
         <v>0</v>
       </c>
       <c r="K145" s="3">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="L145" s="3">
         <v>0</v>
@@ -25878,7 +25878,7 @@
         <v>0</v>
       </c>
       <c r="K150" s="3">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="L150" s="3">
         <v>0</v>
@@ -26643,7 +26643,7 @@
         <v>0</v>
       </c>
       <c r="K155" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L155" s="3">
         <v>0</v>
@@ -26796,7 +26796,7 @@
         <v>0</v>
       </c>
       <c r="K156" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L156" s="3">
         <v>0</v>
@@ -26949,7 +26949,7 @@
         <v>0</v>
       </c>
       <c r="K157" s="3">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="L157" s="3">
         <v>0</v>
@@ -27102,7 +27102,7 @@
         <v>0</v>
       </c>
       <c r="K158" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L158" s="3">
         <v>0</v>
@@ -27561,7 +27561,7 @@
         <v>0</v>
       </c>
       <c r="K161" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L161" s="3">
         <v>0</v>
@@ -27714,7 +27714,7 @@
         <v>0</v>
       </c>
       <c r="K162" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L162" s="3">
         <v>0</v>
@@ -27867,7 +27867,7 @@
         <v>0</v>
       </c>
       <c r="K163" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L163" s="3">
         <v>0</v>
@@ -28020,7 +28020,7 @@
         <v>0</v>
       </c>
       <c r="K164" s="3">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="L164" s="3">
         <v>0</v>
@@ -28326,7 +28326,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L166" s="3">
         <v>0</v>
@@ -28479,7 +28479,7 @@
         <v>0</v>
       </c>
       <c r="K167" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L167" s="3">
         <v>0</v>
@@ -28938,7 +28938,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L170" s="3">
         <v>0</v>
@@ -29091,7 +29091,7 @@
         <v>0</v>
       </c>
       <c r="K171" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L171" s="3">
         <v>0</v>
@@ -29244,7 +29244,7 @@
         <v>0</v>
       </c>
       <c r="K172" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L172" s="3">
         <v>0</v>
@@ -29703,7 +29703,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L175" s="3">
         <v>0</v>
@@ -29856,7 +29856,7 @@
         <v>0</v>
       </c>
       <c r="K176" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L176" s="3">
         <v>0</v>
@@ -30009,7 +30009,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="3">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L177" s="3">
         <v>0</v>
@@ -44286,7 +44286,7 @@
         <v>30</v>
       </c>
       <c r="AA270" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB270" s="3">
         <v>0</v>
@@ -44409,7 +44409,7 @@
         <v>0</v>
       </c>
       <c r="Q271" s="3">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="R271" s="3">
         <v>0</v>
@@ -44439,7 +44439,7 @@
         <v>30</v>
       </c>
       <c r="AA271" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB271" s="3">
         <v>0</v>
@@ -44592,7 +44592,7 @@
         <v>30</v>
       </c>
       <c r="AA272" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB272" s="3">
         <v>0</v>
@@ -44832,7 +44832,7 @@
         <v>7</v>
       </c>
       <c r="E274" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F274" s="3">
         <v>0</v>
@@ -44868,7 +44868,7 @@
         <v>0</v>
       </c>
       <c r="Q274" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R274" s="3">
         <v>0</v>
@@ -44895,7 +44895,7 @@
         <v>0</v>
       </c>
       <c r="Z274" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA274" s="3">
         <v>0</v>
@@ -44985,7 +44985,7 @@
         <v>7</v>
       </c>
       <c r="E275" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F275" s="3">
         <v>0</v>
@@ -45006,7 +45006,7 @@
         <v>0</v>
       </c>
       <c r="L275" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M275" s="3">
         <v>0</v>
@@ -45021,7 +45021,7 @@
         <v>0</v>
       </c>
       <c r="Q275" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R275" s="3">
         <v>0</v>
@@ -45048,10 +45048,10 @@
         <v>0</v>
       </c>
       <c r="Z275" s="3">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AA275" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB275" s="3">
         <v>0</v>
@@ -45138,7 +45138,7 @@
         <v>7</v>
       </c>
       <c r="E276" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F276" s="3">
         <v>0</v>
@@ -45174,7 +45174,7 @@
         <v>0</v>
       </c>
       <c r="Q276" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R276" s="3">
         <v>0</v>
@@ -45201,10 +45201,10 @@
         <v>0</v>
       </c>
       <c r="Z276" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA276" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB276" s="3">
         <v>0</v>
@@ -45480,7 +45480,7 @@
         <v>0</v>
       </c>
       <c r="Q278" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R278" s="3">
         <v>0</v>
@@ -45633,7 +45633,7 @@
         <v>0</v>
       </c>
       <c r="Q279" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R279" s="3">
         <v>0</v>
@@ -45786,7 +45786,7 @@
         <v>0</v>
       </c>
       <c r="Q280" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R280" s="3">
         <v>0</v>
@@ -45939,7 +45939,7 @@
         <v>0</v>
       </c>
       <c r="Q281" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R281" s="3">
         <v>0</v>
@@ -46092,7 +46092,7 @@
         <v>0</v>
       </c>
       <c r="Q282" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R282" s="3">
         <v>0</v>
@@ -46245,7 +46245,7 @@
         <v>0</v>
       </c>
       <c r="Q283" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R283" s="3">
         <v>0</v>
@@ -46398,7 +46398,7 @@
         <v>0</v>
       </c>
       <c r="Q284" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R284" s="3">
         <v>0</v>
@@ -46425,7 +46425,7 @@
         <v>0</v>
       </c>
       <c r="Z284" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA284" s="3">
         <v>0</v>
@@ -46551,7 +46551,7 @@
         <v>0</v>
       </c>
       <c r="Q285" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R285" s="3">
         <v>0</v>
@@ -46704,7 +46704,7 @@
         <v>0</v>
       </c>
       <c r="Q286" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R286" s="3">
         <v>0</v>
@@ -46857,7 +46857,7 @@
         <v>0</v>
       </c>
       <c r="Q287" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R287" s="3">
         <v>0</v>
@@ -46884,7 +46884,7 @@
         <v>0</v>
       </c>
       <c r="Z287" s="3">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA287" s="3">
         <v>0</v>
@@ -47010,7 +47010,7 @@
         <v>0</v>
       </c>
       <c r="Q288" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R288" s="3">
         <v>0</v>
@@ -47163,7 +47163,7 @@
         <v>0</v>
       </c>
       <c r="Q289" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R289" s="3">
         <v>0</v>
@@ -47316,7 +47316,7 @@
         <v>0</v>
       </c>
       <c r="Q290" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R290" s="3">
         <v>0</v>
@@ -47469,7 +47469,7 @@
         <v>0</v>
       </c>
       <c r="Q291" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R291" s="3">
         <v>0</v>
@@ -47622,7 +47622,7 @@
         <v>0</v>
       </c>
       <c r="Q292" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R292" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7ADB123-1F64-48CA-B911-991C7DC2D579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA2C9B8-EB79-4C6D-B07C-F0B03658E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1185" windowWidth="25005" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1215" yWindow="990" windowWidth="25005" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -8976,7 +8976,7 @@
         <v>7</v>
       </c>
       <c r="AL39" s="5">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="AM39" s="5">
         <v>50</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="J43" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -9657,7 +9657,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -9810,7 +9810,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -10116,7 +10116,7 @@
         <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -10179,7 +10179,7 @@
         <v>245</v>
       </c>
       <c r="AE47" s="5" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="AF47" s="5" t="s">
         <v>7</v>
@@ -10206,7 +10206,7 @@
         <v>30</v>
       </c>
       <c r="AN47" s="5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AO47" s="5">
         <v>0</v>
@@ -10269,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="J48" s="3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA2C9B8-EB79-4C6D-B07C-F0B03658E12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BF340F-C70A-4D80-B028-850FB7CDD3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="990" windowWidth="25005" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1995" yWindow="1185" windowWidth="25005" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -13656,7 +13656,7 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R70" s="3">
         <v>0</v>
@@ -13809,7 +13809,7 @@
         <v>0</v>
       </c>
       <c r="Q71" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R71" s="3">
         <v>0</v>
@@ -13962,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="Q72" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aritashogo\Documents\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9BF340F-C70A-4D80-B028-850FB7CDD3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630A371-5DDE-4E03-AFE7-59E93AA09347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1995" yWindow="1185" windowWidth="25005" windowHeight="14355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="25050" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -6756,7 +6756,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M25" s="3">
         <v>0</v>
@@ -15102,7 +15102,7 @@
         <v>20</v>
       </c>
       <c r="AN79" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO79" s="5">
         <v>0</v>
@@ -15255,7 +15255,7 @@
         <v>20</v>
       </c>
       <c r="AN80" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO80" s="5">
         <v>0</v>
@@ -15609,7 +15609,7 @@
         <v>7</v>
       </c>
       <c r="E83" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -15711,10 +15711,10 @@
         <v>10</v>
       </c>
       <c r="AM83" s="5">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AN83" s="5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AO83" s="5">
         <v>0</v>
@@ -15864,10 +15864,10 @@
         <v>10</v>
       </c>
       <c r="AM84" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN84" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO84" s="5">
         <v>30</v>
@@ -15915,7 +15915,7 @@
         <v>7</v>
       </c>
       <c r="E85" s="3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F85" s="3">
         <v>0</v>
@@ -16017,10 +16017,10 @@
         <v>10</v>
       </c>
       <c r="AM85" s="5">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AN85" s="5">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="AO85" s="5">
         <v>30</v>
@@ -16173,7 +16173,7 @@
         <v>20</v>
       </c>
       <c r="AN86" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO86" s="5">
         <v>30</v>
@@ -16326,7 +16326,7 @@
         <v>20</v>
       </c>
       <c r="AN87" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO87" s="5">
         <v>0</v>
@@ -16479,7 +16479,7 @@
         <v>20</v>
       </c>
       <c r="AN88" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO88" s="5">
         <v>0</v>
@@ -16632,7 +16632,7 @@
         <v>20</v>
       </c>
       <c r="AN89" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO89" s="5">
         <v>0</v>
@@ -16785,7 +16785,7 @@
         <v>20</v>
       </c>
       <c r="AN90" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO90" s="5">
         <v>10</v>
@@ -16935,10 +16935,10 @@
         <v>10</v>
       </c>
       <c r="AM91" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN91" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO91" s="5">
         <v>10</v>
@@ -17091,7 +17091,7 @@
         <v>20</v>
       </c>
       <c r="AN92" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO92" s="5">
         <v>10</v>
@@ -17241,10 +17241,10 @@
         <v>10</v>
       </c>
       <c r="AM93" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN93" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO93" s="5">
         <v>10</v>
@@ -17394,10 +17394,10 @@
         <v>10</v>
       </c>
       <c r="AM94" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AN94" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO94" s="5">
         <v>30</v>
@@ -17550,7 +17550,7 @@
         <v>20</v>
       </c>
       <c r="AN95" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO95" s="5">
         <v>0</v>
@@ -17703,7 +17703,7 @@
         <v>20</v>
       </c>
       <c r="AN96" s="5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AO96" s="5">
         <v>0</v>
@@ -28308,7 +28308,7 @@
         <v>7</v>
       </c>
       <c r="E166" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
@@ -28461,7 +28461,7 @@
         <v>7</v>
       </c>
       <c r="E167" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F167" s="3">
         <v>0</v>
@@ -28920,7 +28920,7 @@
         <v>7</v>
       </c>
       <c r="E170" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F170" s="3">
         <v>0</v>
@@ -29073,7 +29073,7 @@
         <v>7</v>
       </c>
       <c r="E171" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F171" s="3">
         <v>0</v>
@@ -29226,7 +29226,7 @@
         <v>7</v>
       </c>
       <c r="E172" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
@@ -29379,7 +29379,7 @@
         <v>7</v>
       </c>
       <c r="E173" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F173" s="3">
         <v>0</v>
@@ -29685,7 +29685,7 @@
         <v>7</v>
       </c>
       <c r="E175" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F175" s="3">
         <v>0</v>
@@ -29838,7 +29838,7 @@
         <v>7</v>
       </c>
       <c r="E176" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F176" s="3">
         <v>0</v>
@@ -31521,7 +31521,7 @@
         <v>7</v>
       </c>
       <c r="E187" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F187" s="3">
         <v>0</v>
@@ -32592,7 +32592,7 @@
         <v>485</v>
       </c>
       <c r="E194" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F194" s="3">
         <v>0</v>
@@ -32745,7 +32745,7 @@
         <v>7</v>
       </c>
       <c r="E195" s="3">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F195" s="3">
         <v>0</v>
@@ -33072,7 +33072,7 @@
         <v>0</v>
       </c>
       <c r="L197" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M197" s="3">
         <v>0</v>
@@ -33225,7 +33225,7 @@
         <v>0</v>
       </c>
       <c r="L198" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M198" s="3">
         <v>0</v>
@@ -33378,7 +33378,7 @@
         <v>0</v>
       </c>
       <c r="L199" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M199" s="3">
         <v>0</v>
@@ -33531,7 +33531,7 @@
         <v>0</v>
       </c>
       <c r="L200" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M200" s="3">
         <v>0</v>
@@ -33684,7 +33684,7 @@
         <v>0</v>
       </c>
       <c r="L201" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M201" s="3">
         <v>0</v>
@@ -33837,7 +33837,7 @@
         <v>0</v>
       </c>
       <c r="L202" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M202" s="3">
         <v>0</v>
@@ -33969,7 +33969,7 @@
         <v>7</v>
       </c>
       <c r="E203" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F203" s="3">
         <v>0</v>
@@ -33990,7 +33990,7 @@
         <v>0</v>
       </c>
       <c r="L203" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M203" s="3">
         <v>0</v>
@@ -34143,7 +34143,7 @@
         <v>0</v>
       </c>
       <c r="L204" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M204" s="3">
         <v>0</v>
@@ -34296,7 +34296,7 @@
         <v>0</v>
       </c>
       <c r="L205" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M205" s="3">
         <v>0</v>
@@ -34449,7 +34449,7 @@
         <v>0</v>
       </c>
       <c r="L206" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M206" s="3">
         <v>0</v>
@@ -34581,7 +34581,7 @@
         <v>7</v>
       </c>
       <c r="E207" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F207" s="3">
         <v>0</v>
@@ -34602,7 +34602,7 @@
         <v>0</v>
       </c>
       <c r="L207" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="M207" s="3">
         <v>0</v>
@@ -34734,7 +34734,7 @@
         <v>7</v>
       </c>
       <c r="E208" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F208" s="3">
         <v>0</v>
@@ -34755,7 +34755,7 @@
         <v>0</v>
       </c>
       <c r="L208" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="M208" s="3">
         <v>0</v>
@@ -35040,7 +35040,7 @@
         <v>7</v>
       </c>
       <c r="E210" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F210" s="3">
         <v>0</v>
@@ -35061,7 +35061,7 @@
         <v>0</v>
       </c>
       <c r="L210" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="M210" s="3">
         <v>0</v>
@@ -36111,7 +36111,7 @@
         <v>7</v>
       </c>
       <c r="E217" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F217" s="3">
         <v>0</v>
@@ -37947,7 +37947,7 @@
         <v>7</v>
       </c>
       <c r="E229" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F229" s="3">
         <v>0</v>
@@ -38100,7 +38100,7 @@
         <v>7</v>
       </c>
       <c r="E230" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F230" s="3">
         <v>0</v>
@@ -38253,7 +38253,7 @@
         <v>7</v>
       </c>
       <c r="E231" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F231" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4630A371-5DDE-4E03-AFE7-59E93AA09347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5766B290-F604-4438-AE6F-34CC1076501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="25050" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3405" yWindow="1185" windowWidth="21915" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -6465,7 +6465,7 @@
         <v>0</v>
       </c>
       <c r="Q23" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R23" s="3">
         <v>0</v>
@@ -6582,7 +6582,7 @@
         <v>56</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>0</v>
       </c>
       <c r="Q25" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R25" s="3">
         <v>0</v>
@@ -7077,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="Q27" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R27" s="3">
         <v>0</v>
@@ -11478,7 +11478,7 @@
         <v>7</v>
       </c>
       <c r="E56" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F56" s="3">
         <v>0</v>
@@ -11514,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="Q56" s="3">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="R56" s="3">
         <v>0</v>
@@ -11631,7 +11631,7 @@
         <v>7</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -11667,7 +11667,7 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -15033,7 +15033,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R79" s="3">
         <v>0</v>
@@ -15186,7 +15186,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R80" s="3">
         <v>0</v>
@@ -15339,7 +15339,7 @@
         <v>0</v>
       </c>
       <c r="Q81" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R81" s="3">
         <v>0</v>
@@ -15492,7 +15492,7 @@
         <v>0</v>
       </c>
       <c r="Q82" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R82" s="3">
         <v>0</v>
@@ -15645,7 +15645,7 @@
         <v>0</v>
       </c>
       <c r="Q83" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -15798,7 +15798,7 @@
         <v>0</v>
       </c>
       <c r="Q84" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R84" s="3">
         <v>0</v>
@@ -15951,7 +15951,7 @@
         <v>0</v>
       </c>
       <c r="Q85" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R85" s="3">
         <v>0</v>
@@ -16104,7 +16104,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R86" s="3">
         <v>0</v>
@@ -16257,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="Q87" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R87" s="3">
         <v>0</v>
@@ -16410,7 +16410,7 @@
         <v>0</v>
       </c>
       <c r="Q88" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R88" s="3">
         <v>0</v>
@@ -16563,7 +16563,7 @@
         <v>0</v>
       </c>
       <c r="Q89" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R89" s="3">
         <v>0</v>
@@ -16716,7 +16716,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R90" s="3">
         <v>0</v>
@@ -16869,7 +16869,7 @@
         <v>0</v>
       </c>
       <c r="Q91" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -17022,7 +17022,7 @@
         <v>0</v>
       </c>
       <c r="Q92" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R92" s="3">
         <v>0</v>
@@ -17175,7 +17175,7 @@
         <v>0</v>
       </c>
       <c r="Q93" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R93" s="3">
         <v>0</v>
@@ -17328,7 +17328,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="R94" s="3">
         <v>0</v>
@@ -17481,7 +17481,7 @@
         <v>0</v>
       </c>
       <c r="Q95" s="3">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="R95" s="3">
         <v>0</v>
@@ -17634,7 +17634,7 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -18858,7 +18858,7 @@
         <v>0</v>
       </c>
       <c r="Q104" s="3">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="R104" s="3">
         <v>50</v>
@@ -22377,7 +22377,7 @@
         <v>0</v>
       </c>
       <c r="Q127" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R127" s="3">
         <v>0</v>
@@ -22494,7 +22494,7 @@
         <v>7</v>
       </c>
       <c r="E128" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F128" s="3">
         <v>0</v>
@@ -22800,7 +22800,7 @@
         <v>7</v>
       </c>
       <c r="E130" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F130" s="3">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>0</v>
       </c>
       <c r="Q131" s="3">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R131" s="3">
         <v>0</v>
@@ -23259,7 +23259,7 @@
         <v>7</v>
       </c>
       <c r="E133" s="3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F133" s="3">
         <v>0</v>
@@ -23412,7 +23412,7 @@
         <v>7</v>
       </c>
       <c r="E134" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F134" s="3">
         <v>0</v>
@@ -24672,7 +24672,7 @@
         <v>0</v>
       </c>
       <c r="Q142" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R142" s="3">
         <v>0</v>
@@ -24825,7 +24825,7 @@
         <v>0</v>
       </c>
       <c r="Q143" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R143" s="3">
         <v>0</v>
@@ -26049,7 +26049,7 @@
         <v>0</v>
       </c>
       <c r="Q151" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R151" s="3">
         <v>0</v>
@@ -26202,7 +26202,7 @@
         <v>0</v>
       </c>
       <c r="Q152" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R152" s="3">
         <v>0</v>
@@ -26355,7 +26355,7 @@
         <v>0</v>
       </c>
       <c r="Q153" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R153" s="3">
         <v>0</v>
@@ -26508,7 +26508,7 @@
         <v>0</v>
       </c>
       <c r="Q154" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R154" s="3">
         <v>0</v>
@@ -27273,7 +27273,7 @@
         <v>0</v>
       </c>
       <c r="Q159" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R159" s="3">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>0</v>
       </c>
       <c r="Q160" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="R160" s="3">
         <v>0</v>
@@ -28344,7 +28344,7 @@
         <v>0</v>
       </c>
       <c r="Q166" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R166" s="3">
         <v>0</v>
@@ -28497,7 +28497,7 @@
         <v>0</v>
       </c>
       <c r="Q167" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R167" s="3">
         <v>0</v>
@@ -28614,7 +28614,7 @@
         <v>7</v>
       </c>
       <c r="E168" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F168" s="3">
         <v>0</v>
@@ -28767,7 +28767,7 @@
         <v>7</v>
       </c>
       <c r="E169" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F169" s="3">
         <v>0</v>
@@ -28956,7 +28956,7 @@
         <v>0</v>
       </c>
       <c r="Q170" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R170" s="3">
         <v>0</v>
@@ -29109,7 +29109,7 @@
         <v>0</v>
       </c>
       <c r="Q171" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R171" s="3">
         <v>0</v>
@@ -29262,7 +29262,7 @@
         <v>0</v>
       </c>
       <c r="Q172" s="3">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R172" s="3">
         <v>0</v>
@@ -29721,7 +29721,7 @@
         <v>0</v>
       </c>
       <c r="Q175" s="3">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="R175" s="3">
         <v>0</v>
@@ -29874,7 +29874,7 @@
         <v>0</v>
       </c>
       <c r="Q176" s="3">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="R176" s="3">
         <v>0</v>
@@ -30027,7 +30027,7 @@
         <v>0</v>
       </c>
       <c r="Q177" s="3">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="R177" s="3">
         <v>0</v>
@@ -30333,7 +30333,7 @@
         <v>0</v>
       </c>
       <c r="Q179" s="3">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="R179" s="3">
         <v>0</v>
@@ -33051,7 +33051,7 @@
         <v>7</v>
       </c>
       <c r="E197" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F197" s="3">
         <v>0</v>
@@ -33087,7 +33087,7 @@
         <v>0</v>
       </c>
       <c r="Q197" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R197" s="3">
         <v>0</v>
@@ -33204,7 +33204,7 @@
         <v>7</v>
       </c>
       <c r="E198" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F198" s="3">
         <v>0</v>
@@ -33240,7 +33240,7 @@
         <v>0</v>
       </c>
       <c r="Q198" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R198" s="3">
         <v>0</v>
@@ -33357,7 +33357,7 @@
         <v>7</v>
       </c>
       <c r="E199" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F199" s="3">
         <v>0</v>
@@ -33393,7 +33393,7 @@
         <v>0</v>
       </c>
       <c r="Q199" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R199" s="3">
         <v>0</v>
@@ -33510,7 +33510,7 @@
         <v>7</v>
       </c>
       <c r="E200" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F200" s="3">
         <v>0</v>
@@ -33546,7 +33546,7 @@
         <v>0</v>
       </c>
       <c r="Q200" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R200" s="3">
         <v>0</v>
@@ -33663,7 +33663,7 @@
         <v>7</v>
       </c>
       <c r="E201" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F201" s="3">
         <v>0</v>
@@ -33699,7 +33699,7 @@
         <v>0</v>
       </c>
       <c r="Q201" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R201" s="3">
         <v>0</v>
@@ -33816,7 +33816,7 @@
         <v>7</v>
       </c>
       <c r="E202" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F202" s="3">
         <v>0</v>
@@ -33852,7 +33852,7 @@
         <v>0</v>
       </c>
       <c r="Q202" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R202" s="3">
         <v>0</v>
@@ -34005,7 +34005,7 @@
         <v>0</v>
       </c>
       <c r="Q203" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R203" s="3">
         <v>0</v>
@@ -34122,7 +34122,7 @@
         <v>7</v>
       </c>
       <c r="E204" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F204" s="3">
         <v>0</v>
@@ -34158,7 +34158,7 @@
         <v>0</v>
       </c>
       <c r="Q204" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R204" s="3">
         <v>0</v>
@@ -34275,7 +34275,7 @@
         <v>7</v>
       </c>
       <c r="E205" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F205" s="3">
         <v>0</v>
@@ -34311,7 +34311,7 @@
         <v>0</v>
       </c>
       <c r="Q205" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R205" s="3">
         <v>0</v>
@@ -34428,7 +34428,7 @@
         <v>7</v>
       </c>
       <c r="E206" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F206" s="3">
         <v>0</v>
@@ -34464,7 +34464,7 @@
         <v>0</v>
       </c>
       <c r="Q206" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R206" s="3">
         <v>0</v>
@@ -34617,7 +34617,7 @@
         <v>0</v>
       </c>
       <c r="Q207" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R207" s="3">
         <v>0</v>
@@ -34770,7 +34770,7 @@
         <v>0</v>
       </c>
       <c r="Q208" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R208" s="3">
         <v>0</v>
@@ -34887,7 +34887,7 @@
         <v>7</v>
       </c>
       <c r="E209" s="3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F209" s="3">
         <v>0</v>
@@ -34923,7 +34923,7 @@
         <v>0</v>
       </c>
       <c r="Q209" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R209" s="3">
         <v>0</v>
@@ -35076,7 +35076,7 @@
         <v>0</v>
       </c>
       <c r="Q210" s="3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="R210" s="3">
         <v>0</v>
@@ -39207,7 +39207,7 @@
         <v>0</v>
       </c>
       <c r="Q237" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R237" s="3">
         <v>0</v>
@@ -39360,7 +39360,7 @@
         <v>0</v>
       </c>
       <c r="Q238" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R238" s="3">
         <v>0</v>
@@ -39513,7 +39513,7 @@
         <v>0</v>
       </c>
       <c r="Q239" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R239" s="3">
         <v>0</v>
@@ -39666,7 +39666,7 @@
         <v>0</v>
       </c>
       <c r="Q240" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R240" s="3">
         <v>0</v>
@@ -39819,7 +39819,7 @@
         <v>0</v>
       </c>
       <c r="Q241" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R241" s="3">
         <v>0</v>
@@ -39972,7 +39972,7 @@
         <v>0</v>
       </c>
       <c r="Q242" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R242" s="3">
         <v>0</v>
@@ -40125,7 +40125,7 @@
         <v>0</v>
       </c>
       <c r="Q243" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="R243" s="3">
         <v>70</v>
@@ -43644,7 +43644,7 @@
         <v>70</v>
       </c>
       <c r="Q266" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="R266" s="3">
         <v>0</v>
@@ -51294,7 +51294,7 @@
         <v>0</v>
       </c>
       <c r="Q316" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R316" s="3">
         <v>0</v>
@@ -51447,7 +51447,7 @@
         <v>0</v>
       </c>
       <c r="Q317" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="R317" s="3">
         <v>0</v>

--- a/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
+++ b/Assets/Resources/Excel/Entity_GirlLikeSetDataBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mator\OneDrive\ドキュメント\Unity\Okashi_Atlier2\Assets\Resources\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5766B290-F604-4438-AE6F-34CC1076501A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64868D8B-1F05-445E-BB4C-3505C2CE11AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3405" yWindow="1185" windowWidth="21915" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="1005" windowWidth="21915" windowHeight="13455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_GirlLikeSetData" sheetId="1" r:id="rId1"/>
@@ -6582,7 +6582,7 @@
         <v>56</v>
       </c>
       <c r="E24" s="3">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F24" s="3">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -9207,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="3">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="N41" s="3">
         <v>0</v>
@@ -13941,7 +13941,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="K133" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L133" s="3">
         <v>0</v>
@@ -23430,7 +23430,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="L134" s="3">
         <v>0</v>
@@ -23736,7 +23736,7 @@
         <v>0</v>
       </c>
       <c r="K136" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="L136" s="3">
         <v>0</v>
@@ -23889,7 +23889,7 @@
         <v>0</v>
       </c>
       <c r="K137" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="L137" s="3">
         <v>0</v>
@@ -24042,7 +24042,7 @@
         <v>0</v>
       </c>
       <c r="K138" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="L138" s="3">
         <v>0</v>
@@ -24195,7 +24195,7 @@
         <v>0</v>
       </c>
       <c r="K139" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="L139" s="3">
         <v>0</v>
@@ -24348,7 +24348,7 @@
         <v>0</v>
       </c>
       <c r="K140" s="3">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="L140" s="3">
         <v>0</v>
@@ -28308,7 +28308,7 @@
         <v>7</v>
       </c>
       <c r="E166" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F166" s="3">
         <v>0</v>
@@ -28326,7 +28326,7 @@
         <v>0</v>
       </c>
       <c r="K166" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L166" s="3">
         <v>0</v>
@@ -28461,7 +28461,7 @@
         <v>7</v>
       </c>
       <c r="E167" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F167" s="3">
         <v>0</v>
@@ -28479,7 +28479,7 @@
         <v>0</v>
       </c>
       <c r="K167" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L167" s="3">
         <v>0</v>
@@ -28614,7 +28614,7 @@
         <v>7</v>
       </c>
       <c r="E168" s="3">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F168" s="3">
         <v>0</v>
@@ -28632,7 +28632,7 @@
         <v>0</v>
       </c>
       <c r="K168" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L168" s="3">
         <v>0</v>
@@ -28767,7 +28767,7 @@
         <v>7</v>
       </c>
       <c r="E169" s="3">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="F169" s="3">
         <v>0</v>
@@ -28785,7 +28785,7 @@
         <v>0</v>
       </c>
       <c r="K169" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L169" s="3">
         <v>0</v>
@@ -28920,7 +28920,7 @@
         <v>7</v>
       </c>
       <c r="E170" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F170" s="3">
         <v>0</v>
@@ -28938,7 +28938,7 @@
         <v>0</v>
       </c>
       <c r="K170" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L170" s="3">
         <v>0</v>
@@ -29073,7 +29073,7 @@
         <v>7</v>
       </c>
       <c r="E171" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F171" s="3">
         <v>0</v>
@@ -29091,7 +29091,7 @@
         <v>0</v>
       </c>
       <c r="K171" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L171" s="3">
         <v>0</v>
@@ -29226,7 +29226,7 @@
         <v>7</v>
       </c>
       <c r="E172" s="3">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="F172" s="3">
         <v>0</v>
@@ -29244,7 +29244,7 @@
         <v>0</v>
       </c>
       <c r="K172" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L172" s="3">
         <v>0</v>
@@ -29379,7 +29379,7 @@
         <v>7</v>
       </c>
       <c r="E173" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F173" s="3">
         <v>0</v>
@@ -29397,7 +29397,7 @@
         <v>0</v>
       </c>
       <c r="K173" s="3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="L173" s="3">
         <v>0</v>
@@ -29685,7 +29685,7 @@
         <v>7</v>
       </c>
       <c r="E175" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F175" s="3">
         <v>0</v>
@@ -29703,7 +29703,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L175" s="3">
         <v>0</v>
@@ -29838,7 +29838,7 @@
         <v>7</v>
       </c>
       <c r="E176" s="3">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="F176" s="3">
         <v>0</v>
@@ -29856,7 +29856,7 @@
         <v>0</v>
       </c>
       <c r="K176" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L176" s="3">
         <v>0</v>
@@ -30009,7 +30009,7 @@
         <v>0</v>
       </c>
       <c r="K177" s="3">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L177" s="3">
         <v>0</v>
@@ -40146,7 +40146,7 @@
         <v>0</v>
       </c>
       <c r="X243" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y243" s="3">
         <v>0</v>
@@ -43914,7 +43914,7 @@
         <v>7</v>
       </c>
       <c r="E268" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F268" s="3">
         <v>0</v>
@@ -43971,7 +43971,7 @@
         <v>0</v>
       </c>
       <c r="X268" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y268" s="3">
         <v>0</v>
@@ -45453,7 +45453,7 @@
         <v>80</v>
       </c>
       <c r="H278" s="3">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="I278" s="3">
         <v>0</v>
@@ -45639,7 +45639,7 @@
         <v>0</v>
       </c>
       <c r="S279" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T279" s="3">
         <v>0</v>
@@ -45759,7 +45759,7 @@
         <v>80</v>
       </c>
       <c r="H280" s="3">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I280" s="3">
         <v>0</v>
@@ -45795,7 +45795,7 @@
         <v>0</v>
       </c>
       <c r="T280" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U280" s="3">
         <v>0</v>
@@ -45951,7 +45951,7 @@
         <v>0</v>
       </c>
       <c r="U281" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V281" s="3">
         <v>0</v>
@@ -46116,7 +46116,7 @@
         <v>0</v>
       </c>
       <c r="Y282" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Z282" s="3">
         <v>0</v>
@@ -46254,7 +46254,7 @@
         <v>0</v>
       </c>
       <c r="T283" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U283" s="3">
         <v>0</v>
@@ -46371,7 +46371,7 @@
         <v>80</v>
       </c>
       <c r="H284" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="I284" s="3">
         <v>0</v>
@@ -46404,7 +46404,7 @@
         <v>0</v>
       </c>
       <c r="S284" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="T284" s="3">
         <v>0</v>
@@ -46524,7 +46524,7 @@
         <v>80</v>
       </c>
       <c r="H285" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="I285" s="3">
         <v>0</v>
@@ -46716,7 +46716,7 @@
         <v>0</v>
       </c>
       <c r="U286" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V286" s="3">
         <v>0</v>
@@ -46830,7 +46830,7 @@
         <v>80</v>
       </c>
       <c r="H287" s="3">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="I287" s="3">
         <v>0</v>
@@ -47184,7 +47184,7 @@
         <v>0</v>
       </c>
       <c r="X289" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y289" s="3">
         <v>0</v>
@@ -47337,7 +47337,7 @@
         <v>0</v>
       </c>
       <c r="X290" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y290" s="3">
         <v>0</v>
